--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -488,12 +488,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12960"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -77,7 +77,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="0">
+    <comment ref="J3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -99,7 +99,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K3" authorId="0">
+    <comment ref="L3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -122,7 +122,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L3" authorId="0">
+    <comment ref="M3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -145,7 +145,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M3" authorId="0">
+    <comment ref="N3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -172,7 +172,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="47">
   <si>
     <t>Id</t>
   </si>
@@ -186,6 +186,9 @@
     <t>技能攻击类型</t>
   </si>
   <si>
+    <t>脚本名称</t>
+  </si>
+  <si>
     <t>技能CD</t>
   </si>
   <si>
@@ -219,6 +222,9 @@
     <t>SkillActType</t>
   </si>
   <si>
+    <t>SkillHandler</t>
+  </si>
+  <si>
     <t>SkillCD</t>
   </si>
   <si>
@@ -256,6 +262,9 @@
   </si>
   <si>
     <t>战士普通攻击</t>
+  </si>
+  <si>
+    <t>Skill_Action_Common</t>
   </si>
   <si>
     <t>Test_1</t>
@@ -1349,18 +1358,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:N12"/>
+  <dimension ref="C1:O12"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="10.875" style="2" customWidth="1"/>
-    <col min="3" max="13" width="17.875" style="2"/>
-    <col min="14" max="14" width="50.625" style="2" customWidth="1"/>
-    <col min="15" max="16384" width="17.875" style="2"/>
+    <col min="3" max="14" width="17.875" style="2"/>
+    <col min="15" max="15" width="50.625" style="2" customWidth="1"/>
+    <col min="16" max="16384" width="17.875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1"/>
     <row r="2" s="1" customFormat="1" customHeight="1"/>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1397,89 +1406,98 @@
       <c r="N3" s="4" t="s">
         <v>11</v>
       </c>
+      <c r="O3" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C5" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>23</v>
-      </c>
       <c r="J5" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="M5" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>24</v>
+      <c r="O5" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:13">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C6" s="2">
         <v>10000001</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E6" s="2">
         <v>10000001</v>
@@ -1487,34 +1505,37 @@
       <c r="F6" s="2">
         <v>0</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="2">
         <v>0</v>
       </c>
-      <c r="H6" s="2">
+      <c r="I6" s="2">
         <v>1000</v>
       </c>
-      <c r="I6" s="2">
+      <c r="J6" s="2">
         <v>10</v>
       </c>
-      <c r="J6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K6" s="2">
+      <c r="K6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L6" s="2">
         <v>10000001</v>
       </c>
-      <c r="L6" s="2">
+      <c r="M6" s="2">
         <v>0</v>
       </c>
-      <c r="M6" s="2" t="s">
-        <v>29</v>
+      <c r="N6" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:13">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C7" s="2">
         <v>10000002</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E7" s="2">
         <v>10000002</v>
@@ -1522,34 +1543,37 @@
       <c r="F7" s="2">
         <v>0</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" s="2">
         <v>0</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>1000</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>20</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="K7" s="2">
+      <c r="K7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="2">
         <v>10000002</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>0</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>32</v>
+      <c r="N7" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:13">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C8" s="2">
         <v>10000003</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E8" s="2">
         <v>10000003</v>
@@ -1557,34 +1581,37 @@
       <c r="F8" s="2">
         <v>0</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H8" s="2">
         <v>0</v>
       </c>
-      <c r="H8" s="2">
+      <c r="I8" s="2">
         <v>1000</v>
       </c>
-      <c r="I8" s="2">
+      <c r="J8" s="2">
         <v>15</v>
       </c>
-      <c r="J8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="K8" s="2">
+      <c r="K8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L8" s="2">
         <v>10000003</v>
       </c>
-      <c r="L8" s="2">
+      <c r="M8" s="2">
         <v>0</v>
       </c>
-      <c r="M8" s="2" t="s">
-        <v>29</v>
+      <c r="N8" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C9" s="2">
         <v>10000004</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E9" s="2">
         <v>10000004</v>
@@ -1592,37 +1619,40 @@
       <c r="F9" s="2">
         <v>1</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="2">
         <v>11</v>
       </c>
-      <c r="H9" s="2">
+      <c r="I9" s="2">
         <v>2000</v>
       </c>
-      <c r="I9" s="2">
+      <c r="J9" s="2">
         <v>100</v>
       </c>
-      <c r="J9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K9" s="2">
+      <c r="K9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L9" s="2">
         <v>10000004</v>
       </c>
-      <c r="L9" s="2">
+      <c r="M9" s="2">
         <v>0</v>
       </c>
-      <c r="M9" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="N9" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C10" s="2">
         <v>10000005</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E10" s="2">
         <v>10000005</v>
@@ -1630,37 +1660,40 @@
       <c r="F10" s="2">
         <v>1</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10" s="2">
         <v>12</v>
       </c>
-      <c r="H10" s="2">
+      <c r="I10" s="2">
         <v>3000</v>
       </c>
-      <c r="I10" s="2">
+      <c r="J10" s="2">
         <v>200</v>
       </c>
-      <c r="J10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="K10" s="2">
+      <c r="K10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L10" s="2">
         <v>10000005</v>
       </c>
-      <c r="L10" s="2">
+      <c r="M10" s="2">
         <v>10000002</v>
       </c>
-      <c r="M10" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="N10" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="3:14">
+    <row r="11" customHeight="1" spans="3:15">
       <c r="C11" s="2">
         <v>10000006</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E11" s="2">
         <v>10000006</v>
@@ -1668,37 +1701,40 @@
       <c r="F11" s="2">
         <v>1</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" s="2">
         <v>10</v>
       </c>
-      <c r="H11" s="2">
+      <c r="I11" s="2">
         <v>2000</v>
       </c>
-      <c r="I11" s="2">
+      <c r="J11" s="2">
         <v>400</v>
       </c>
-      <c r="J11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="K11" s="2">
+      <c r="K11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L11" s="2">
         <v>10000006</v>
       </c>
-      <c r="L11" s="2">
+      <c r="M11" s="2">
         <v>10000001</v>
       </c>
-      <c r="M11" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="N11" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>44</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="3:14">
+    <row r="12" customHeight="1" spans="3:15">
       <c r="C12" s="2">
         <v>20000001</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E12" s="2">
         <v>10000007</v>
@@ -1706,29 +1742,32 @@
       <c r="F12" s="2">
         <v>1</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H12" s="2">
         <v>10</v>
       </c>
-      <c r="H12" s="2">
+      <c r="I12" s="2">
         <v>3000</v>
       </c>
-      <c r="I12" s="2">
+      <c r="J12" s="2">
         <v>500</v>
       </c>
-      <c r="J12" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K12" s="2">
+      <c r="K12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L12" s="2">
         <v>10000006</v>
       </c>
-      <c r="L12" s="2">
+      <c r="M12" s="2">
         <v>10000003</v>
       </c>
-      <c r="M12" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="N12" s="2" t="s">
-        <v>43</v>
+        <v>32</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -172,7 +172,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="48">
   <si>
     <t>Id</t>
   </si>
@@ -264,16 +264,19 @@
     <t>战士普通攻击</t>
   </si>
   <si>
+    <t>Skill_SingleTarget</t>
+  </si>
+  <si>
+    <t>Test_1</t>
+  </si>
+  <si>
+    <t>gong</t>
+  </si>
+  <si>
+    <t>箭手普通攻击</t>
+  </si>
+  <si>
     <t>Skill_Action_Common</t>
-  </si>
-  <si>
-    <t>Test_1</t>
-  </si>
-  <si>
-    <t>gong</t>
-  </si>
-  <si>
-    <t>箭手普通攻击</t>
   </si>
   <si>
     <t>Test_2</t>
@@ -1544,7 +1547,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H7" s="2">
         <v>0</v>
@@ -1556,7 +1559,7 @@
         <v>20</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L7" s="2">
         <v>10000002</v>
@@ -1565,7 +1568,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:14">
@@ -1573,7 +1576,7 @@
         <v>10000003</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E8" s="2">
         <v>10000003</v>
@@ -1582,7 +1585,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H8" s="2">
         <v>0</v>
@@ -1594,7 +1597,7 @@
         <v>15</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L8" s="2">
         <v>10000003</v>
@@ -1611,7 +1614,7 @@
         <v>10000004</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E9" s="2">
         <v>10000004</v>
@@ -1620,7 +1623,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H9" s="2">
         <v>11</v>
@@ -1641,10 +1644,10 @@
         <v>0</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -1652,7 +1655,7 @@
         <v>10000005</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E10" s="2">
         <v>10000005</v>
@@ -1661,7 +1664,7 @@
         <v>1</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H10" s="2">
         <v>12</v>
@@ -1673,7 +1676,7 @@
         <v>200</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L10" s="2">
         <v>10000005</v>
@@ -1685,7 +1688,7 @@
         <v>32</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:15">
@@ -1693,7 +1696,7 @@
         <v>10000006</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E11" s="2">
         <v>10000006</v>
@@ -1702,7 +1705,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H11" s="2">
         <v>10</v>
@@ -1714,7 +1717,7 @@
         <v>400</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L11" s="2">
         <v>10000006</v>
@@ -1726,7 +1729,7 @@
         <v>32</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:15">
@@ -1734,7 +1737,7 @@
         <v>20000001</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E12" s="2">
         <v>10000007</v>
@@ -1743,7 +1746,7 @@
         <v>1</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H12" s="2">
         <v>10</v>
@@ -1767,7 +1770,7 @@
         <v>32</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -172,7 +172,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="49">
   <si>
     <t>Id</t>
   </si>
@@ -276,22 +276,25 @@
     <t>箭手普通攻击</t>
   </si>
   <si>
+    <t>Skill_Projectile_Track</t>
+  </si>
+  <si>
+    <t>Test_2</t>
+  </si>
+  <si>
+    <t>gongjian</t>
+  </si>
+  <si>
+    <t>法师普通攻击</t>
+  </si>
+  <si>
+    <t>Test_3</t>
+  </si>
+  <si>
+    <t>箭雨</t>
+  </si>
+  <si>
     <t>Skill_Action_Common</t>
-  </si>
-  <si>
-    <t>Test_2</t>
-  </si>
-  <si>
-    <t>gongjian</t>
-  </si>
-  <si>
-    <t>法师普通攻击</t>
-  </si>
-  <si>
-    <t>Test_3</t>
-  </si>
-  <si>
-    <t>箭雨</t>
   </si>
   <si>
     <t>jianyu</t>
@@ -1623,7 +1626,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H9" s="2">
         <v>11</v>
@@ -1644,10 +1647,10 @@
         <v>0</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -1655,7 +1658,7 @@
         <v>10000005</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E10" s="2">
         <v>10000005</v>
@@ -1664,7 +1667,7 @@
         <v>1</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H10" s="2">
         <v>12</v>
@@ -1688,7 +1691,7 @@
         <v>32</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:15">
@@ -1696,7 +1699,7 @@
         <v>10000006</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E11" s="2">
         <v>10000006</v>
@@ -1705,7 +1708,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H11" s="2">
         <v>10</v>
@@ -1729,7 +1732,7 @@
         <v>32</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:15">
@@ -1737,7 +1740,7 @@
         <v>20000001</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E12" s="2">
         <v>10000007</v>
@@ -1746,7 +1749,7 @@
         <v>1</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H12" s="2">
         <v>10</v>
@@ -1770,7 +1773,7 @@
         <v>32</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -172,7 +172,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="49">
   <si>
     <t>Id</t>
   </si>
@@ -294,7 +294,7 @@
     <t>箭雨</t>
   </si>
   <si>
-    <t>Skill_Action_Common</t>
+    <t>Skill_Circle</t>
   </si>
   <si>
     <t>jianyu</t>
@@ -503,18 +503,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1666,9 +1666,7 @@
       <c r="F10" s="2">
         <v>1</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>40</v>
-      </c>
+      <c r="G10" s="2"/>
       <c r="H10" s="2">
         <v>12</v>
       </c>
@@ -1707,9 +1705,7 @@
       <c r="F11" s="2">
         <v>1</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>40</v>
-      </c>
+      <c r="G11" s="2"/>
       <c r="H11" s="2">
         <v>10</v>
       </c>
@@ -1748,9 +1744,7 @@
       <c r="F12" s="2">
         <v>1</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>40</v>
-      </c>
+      <c r="G12" s="2"/>
       <c r="H12" s="2">
         <v>10</v>
       </c>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12960"/>
+    <workbookView windowWidth="28800" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="E3" authorId="0">
+    <comment ref="D3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -54,7 +54,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F3" authorId="0">
+    <comment ref="E3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -77,7 +77,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="0">
+    <comment ref="I3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -99,7 +99,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L3" authorId="0">
+    <comment ref="K3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -122,7 +122,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M3" authorId="0">
+    <comment ref="L3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -145,7 +145,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N3" authorId="0">
+    <comment ref="M3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -172,11 +172,68 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="52">
+  <si>
+    <t>##var</t>
+  </si>
   <si>
     <t>Id</t>
   </si>
   <si>
+    <t>SkillName</t>
+  </si>
+  <si>
+    <t>SkillIcon</t>
+  </si>
+  <si>
+    <t>SkillActType</t>
+  </si>
+  <si>
+    <t>SkillHandler</t>
+  </si>
+  <si>
+    <t>SkillCD</t>
+  </si>
+  <si>
+    <t>SkillLiveTime</t>
+  </si>
+  <si>
+    <t>DamgeValue</t>
+  </si>
+  <si>
+    <t>SkillAnimation</t>
+  </si>
+  <si>
+    <t>SkillHitEffectID</t>
+  </si>
+  <si>
+    <t>BuffID</t>
+  </si>
+  <si>
+    <t>SkillMusic</t>
+  </si>
+  <si>
+    <t>SkillDescribe</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>double</t>
+  </si>
+  <si>
+    <t>array,int#sep=,</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
     <t>技能名称</t>
   </si>
   <si>
@@ -211,54 +268,6 @@
   </si>
   <si>
     <t>技能描述</t>
-  </si>
-  <si>
-    <t>SkillName</t>
-  </si>
-  <si>
-    <t>SkillIcon</t>
-  </si>
-  <si>
-    <t>SkillActType</t>
-  </si>
-  <si>
-    <t>SkillHandler</t>
-  </si>
-  <si>
-    <t>SkillCD</t>
-  </si>
-  <si>
-    <t>SkillLiveTime</t>
-  </si>
-  <si>
-    <t>DamgeValue</t>
-  </si>
-  <si>
-    <t>SkillAnimation</t>
-  </si>
-  <si>
-    <t>SkillHitEffectID</t>
-  </si>
-  <si>
-    <t>BuffID</t>
-  </si>
-  <si>
-    <t>SkillMusic</t>
-  </si>
-  <si>
-    <t>SkillDescribe</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>double</t>
-  </si>
-  <si>
-    <t>int[]</t>
   </si>
   <si>
     <t>战士普通攻击</t>
@@ -503,17 +512,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -758,9 +767,7 @@
       <top style="thin">
         <color theme="0"/>
       </top>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -773,7 +780,9 @@
       <top style="thin">
         <color theme="0"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1364,410 +1373,415 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:O12"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="10.875" style="2" customWidth="1"/>
-    <col min="3" max="14" width="17.875" style="2"/>
-    <col min="15" max="15" width="50.625" style="2" customWidth="1"/>
-    <col min="16" max="16384" width="17.875" style="2"/>
+    <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
+    <col min="2" max="13" width="17.875" style="2"/>
+    <col min="14" max="14" width="50.625" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="17.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1"/>
-    <row r="2" s="1" customFormat="1" customHeight="1"/>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C3" s="3" t="s">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C4" s="3" t="s">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="2:13">
+      <c r="B4" s="2">
+        <v>10000001</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="2">
+        <v>10000001</v>
+      </c>
+      <c r="E4" s="2">
         <v>0</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I4" s="2">
+        <v>10</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" s="2">
+        <v>10000001</v>
+      </c>
+      <c r="L4" s="2">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="2:13">
+      <c r="B5" s="2">
+        <v>10000002</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="2">
+        <v>10000002</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I5" s="2">
+        <v>20</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K5" s="2">
+        <v>10000002</v>
+      </c>
+      <c r="L5" s="2">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="2:13">
+      <c r="B6" s="2">
+        <v>10000003</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="2">
+        <v>10000003</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I6" s="2">
         <v>15</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>24</v>
+      <c r="J6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K6" s="2">
+        <v>10000003</v>
+      </c>
+      <c r="L6" s="2">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>26</v>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="2:14">
+      <c r="B7" s="2">
+        <v>10000004</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="2">
+        <v>10000004</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" s="2">
+        <v>11</v>
+      </c>
+      <c r="H7" s="2">
+        <v>2000</v>
+      </c>
+      <c r="I7" s="2">
+        <v>100</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K7" s="2">
+        <v>10000004</v>
+      </c>
+      <c r="L7" s="2">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C6" s="2">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="2:14">
+      <c r="B8" s="2">
+        <v>10000005</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="2">
+        <v>10000005</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2">
+        <v>12</v>
+      </c>
+      <c r="H8" s="2">
+        <v>3000</v>
+      </c>
+      <c r="I8" s="2">
+        <v>200</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K8" s="2">
+        <v>10000005</v>
+      </c>
+      <c r="L8" s="2">
+        <v>10000002</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="2:14">
+      <c r="B9" s="2">
+        <v>10000006</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="2">
+        <v>10000006</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2">
+        <v>10</v>
+      </c>
+      <c r="H9" s="2">
+        <v>2000</v>
+      </c>
+      <c r="I9" s="2">
+        <v>400</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K9" s="2">
+        <v>10000006</v>
+      </c>
+      <c r="L9" s="2">
         <v>10000001</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" s="2">
-        <v>10000001</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" s="2">
-        <v>0</v>
-      </c>
-      <c r="I6" s="2">
-        <v>1000</v>
-      </c>
-      <c r="J6" s="2">
+      <c r="M9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="2:14">
+      <c r="B10" s="2">
+        <v>20000001</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="2">
+        <v>10000007</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1</v>
+      </c>
+      <c r="G10" s="2">
         <v>10</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L6" s="2">
-        <v>10000001</v>
-      </c>
-      <c r="M6" s="2">
-        <v>0</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C7" s="2">
-        <v>10000002</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" s="2">
-        <v>10000002</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
-      <c r="G7" s="2" t="s">
+      <c r="H10" s="2">
+        <v>3000</v>
+      </c>
+      <c r="I10" s="2">
+        <v>500</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="H7" s="2">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2">
-        <v>1000</v>
-      </c>
-      <c r="J7" s="2">
-        <v>20</v>
-      </c>
-      <c r="K7" s="2" t="s">
+      <c r="K10" s="2">
+        <v>10000006</v>
+      </c>
+      <c r="L10" s="2">
+        <v>10000003</v>
+      </c>
+      <c r="M10" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="L7" s="2">
-        <v>10000002</v>
-      </c>
-      <c r="M7" s="2">
-        <v>0</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C8" s="2">
-        <v>10000003</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" s="2">
-        <v>10000003</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H8" s="2">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2">
-        <v>1000</v>
-      </c>
-      <c r="J8" s="2">
-        <v>15</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L8" s="2">
-        <v>10000003</v>
-      </c>
-      <c r="M8" s="2">
-        <v>0</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C9" s="2">
-        <v>10000004</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" s="2">
-        <v>10000004</v>
-      </c>
-      <c r="F9" s="2">
-        <v>1</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H9" s="2">
-        <v>11</v>
-      </c>
-      <c r="I9" s="2">
-        <v>2000</v>
-      </c>
-      <c r="J9" s="2">
-        <v>100</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L9" s="2">
-        <v>10000004</v>
-      </c>
-      <c r="M9" s="2">
-        <v>0</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C10" s="2">
-        <v>10000005</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="2">
-        <v>10000005</v>
-      </c>
-      <c r="F10" s="2">
-        <v>1</v>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2">
-        <v>12</v>
-      </c>
-      <c r="I10" s="2">
-        <v>3000</v>
-      </c>
-      <c r="J10" s="2">
-        <v>200</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L10" s="2">
-        <v>10000005</v>
-      </c>
-      <c r="M10" s="2">
-        <v>10000002</v>
-      </c>
       <c r="N10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="3:15">
-      <c r="C11" s="2">
-        <v>10000006</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11" s="2">
-        <v>10000006</v>
-      </c>
-      <c r="F11" s="2">
-        <v>1</v>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2">
-        <v>10</v>
-      </c>
-      <c r="I11" s="2">
-        <v>2000</v>
-      </c>
-      <c r="J11" s="2">
-        <v>400</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L11" s="2">
-        <v>10000006</v>
-      </c>
-      <c r="M11" s="2">
-        <v>10000001</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="3:15">
-      <c r="C12" s="2">
-        <v>20000001</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E12" s="2">
-        <v>10000007</v>
-      </c>
-      <c r="F12" s="2">
-        <v>1</v>
-      </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2">
-        <v>10</v>
-      </c>
-      <c r="I12" s="2">
-        <v>3000</v>
-      </c>
-      <c r="J12" s="2">
-        <v>500</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L12" s="2">
-        <v>10000006</v>
-      </c>
-      <c r="M12" s="2">
-        <v>10000003</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\DreamGit\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AE6FD3F-CC18-46A5-B0B5-6A4F5A956EA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F273DCB3-E806-4016-BD5A-F96B5CF48954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -123,7 +123,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{2B9772A6-C32C-4D2B-9ADC-599487AE6118}">
+    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{2B9772A6-C32C-4D2B-9ADC-599487AE6118}">
       <text>
         <r>
           <rPr>
@@ -150,7 +150,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{7F6128C4-DBCE-4EE3-99FA-014D9736FEEB}">
+    <comment ref="K3" authorId="0" shapeId="0" xr:uid="{7F6128C4-DBCE-4EE3-99FA-014D9736FEEB}">
       <text>
         <r>
           <rPr>
@@ -178,14 +178,11 @@
 0：无视
 1：受到伤害触发概率
 2：普通攻击触发概率
-2：血量低于多少百分比触发
-4: 暴击时触发效果
-5：闪避时触发效果
-6：即将死亡时触发</t>
+3：血量低于多少百分比触发</t>
         </r>
       </text>
     </comment>
-    <comment ref="K3" authorId="0" shapeId="0" xr:uid="{8C9963A2-D47B-4BC9-84FA-9E6C60A29122}">
+    <comment ref="L3" authorId="0" shapeId="0" xr:uid="{8C9963A2-D47B-4BC9-84FA-9E6C60A29122}">
       <text>
         <r>
           <rPr>
@@ -211,7 +208,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L3" authorId="0" shapeId="0" xr:uid="{DB83C9A5-AFE2-4375-AB4F-95C2ED481D5C}">
+    <comment ref="M3" authorId="0" shapeId="0" xr:uid="{DB83C9A5-AFE2-4375-AB4F-95C2ED481D5C}">
       <text>
         <r>
           <rPr>
@@ -241,7 +238,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O3" authorId="0" shapeId="0" xr:uid="{FEF92B9C-3263-4FB8-837A-F0B1BEC7FF7A}">
+    <comment ref="P3" authorId="0" shapeId="0" xr:uid="{FEF92B9C-3263-4FB8-837A-F0B1BEC7FF7A}">
       <text>
         <r>
           <rPr>
@@ -267,7 +264,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="Q3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -289,7 +286,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="S3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -311,7 +308,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S3" authorId="0" shapeId="0" xr:uid="{8EF5F397-BE4E-40FF-94E8-006F8482525C}">
+    <comment ref="T3" authorId="0" shapeId="0" xr:uid="{8EF5F397-BE4E-40FF-94E8-006F8482525C}">
       <text>
         <r>
           <rPr>
@@ -342,7 +339,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="0" shapeId="0" xr:uid="{3BCCCB13-76C2-4EC2-B1C1-C6978B3A4870}">
+    <comment ref="U3" authorId="0" shapeId="0" xr:uid="{3BCCCB13-76C2-4EC2-B1C1-C6978B3A4870}">
       <text>
         <r>
           <rPr>
@@ -369,7 +366,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U3" authorId="0" shapeId="0" xr:uid="{11E1267C-E7F4-415F-BDF0-181748645284}">
+    <comment ref="V3" authorId="0" shapeId="0" xr:uid="{11E1267C-E7F4-415F-BDF0-181748645284}">
       <text>
         <r>
           <rPr>
@@ -399,7 +396,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="W3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -422,7 +419,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="Y3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -450,7 +447,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="106">
   <si>
     <t>##var</t>
   </si>
@@ -604,10 +601,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>生命值低于30%的敌人，造成350%物理伤害；若成功击杀，将额外恢复50%的能量。</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>SkillDescribe</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -764,7 +757,81 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>10000001,10000005</t>
+    <t>对敌人造成350%物理伤害，如果敌人生命值低于30%，造成400%物理伤害；若成功击杀，将额外恢复50%的怒气。</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加额外的100%攻击力,持续5秒,并且自身的普通攻击变成溅射伤害。</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Test_1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>jianyu</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>10000006,</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>在受到攻击时有17%的概率触发旋风斩,对附近单位造成150%伤害。</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次攻击有概率对当前目标造成血量流失效果,使其每秒造成40%伤害,且造成伤害降低20%，持续4秒。</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>巨力挥舞</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>溅射</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>战吼</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到攻击有20%概率触发,提升自身的30%攻击速度和移动速度,并使自身的受到的伤害降低30%,持续5秒。</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击有20%概率释放,向目标区域的敌人投掷风暴之锤,造成200%伤害,并使其造成眩晕效果,持续1秒。</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>10000009,10000010,100000111</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>剑刃风暴</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>挥动剑刃造成风暴,对附近敌人持续旋转3秒,每0.5秒造成100%伤害。</t>
+  </si>
+  <si>
+    <t>治疗守卫</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>10000001,10000006</t>
+  </si>
+  <si>
+    <t>脚本参数</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>GameObjectParameter</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -859,7 +926,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -875,6 +942,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1" tint="0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -937,7 +1010,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -965,7 +1038,25 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1244,19 +1335,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y18"/>
+  <dimension ref="A1:Z21"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
-    <col min="2" max="11" width="17.875" style="2"/>
-    <col min="12" max="12" width="19.125" style="2" customWidth="1"/>
-    <col min="13" max="22" width="17.875" style="2"/>
-    <col min="23" max="24" width="20.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="100.625" style="2" customWidth="1"/>
-    <col min="26" max="16384" width="17.875" style="2"/>
+    <col min="2" max="8" width="17.875" style="2"/>
+    <col min="9" max="9" width="21.875" style="2" customWidth="1"/>
+    <col min="10" max="12" width="17.875" style="2"/>
+    <col min="13" max="13" width="19.125" style="2" customWidth="1"/>
+    <col min="14" max="23" width="17.875" style="2"/>
+    <col min="24" max="25" width="20.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="100.625" style="2" customWidth="1"/>
+    <col min="27" max="16384" width="17.875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:26" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1273,67 +1366,70 @@
         <v>4</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
       <c r="I1" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J1" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="P1" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="T1" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="U1" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="P1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="R1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="S1" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="T1" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="U1" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="V1" s="4" t="s">
+      <c r="V1" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="W1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="W1" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="X1" s="4" t="s">
+      <c r="X1" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="Y1" s="6" t="s">
-        <v>48</v>
+      <c r="Z1" s="6" t="s">
+        <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:25" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
@@ -1359,58 +1455,61 @@
         <v>15</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>42</v>
+        <v>104</v>
       </c>
       <c r="J2" s="6" t="s">
         <v>42</v>
       </c>
       <c r="K2" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="L2" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="M2" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="N2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="O2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="P2" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="Q2" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>15</v>
       </c>
       <c r="R2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="S2" s="6" t="s">
-        <v>42</v>
+      <c r="S2" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="T2" s="6" t="s">
         <v>42</v>
       </c>
       <c r="U2" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="V2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="V2" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="W2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="W2" s="6" t="s">
-        <v>60</v>
-      </c>
       <c r="X2" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="Y2" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y2" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z2" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:25" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:26" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
@@ -1427,72 +1526,75 @@
         <v>20</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>21</v>
       </c>
       <c r="I3" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="J3" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="K3" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="L3" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="M3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="N3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="O3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="O3" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="P3" s="5" t="s">
+      <c r="P3" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="Q3" s="5" t="s">
+      <c r="R3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="R3" s="5" t="s">
+      <c r="S3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="S3" s="7" t="s">
-        <v>55</v>
-      </c>
       <c r="T3" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="U3" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="V3" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="U3" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="V3" s="5" t="s">
+      <c r="W3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="W3" s="7" t="s">
-        <v>61</v>
-      </c>
       <c r="X3" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="Y3" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y3" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z3" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:25" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="2">
         <v>10000001</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D4" s="2">
         <v>10000001</v>
@@ -1507,63 +1609,64 @@
         <v>5</v>
       </c>
       <c r="H4" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I4" s="8"/>
+      <c r="J4" s="2">
+        <v>1</v>
+      </c>
+      <c r="K4" s="2">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2">
+        <v>1</v>
+      </c>
+      <c r="O4" s="2">
+        <v>3000</v>
+      </c>
+      <c r="P4" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>0</v>
+      </c>
+      <c r="R4" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="S4" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="I4" s="2">
-        <v>1</v>
-      </c>
-      <c r="J4" s="2">
-        <v>0</v>
-      </c>
-      <c r="K4" s="2">
-        <v>0</v>
-      </c>
-      <c r="L4" s="2">
-        <v>0</v>
-      </c>
-      <c r="M4" s="2">
-        <v>1</v>
-      </c>
-      <c r="N4" s="2">
-        <v>3000</v>
-      </c>
-      <c r="O4" s="2">
-        <v>1</v>
-      </c>
-      <c r="P4" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="R4" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="S4" s="2">
+      <c r="T4" s="2">
         <v>2</v>
       </c>
-      <c r="T4" s="2">
-        <v>0</v>
-      </c>
       <c r="U4" s="2">
         <v>0</v>
       </c>
       <c r="V4" s="2">
+        <v>0</v>
+      </c>
+      <c r="W4" s="2">
         <v>10000001</v>
       </c>
-      <c r="W4" s="2">
-        <v>0</v>
-      </c>
       <c r="X4" s="2">
         <v>0</v>
       </c>
+      <c r="Y4" s="2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:25" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="2">
         <v>10000002</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D5" s="2">
         <v>10000002</v>
@@ -1578,63 +1681,64 @@
         <v>5</v>
       </c>
       <c r="H5" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I5" s="8"/>
+      <c r="J5" s="2">
+        <v>1</v>
+      </c>
+      <c r="K5" s="2">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2">
+        <v>0</v>
+      </c>
+      <c r="N5" s="2">
+        <v>1</v>
+      </c>
+      <c r="O5" s="2">
+        <v>3000</v>
+      </c>
+      <c r="P5" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>0</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S5" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="I5" s="2">
-        <v>1</v>
-      </c>
-      <c r="J5" s="2">
-        <v>0</v>
-      </c>
-      <c r="K5" s="2">
-        <v>0</v>
-      </c>
-      <c r="L5" s="2">
-        <v>0</v>
-      </c>
-      <c r="M5" s="2">
-        <v>1</v>
-      </c>
-      <c r="N5" s="2">
-        <v>3000</v>
-      </c>
-      <c r="O5" s="2">
-        <v>1</v>
-      </c>
-      <c r="P5" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="R5" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="S5" s="2">
+      <c r="T5" s="2">
         <v>2</v>
       </c>
-      <c r="T5" s="2">
-        <v>0</v>
-      </c>
       <c r="U5" s="2">
         <v>0</v>
       </c>
       <c r="V5" s="2">
+        <v>0</v>
+      </c>
+      <c r="W5" s="2">
         <v>10000002</v>
       </c>
-      <c r="W5" s="2">
-        <v>0</v>
-      </c>
       <c r="X5" s="2">
         <v>0</v>
       </c>
+      <c r="Y5" s="2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:25" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="2">
         <v>10000003</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D6" s="2">
         <v>10000003</v>
@@ -1649,58 +1753,59 @@
         <v>5</v>
       </c>
       <c r="H6" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I6" s="8"/>
+      <c r="J6" s="2">
+        <v>1</v>
+      </c>
+      <c r="K6" s="2">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2">
+        <v>1</v>
+      </c>
+      <c r="O6" s="2">
+        <v>3000</v>
+      </c>
+      <c r="P6" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="S6" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="I6" s="2">
-        <v>1</v>
-      </c>
-      <c r="J6" s="2">
-        <v>0</v>
-      </c>
-      <c r="K6" s="2">
-        <v>0</v>
-      </c>
-      <c r="L6" s="2">
-        <v>0</v>
-      </c>
-      <c r="M6" s="2">
-        <v>1</v>
-      </c>
-      <c r="N6" s="2">
-        <v>3000</v>
-      </c>
-      <c r="O6" s="2">
-        <v>1</v>
-      </c>
-      <c r="P6" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="R6" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="S6" s="2">
+      <c r="T6" s="2">
         <v>2</v>
       </c>
-      <c r="T6" s="2">
-        <v>0</v>
-      </c>
       <c r="U6" s="2">
         <v>0</v>
       </c>
       <c r="V6" s="2">
+        <v>0</v>
+      </c>
+      <c r="W6" s="2">
         <v>10000003</v>
       </c>
-      <c r="W6" s="2">
-        <v>0</v>
-      </c>
       <c r="X6" s="2">
         <v>0</v>
       </c>
+      <c r="Y6" s="2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:25" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="2">
         <v>10000004</v>
       </c>
@@ -1722,11 +1827,9 @@
       <c r="H7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="I7" s="2">
-        <v>1</v>
-      </c>
+      <c r="I7" s="2"/>
       <c r="J7" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="2">
         <v>0</v>
@@ -1735,169 +1838,190 @@
         <v>0</v>
       </c>
       <c r="M7" s="2">
+        <v>0</v>
+      </c>
+      <c r="N7" s="2">
         <v>11</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>5000</v>
       </c>
-      <c r="O7" s="2">
-        <v>1</v>
-      </c>
       <c r="P7" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2">
         <v>100</v>
       </c>
-      <c r="Q7" s="2" t="s">
+      <c r="R7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="R7" s="2" t="s">
+      <c r="S7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="S7" s="2">
-        <v>1</v>
-      </c>
       <c r="T7" s="2">
         <v>1</v>
       </c>
       <c r="U7" s="2">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2">
         <v>4</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>10000004</v>
       </c>
-      <c r="W7" s="2">
-        <v>0</v>
-      </c>
       <c r="X7" s="2">
         <v>0</v>
       </c>
-      <c r="Y7" s="2" t="s">
+      <c r="Y7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="2">
+    <row r="8" spans="1:26" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="11">
         <v>20000001</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="11">
         <v>20000001</v>
       </c>
-      <c r="E8" s="2">
-        <v>1</v>
-      </c>
-      <c r="F8" s="2">
-        <v>1</v>
-      </c>
-      <c r="G8" s="2">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2">
-        <v>1</v>
-      </c>
-      <c r="J8" s="2">
-        <v>0</v>
-      </c>
-      <c r="K8" s="2">
-        <v>0</v>
-      </c>
-      <c r="L8" s="2">
-        <v>0</v>
-      </c>
-      <c r="M8" s="2">
-        <v>1</v>
-      </c>
-      <c r="N8" s="2">
+      <c r="E8" s="11">
+        <v>1</v>
+      </c>
+      <c r="F8" s="11">
+        <v>1</v>
+      </c>
+      <c r="G8" s="11">
+        <v>0</v>
+      </c>
+      <c r="J8" s="11">
+        <v>1</v>
+      </c>
+      <c r="K8" s="11">
+        <v>0</v>
+      </c>
+      <c r="L8" s="11">
+        <v>0</v>
+      </c>
+      <c r="M8" s="11">
+        <v>0</v>
+      </c>
+      <c r="N8" s="11">
+        <v>1</v>
+      </c>
+      <c r="O8" s="11">
         <v>3000</v>
       </c>
-      <c r="O8" s="2">
+      <c r="P8" s="11">
         <v>3.5</v>
       </c>
-      <c r="P8" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="2" t="s">
+      <c r="Q8" s="11">
+        <v>0</v>
+      </c>
+      <c r="R8" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="R8" s="8" t="s">
+      <c r="S8" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="T8" s="11">
+        <v>2</v>
+      </c>
+      <c r="U8" s="11">
+        <v>0</v>
+      </c>
+      <c r="V8" s="11">
+        <v>0</v>
+      </c>
+      <c r="W8" s="11">
+        <v>10000001</v>
+      </c>
+      <c r="Z8" s="12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="11">
+        <v>20000002</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="T8" s="2">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2">
-        <v>20000001</v>
-      </c>
-      <c r="Y8" s="8" t="s">
-        <v>47</v>
+      <c r="D9" s="11">
+        <v>20000002</v>
+      </c>
+      <c r="E9" s="11">
+        <v>1</v>
+      </c>
+      <c r="F9" s="11">
+        <v>1</v>
+      </c>
+      <c r="G9" s="11">
+        <v>0</v>
+      </c>
+      <c r="J9" s="11">
+        <v>1</v>
+      </c>
+      <c r="K9" s="11">
+        <v>0</v>
+      </c>
+      <c r="L9" s="11">
+        <v>0</v>
+      </c>
+      <c r="M9" s="11">
+        <v>0</v>
+      </c>
+      <c r="N9" s="11">
+        <v>1</v>
+      </c>
+      <c r="O9" s="11">
+        <v>5000</v>
+      </c>
+      <c r="P9" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>0</v>
+      </c>
+      <c r="R9" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="S9" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="T9" s="11">
+        <v>3</v>
+      </c>
+      <c r="U9" s="11">
+        <v>0</v>
+      </c>
+      <c r="V9" s="11">
+        <v>0</v>
+      </c>
+      <c r="W9" s="11">
+        <v>10000001</v>
+      </c>
+      <c r="X9" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="Y9" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="12" t="s">
+        <v>87</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="2">
-        <v>20000002</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D9" s="2">
-        <v>20000002</v>
-      </c>
-      <c r="E9" s="2">
-        <v>1</v>
-      </c>
-      <c r="F9" s="2">
-        <v>1</v>
-      </c>
-      <c r="G9" s="2">
-        <v>0</v>
-      </c>
-      <c r="I9" s="2">
-        <v>1</v>
-      </c>
-      <c r="J9" s="2">
-        <v>0</v>
-      </c>
-      <c r="K9" s="2">
-        <v>0</v>
-      </c>
-      <c r="L9" s="2">
-        <v>0</v>
-      </c>
-      <c r="M9" s="2">
-        <v>1</v>
-      </c>
-      <c r="N9" s="2">
-        <v>5000</v>
-      </c>
-      <c r="O9" s="2">
-        <v>0</v>
-      </c>
-      <c r="P9" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="S9" s="2">
-        <v>3</v>
-      </c>
-      <c r="T9" s="2">
-        <v>3</v>
-      </c>
-      <c r="U9" s="2">
-        <v>3</v>
-      </c>
-      <c r="X9" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="2">
         <v>20000003</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D10" s="2">
         <v>20000003</v>
@@ -1911,11 +2035,8 @@
       <c r="G10" s="2">
         <v>0</v>
       </c>
-      <c r="I10" s="2">
-        <v>1</v>
-      </c>
       <c r="J10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" s="2">
         <v>0</v>
@@ -1924,45 +2045,54 @@
         <v>0</v>
       </c>
       <c r="M10" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" s="2">
+        <v>1</v>
+      </c>
+      <c r="O10" s="2">
         <v>2000</v>
       </c>
-      <c r="O10" s="2">
-        <v>0</v>
-      </c>
       <c r="P10" s="2">
-        <v>0</v>
-      </c>
-      <c r="S10" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>0</v>
+      </c>
+      <c r="R10" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="S10" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="T10" s="2">
         <v>4</v>
       </c>
-      <c r="T10" s="2">
-        <v>0</v>
-      </c>
       <c r="U10" s="2">
         <v>0</v>
       </c>
       <c r="V10" s="2">
-        <v>20000003</v>
+        <v>0</v>
       </c>
       <c r="W10" s="2">
+        <v>10000001</v>
+      </c>
+      <c r="X10" s="2">
         <v>10000002</v>
       </c>
-      <c r="X10" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="8" t="s">
-        <v>81</v>
+      <c r="Y10" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="8" t="s">
+        <v>80</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="2">
         <v>20000004</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D11" s="2">
         <v>20000004</v>
@@ -1976,11 +2106,8 @@
       <c r="G11" s="2">
         <v>0</v>
       </c>
-      <c r="I11" s="2">
-        <v>1</v>
-      </c>
       <c r="J11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="2">
         <v>0</v>
@@ -1989,45 +2116,54 @@
         <v>0</v>
       </c>
       <c r="M11" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" s="2">
+        <v>1</v>
+      </c>
+      <c r="O11" s="2">
         <v>3000</v>
       </c>
-      <c r="O11" s="2">
+      <c r="P11" s="2">
         <v>1.5</v>
       </c>
-      <c r="P11" s="2">
-        <v>0</v>
-      </c>
-      <c r="S11" s="2">
-        <v>1</v>
+      <c r="Q11" s="2">
+        <v>0</v>
+      </c>
+      <c r="R11" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="S11" s="8" t="s">
+        <v>89</v>
       </c>
       <c r="T11" s="2">
         <v>1</v>
       </c>
       <c r="U11" s="2">
+        <v>1</v>
+      </c>
+      <c r="V11" s="2">
         <v>6</v>
       </c>
-      <c r="V11" s="2">
-        <v>20000004</v>
-      </c>
       <c r="W11" s="2">
-        <v>0</v>
+        <v>10000001</v>
       </c>
       <c r="X11" s="2">
         <v>0</v>
       </c>
-      <c r="Y11" s="8" t="s">
-        <v>82</v>
+      <c r="Y11" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="8" t="s">
+        <v>81</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="2">
         <v>20000005</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D12" s="2">
         <v>20000005</v>
@@ -2041,11 +2177,8 @@
       <c r="G12" s="2">
         <v>0</v>
       </c>
-      <c r="I12" s="2">
-        <v>1</v>
-      </c>
       <c r="J12" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="2">
         <v>0</v>
@@ -2054,107 +2187,125 @@
         <v>0</v>
       </c>
       <c r="M12" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" s="2">
+        <v>1</v>
+      </c>
+      <c r="O12" s="2">
         <v>5000</v>
       </c>
-      <c r="O12" s="2">
-        <v>0</v>
-      </c>
       <c r="P12" s="2">
         <v>0</v>
       </c>
-      <c r="S12" s="2">
-        <v>0</v>
+      <c r="Q12" s="2">
+        <v>0</v>
+      </c>
+      <c r="R12" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="S12" s="8" t="s">
+        <v>89</v>
       </c>
       <c r="T12" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U12" s="2">
+        <v>1</v>
+      </c>
+      <c r="V12" s="2">
         <v>3</v>
       </c>
-      <c r="V12" s="2">
-        <v>20000005</v>
-      </c>
       <c r="W12" s="2">
-        <v>0</v>
-      </c>
-      <c r="X12" s="9" t="s">
+        <v>10000001</v>
+      </c>
+      <c r="X12" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z12" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="Y12" s="8" t="s">
+    </row>
+    <row r="13" spans="1:26" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="11">
+        <v>20000006</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" s="11">
+        <v>20000006</v>
+      </c>
+      <c r="E13" s="11">
+        <v>1</v>
+      </c>
+      <c r="F13" s="11">
+        <v>2</v>
+      </c>
+      <c r="G13" s="11">
+        <v>0</v>
+      </c>
+      <c r="J13" s="11">
+        <v>1</v>
+      </c>
+      <c r="K13" s="11">
+        <v>0</v>
+      </c>
+      <c r="L13" s="11">
+        <v>0</v>
+      </c>
+      <c r="M13" s="11">
+        <v>0</v>
+      </c>
+      <c r="N13" s="11">
+        <v>1</v>
+      </c>
+      <c r="O13" s="11">
+        <v>5000</v>
+      </c>
+      <c r="P13" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>0</v>
+      </c>
+      <c r="R13" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="S13" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="T13" s="11">
+        <v>0</v>
+      </c>
+      <c r="U13" s="11">
+        <v>0</v>
+      </c>
+      <c r="V13" s="11">
+        <v>0</v>
+      </c>
+      <c r="W13" s="11">
+        <v>10000001</v>
+      </c>
+      <c r="X13" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="12" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="2">
-        <v>20000006</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D13" s="2">
-        <v>20000006</v>
-      </c>
-      <c r="E13" s="2">
-        <v>1</v>
-      </c>
-      <c r="F13" s="2">
-        <v>2</v>
-      </c>
-      <c r="G13" s="2">
-        <v>0</v>
-      </c>
-      <c r="I13" s="2">
-        <v>1</v>
-      </c>
-      <c r="J13" s="2">
-        <v>0</v>
-      </c>
-      <c r="K13" s="2">
-        <v>0</v>
-      </c>
-      <c r="L13" s="2">
-        <v>0</v>
-      </c>
-      <c r="M13" s="2">
-        <v>1</v>
-      </c>
-      <c r="N13" s="2">
-        <v>5000</v>
-      </c>
-      <c r="O13" s="2">
-        <v>0</v>
-      </c>
-      <c r="P13" s="2">
-        <v>0</v>
-      </c>
-      <c r="S13" s="2">
-        <v>0</v>
-      </c>
-      <c r="T13" s="2">
-        <v>0</v>
-      </c>
-      <c r="U13" s="2">
-        <v>0</v>
-      </c>
-      <c r="W13" s="2">
-        <v>0</v>
-      </c>
-      <c r="X13" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="2">
         <v>30000001</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D14" s="2">
         <v>30000001</v>
@@ -2168,55 +2319,64 @@
       <c r="G14" s="2">
         <v>0</v>
       </c>
-      <c r="I14" s="2">
-        <v>2</v>
-      </c>
       <c r="J14" s="2">
         <v>2</v>
       </c>
       <c r="K14" s="2">
+        <v>2</v>
+      </c>
+      <c r="L14" s="2">
         <v>0.2</v>
       </c>
-      <c r="L14" s="2">
-        <v>0</v>
-      </c>
       <c r="M14" s="2">
+        <v>0</v>
+      </c>
+      <c r="N14" s="2">
         <v>9</v>
       </c>
-      <c r="N14" s="2">
+      <c r="O14" s="2">
         <v>3000</v>
       </c>
-      <c r="O14" s="2">
-        <v>0</v>
-      </c>
       <c r="P14" s="2">
         <v>0</v>
       </c>
-      <c r="S14" s="2">
-        <v>0</v>
+      <c r="Q14" s="2">
+        <v>0</v>
+      </c>
+      <c r="R14" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="S14" s="8" t="s">
+        <v>74</v>
       </c>
       <c r="T14" s="2">
         <v>0</v>
       </c>
       <c r="U14" s="2">
-        <v>0</v>
-      </c>
-      <c r="W14" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="X14" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="8" t="s">
-        <v>86</v>
+        <v>1</v>
+      </c>
+      <c r="V14" s="2">
+        <v>2</v>
+      </c>
+      <c r="W14" s="2">
+        <v>10000001</v>
+      </c>
+      <c r="X14" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="Z14" s="8" t="s">
+        <v>85</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="2">
         <v>30000002</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D15" s="2">
         <v>30000002</v>
@@ -2224,68 +2384,422 @@
       <c r="E15" s="2">
         <v>1</v>
       </c>
-      <c r="I15" s="2">
+      <c r="F15" s="2">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2">
         <v>2</v>
       </c>
-      <c r="J15" s="2">
-        <v>1</v>
-      </c>
       <c r="K15" s="2">
-        <v>0.15</v>
+        <v>1</v>
       </c>
       <c r="L15" s="2">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="M15" s="2">
+        <v>0</v>
+      </c>
+      <c r="N15" s="2">
         <v>3</v>
       </c>
+      <c r="O15" s="2">
+        <v>2000</v>
+      </c>
+      <c r="P15" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>0</v>
+      </c>
+      <c r="R15" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="S15" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="T15" s="2">
+        <v>1</v>
+      </c>
+      <c r="U15" s="2">
+        <v>1</v>
+      </c>
+      <c r="V15" s="2">
+        <v>3</v>
+      </c>
+      <c r="W15" s="2">
+        <v>10000001</v>
+      </c>
+      <c r="X15" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="8" t="s">
+        <v>91</v>
+      </c>
     </row>
-    <row r="16" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="2">
+    <row r="16" spans="1:26" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="11">
         <v>30000003</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="D16" s="2">
+      <c r="C16" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="11">
         <v>30000003</v>
       </c>
-      <c r="E16" s="2">
-        <v>1</v>
-      </c>
-      <c r="I16" s="2">
+      <c r="E16" s="11">
+        <v>1</v>
+      </c>
+      <c r="F16" s="11">
+        <v>1</v>
+      </c>
+      <c r="G16" s="11">
+        <v>0</v>
+      </c>
+      <c r="J16" s="11">
         <v>2</v>
       </c>
-      <c r="J16" s="2">
+      <c r="K16" s="11">
         <v>2</v>
       </c>
-      <c r="K16" s="2">
+      <c r="L16" s="11">
         <v>0.2</v>
       </c>
-      <c r="L16" s="2">
-        <v>0</v>
-      </c>
-      <c r="M16" s="2">
+      <c r="M16" s="11">
+        <v>0</v>
+      </c>
+      <c r="N16" s="11">
         <v>10</v>
       </c>
-      <c r="N16" s="2">
-        <v>4</v>
+      <c r="O16" s="11">
+        <v>4000</v>
+      </c>
+      <c r="P16" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="Q16" s="11">
+        <v>0</v>
+      </c>
+      <c r="R16" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="S16" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="T16" s="11">
+        <v>2</v>
+      </c>
+      <c r="U16" s="11">
+        <v>0</v>
+      </c>
+      <c r="V16" s="11">
+        <v>0</v>
+      </c>
+      <c r="W16" s="11">
+        <v>10000001</v>
+      </c>
+      <c r="X16" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="15">
+        <v>10000007</v>
+      </c>
+      <c r="Z16" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="2">
         <v>30000004</v>
       </c>
+      <c r="C17" s="8" t="s">
+        <v>93</v>
+      </c>
       <c r="D17" s="2">
         <v>30000004</v>
       </c>
+      <c r="E17" s="2">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>1</v>
+      </c>
+      <c r="G17" s="2">
+        <v>0</v>
+      </c>
+      <c r="J17" s="2">
+        <v>2</v>
+      </c>
+      <c r="K17" s="2">
+        <v>2</v>
+      </c>
+      <c r="L17" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="M17" s="2">
+        <v>0</v>
+      </c>
+      <c r="N17" s="2">
+        <v>10</v>
+      </c>
+      <c r="O17" s="2">
+        <v>2000</v>
+      </c>
+      <c r="P17" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>0</v>
+      </c>
+      <c r="R17" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="S17" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="T17" s="2">
+        <v>1</v>
+      </c>
+      <c r="U17" s="2">
+        <v>1</v>
+      </c>
+      <c r="V17" s="2">
+        <v>3</v>
+      </c>
+      <c r="W17" s="2">
+        <v>10000001</v>
+      </c>
+      <c r="X17" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="2">
+        <v>10000008</v>
+      </c>
+      <c r="Z17" s="8" t="s">
+        <v>97</v>
+      </c>
     </row>
-    <row r="18" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="2">
+    <row r="18" spans="2:26" s="11" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="11">
         <v>30000005</v>
       </c>
-      <c r="D18" s="2">
+      <c r="C18" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" s="11">
         <v>30000005</v>
+      </c>
+    </row>
+    <row r="19" spans="2:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="2">
+        <v>30000006</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="D19" s="2">
+        <v>30000006</v>
+      </c>
+      <c r="E19" s="2">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2">
+        <v>0</v>
+      </c>
+      <c r="J19" s="2">
+        <v>2</v>
+      </c>
+      <c r="K19" s="2">
+        <v>1</v>
+      </c>
+      <c r="L19" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="M19" s="2">
+        <v>0</v>
+      </c>
+      <c r="N19" s="2">
+        <v>10</v>
+      </c>
+      <c r="O19" s="2">
+        <v>5000</v>
+      </c>
+      <c r="P19" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="2">
+        <v>0</v>
+      </c>
+      <c r="R19" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="S19" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="T19" s="2">
+        <v>3</v>
+      </c>
+      <c r="U19" s="2">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2">
+        <v>0</v>
+      </c>
+      <c r="W19" s="2">
+        <v>10000001</v>
+      </c>
+      <c r="X19" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z19" s="8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="20" spans="2:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="2">
+        <v>30000007</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="D20" s="2">
+        <v>30000007</v>
+      </c>
+      <c r="E20" s="2">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2">
+        <v>0</v>
+      </c>
+      <c r="J20" s="2">
+        <v>2</v>
+      </c>
+      <c r="K20" s="2">
+        <v>2</v>
+      </c>
+      <c r="L20" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="M20" s="2">
+        <v>0</v>
+      </c>
+      <c r="N20" s="2">
+        <v>10</v>
+      </c>
+      <c r="O20" s="2">
+        <v>3000</v>
+      </c>
+      <c r="P20" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="2">
+        <v>0</v>
+      </c>
+      <c r="R20" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="S20" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="T20" s="2">
+        <v>0</v>
+      </c>
+      <c r="U20" s="2">
+        <v>1</v>
+      </c>
+      <c r="V20" s="2">
+        <v>3</v>
+      </c>
+      <c r="W20" s="2">
+        <v>10000001</v>
+      </c>
+      <c r="X20" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="2:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="2">
+        <v>30000008</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D21" s="2">
+        <v>30000008</v>
+      </c>
+      <c r="E21" s="2">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>1</v>
+      </c>
+      <c r="G21" s="2">
+        <v>0</v>
+      </c>
+      <c r="J21" s="2">
+        <v>2</v>
+      </c>
+      <c r="K21" s="2">
+        <v>3</v>
+      </c>
+      <c r="L21" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="M21" s="2">
+        <v>1</v>
+      </c>
+      <c r="N21" s="2">
+        <v>999</v>
+      </c>
+      <c r="O21" s="2">
+        <v>5000</v>
+      </c>
+      <c r="P21" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="2">
+        <v>0</v>
+      </c>
+      <c r="R21" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="S21" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="T21" s="2">
+        <v>1</v>
+      </c>
+      <c r="U21" s="2">
+        <v>1</v>
+      </c>
+      <c r="V21" s="2">
+        <v>4</v>
+      </c>
+      <c r="W21" s="2">
+        <v>10000001</v>
+      </c>
+      <c r="X21" s="2">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\DreamGit\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F273DCB3-E806-4016-BD5A-F96B5CF48954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C6C9A57-8F24-4555-A149-16F6AB1BBB81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -1010,7 +1011,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1054,9 +1055,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2506,7 +2504,7 @@
       <c r="X16" s="14">
         <v>0</v>
       </c>
-      <c r="Y16" s="15">
+      <c r="Y16" s="12">
         <v>10000007</v>
       </c>
       <c r="Z16" s="12" t="s">

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\DreamGit\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C486B40-7690-41C2-A9BA-6689EBD97A1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{300661A5-248F-4ADF-8D79-0EAEBD922036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -174,7 +174,9 @@
 0：无视
 1：受到伤害触发概率
 2：普通攻击触发概率
-3：血量低于多少百分比触发</t>
+3：血量低于多少百分比触发
+4：开始战斗就触发
+5：队友血量低于多少百分比触发</t>
         </r>
       </text>
     </comment>
@@ -439,7 +441,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="120">
   <si>
     <t>##var</t>
   </si>
@@ -457,9 +459,6 @@
   </si>
   <si>
     <t>DamageType</t>
-  </si>
-  <si>
-    <t>SkillAddAnger</t>
   </si>
   <si>
     <t>SkillHandler</t>
@@ -770,6 +769,57 @@
   </si>
   <si>
     <t>10000007,10000010</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>立即对目标及其周围的单位造成200%伤害,并且使其移动速度和攻击速度降低50%,持续4秒。</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>10000017,10000018</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰封禁制</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰霜新星</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>将当前目标锁定在冰块之中,使其不能移动和攻击，并且造成每秒50%伤害的冻伤效果,持续3秒。</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>10000019,10000020</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>辉煌光环</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>提升场内所有队友的怒气恢复速度,每秒恢复1点。</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>洗礼</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>立即恢复一个友方20%的最大生命值,并对其附近单位造成100%伤害。</t>
+  </si>
+  <si>
+    <t>驱逐</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillAddAnger</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>当己方有队友血量下降到30%后会激励保护其免受后面4次的攻击或技能伤害。</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1239,7 +1289,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z22"/>
+  <dimension ref="A1:Z29"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
@@ -1273,224 +1323,224 @@
         <v>5</v>
       </c>
       <c r="G1" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="U1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="V1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="W1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="X1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="Y1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="Z1" s="4" t="s">
         <v>24</v>
-      </c>
-      <c r="Z1" s="4" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:26" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="M2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="O2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="R2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="S2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="T2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z2" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="W2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="X2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="Y2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="Z2" s="4" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:26" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="I3" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="J3" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="K3" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="L3" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="M3" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="N3" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="O3" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="P3" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="P3" s="5" t="s">
+      <c r="Q3" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="Q3" s="5" t="s">
+      <c r="R3" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="R3" s="5" t="s">
+      <c r="S3" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="S3" s="5" t="s">
+      <c r="T3" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="T3" s="5" t="s">
+      <c r="U3" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="U3" s="5" t="s">
+      <c r="V3" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="V3" s="5" t="s">
+      <c r="W3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="W3" s="5" t="s">
+      <c r="X3" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="X3" s="5" t="s">
+      <c r="Y3" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="Y3" s="5" t="s">
+      <c r="Z3" s="5" t="s">
         <v>55</v>
-      </c>
-      <c r="Z3" s="5" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:26" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -1498,7 +1548,7 @@
         <v>10000001</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D4" s="2">
         <v>10000001</v>
@@ -1513,7 +1563,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2">
@@ -1541,10 +1591,10 @@
         <v>0</v>
       </c>
       <c r="R4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="S4" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="T4" s="2">
         <v>2</v>
@@ -1570,7 +1620,7 @@
         <v>10000002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D5" s="2">
         <v>10000002</v>
@@ -1585,7 +1635,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2">
@@ -1613,10 +1663,10 @@
         <v>0</v>
       </c>
       <c r="R5" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="S5" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="T5" s="2">
         <v>2</v>
@@ -1642,7 +1692,7 @@
         <v>10000003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D6" s="2">
         <v>10000003</v>
@@ -1657,7 +1707,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I6" s="2"/>
       <c r="J6" s="2">
@@ -1685,10 +1735,10 @@
         <v>0</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="T6" s="2">
         <v>2</v>
@@ -1714,7 +1764,7 @@
         <v>10000004</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D7" s="2">
         <v>10000004</v>
@@ -1729,7 +1779,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2">
@@ -1757,10 +1807,10 @@
         <v>100</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="T7" s="2">
         <v>1</v>
@@ -1781,7 +1831,7 @@
         <v>0</v>
       </c>
       <c r="Z7" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:26" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -1789,7 +1839,7 @@
         <v>20000001</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D8" s="7">
         <v>20000001</v>
@@ -1828,10 +1878,10 @@
         <v>0</v>
       </c>
       <c r="R8" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="S8" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T8" s="7">
         <v>2</v>
@@ -1852,7 +1902,7 @@
         <v>0</v>
       </c>
       <c r="Z8" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:26" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -1860,7 +1910,7 @@
         <v>20000002</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D9" s="7">
         <v>20000002</v>
@@ -1899,10 +1949,10 @@
         <v>0</v>
       </c>
       <c r="R9" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="S9" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T9" s="7">
         <v>3</v>
@@ -1917,13 +1967,13 @@
         <v>10000001</v>
       </c>
       <c r="X9" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Y9" s="7">
         <v>0</v>
       </c>
       <c r="Z9" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -1931,7 +1981,7 @@
         <v>20000003</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D10" s="2">
         <v>20000003</v>
@@ -1970,10 +2020,10 @@
         <v>0</v>
       </c>
       <c r="R10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="S10" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="S10" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="T10" s="2">
         <v>4</v>
@@ -1994,7 +2044,7 @@
         <v>0</v>
       </c>
       <c r="Z10" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -2002,7 +2052,7 @@
         <v>20000004</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D11" s="2">
         <v>20000004</v>
@@ -2041,10 +2091,10 @@
         <v>0</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="T11" s="2">
         <v>1</v>
@@ -2065,7 +2115,7 @@
         <v>0</v>
       </c>
       <c r="Z11" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -2073,7 +2123,7 @@
         <v>20000005</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D12" s="2">
         <v>20000005</v>
@@ -2112,10 +2162,10 @@
         <v>0</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="T12" s="2">
         <v>0</v>
@@ -2133,10 +2183,10 @@
         <v>0</v>
       </c>
       <c r="Y12" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z12" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="Z12" s="2" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:26" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -2144,7 +2194,7 @@
         <v>20000006</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D13" s="7">
         <v>20000006</v>
@@ -2183,10 +2233,10 @@
         <v>0</v>
       </c>
       <c r="R13" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S13" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="T13" s="7">
         <v>0</v>
@@ -2207,7 +2257,7 @@
         <v>0</v>
       </c>
       <c r="Z13" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -2215,7 +2265,7 @@
         <v>30000001</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D14" s="2">
         <v>30000001</v>
@@ -2254,10 +2304,10 @@
         <v>0</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T14" s="2">
         <v>0</v>
@@ -2275,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="Y14" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z14" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="Z14" s="2" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -2286,7 +2336,7 @@
         <v>30000002</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D15" s="2">
         <v>30000002</v>
@@ -2325,10 +2375,10 @@
         <v>0</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T15" s="2">
         <v>1</v>
@@ -2349,7 +2399,7 @@
         <v>0</v>
       </c>
       <c r="Z15" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:26" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -2357,7 +2407,7 @@
         <v>30000003</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D16" s="7">
         <v>30000003</v>
@@ -2396,10 +2446,10 @@
         <v>0</v>
       </c>
       <c r="R16" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="S16" s="7" t="s">
         <v>59</v>
-      </c>
-      <c r="S16" s="7" t="s">
-        <v>60</v>
       </c>
       <c r="T16" s="7">
         <v>2</v>
@@ -2417,10 +2467,10 @@
         <v>0</v>
       </c>
       <c r="Y16" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Z16" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="2:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -2428,7 +2478,7 @@
         <v>30000004</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D17" s="2">
         <v>30000004</v>
@@ -2467,10 +2517,10 @@
         <v>0</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T17" s="2">
         <v>1</v>
@@ -2491,7 +2541,7 @@
         <v>10000008</v>
       </c>
       <c r="Z17" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="2:26" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -2499,7 +2549,7 @@
         <v>30000005</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D18" s="7">
         <v>30000005</v>
@@ -2538,10 +2588,10 @@
         <v>0</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="S18" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T18" s="7">
         <v>1</v>
@@ -2562,7 +2612,7 @@
         <v>0</v>
       </c>
       <c r="Z18" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="2:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -2570,7 +2620,7 @@
         <v>30000006</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D19" s="2">
         <v>30000006</v>
@@ -2609,10 +2659,10 @@
         <v>0</v>
       </c>
       <c r="R19" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="S19" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="S19" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="T19" s="2">
         <v>3</v>
@@ -2630,10 +2680,10 @@
         <v>0</v>
       </c>
       <c r="Y19" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z19" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="Z19" s="2" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="20" spans="2:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -2641,7 +2691,7 @@
         <v>30000007</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D20" s="2">
         <v>30000007</v>
@@ -2680,10 +2730,10 @@
         <v>0</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T20" s="2">
         <v>0</v>
@@ -2704,7 +2754,7 @@
         <v>0</v>
       </c>
       <c r="Z20" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="2:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -2712,7 +2762,7 @@
         <v>30000008</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D21" s="2">
         <v>30000008</v>
@@ -2751,10 +2801,10 @@
         <v>0</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T21" s="2">
         <v>1</v>
@@ -2775,7 +2825,7 @@
         <v>10000014</v>
       </c>
       <c r="Z21" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="2:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -2783,7 +2833,7 @@
         <v>30000009</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D22" s="2">
         <v>30000009</v>
@@ -2801,10 +2851,10 @@
         <v>2</v>
       </c>
       <c r="K22" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L22" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2">
         <v>0</v>
@@ -2822,10 +2872,10 @@
         <v>0</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T22" s="2">
         <v>3</v>
@@ -2840,13 +2890,378 @@
         <v>10000001</v>
       </c>
       <c r="X22" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Y22" s="2">
         <v>0</v>
       </c>
       <c r="Z22" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="23" spans="2:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="2">
+        <v>30000010</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="2">
+        <v>30000010</v>
+      </c>
+      <c r="E23" s="2">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>2</v>
+      </c>
+      <c r="G23" s="2">
+        <v>0</v>
+      </c>
+      <c r="J23" s="2">
+        <v>2</v>
+      </c>
+      <c r="K23" s="2">
+        <v>2</v>
+      </c>
+      <c r="L23" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="M23" s="2">
+        <v>0</v>
+      </c>
+      <c r="N23" s="2">
+        <v>10</v>
+      </c>
+      <c r="O23" s="2">
+        <v>4000</v>
+      </c>
+      <c r="P23" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q23" s="2">
+        <v>0</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="T23" s="2">
+        <v>1</v>
+      </c>
+      <c r="U23" s="2">
+        <v>1</v>
+      </c>
+      <c r="V23" s="2">
+        <v>3</v>
+      </c>
+      <c r="W23" s="2">
+        <v>10000001</v>
+      </c>
+      <c r="X23" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z23" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="24" spans="2:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="2">
+        <v>30000011</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" s="2">
+        <v>30000011</v>
+      </c>
+      <c r="E24" s="2">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>2</v>
+      </c>
+      <c r="G24" s="2">
+        <v>0</v>
+      </c>
+      <c r="J24" s="2">
+        <v>2</v>
+      </c>
+      <c r="K24" s="2">
+        <v>2</v>
+      </c>
+      <c r="L24" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="M24" s="2">
+        <v>0</v>
+      </c>
+      <c r="N24" s="2">
+        <v>10</v>
+      </c>
+      <c r="O24" s="2">
+        <v>3000</v>
+      </c>
+      <c r="P24" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="Q24" s="2">
+        <v>0</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="S24" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="T24" s="2">
+        <v>2</v>
+      </c>
+      <c r="U24" s="2">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2">
+        <v>0</v>
+      </c>
+      <c r="W24" s="2">
+        <v>10000001</v>
+      </c>
+      <c r="X24" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z24" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="25" spans="2:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="2">
+        <v>30000012</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D25" s="2">
+        <v>30000012</v>
+      </c>
+      <c r="E25" s="2">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>2</v>
+      </c>
+      <c r="G25" s="2">
+        <v>0</v>
+      </c>
+      <c r="J25" s="2">
+        <v>2</v>
+      </c>
+      <c r="K25" s="2">
+        <v>4</v>
+      </c>
+      <c r="L25" s="2">
+        <v>1</v>
+      </c>
+      <c r="M25" s="2">
+        <v>0</v>
+      </c>
+      <c r="N25" s="2">
+        <v>0</v>
+      </c>
+      <c r="O25" s="2">
+        <v>3600000</v>
+      </c>
+      <c r="P25" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="2">
+        <v>0</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="T25" s="2">
+        <v>0</v>
+      </c>
+      <c r="U25" s="2">
+        <v>1</v>
+      </c>
+      <c r="V25" s="2">
+        <v>10</v>
+      </c>
+      <c r="W25" s="2">
+        <v>1000001</v>
+      </c>
+      <c r="X25" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="2">
+        <v>10000021</v>
+      </c>
+      <c r="Z25" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="26" spans="2:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="2">
+        <v>30000013</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D26" s="2">
+        <v>30000013</v>
+      </c>
+      <c r="E26" s="2">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>1</v>
+      </c>
+      <c r="G26" s="2">
+        <v>0</v>
+      </c>
+      <c r="J26" s="2">
+        <v>2</v>
+      </c>
+      <c r="K26" s="2">
+        <v>5</v>
+      </c>
+      <c r="L26" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="M26" s="2">
+        <v>0</v>
+      </c>
+      <c r="N26" s="2">
+        <v>10</v>
+      </c>
+      <c r="O26" s="2">
+        <v>3000</v>
+      </c>
+      <c r="P26" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="2">
+        <v>0</v>
+      </c>
+      <c r="R26" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="S26" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="T26" s="2">
+        <v>1</v>
+      </c>
+      <c r="U26" s="2">
+        <v>1</v>
+      </c>
+      <c r="V26" s="2">
+        <v>3</v>
+      </c>
+      <c r="W26" s="2">
+        <v>1000001</v>
+      </c>
+      <c r="X26" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="2">
+        <v>10000022</v>
+      </c>
+      <c r="Z26" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="27" spans="2:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="2">
+        <v>30000014</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D27" s="2">
+        <v>30000014</v>
+      </c>
+      <c r="E27" s="2">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>1</v>
+      </c>
+      <c r="G27" s="2">
+        <v>0</v>
+      </c>
+      <c r="J27" s="2">
+        <v>2</v>
+      </c>
+      <c r="K27" s="2">
+        <v>5</v>
+      </c>
+      <c r="L27" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="M27" s="2">
+        <v>0</v>
+      </c>
+      <c r="N27" s="2">
+        <v>10</v>
+      </c>
+      <c r="O27" s="2">
+        <v>3000</v>
+      </c>
+      <c r="P27" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="2">
+        <v>0</v>
+      </c>
+      <c r="R27" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="S27" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="T27" s="2">
+        <v>2</v>
+      </c>
+      <c r="U27" s="2">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2">
+        <v>0</v>
+      </c>
+      <c r="W27" s="2">
+        <v>1000001</v>
+      </c>
+      <c r="X27" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="2">
+        <v>10000023</v>
+      </c>
+      <c r="Z27" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="28" spans="2:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="2">
+        <v>30000015</v>
+      </c>
+    </row>
+    <row r="29" spans="2:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="2">
+        <v>30000016</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\DreamGit\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{300661A5-248F-4ADF-8D79-0EAEBD922036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40DB62EF-D5D3-4B4E-95FB-C877ECF96B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -329,7 +329,8 @@
 2  单体指定目标
 3  单体指定自己
 4  单体技能多个目标
-</t>
+5  全体队友
+6  全体敌人</t>
         </r>
       </text>
     </comment>
@@ -441,7 +442,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="130">
   <si>
     <t>##var</t>
   </si>
@@ -820,6 +821,43 @@
   </si>
   <si>
     <t>当己方有队友血量下降到30%后会激励保护其免受后面4次的攻击或技能伤害。</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>退化光环</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>对附近单位造成退化效果,使其移动速度降低25%,并使其造成伤害降低10%。</t>
+  </si>
+  <si>
+    <t>10000024,10000025</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>致命链接</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>将敌方所有目标链接到一起,其中任意一个受到伤害,其他所有单位都额外承受当前伤害的10%,持续5秒。</t>
+  </si>
+  <si>
+    <t>暗言术</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>剧变</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>对一个区域进行施法,使其攻击速度和移动速度降低至50%,持续3秒。</t>
+  </si>
+  <si>
+    <t>10000026,10000027</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>释放强大的魔法治疗一个队友或伤害一个敌人,使其每秒造成60%伤害或每秒恢复2.5%最大生命生命,持续5秒。</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1289,7 +1327,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z29"/>
+  <dimension ref="A1:Z31"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
@@ -3091,16 +3129,16 @@
         <v>100</v>
       </c>
       <c r="T25" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U25" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W25" s="2">
-        <v>1000001</v>
+        <v>10000001</v>
       </c>
       <c r="X25" s="2">
         <v>0</v>
@@ -3171,7 +3209,7 @@
         <v>3</v>
       </c>
       <c r="W26" s="2">
-        <v>1000001</v>
+        <v>10000001</v>
       </c>
       <c r="X26" s="2">
         <v>0</v>
@@ -3242,7 +3280,7 @@
         <v>0</v>
       </c>
       <c r="W27" s="2">
-        <v>1000001</v>
+        <v>10000001</v>
       </c>
       <c r="X27" s="2">
         <v>0</v>
@@ -3258,10 +3296,236 @@
       <c r="B28" s="2">
         <v>30000015</v>
       </c>
+      <c r="C28" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D28" s="2">
+        <v>30000015</v>
+      </c>
+      <c r="E28" s="2">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>1</v>
+      </c>
+      <c r="G28" s="2">
+        <v>0</v>
+      </c>
+      <c r="J28" s="2">
+        <v>2</v>
+      </c>
+      <c r="K28" s="2">
+        <v>4</v>
+      </c>
+      <c r="L28" s="2">
+        <v>1</v>
+      </c>
+      <c r="M28" s="2">
+        <v>0</v>
+      </c>
+      <c r="N28" s="2">
+        <v>0</v>
+      </c>
+      <c r="O28" s="2">
+        <v>3600000</v>
+      </c>
+      <c r="P28" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="2">
+        <v>0</v>
+      </c>
+      <c r="R28" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="S28" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="T28" s="2">
+        <v>0</v>
+      </c>
+      <c r="U28" s="2">
+        <v>1</v>
+      </c>
+      <c r="V28" s="2">
+        <v>4</v>
+      </c>
+      <c r="W28" s="2">
+        <v>10000001</v>
+      </c>
+      <c r="X28" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="Z28" s="2" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="29" spans="2:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="2">
         <v>30000016</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D29" s="2">
+        <v>30000016</v>
+      </c>
+      <c r="E29" s="2">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>2</v>
+      </c>
+      <c r="G29" s="2">
+        <v>0</v>
+      </c>
+      <c r="J29" s="2">
+        <v>2</v>
+      </c>
+      <c r="K29" s="2">
+        <v>2</v>
+      </c>
+      <c r="L29" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="M29" s="2">
+        <v>0</v>
+      </c>
+      <c r="N29" s="2">
+        <v>10</v>
+      </c>
+      <c r="O29" s="2">
+        <v>5000</v>
+      </c>
+      <c r="P29" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="Q29" s="2">
+        <v>0</v>
+      </c>
+      <c r="R29" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="S29" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="T29" s="2">
+        <v>6</v>
+      </c>
+      <c r="U29" s="2">
+        <v>0</v>
+      </c>
+      <c r="V29" s="2">
+        <v>0</v>
+      </c>
+      <c r="W29" s="2">
+        <v>10000001</v>
+      </c>
+      <c r="Z29" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="30" spans="2:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="2">
+        <v>30000017</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D30" s="2">
+        <v>30000017</v>
+      </c>
+      <c r="E30" s="2">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>2</v>
+      </c>
+      <c r="G30" s="2">
+        <v>0</v>
+      </c>
+      <c r="N30" s="2">
+        <v>10</v>
+      </c>
+      <c r="O30" s="2">
+        <v>5000</v>
+      </c>
+      <c r="Z30" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="31" spans="2:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="2">
+        <v>30000018</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D31" s="2">
+        <v>30000018</v>
+      </c>
+      <c r="E31" s="2">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>2</v>
+      </c>
+      <c r="G31" s="2">
+        <v>0</v>
+      </c>
+      <c r="J31" s="2">
+        <v>2</v>
+      </c>
+      <c r="K31" s="2">
+        <v>2</v>
+      </c>
+      <c r="L31" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="M31" s="2">
+        <v>0</v>
+      </c>
+      <c r="N31" s="2">
+        <v>10</v>
+      </c>
+      <c r="O31" s="2">
+        <v>3000</v>
+      </c>
+      <c r="P31" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="2">
+        <v>0</v>
+      </c>
+      <c r="R31" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="S31" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="T31" s="2">
+        <v>1</v>
+      </c>
+      <c r="U31" s="2">
+        <v>1</v>
+      </c>
+      <c r="V31" s="2">
+        <v>4</v>
+      </c>
+      <c r="W31" s="2">
+        <v>10000001</v>
+      </c>
+      <c r="X31" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="Z31" s="2" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -1,38 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\DreamGit\Unity\Assets\Config\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7DF608E-ADBD-44A3-B098-17DD40641906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="D3" authorId="0">
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -54,7 +47,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E3" authorId="0">
+    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -77,7 +70,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F3" authorId="0">
+    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -100,7 +93,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0">
+    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -122,7 +115,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="0">
+    <comment ref="K3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -145,7 +138,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K3" authorId="0">
+    <comment ref="L3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -175,7 +168,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L3" authorId="0">
+    <comment ref="M3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
@@ -197,7 +190,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M3" authorId="0">
+    <comment ref="N3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
       <text>
         <r>
           <rPr>
@@ -223,7 +216,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P3" authorId="0">
+    <comment ref="Q3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
       <text>
         <r>
           <rPr>
@@ -245,7 +238,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q3" authorId="0">
+    <comment ref="R3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -267,7 +260,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S3" authorId="0">
+    <comment ref="T3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -289,7 +282,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="0">
+    <comment ref="U3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
       <text>
         <r>
           <rPr>
@@ -317,7 +310,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U3" authorId="0">
+    <comment ref="V3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000D000000}">
       <text>
         <r>
           <rPr>
@@ -340,7 +333,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V3" authorId="0">
+    <comment ref="W3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
       <text>
         <r>
           <rPr>
@@ -366,7 +359,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W3" authorId="0">
+    <comment ref="X3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000F000000}">
       <text>
         <r>
           <rPr>
@@ -389,7 +382,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y3" authorId="0">
+    <comment ref="Z3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000010000000}">
       <text>
         <r>
           <rPr>
@@ -417,7 +410,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="132">
   <si>
     <t>##var</t>
   </si>
@@ -804,20 +797,28 @@
   </si>
   <si>
     <t>对一个区域进行施法,使其攻击速度和移动速度降低至50%,持续3秒。</t>
+  </si>
+  <si>
+    <t>解锁星级</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>UnlockStar</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.00_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="178" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -845,150 +846,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -1011,8 +868,21 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="36">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1037,194 +907,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="12">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1275,256 +959,14 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1540,13 +982,13 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1555,66 +997,28 @@
     <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 6" xfId="49"/>
+    <cellStyle name="常规 6" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1872,27 +1276,27 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:Z31"/>
-  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AA31"/>
+  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.875" style="3" customWidth="1"/>
     <col min="2" max="8" width="17.875" style="3"/>
     <col min="9" max="9" width="21.875" style="3" customWidth="1"/>
-    <col min="10" max="12" width="17.875" style="3"/>
-    <col min="13" max="13" width="19.125" style="3" customWidth="1"/>
-    <col min="14" max="23" width="17.875" style="3"/>
-    <col min="24" max="25" width="20.375" style="3" customWidth="1"/>
-    <col min="26" max="26" width="100.625" style="3" customWidth="1"/>
-    <col min="27" max="16384" width="17.875" style="3"/>
+    <col min="10" max="13" width="17.875" style="3"/>
+    <col min="14" max="14" width="19.125" style="3" customWidth="1"/>
+    <col min="15" max="24" width="17.875" style="3"/>
+    <col min="25" max="26" width="20.375" style="3" customWidth="1"/>
+    <col min="27" max="27" width="100.625" style="3" customWidth="1"/>
+    <col min="28" max="16384" width="17.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:26">
+    <row r="1" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1920,59 +1324,62 @@
       <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="R1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="S1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="T1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="U1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="V1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="W1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="X1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="Y1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="Z1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="5" t="s">
+      <c r="AA1" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:26">
+    <row r="2" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -2000,59 +1407,62 @@
       <c r="I2" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="5" t="s">
-        <v>27</v>
+      <c r="J2" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="K2" s="5" t="s">
         <v>27</v>
       </c>
       <c r="L2" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="N2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="O2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="P2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="Q2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="R2" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>28</v>
       </c>
       <c r="S2" s="5" t="s">
         <v>28</v>
       </c>
       <c r="T2" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="U2" s="5" t="s">
         <v>27</v>
       </c>
       <c r="V2" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="W2" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="W2" s="5" t="s">
+      <c r="X2" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="X2" s="5" t="s">
-        <v>31</v>
       </c>
       <c r="Y2" s="5" t="s">
         <v>31</v>
       </c>
       <c r="Z2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA2" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:26">
+    <row r="3" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>32</v>
       </c>
@@ -2080,59 +1490,62 @@
       <c r="I3" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="K3" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="L3" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="M3" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="N3" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="O3" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="P3" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="Q3" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="Q3" s="6" t="s">
+      <c r="R3" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="R3" s="6" t="s">
+      <c r="S3" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="S3" s="6" t="s">
+      <c r="T3" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="T3" s="6" t="s">
+      <c r="U3" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="U3" s="6" t="s">
+      <c r="V3" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="V3" s="6" t="s">
+      <c r="W3" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="W3" s="6" t="s">
+      <c r="X3" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="X3" s="6" t="s">
+      <c r="Y3" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="Y3" s="6" t="s">
+      <c r="Z3" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="Z3" s="6" t="s">
+      <c r="AA3" s="6" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="2:25">
+    <row r="4" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="3">
         <v>10000001</v>
       </c>
@@ -2156,10 +1569,10 @@
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="3">
         <v>0</v>
@@ -2168,43 +1581,46 @@
         <v>0</v>
       </c>
       <c r="N4" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" s="3">
+        <v>1</v>
+      </c>
+      <c r="P4" s="3">
         <v>3000</v>
       </c>
-      <c r="P4" s="3">
-        <v>1</v>
-      </c>
       <c r="Q4" s="3">
-        <v>0</v>
-      </c>
-      <c r="R4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="R4" s="3">
+        <v>0</v>
+      </c>
+      <c r="S4" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="S4" s="3" t="s">
+      <c r="T4" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="T4" s="3">
-        <v>2</v>
-      </c>
       <c r="U4" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V4" s="3">
         <v>0</v>
       </c>
       <c r="W4" s="3">
+        <v>0</v>
+      </c>
+      <c r="X4" s="3">
         <v>10000001</v>
       </c>
-      <c r="X4" s="3">
-        <v>0</v>
-      </c>
       <c r="Y4" s="3">
         <v>0</v>
       </c>
+      <c r="Z4" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="2:25">
+    <row r="5" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="3">
         <v>10000002</v>
       </c>
@@ -2228,10 +1644,10 @@
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="3">
         <v>0</v>
@@ -2240,43 +1656,46 @@
         <v>0</v>
       </c>
       <c r="N5" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" s="3">
+        <v>1</v>
+      </c>
+      <c r="P5" s="3">
         <v>3000</v>
       </c>
-      <c r="P5" s="3">
-        <v>1</v>
-      </c>
       <c r="Q5" s="3">
-        <v>0</v>
-      </c>
-      <c r="R5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="R5" s="3">
+        <v>0</v>
+      </c>
+      <c r="S5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="S5" s="3" t="s">
+      <c r="T5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="T5" s="3">
-        <v>2</v>
-      </c>
       <c r="U5" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V5" s="3">
         <v>0</v>
       </c>
       <c r="W5" s="3">
+        <v>0</v>
+      </c>
+      <c r="X5" s="3">
         <v>10000002</v>
       </c>
-      <c r="X5" s="3">
-        <v>0</v>
-      </c>
       <c r="Y5" s="3">
         <v>0</v>
       </c>
+      <c r="Z5" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="2:25">
+    <row r="6" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="3">
         <v>10000003</v>
       </c>
@@ -2300,10 +1719,10 @@
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="3">
         <v>0</v>
@@ -2312,43 +1731,46 @@
         <v>0</v>
       </c>
       <c r="N6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" s="3">
+        <v>1</v>
+      </c>
+      <c r="P6" s="3">
         <v>3000</v>
       </c>
-      <c r="P6" s="3">
-        <v>1</v>
-      </c>
       <c r="Q6" s="3">
-        <v>0</v>
-      </c>
-      <c r="R6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="R6" s="3">
+        <v>0</v>
+      </c>
+      <c r="S6" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="S6" s="3" t="s">
+      <c r="T6" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="T6" s="3">
-        <v>2</v>
-      </c>
       <c r="U6" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V6" s="3">
         <v>0</v>
       </c>
       <c r="W6" s="3">
+        <v>0</v>
+      </c>
+      <c r="X6" s="3">
         <v>10000003</v>
       </c>
-      <c r="X6" s="3">
-        <v>0</v>
-      </c>
       <c r="Y6" s="3">
         <v>0</v>
       </c>
+      <c r="Z6" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="2:26">
+    <row r="7" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="3">
         <v>10000004</v>
       </c>
@@ -2372,10 +1794,10 @@
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="3">
         <v>0</v>
@@ -2384,46 +1806,49 @@
         <v>0</v>
       </c>
       <c r="N7" s="3">
+        <v>0</v>
+      </c>
+      <c r="O7" s="3">
         <v>11</v>
       </c>
-      <c r="O7" s="3">
+      <c r="P7" s="3">
         <v>5000</v>
       </c>
-      <c r="P7" s="3">
-        <v>1</v>
-      </c>
       <c r="Q7" s="3">
+        <v>1</v>
+      </c>
+      <c r="R7" s="3">
         <v>100</v>
       </c>
-      <c r="R7" s="3" t="s">
+      <c r="S7" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="S7" s="3" t="s">
+      <c r="T7" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="T7" s="3">
-        <v>1</v>
-      </c>
       <c r="U7" s="3">
         <v>1</v>
       </c>
       <c r="V7" s="3">
+        <v>1</v>
+      </c>
+      <c r="W7" s="3">
         <v>4</v>
       </c>
-      <c r="W7" s="3">
+      <c r="X7" s="3">
         <v>10000004</v>
       </c>
-      <c r="X7" s="3">
-        <v>0</v>
-      </c>
       <c r="Y7" s="3">
         <v>0</v>
       </c>
-      <c r="Z7" s="3" t="s">
+      <c r="Z7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="2:26">
+    <row r="8" spans="1:27" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="2">
         <v>20000001</v>
       </c>
@@ -2442,11 +1867,11 @@
       <c r="G8" s="2">
         <v>0</v>
       </c>
-      <c r="J8" s="2">
-        <v>1</v>
+      <c r="J8" s="3">
+        <v>0</v>
       </c>
       <c r="K8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="2">
         <v>0</v>
@@ -2455,46 +1880,49 @@
         <v>0</v>
       </c>
       <c r="N8" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" s="2">
+        <v>1</v>
+      </c>
+      <c r="P8" s="2">
         <v>3000</v>
       </c>
-      <c r="P8" s="2">
+      <c r="Q8" s="2">
         <v>3.5</v>
       </c>
-      <c r="Q8" s="2">
-        <v>0</v>
-      </c>
-      <c r="R8" s="2" t="s">
+      <c r="R8" s="2">
+        <v>0</v>
+      </c>
+      <c r="S8" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="S8" s="2" t="s">
+      <c r="T8" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="T8" s="2">
-        <v>2</v>
-      </c>
       <c r="U8" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V8" s="2">
         <v>0</v>
       </c>
       <c r="W8" s="2">
+        <v>0</v>
+      </c>
+      <c r="X8" s="2">
         <v>10000001</v>
       </c>
-      <c r="X8" s="2">
-        <v>0</v>
-      </c>
       <c r="Y8" s="2">
         <v>0</v>
       </c>
-      <c r="Z8" s="2" t="s">
+      <c r="Z8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="2:26">
+    <row r="9" spans="1:27" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="2">
         <v>20000002</v>
       </c>
@@ -2513,11 +1941,11 @@
       <c r="G9" s="2">
         <v>0</v>
       </c>
-      <c r="J9" s="2">
-        <v>1</v>
+      <c r="J9" s="3">
+        <v>0</v>
       </c>
       <c r="K9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="2">
         <v>0</v>
@@ -2526,46 +1954,49 @@
         <v>0</v>
       </c>
       <c r="N9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" s="2">
+        <v>1</v>
+      </c>
+      <c r="P9" s="2">
         <v>5000</v>
       </c>
-      <c r="P9" s="2">
-        <v>0</v>
-      </c>
       <c r="Q9" s="2">
         <v>0</v>
       </c>
-      <c r="R9" s="2" t="s">
+      <c r="R9" s="2">
+        <v>0</v>
+      </c>
+      <c r="S9" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="S9" s="2" t="s">
+      <c r="T9" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="T9" s="2">
+      <c r="U9" s="2">
         <v>3</v>
       </c>
-      <c r="U9" s="2">
-        <v>0</v>
-      </c>
       <c r="V9" s="2">
         <v>0</v>
       </c>
       <c r="W9" s="2">
+        <v>0</v>
+      </c>
+      <c r="X9" s="2">
         <v>10000001</v>
       </c>
-      <c r="X9" s="7" t="s">
+      <c r="Y9" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="Y9" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="2" t="s">
+      <c r="Z9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="2:26">
+    <row r="10" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="3">
         <v>20000003</v>
       </c>
@@ -2585,10 +2016,10 @@
         <v>0</v>
       </c>
       <c r="J10" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="3">
         <v>0</v>
@@ -2597,46 +2028,49 @@
         <v>0</v>
       </c>
       <c r="N10" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" s="3">
+        <v>1</v>
+      </c>
+      <c r="P10" s="3">
         <v>2000</v>
       </c>
-      <c r="P10" s="3">
-        <v>1</v>
-      </c>
       <c r="Q10" s="3">
-        <v>0</v>
-      </c>
-      <c r="R10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="R10" s="3">
+        <v>0</v>
+      </c>
+      <c r="S10" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="S10" s="3" t="s">
+      <c r="T10" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>4</v>
       </c>
-      <c r="U10" s="3">
-        <v>0</v>
-      </c>
       <c r="V10" s="3">
         <v>0</v>
       </c>
       <c r="W10" s="3">
+        <v>0</v>
+      </c>
+      <c r="X10" s="3">
         <v>10000001</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>10000002</v>
       </c>
-      <c r="Y10" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="3" t="s">
+      <c r="Z10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="3" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="2:26">
+    <row r="11" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="3">
         <v>20000004</v>
       </c>
@@ -2656,10 +2090,10 @@
         <v>0</v>
       </c>
       <c r="J11" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="3">
         <v>0</v>
@@ -2668,46 +2102,49 @@
         <v>0</v>
       </c>
       <c r="N11" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" s="3">
+        <v>1</v>
+      </c>
+      <c r="P11" s="3">
         <v>3000</v>
       </c>
-      <c r="P11" s="3">
+      <c r="Q11" s="3">
         <v>1.5</v>
       </c>
-      <c r="Q11" s="3">
-        <v>0</v>
-      </c>
-      <c r="R11" s="3" t="s">
+      <c r="R11" s="3">
+        <v>0</v>
+      </c>
+      <c r="S11" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="S11" s="3" t="s">
+      <c r="T11" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="T11" s="3">
-        <v>1</v>
-      </c>
       <c r="U11" s="3">
         <v>1</v>
       </c>
       <c r="V11" s="3">
+        <v>1</v>
+      </c>
+      <c r="W11" s="3">
         <v>6</v>
       </c>
-      <c r="W11" s="3">
+      <c r="X11" s="3">
         <v>10000001</v>
       </c>
-      <c r="X11" s="3">
-        <v>0</v>
-      </c>
       <c r="Y11" s="3">
         <v>0</v>
       </c>
-      <c r="Z11" s="3" t="s">
+      <c r="Z11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="3" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="2:26">
+    <row r="12" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="3">
         <v>20000005</v>
       </c>
@@ -2727,10 +2164,10 @@
         <v>0</v>
       </c>
       <c r="J12" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="3">
         <v>0</v>
@@ -2739,46 +2176,49 @@
         <v>0</v>
       </c>
       <c r="N12" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" s="3">
+        <v>1</v>
+      </c>
+      <c r="P12" s="3">
         <v>5000</v>
       </c>
-      <c r="P12" s="3">
-        <v>0</v>
-      </c>
       <c r="Q12" s="3">
         <v>0</v>
       </c>
-      <c r="R12" s="3" t="s">
+      <c r="R12" s="3">
+        <v>0</v>
+      </c>
+      <c r="S12" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="S12" s="3" t="s">
+      <c r="T12" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="T12" s="3">
-        <v>0</v>
-      </c>
       <c r="U12" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" s="3">
+        <v>1</v>
+      </c>
+      <c r="W12" s="3">
         <v>3</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>10000001</v>
       </c>
-      <c r="X12" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="10" t="s">
+      <c r="Y12" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="Z12" s="3" t="s">
+      <c r="AA12" s="3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="2:26">
+    <row r="13" spans="1:27" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="2">
         <v>20000006</v>
       </c>
@@ -2797,11 +2237,11 @@
       <c r="G13" s="2">
         <v>0</v>
       </c>
-      <c r="J13" s="2">
-        <v>1</v>
+      <c r="J13" s="3">
+        <v>0</v>
       </c>
       <c r="K13" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="2">
         <v>0</v>
@@ -2810,26 +2250,26 @@
         <v>0</v>
       </c>
       <c r="N13" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" s="2">
+        <v>1</v>
+      </c>
+      <c r="P13" s="2">
         <v>5000</v>
       </c>
-      <c r="P13" s="2">
-        <v>0</v>
-      </c>
       <c r="Q13" s="2">
         <v>0</v>
       </c>
-      <c r="R13" s="2" t="s">
+      <c r="R13" s="2">
+        <v>0</v>
+      </c>
+      <c r="S13" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="S13" s="2" t="s">
+      <c r="T13" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="T13" s="2">
-        <v>0</v>
-      </c>
       <c r="U13" s="2">
         <v>0</v>
       </c>
@@ -2837,19 +2277,22 @@
         <v>0</v>
       </c>
       <c r="W13" s="2">
+        <v>0</v>
+      </c>
+      <c r="X13" s="2">
         <v>10000001</v>
       </c>
-      <c r="X13" s="2">
-        <v>0</v>
-      </c>
       <c r="Y13" s="2">
         <v>0</v>
       </c>
-      <c r="Z13" s="2" t="s">
+      <c r="Z13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="2" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="2:26">
+    <row r="14" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="3">
         <v>30000001</v>
       </c>
@@ -2869,58 +2312,61 @@
         <v>0</v>
       </c>
       <c r="J14" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K14" s="3">
         <v>2</v>
       </c>
       <c r="L14" s="3">
+        <v>2</v>
+      </c>
+      <c r="M14" s="3">
         <v>0.2</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>9</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>3000</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3" t="s">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="S14" s="3" t="s">
+      <c r="T14" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W14" s="3">
+        <v>2</v>
+      </c>
+      <c r="X14" s="3">
         <v>10000001</v>
       </c>
-      <c r="X14" s="8">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="10" t="s">
+      <c r="Y14" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="Z14" s="3" t="s">
+      <c r="AA14" s="3" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="2:26">
+    <row r="15" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="3">
         <v>30000002</v>
       </c>
@@ -2940,58 +2386,61 @@
         <v>0</v>
       </c>
       <c r="J15" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L15" s="3">
+        <v>1</v>
+      </c>
+      <c r="M15" s="3">
         <v>0.17</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3">
         <v>3</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1.5</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3" t="s">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="S15" s="3" t="s">
+      <c r="T15" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="T15" s="3">
-        <v>1</v>
-      </c>
       <c r="U15" s="3">
         <v>1</v>
       </c>
       <c r="V15" s="3">
+        <v>1</v>
+      </c>
+      <c r="W15" s="3">
         <v>3</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>10000001</v>
       </c>
-      <c r="X15" s="3">
-        <v>0</v>
-      </c>
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-      <c r="Z15" s="3" t="s">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="3" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="2:26">
+    <row r="16" spans="1:27" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="2">
         <v>30000003</v>
       </c>
@@ -3010,59 +2459,62 @@
       <c r="G16" s="2">
         <v>0</v>
       </c>
-      <c r="J16" s="2">
-        <v>2</v>
+      <c r="J16" s="3">
+        <v>5</v>
       </c>
       <c r="K16" s="2">
         <v>2</v>
       </c>
       <c r="L16" s="2">
+        <v>2</v>
+      </c>
+      <c r="M16" s="2">
         <v>0.2</v>
       </c>
-      <c r="M16" s="2">
-        <v>0</v>
-      </c>
       <c r="N16" s="2">
+        <v>0</v>
+      </c>
+      <c r="O16" s="2">
         <v>10</v>
       </c>
-      <c r="O16" s="2">
+      <c r="P16" s="2">
         <v>4000</v>
       </c>
-      <c r="P16" s="2">
+      <c r="Q16" s="2">
         <v>0.4</v>
       </c>
-      <c r="Q16" s="2">
-        <v>0</v>
-      </c>
-      <c r="R16" s="2" t="s">
+      <c r="R16" s="2">
+        <v>0</v>
+      </c>
+      <c r="S16" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="S16" s="2" t="s">
+      <c r="T16" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="T16" s="2">
-        <v>2</v>
-      </c>
       <c r="U16" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V16" s="2">
         <v>0</v>
       </c>
       <c r="W16" s="2">
+        <v>0</v>
+      </c>
+      <c r="X16" s="2">
         <v>10000001</v>
       </c>
-      <c r="X16" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="7" t="s">
+      <c r="Y16" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="Z16" s="2" t="s">
+      <c r="AA16" s="2" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="2:26">
+    <row r="17" spans="2:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="3">
         <v>30000004</v>
       </c>
@@ -3082,58 +2534,61 @@
         <v>0</v>
       </c>
       <c r="J17" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K17" s="3">
         <v>2</v>
       </c>
       <c r="L17" s="3">
+        <v>2</v>
+      </c>
+      <c r="M17" s="3">
         <v>0.2</v>
       </c>
-      <c r="M17" s="3">
-        <v>0</v>
-      </c>
       <c r="N17" s="3">
+        <v>0</v>
+      </c>
+      <c r="O17" s="3">
         <v>10</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2000</v>
       </c>
-      <c r="P17" s="3">
-        <v>2</v>
-      </c>
       <c r="Q17" s="3">
-        <v>0</v>
-      </c>
-      <c r="R17" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="R17" s="3">
+        <v>0</v>
+      </c>
+      <c r="S17" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="S17" s="3" t="s">
+      <c r="T17" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="T17" s="3">
-        <v>1</v>
-      </c>
       <c r="U17" s="3">
         <v>1</v>
       </c>
       <c r="V17" s="3">
+        <v>1</v>
+      </c>
+      <c r="W17" s="3">
         <v>3</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>10000001</v>
       </c>
-      <c r="X17" s="3">
-        <v>0</v>
-      </c>
       <c r="Y17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="3">
         <v>10000008</v>
       </c>
-      <c r="Z17" s="3" t="s">
+      <c r="AA17" s="3" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="18" s="2" customFormat="1" customHeight="1" spans="2:26">
+    <row r="18" spans="2:27" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="2">
         <v>30000005</v>
       </c>
@@ -3153,58 +2608,61 @@
         <v>0</v>
       </c>
       <c r="J18" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K18" s="2">
         <v>2</v>
       </c>
       <c r="L18" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M18" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" s="2">
         <v>0</v>
       </c>
       <c r="O18" s="2">
+        <v>0</v>
+      </c>
+      <c r="P18" s="2">
         <v>3000</v>
       </c>
-      <c r="P18" s="2">
+      <c r="Q18" s="2">
         <v>0.5</v>
       </c>
-      <c r="Q18" s="2">
-        <v>0</v>
-      </c>
-      <c r="R18" s="3" t="s">
+      <c r="R18" s="2">
+        <v>0</v>
+      </c>
+      <c r="S18" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="S18" s="2" t="s">
+      <c r="T18" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="T18" s="2">
-        <v>1</v>
-      </c>
       <c r="U18" s="2">
         <v>1</v>
       </c>
       <c r="V18" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W18" s="2">
+        <v>2</v>
+      </c>
+      <c r="X18" s="2">
         <v>10000001</v>
       </c>
-      <c r="X18" s="2">
-        <v>0</v>
-      </c>
       <c r="Y18" s="2">
         <v>0</v>
       </c>
-      <c r="Z18" s="2" t="s">
+      <c r="Z18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="2:26">
+    <row r="19" spans="2:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="3">
         <v>30000006</v>
       </c>
@@ -3223,59 +2681,62 @@
       <c r="G19" s="3">
         <v>0</v>
       </c>
-      <c r="J19" s="3">
-        <v>2</v>
+      <c r="J19" s="2">
+        <v>5</v>
       </c>
       <c r="K19" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L19" s="3">
+        <v>1</v>
+      </c>
+      <c r="M19" s="3">
         <v>0.2</v>
       </c>
-      <c r="M19" s="3">
-        <v>0</v>
-      </c>
       <c r="N19" s="3">
+        <v>0</v>
+      </c>
+      <c r="O19" s="3">
         <v>10</v>
       </c>
-      <c r="O19" s="3">
+      <c r="P19" s="3">
         <v>5000</v>
       </c>
-      <c r="P19" s="3">
-        <v>0</v>
-      </c>
       <c r="Q19" s="3">
         <v>0</v>
       </c>
-      <c r="R19" s="3" t="s">
+      <c r="R19" s="3">
+        <v>0</v>
+      </c>
+      <c r="S19" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="S19" s="3" t="s">
+      <c r="T19" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="T19" s="3">
+      <c r="U19" s="3">
         <v>3</v>
       </c>
-      <c r="U19" s="3">
-        <v>0</v>
-      </c>
       <c r="V19" s="3">
         <v>0</v>
       </c>
       <c r="W19" s="3">
+        <v>0</v>
+      </c>
+      <c r="X19" s="3">
         <v>10000001</v>
       </c>
-      <c r="X19" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="10" t="s">
+      <c r="Y19" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="Z19" s="3" t="s">
+      <c r="AA19" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="2:26">
+    <row r="20" spans="2:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="3">
         <v>30000007</v>
       </c>
@@ -3294,59 +2755,62 @@
       <c r="G20" s="3">
         <v>0</v>
       </c>
-      <c r="J20" s="3">
-        <v>2</v>
+      <c r="J20" s="2">
+        <v>1</v>
       </c>
       <c r="K20" s="3">
         <v>2</v>
       </c>
       <c r="L20" s="3">
+        <v>2</v>
+      </c>
+      <c r="M20" s="3">
         <v>0.2</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>10</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>3000</v>
       </c>
-      <c r="P20" s="3">
-        <v>1</v>
-      </c>
       <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="S20" s="3" t="s">
+      <c r="T20" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="3">
+        <v>1</v>
+      </c>
+      <c r="W20" s="3">
         <v>3</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>10000001</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
         <v>0</v>
       </c>
-      <c r="Z20" s="3" t="s">
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="2:26">
+    <row r="21" spans="2:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="3">
         <v>30000008</v>
       </c>
@@ -3365,59 +2829,62 @@
       <c r="G21" s="3">
         <v>0</v>
       </c>
-      <c r="J21" s="3">
-        <v>2</v>
+      <c r="J21" s="2">
+        <v>3</v>
       </c>
       <c r="K21" s="3">
+        <v>2</v>
+      </c>
+      <c r="L21" s="3">
         <v>3</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>0.8</v>
       </c>
-      <c r="M21" s="3">
-        <v>0</v>
-      </c>
       <c r="N21" s="3">
+        <v>0</v>
+      </c>
+      <c r="O21" s="3">
         <v>10</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>5000</v>
       </c>
-      <c r="P21" s="3">
-        <v>0</v>
-      </c>
       <c r="Q21" s="3">
         <v>0</v>
       </c>
-      <c r="R21" s="3" t="s">
+      <c r="R21" s="3">
+        <v>0</v>
+      </c>
+      <c r="S21" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="S21" s="3" t="s">
+      <c r="T21" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="T21" s="3">
-        <v>1</v>
-      </c>
       <c r="U21" s="3">
         <v>1</v>
       </c>
       <c r="V21" s="3">
+        <v>1</v>
+      </c>
+      <c r="W21" s="3">
         <v>4</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>10000001</v>
       </c>
-      <c r="X21" s="3">
-        <v>0</v>
-      </c>
       <c r="Y21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="3">
         <v>10000014</v>
       </c>
-      <c r="Z21" s="3" t="s">
+      <c r="AA21" s="3" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="2:26">
+    <row r="22" spans="2:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="3">
         <v>30000009</v>
       </c>
@@ -3436,59 +2903,62 @@
       <c r="G22" s="3">
         <v>0</v>
       </c>
-      <c r="J22" s="3">
-        <v>2</v>
+      <c r="J22" s="2">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
+        <v>2</v>
+      </c>
+      <c r="L22" s="3">
         <v>4</v>
       </c>
-      <c r="L22" s="3">
-        <v>1</v>
-      </c>
       <c r="M22" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
       <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
         <v>3600000</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3" t="s">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="S22" s="3" t="s">
+      <c r="T22" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>3</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
-      </c>
       <c r="V22" s="3">
         <v>0</v>
       </c>
       <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
         <v>10000001</v>
       </c>
-      <c r="X22" s="10" t="s">
+      <c r="Y22" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="Y22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="3" t="s">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="2:26">
+    <row r="23" spans="2:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="3">
         <v>30000010</v>
       </c>
@@ -3507,59 +2977,62 @@
       <c r="G23" s="3">
         <v>0</v>
       </c>
-      <c r="J23" s="3">
-        <v>2</v>
+      <c r="J23" s="2">
+        <v>1</v>
       </c>
       <c r="K23" s="3">
         <v>2</v>
       </c>
       <c r="L23" s="3">
+        <v>2</v>
+      </c>
+      <c r="M23" s="3">
         <v>0.2</v>
       </c>
-      <c r="M23" s="3">
-        <v>0</v>
-      </c>
       <c r="N23" s="3">
+        <v>0</v>
+      </c>
+      <c r="O23" s="3">
         <v>10</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>4000</v>
       </c>
-      <c r="P23" s="3">
-        <v>2</v>
-      </c>
       <c r="Q23" s="3">
-        <v>0</v>
-      </c>
-      <c r="R23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="R23" s="3">
+        <v>0</v>
+      </c>
+      <c r="S23" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="S23" s="3" t="s">
+      <c r="T23" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="T23" s="3">
-        <v>1</v>
-      </c>
       <c r="U23" s="3">
         <v>1</v>
       </c>
       <c r="V23" s="3">
+        <v>1</v>
+      </c>
+      <c r="W23" s="3">
         <v>3</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>10000001</v>
       </c>
-      <c r="X23" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="10" t="s">
+      <c r="Y23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="Z23" s="3" t="s">
+      <c r="AA23" s="3" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="2:26">
+    <row r="24" spans="2:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B24" s="3">
         <v>30000011</v>
       </c>
@@ -3578,59 +3051,62 @@
       <c r="G24" s="3">
         <v>0</v>
       </c>
-      <c r="J24" s="3">
-        <v>2</v>
+      <c r="J24" s="2">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>2</v>
       </c>
       <c r="L24" s="3">
+        <v>2</v>
+      </c>
+      <c r="M24" s="3">
         <v>0.2</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>10</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>0.5</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
-      <c r="R24" s="3" t="s">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="S24" s="3" t="s">
+      <c r="T24" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="T24" s="3">
-        <v>2</v>
-      </c>
       <c r="U24" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>10000001</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="10" t="s">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="Z24" s="3" t="s">
+      <c r="AA24" s="3" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="2:26">
+    <row r="25" spans="2:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="3">
         <v>30000012</v>
       </c>
@@ -3650,58 +3126,61 @@
         <v>0</v>
       </c>
       <c r="J25" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K25" s="3">
+        <v>2</v>
+      </c>
+      <c r="L25" s="3">
         <v>4</v>
       </c>
-      <c r="L25" s="3">
-        <v>1</v>
-      </c>
       <c r="M25" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" s="3">
         <v>0</v>
       </c>
       <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
         <v>3600000</v>
       </c>
-      <c r="P25" s="3">
-        <v>0</v>
-      </c>
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3" t="s">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="S25" s="3" t="s">
+      <c r="T25" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="T25" s="3">
+      <c r="U25" s="3">
         <v>5</v>
       </c>
-      <c r="U25" s="3">
-        <v>0</v>
-      </c>
       <c r="V25" s="3">
         <v>0</v>
       </c>
       <c r="W25" s="3">
+        <v>0</v>
+      </c>
+      <c r="X25" s="3">
         <v>10000001</v>
       </c>
-      <c r="X25" s="3">
-        <v>0</v>
-      </c>
       <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="3">
         <v>10000021</v>
       </c>
-      <c r="Z25" s="3" t="s">
+      <c r="AA25" s="3" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="2:26">
+    <row r="26" spans="2:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="3">
         <v>30000013</v>
       </c>
@@ -3721,58 +3200,61 @@
         <v>0</v>
       </c>
       <c r="J26" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K26" s="3">
+        <v>2</v>
+      </c>
+      <c r="L26" s="3">
         <v>5</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>0.6</v>
       </c>
-      <c r="M26" s="3">
-        <v>0</v>
-      </c>
       <c r="N26" s="3">
+        <v>0</v>
+      </c>
+      <c r="O26" s="3">
         <v>10</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3000</v>
       </c>
-      <c r="P26" s="3">
-        <v>1</v>
-      </c>
       <c r="Q26" s="3">
-        <v>0</v>
-      </c>
-      <c r="R26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="R26" s="3">
+        <v>0</v>
+      </c>
+      <c r="S26" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="S26" s="3" t="s">
+      <c r="T26" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="T26" s="3">
-        <v>1</v>
-      </c>
       <c r="U26" s="3">
         <v>1</v>
       </c>
       <c r="V26" s="3">
+        <v>1</v>
+      </c>
+      <c r="W26" s="3">
         <v>3</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>10000001</v>
       </c>
-      <c r="X26" s="3">
-        <v>0</v>
-      </c>
       <c r="Y26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="3">
         <v>10000022</v>
       </c>
-      <c r="Z26" s="3" t="s">
+      <c r="AA26" s="3" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="27" customHeight="1" spans="2:26">
+    <row r="27" spans="2:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B27" s="3">
         <v>30000014</v>
       </c>
@@ -3792,58 +3274,61 @@
         <v>0</v>
       </c>
       <c r="J27" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27" s="3">
+        <v>2</v>
+      </c>
+      <c r="L27" s="3">
         <v>5</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>0.3</v>
       </c>
-      <c r="M27" s="3">
-        <v>0</v>
-      </c>
       <c r="N27" s="3">
+        <v>0</v>
+      </c>
+      <c r="O27" s="3">
         <v>10</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3000</v>
       </c>
-      <c r="P27" s="3">
-        <v>0</v>
-      </c>
       <c r="Q27" s="3">
         <v>0</v>
       </c>
-      <c r="R27" s="3" t="s">
+      <c r="R27" s="3">
+        <v>0</v>
+      </c>
+      <c r="S27" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="S27" s="3" t="s">
+      <c r="T27" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="T27" s="3">
-        <v>2</v>
-      </c>
       <c r="U27" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V27" s="3">
         <v>0</v>
       </c>
       <c r="W27" s="3">
+        <v>0</v>
+      </c>
+      <c r="X27" s="3">
         <v>10000001</v>
       </c>
-      <c r="X27" s="3">
-        <v>0</v>
-      </c>
       <c r="Y27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="3">
         <v>10000023</v>
       </c>
-      <c r="Z27" s="3" t="s">
+      <c r="AA27" s="3" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="28" customHeight="1" spans="2:26">
+    <row r="28" spans="2:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28" s="3">
         <v>30000015</v>
       </c>
@@ -3863,58 +3348,61 @@
         <v>0</v>
       </c>
       <c r="J28" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K28" s="3">
+        <v>2</v>
+      </c>
+      <c r="L28" s="3">
         <v>4</v>
       </c>
-      <c r="L28" s="3">
-        <v>1</v>
-      </c>
       <c r="M28" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N28" s="3">
         <v>0</v>
       </c>
       <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
         <v>3600000</v>
       </c>
-      <c r="P28" s="3">
-        <v>0</v>
-      </c>
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3" t="s">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="S28" s="3" t="s">
+      <c r="T28" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="T28" s="3">
-        <v>0</v>
-      </c>
       <c r="U28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="3">
+        <v>1</v>
+      </c>
+      <c r="W28" s="3">
         <v>4</v>
       </c>
-      <c r="W28" s="3">
+      <c r="X28" s="3">
         <v>10000001</v>
       </c>
-      <c r="X28" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y28" s="10" t="s">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="Z28" s="3" t="s">
+      <c r="AA28" s="3" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="2:26">
+    <row r="29" spans="2:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="3">
         <v>30000016</v>
       </c>
@@ -3934,52 +3422,55 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K29" s="3">
         <v>2</v>
       </c>
       <c r="L29" s="3">
+        <v>2</v>
+      </c>
+      <c r="M29" s="3">
         <v>0.2</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>10</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>5000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>0.1</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3" t="s">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="S29" s="3" t="s">
+      <c r="T29" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>6</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
       <c r="V29" s="3">
         <v>0</v>
       </c>
       <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>10000001</v>
       </c>
-      <c r="Z29" s="3" t="s">
+      <c r="AA29" s="3" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="2:26">
+    <row r="30" spans="2:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="3">
         <v>30000017</v>
       </c>
@@ -3998,17 +3489,20 @@
       <c r="G30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="3">
+      <c r="J30" s="3">
+        <v>3</v>
+      </c>
+      <c r="O30" s="3">
         <v>10</v>
       </c>
-      <c r="O30" s="3">
+      <c r="P30" s="3">
         <v>5000</v>
       </c>
-      <c r="Z30" s="3" t="s">
+      <c r="AA30" s="3" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="31" customHeight="1" spans="2:26">
+    <row r="31" spans="2:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B31" s="3">
         <v>30000018</v>
       </c>
@@ -4028,60 +3522,63 @@
         <v>0</v>
       </c>
       <c r="J31" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K31" s="3">
         <v>2</v>
       </c>
       <c r="L31" s="3">
+        <v>2</v>
+      </c>
+      <c r="M31" s="3">
         <v>0.2</v>
       </c>
-      <c r="M31" s="3">
-        <v>0</v>
-      </c>
       <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3">
         <v>10</v>
       </c>
-      <c r="O31" s="3">
+      <c r="P31" s="3">
         <v>3000</v>
       </c>
-      <c r="P31" s="3">
-        <v>0</v>
-      </c>
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3" t="s">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="S31" s="3" t="s">
+      <c r="T31" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="T31" s="3">
-        <v>1</v>
-      </c>
       <c r="U31" s="3">
         <v>1</v>
       </c>
       <c r="V31" s="3">
+        <v>1</v>
+      </c>
+      <c r="W31" s="3">
         <v>4</v>
       </c>
-      <c r="W31" s="3">
+      <c r="X31" s="3">
         <v>10000001</v>
       </c>
-      <c r="X31" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y31" s="10" t="s">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="Z31" s="3" t="s">
+      <c r="AA31" s="3" t="s">
         <v>128</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -1,31 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\DreamGit\Unity\Assets\Config\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7DF608E-ADBD-44A3-B098-17DD40641906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="D3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -47,7 +54,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="E3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -70,7 +77,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="F3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -93,7 +100,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="G3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -115,7 +122,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="K3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -138,7 +145,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="L3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -168,7 +175,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+    <comment ref="M3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -190,7 +197,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
+    <comment ref="N3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -216,7 +223,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
+    <comment ref="Q3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -238,7 +245,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
+    <comment ref="R3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -260,7 +267,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
+    <comment ref="T3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -282,7 +289,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
+    <comment ref="U3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -310,7 +317,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000D000000}">
+    <comment ref="V3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -333,7 +340,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
+    <comment ref="W3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -359,7 +366,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000F000000}">
+    <comment ref="X3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -382,7 +389,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000010000000}">
+    <comment ref="Z3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -410,7 +417,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="131">
   <si>
     <t>##var</t>
   </si>
@@ -439,6 +446,9 @@
     <t>GameObjectParameter</t>
   </si>
   <si>
+    <t>UnlockStar</t>
+  </si>
+  <si>
     <t>SkillType</t>
   </si>
   <si>
@@ -532,6 +542,9 @@
     <t>脚本参数</t>
   </si>
   <si>
+    <t>解锁星级</t>
+  </si>
+  <si>
     <t>技能类型</t>
   </si>
   <si>
@@ -586,7 +599,7 @@
     <t>近战普通攻击1</t>
   </si>
   <si>
-    <t>Skill_SingleTarget</t>
+    <t>Skill_MeleeBasicAttack</t>
   </si>
   <si>
     <t>Test_1</t>
@@ -797,28 +810,20 @@
   </si>
   <si>
     <t>对一个区域进行施法,使其攻击速度和移动速度降低至50%,持续3秒。</t>
-  </si>
-  <si>
-    <t>解锁星级</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>UnlockStar</t>
-    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="0.00_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -846,10 +851,153 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -868,21 +1016,8 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="0"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -907,8 +1042,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -959,12 +1280,254 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -982,13 +1545,22 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -997,28 +1569,63 @@
     <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 6" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 6" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1276,17 +1883,18 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:AA31"/>
-  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.875" style="3" customWidth="1"/>
-    <col min="2" max="8" width="17.875" style="3"/>
+    <col min="2" max="7" width="17.875" style="3"/>
+    <col min="8" max="8" width="20.375" style="3" customWidth="1"/>
     <col min="9" max="9" width="21.875" style="3" customWidth="1"/>
     <col min="10" max="13" width="17.875" style="3"/>
     <col min="14" max="14" width="19.125" style="3" customWidth="1"/>
@@ -1296,7 +1904,7 @@
     <col min="28" max="16384" width="17.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1324,233 +1932,233 @@
       <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="12" t="s">
-        <v>131</v>
+      <c r="J1" s="7" t="s">
+        <v>9</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T1" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U1" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V1" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W1" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X1" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y1" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z1" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA1" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:27">
       <c r="A2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="G2" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="K2" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="L2" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="S2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="N2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="O2" s="5" t="s">
+      <c r="T2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="P2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q2" s="5" t="s">
+      <c r="U2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="W2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="X2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="R2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="S2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="T2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="V2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="W2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="X2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y2" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="Z2" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="AA2" s="5" t="s">
-        <v>28</v>
-      </c>
     </row>
-    <row r="3" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:27">
       <c r="A3" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="J3" s="11" t="s">
-        <v>129</v>
+        <v>40</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>41</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="T3" s="6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="U3" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="V3" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="W3" s="6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="X3" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Y3" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Z3" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AA3" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="2:26">
       <c r="B4" s="3">
         <v>10000001</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D4" s="3">
         <v>10000001</v>
@@ -1565,7 +2173,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3">
@@ -1596,10 +2204,10 @@
         <v>0</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="U4" s="3">
         <v>2</v>
@@ -1620,12 +2228,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="2:26">
       <c r="B5" s="3">
         <v>10000002</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D5" s="3">
         <v>10000002</v>
@@ -1640,7 +2248,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3">
@@ -1671,10 +2279,10 @@
         <v>0</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="U5" s="3">
         <v>2</v>
@@ -1695,12 +2303,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="2:26">
       <c r="B6" s="3">
         <v>10000003</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D6" s="3">
         <v>10000003</v>
@@ -1715,7 +2323,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3">
@@ -1746,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="S6" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="T6" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="T6" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="U6" s="3">
         <v>2</v>
@@ -1770,12 +2378,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="2:27">
       <c r="B7" s="3">
         <v>10000004</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D7" s="3">
         <v>10000004</v>
@@ -1790,7 +2398,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3">
@@ -1821,10 +2429,10 @@
         <v>100</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="U7" s="3">
         <v>1</v>
@@ -1845,15 +2453,15 @@
         <v>0</v>
       </c>
       <c r="AA7" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
-    <row r="8" spans="1:27" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="2:27">
       <c r="B8" s="2">
         <v>20000001</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D8" s="3">
         <v>10000005</v>
@@ -1895,10 +2503,10 @@
         <v>0</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="U8" s="2">
         <v>2</v>
@@ -1919,15 +2527,15 @@
         <v>0</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
-    <row r="9" spans="1:27" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="2:27">
       <c r="B9" s="2">
         <v>20000002</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D9" s="3">
         <v>10000006</v>
@@ -1969,10 +2577,10 @@
         <v>0</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="U9" s="2">
         <v>3</v>
@@ -1986,22 +2594,22 @@
       <c r="X9" s="2">
         <v>10000001</v>
       </c>
-      <c r="Y9" s="7" t="s">
-        <v>74</v>
+      <c r="Y9" s="9" t="s">
+        <v>76</v>
       </c>
       <c r="Z9" s="2">
         <v>0</v>
       </c>
       <c r="AA9" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" customHeight="1" spans="2:27">
       <c r="B10" s="3">
         <v>20000003</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D10" s="3">
         <v>10000007</v>
@@ -2043,10 +2651,10 @@
         <v>0</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="U10" s="3">
         <v>4</v>
@@ -2067,15 +2675,15 @@
         <v>0</v>
       </c>
       <c r="AA10" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" customHeight="1" spans="2:27">
       <c r="B11" s="3">
         <v>20000004</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D11" s="3">
         <v>10000001</v>
@@ -2117,10 +2725,10 @@
         <v>0</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="U11" s="3">
         <v>1</v>
@@ -2141,15 +2749,15 @@
         <v>0</v>
       </c>
       <c r="AA11" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" customHeight="1" spans="2:27">
       <c r="B12" s="3">
         <v>20000005</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D12" s="3">
         <v>10000002</v>
@@ -2191,10 +2799,10 @@
         <v>0</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="U12" s="3">
         <v>0</v>
@@ -2212,18 +2820,18 @@
         <v>0</v>
       </c>
       <c r="Z12" s="10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AA12" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:27" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="2:27">
       <c r="B13" s="2">
         <v>20000006</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D13" s="3">
         <v>10000003</v>
@@ -2265,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="U13" s="2">
         <v>0</v>
@@ -2289,15 +2897,15 @@
         <v>0</v>
       </c>
       <c r="AA13" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" customHeight="1" spans="2:27">
       <c r="B14" s="3">
         <v>30000001</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D14" s="3">
         <v>10000004</v>
@@ -2339,10 +2947,10 @@
         <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -2356,22 +2964,22 @@
       <c r="X14" s="3">
         <v>10000001</v>
       </c>
-      <c r="Y14" s="8">
+      <c r="Y14" s="11">
         <v>0</v>
       </c>
       <c r="Z14" s="10" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AA14" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" customHeight="1" spans="2:27">
       <c r="B15" s="3">
         <v>30000002</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D15" s="3">
         <v>10000005</v>
@@ -2413,10 +3021,10 @@
         <v>0</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="T15" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="U15" s="3">
         <v>1</v>
@@ -2437,15 +3045,15 @@
         <v>0</v>
       </c>
       <c r="AA15" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
-    <row r="16" spans="1:27" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="2:27">
       <c r="B16" s="2">
         <v>30000003</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D16" s="3">
         <v>10000006</v>
@@ -2487,10 +3095,10 @@
         <v>0</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="U16" s="2">
         <v>2</v>
@@ -2504,22 +3112,22 @@
       <c r="X16" s="2">
         <v>10000001</v>
       </c>
-      <c r="Y16" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="7" t="s">
-        <v>91</v>
+      <c r="Y16" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="9" t="s">
+        <v>93</v>
       </c>
       <c r="AA16" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
-    <row r="17" spans="2:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" customHeight="1" spans="2:27">
       <c r="B17" s="3">
         <v>30000004</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D17" s="3">
         <v>10000007</v>
@@ -2561,10 +3169,10 @@
         <v>0</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="T17" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="U17" s="3">
         <v>1</v>
@@ -2585,15 +3193,15 @@
         <v>10000008</v>
       </c>
       <c r="AA17" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
-    <row r="18" spans="2:27" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="2:27">
       <c r="B18" s="2">
         <v>30000005</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D18" s="2">
         <v>10000001</v>
@@ -2635,10 +3243,10 @@
         <v>0</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="U18" s="2">
         <v>1</v>
@@ -2659,15 +3267,15 @@
         <v>0</v>
       </c>
       <c r="AA18" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
-    <row r="19" spans="2:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" customHeight="1" spans="2:27">
       <c r="B19" s="3">
         <v>30000006</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D19" s="2">
         <v>10000002</v>
@@ -2709,10 +3317,10 @@
         <v>0</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="U19" s="3">
         <v>3</v>
@@ -2730,18 +3338,18 @@
         <v>0</v>
       </c>
       <c r="Z19" s="10" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AA19" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
-    <row r="20" spans="2:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" customHeight="1" spans="2:27">
       <c r="B20" s="3">
         <v>30000007</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D20" s="2">
         <v>10000003</v>
@@ -2783,10 +3391,10 @@
         <v>0</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="T20" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="U20" s="3">
         <v>0</v>
@@ -2807,15 +3415,15 @@
         <v>0</v>
       </c>
       <c r="AA20" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
-    <row r="21" spans="2:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" customHeight="1" spans="2:27">
       <c r="B21" s="3">
         <v>30000008</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D21" s="2">
         <v>10000004</v>
@@ -2857,10 +3465,10 @@
         <v>0</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="T21" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="U21" s="3">
         <v>1</v>
@@ -2881,15 +3489,15 @@
         <v>10000014</v>
       </c>
       <c r="AA21" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
-    <row r="22" spans="2:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" customHeight="1" spans="2:27">
       <c r="B22" s="3">
         <v>30000009</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D22" s="2">
         <v>10000005</v>
@@ -2931,10 +3539,10 @@
         <v>0</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="T22" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="U22" s="3">
         <v>3</v>
@@ -2949,21 +3557,21 @@
         <v>10000001</v>
       </c>
       <c r="Y22" s="10" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="Z22" s="3">
         <v>0</v>
       </c>
       <c r="AA22" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
-    <row r="23" spans="2:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" customHeight="1" spans="2:27">
       <c r="B23" s="3">
         <v>30000010</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D23" s="2">
         <v>10000006</v>
@@ -3005,10 +3613,10 @@
         <v>0</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="T23" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="U23" s="3">
         <v>1</v>
@@ -3026,18 +3634,18 @@
         <v>0</v>
       </c>
       <c r="Z23" s="10" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AA23" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
-    <row r="24" spans="2:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" customHeight="1" spans="2:27">
       <c r="B24" s="3">
         <v>30000011</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D24" s="2">
         <v>10000007</v>
@@ -3079,10 +3687,10 @@
         <v>0</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="T24" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="U24" s="3">
         <v>2</v>
@@ -3100,18 +3708,18 @@
         <v>0</v>
       </c>
       <c r="Z24" s="10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AA24" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
-    <row r="25" spans="2:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" customHeight="1" spans="2:27">
       <c r="B25" s="3">
         <v>30000012</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D25" s="3">
         <v>10000001</v>
@@ -3153,10 +3761,10 @@
         <v>0</v>
       </c>
       <c r="S25" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="T25" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="U25" s="3">
         <v>5</v>
@@ -3177,15 +3785,15 @@
         <v>10000021</v>
       </c>
       <c r="AA25" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
-    <row r="26" spans="2:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" customHeight="1" spans="2:27">
       <c r="B26" s="3">
         <v>30000013</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D26" s="3">
         <v>10000002</v>
@@ -3227,10 +3835,10 @@
         <v>0</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="T26" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="U26" s="3">
         <v>1</v>
@@ -3251,15 +3859,15 @@
         <v>10000022</v>
       </c>
       <c r="AA26" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
-    <row r="27" spans="2:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" customHeight="1" spans="2:27">
       <c r="B27" s="3">
         <v>30000014</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D27" s="3">
         <v>10000003</v>
@@ -3301,10 +3909,10 @@
         <v>0</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="T27" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="U27" s="3">
         <v>2</v>
@@ -3325,15 +3933,15 @@
         <v>10000023</v>
       </c>
       <c r="AA27" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
-    <row r="28" spans="2:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" customHeight="1" spans="2:27">
       <c r="B28" s="3">
         <v>30000015</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D28" s="3">
         <v>10000004</v>
@@ -3375,10 +3983,10 @@
         <v>0</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="T28" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="U28" s="3">
         <v>0</v>
@@ -3396,18 +4004,18 @@
         <v>0</v>
       </c>
       <c r="Z28" s="10" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="AA28" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
-    <row r="29" spans="2:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" customHeight="1" spans="2:27">
       <c r="B29" s="3">
         <v>30000016</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D29" s="3">
         <v>10000005</v>
@@ -3449,10 +4057,10 @@
         <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="T29" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="U29" s="3">
         <v>6</v>
@@ -3467,15 +4075,15 @@
         <v>10000001</v>
       </c>
       <c r="AA29" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
-    <row r="30" spans="2:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" customHeight="1" spans="2:27">
       <c r="B30" s="3">
         <v>30000017</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D30" s="3">
         <v>10000006</v>
@@ -3499,15 +4107,15 @@
         <v>5000</v>
       </c>
       <c r="AA30" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
-    <row r="31" spans="2:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" customHeight="1" spans="2:27">
       <c r="B31" s="3">
         <v>30000018</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D31" s="3">
         <v>10000007</v>
@@ -3549,10 +4157,10 @@
         <v>0</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="T31" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="U31" s="3">
         <v>1</v>
@@ -3570,15 +4178,15 @@
         <v>0</v>
       </c>
       <c r="Z31" s="10" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AA31" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -417,7 +417,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="129">
   <si>
     <t>##var</t>
   </si>
@@ -602,7 +602,7 @@
     <t>Skill_MeleeBasicAttack</t>
   </si>
   <si>
-    <t>Test_1</t>
+    <t>attack</t>
   </si>
   <si>
     <t>dao</t>
@@ -614,16 +614,10 @@
     <t>Skill_Projectile_Track</t>
   </si>
   <si>
-    <t>Test_2</t>
-  </si>
-  <si>
     <t>gongjian</t>
   </si>
   <si>
     <t>远程普通攻击2</t>
-  </si>
-  <si>
-    <t>Test_3</t>
   </si>
   <si>
     <t>箭雨</t>
@@ -823,7 +817,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -841,12 +835,6 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="0"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1398,138 +1386,138 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1549,12 +1537,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1932,7 +1914,7 @@
       <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="5" t="s">
@@ -2015,7 +1997,7 @@
       <c r="I2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="5" t="s">
         <v>28</v>
       </c>
       <c r="K2" s="5" t="s">
@@ -2098,7 +2080,7 @@
       <c r="I3" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="6" t="s">
         <v>41</v>
       </c>
       <c r="K3" s="6" t="s">
@@ -2279,10 +2261,10 @@
         <v>0</v>
       </c>
       <c r="S5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="T5" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="T5" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="U5" s="3">
         <v>2</v>
@@ -2308,7 +2290,7 @@
         <v>10000003</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D6" s="3">
         <v>10000003</v>
@@ -2354,10 +2336,10 @@
         <v>0</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="U6" s="3">
         <v>2</v>
@@ -2383,7 +2365,7 @@
         <v>10000004</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D7" s="3">
         <v>10000004</v>
@@ -2398,7 +2380,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3">
@@ -2432,7 +2414,7 @@
         <v>61</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="U7" s="3">
         <v>1</v>
@@ -2453,7 +2435,7 @@
         <v>0</v>
       </c>
       <c r="AA7" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="2:27">
@@ -2461,7 +2443,7 @@
         <v>20000001</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D8" s="3">
         <v>10000005</v>
@@ -2502,8 +2484,8 @@
       <c r="R8" s="2">
         <v>0</v>
       </c>
-      <c r="S8" s="2" t="s">
-        <v>65</v>
+      <c r="S8" s="3" t="s">
+        <v>61</v>
       </c>
       <c r="T8" s="2" t="s">
         <v>62</v>
@@ -2527,7 +2509,7 @@
         <v>0</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="2:27">
@@ -2535,7 +2517,7 @@
         <v>20000002</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D9" s="3">
         <v>10000006</v>
@@ -2576,8 +2558,8 @@
       <c r="R9" s="2">
         <v>0</v>
       </c>
-      <c r="S9" s="2" t="s">
-        <v>68</v>
+      <c r="S9" s="3" t="s">
+        <v>61</v>
       </c>
       <c r="T9" s="2" t="s">
         <v>62</v>
@@ -2594,14 +2576,14 @@
       <c r="X9" s="2">
         <v>10000001</v>
       </c>
-      <c r="Y9" s="9" t="s">
-        <v>76</v>
+      <c r="Y9" s="7" t="s">
+        <v>74</v>
       </c>
       <c r="Z9" s="2">
         <v>0</v>
       </c>
       <c r="AA9" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="2:27">
@@ -2609,7 +2591,7 @@
         <v>20000003</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D10" s="3">
         <v>10000007</v>
@@ -2675,7 +2657,7 @@
         <v>0</v>
       </c>
       <c r="AA10" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="2:27">
@@ -2683,7 +2665,7 @@
         <v>20000004</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D11" s="3">
         <v>10000001</v>
@@ -2725,10 +2707,10 @@
         <v>0</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="U11" s="3">
         <v>1</v>
@@ -2749,7 +2731,7 @@
         <v>0</v>
       </c>
       <c r="AA11" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="2:27">
@@ -2757,7 +2739,7 @@
         <v>20000005</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D12" s="3">
         <v>10000002</v>
@@ -2799,10 +2781,10 @@
         <v>0</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="U12" s="3">
         <v>0</v>
@@ -2819,11 +2801,11 @@
       <c r="Y12" s="3">
         <v>0</v>
       </c>
-      <c r="Z12" s="10" t="s">
-        <v>83</v>
+      <c r="Z12" s="8" t="s">
+        <v>81</v>
       </c>
       <c r="AA12" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="2:27">
@@ -2831,7 +2813,7 @@
         <v>20000006</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D13" s="3">
         <v>10000003</v>
@@ -2872,11 +2854,11 @@
       <c r="R13" s="2">
         <v>0</v>
       </c>
-      <c r="S13" s="2" t="s">
+      <c r="S13" s="3" t="s">
         <v>61</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="U13" s="2">
         <v>0</v>
@@ -2897,7 +2879,7 @@
         <v>0</v>
       </c>
       <c r="AA13" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="2:27">
@@ -2905,7 +2887,7 @@
         <v>30000001</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D14" s="3">
         <v>10000004</v>
@@ -2947,7 +2929,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>62</v>
@@ -2964,14 +2946,14 @@
       <c r="X14" s="3">
         <v>10000001</v>
       </c>
-      <c r="Y14" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="10" t="s">
-        <v>88</v>
+      <c r="Y14" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="AA14" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="2:27">
@@ -2979,7 +2961,7 @@
         <v>30000002</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D15" s="3">
         <v>10000005</v>
@@ -3021,7 +3003,7 @@
         <v>0</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>62</v>
@@ -3045,7 +3027,7 @@
         <v>0</v>
       </c>
       <c r="AA15" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="2:27">
@@ -3053,7 +3035,7 @@
         <v>30000003</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D16" s="3">
         <v>10000006</v>
@@ -3094,7 +3076,7 @@
       <c r="R16" s="2">
         <v>0</v>
       </c>
-      <c r="S16" s="2" t="s">
+      <c r="S16" s="3" t="s">
         <v>61</v>
       </c>
       <c r="T16" s="2" t="s">
@@ -3112,14 +3094,14 @@
       <c r="X16" s="2">
         <v>10000001</v>
       </c>
-      <c r="Y16" s="12">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="9" t="s">
-        <v>93</v>
+      <c r="Y16" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="7" t="s">
+        <v>91</v>
       </c>
       <c r="AA16" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="2:27">
@@ -3127,7 +3109,7 @@
         <v>30000004</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D17" s="3">
         <v>10000007</v>
@@ -3169,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="T17" s="3" t="s">
         <v>62</v>
@@ -3193,7 +3175,7 @@
         <v>10000008</v>
       </c>
       <c r="AA17" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="2:27">
@@ -3201,7 +3183,7 @@
         <v>30000005</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D18" s="2">
         <v>10000001</v>
@@ -3243,7 +3225,7 @@
         <v>0</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="T18" s="2" t="s">
         <v>62</v>
@@ -3267,7 +3249,7 @@
         <v>0</v>
       </c>
       <c r="AA18" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="2:27">
@@ -3275,7 +3257,7 @@
         <v>30000006</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D19" s="2">
         <v>10000002</v>
@@ -3337,11 +3319,11 @@
       <c r="Y19" s="3">
         <v>0</v>
       </c>
-      <c r="Z19" s="10" t="s">
-        <v>100</v>
+      <c r="Z19" s="8" t="s">
+        <v>98</v>
       </c>
       <c r="AA19" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="2:27">
@@ -3349,7 +3331,7 @@
         <v>30000007</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D20" s="2">
         <v>10000003</v>
@@ -3391,7 +3373,7 @@
         <v>0</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>62</v>
@@ -3415,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="AA20" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="2:27">
@@ -3423,7 +3405,7 @@
         <v>30000008</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D21" s="2">
         <v>10000004</v>
@@ -3465,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="T21" s="3" t="s">
         <v>62</v>
@@ -3489,7 +3471,7 @@
         <v>10000014</v>
       </c>
       <c r="AA21" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="2:27">
@@ -3497,7 +3479,7 @@
         <v>30000009</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D22" s="2">
         <v>10000005</v>
@@ -3539,7 +3521,7 @@
         <v>0</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>62</v>
@@ -3556,14 +3538,14 @@
       <c r="X22" s="3">
         <v>10000001</v>
       </c>
-      <c r="Y22" s="10" t="s">
-        <v>107</v>
+      <c r="Y22" s="8" t="s">
+        <v>105</v>
       </c>
       <c r="Z22" s="3">
         <v>0</v>
       </c>
       <c r="AA22" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="2:27">
@@ -3571,7 +3553,7 @@
         <v>30000010</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D23" s="2">
         <v>10000006</v>
@@ -3613,7 +3595,7 @@
         <v>0</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="T23" s="3" t="s">
         <v>62</v>
@@ -3633,11 +3615,11 @@
       <c r="Y23" s="3">
         <v>0</v>
       </c>
-      <c r="Z23" s="10" t="s">
-        <v>110</v>
+      <c r="Z23" s="8" t="s">
+        <v>108</v>
       </c>
       <c r="AA23" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="2:27">
@@ -3645,7 +3627,7 @@
         <v>30000011</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D24" s="2">
         <v>10000007</v>
@@ -3687,7 +3669,7 @@
         <v>0</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="T24" s="3" t="s">
         <v>62</v>
@@ -3707,11 +3689,11 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-      <c r="Z24" s="10" t="s">
-        <v>113</v>
+      <c r="Z24" s="8" t="s">
+        <v>111</v>
       </c>
       <c r="AA24" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="2:27">
@@ -3719,7 +3701,7 @@
         <v>30000012</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D25" s="3">
         <v>10000001</v>
@@ -3761,7 +3743,7 @@
         <v>0</v>
       </c>
       <c r="S25" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="T25" s="3" t="s">
         <v>62</v>
@@ -3785,7 +3767,7 @@
         <v>10000021</v>
       </c>
       <c r="AA25" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="2:27">
@@ -3793,7 +3775,7 @@
         <v>30000013</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D26" s="3">
         <v>10000002</v>
@@ -3835,7 +3817,7 @@
         <v>0</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="T26" s="3" t="s">
         <v>62</v>
@@ -3859,7 +3841,7 @@
         <v>10000022</v>
       </c>
       <c r="AA26" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="2:27">
@@ -3867,7 +3849,7 @@
         <v>30000014</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D27" s="3">
         <v>10000003</v>
@@ -3909,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="T27" s="3" t="s">
         <v>62</v>
@@ -3933,7 +3915,7 @@
         <v>10000023</v>
       </c>
       <c r="AA27" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="2:27">
@@ -3941,7 +3923,7 @@
         <v>30000015</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D28" s="3">
         <v>10000004</v>
@@ -3983,7 +3965,7 @@
         <v>0</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="T28" s="3" t="s">
         <v>62</v>
@@ -4003,11 +3985,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-      <c r="Z28" s="10" t="s">
-        <v>122</v>
+      <c r="Z28" s="8" t="s">
+        <v>120</v>
       </c>
       <c r="AA28" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="2:27">
@@ -4015,7 +3997,7 @@
         <v>30000016</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D29" s="3">
         <v>10000005</v>
@@ -4057,7 +4039,7 @@
         <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>62</v>
@@ -4075,7 +4057,7 @@
         <v>10000001</v>
       </c>
       <c r="AA29" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="2:27">
@@ -4083,7 +4065,7 @@
         <v>30000017</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D30" s="3">
         <v>10000006</v>
@@ -4106,8 +4088,11 @@
       <c r="P30" s="3">
         <v>5000</v>
       </c>
+      <c r="S30" s="3" t="s">
+        <v>61</v>
+      </c>
       <c r="AA30" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="2:27">
@@ -4115,7 +4100,7 @@
         <v>30000018</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D31" s="3">
         <v>10000007</v>
@@ -4157,7 +4142,7 @@
         <v>0</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="T31" s="3" t="s">
         <v>62</v>
@@ -4177,11 +4162,11 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-      <c r="Z31" s="10" t="s">
-        <v>129</v>
+      <c r="Z31" s="8" t="s">
+        <v>127</v>
       </c>
       <c r="AA31" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -389,7 +389,30 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z3" authorId="0">
+    <comment ref="Y3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+对应配置表EffectConfig
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AA3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -417,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="131">
   <si>
     <t>##var</t>
   </si>
@@ -488,6 +511,9 @@
     <t>DamageRange</t>
   </si>
   <si>
+    <t>SkillEffectID</t>
+  </si>
+  <si>
     <t>SkillHitEffectID</t>
   </si>
   <si>
@@ -585,6 +611,9 @@
   </si>
   <si>
     <t>技能特效Id</t>
+  </si>
+  <si>
+    <t>技能命中特效Id</t>
   </si>
   <si>
     <t>初始化BUFFID</t>
@@ -1871,7 +1900,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA31"/>
+  <dimension ref="A1:AB31"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.875" style="3" customWidth="1"/>
@@ -1880,13 +1909,13 @@
     <col min="9" max="9" width="21.875" style="3" customWidth="1"/>
     <col min="10" max="13" width="17.875" style="3"/>
     <col min="14" max="14" width="19.125" style="3" customWidth="1"/>
-    <col min="15" max="24" width="17.875" style="3"/>
-    <col min="25" max="26" width="20.375" style="3" customWidth="1"/>
-    <col min="27" max="27" width="100.625" style="3" customWidth="1"/>
-    <col min="28" max="16384" width="17.875" style="3"/>
+    <col min="15" max="25" width="17.875" style="3"/>
+    <col min="26" max="27" width="20.375" style="3" customWidth="1"/>
+    <col min="28" max="28" width="100.625" style="3" customWidth="1"/>
+    <col min="29" max="16384" width="17.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:27">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1968,179 +1997,188 @@
       <c r="AA1" s="5" t="s">
         <v>26</v>
       </c>
+      <c r="AB1" s="5" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:27">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>28</v>
-      </c>
       <c r="G2" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="K2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="J2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>28</v>
-      </c>
       <c r="L2" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="S2" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="N2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" s="5" t="s">
+      <c r="T2" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="P2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q2" s="5" t="s">
+      <c r="U2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="W2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="X2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z2" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA2" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB2" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="R2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="S2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="T2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="V2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="W2" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="X2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y2" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z2" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA2" s="5" t="s">
-        <v>29</v>
-      </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:27">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T3" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="U3" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="V3" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="W3" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="X3" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Y3" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Z3" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AA3" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="AB3" s="6" t="s">
+        <v>60</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="2:26">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="2:27">
       <c r="B4" s="3">
         <v>10000001</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D4" s="3">
         <v>10000001</v>
@@ -2155,7 +2193,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3">
@@ -2186,10 +2224,10 @@
         <v>0</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U4" s="3">
         <v>2</v>
@@ -2204,18 +2242,21 @@
         <v>10000001</v>
       </c>
       <c r="Y4" s="3">
-        <v>0</v>
+        <v>20000001</v>
       </c>
       <c r="Z4" s="3">
         <v>0</v>
       </c>
+      <c r="AA4" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="2:26">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="2:27">
       <c r="B5" s="3">
         <v>10000002</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D5" s="3">
         <v>10000002</v>
@@ -2230,7 +2271,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3">
@@ -2261,10 +2302,10 @@
         <v>0</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="U5" s="3">
         <v>2</v>
@@ -2279,18 +2320,21 @@
         <v>10000002</v>
       </c>
       <c r="Y5" s="3">
-        <v>0</v>
+        <v>20000001</v>
       </c>
       <c r="Z5" s="3">
         <v>0</v>
       </c>
+      <c r="AA5" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="2:26">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="2:27">
       <c r="B6" s="3">
         <v>10000003</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D6" s="3">
         <v>10000003</v>
@@ -2305,7 +2349,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3">
@@ -2336,10 +2380,10 @@
         <v>0</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="U6" s="3">
         <v>2</v>
@@ -2354,18 +2398,21 @@
         <v>10000003</v>
       </c>
       <c r="Y6" s="3">
-        <v>0</v>
+        <v>20000001</v>
       </c>
       <c r="Z6" s="3">
         <v>0</v>
       </c>
+      <c r="AA6" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="2:27">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="2:28">
       <c r="B7" s="3">
         <v>10000004</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D7" s="3">
         <v>10000004</v>
@@ -2380,7 +2427,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3">
@@ -2411,10 +2458,10 @@
         <v>100</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="U7" s="3">
         <v>1</v>
@@ -2429,21 +2476,24 @@
         <v>10000004</v>
       </c>
       <c r="Y7" s="3">
-        <v>0</v>
+        <v>20000001</v>
       </c>
       <c r="Z7" s="3">
         <v>0</v>
       </c>
-      <c r="AA7" s="3" t="s">
-        <v>70</v>
+      <c r="AA7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="3" t="s">
+        <v>72</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="2:27">
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="2:28">
       <c r="B8" s="2">
         <v>20000001</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D8" s="3">
         <v>10000005</v>
@@ -2485,10 +2535,10 @@
         <v>0</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U8" s="2">
         <v>2</v>
@@ -2502,22 +2552,25 @@
       <c r="X8" s="2">
         <v>10000001</v>
       </c>
-      <c r="Y8" s="2">
-        <v>0</v>
+      <c r="Y8" s="3">
+        <v>20000001</v>
       </c>
       <c r="Z8" s="2">
         <v>0</v>
       </c>
-      <c r="AA8" s="2" t="s">
-        <v>72</v>
+      <c r="AA8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="2" t="s">
+        <v>74</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="2:27">
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="2:28">
       <c r="B9" s="2">
         <v>20000002</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D9" s="3">
         <v>10000006</v>
@@ -2559,10 +2612,10 @@
         <v>0</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U9" s="2">
         <v>3</v>
@@ -2576,22 +2629,25 @@
       <c r="X9" s="2">
         <v>10000001</v>
       </c>
-      <c r="Y9" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="Z9" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="2" t="s">
-        <v>75</v>
+      <c r="Y9" s="3">
+        <v>20000001</v>
+      </c>
+      <c r="Z9" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="2:27">
+    <row r="10" customHeight="1" spans="2:28">
       <c r="B10" s="3">
         <v>20000003</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D10" s="3">
         <v>10000007</v>
@@ -2633,10 +2689,10 @@
         <v>0</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U10" s="3">
         <v>4</v>
@@ -2651,21 +2707,24 @@
         <v>10000001</v>
       </c>
       <c r="Y10" s="3">
+        <v>20000001</v>
+      </c>
+      <c r="Z10" s="3">
         <v>10000002</v>
       </c>
-      <c r="Z10" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="3" t="s">
-        <v>77</v>
+      <c r="AA10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="3" t="s">
+        <v>79</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="2:27">
+    <row r="11" customHeight="1" spans="2:28">
       <c r="B11" s="3">
         <v>20000004</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D11" s="3">
         <v>10000001</v>
@@ -2707,10 +2766,10 @@
         <v>0</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="U11" s="3">
         <v>1</v>
@@ -2725,21 +2784,24 @@
         <v>10000001</v>
       </c>
       <c r="Y11" s="3">
-        <v>0</v>
+        <v>20000001</v>
       </c>
       <c r="Z11" s="3">
         <v>0</v>
       </c>
-      <c r="AA11" s="3" t="s">
-        <v>79</v>
+      <c r="AA11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="3" t="s">
+        <v>81</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="2:27">
+    <row r="12" customHeight="1" spans="2:28">
       <c r="B12" s="3">
         <v>20000005</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D12" s="3">
         <v>10000002</v>
@@ -2781,10 +2843,10 @@
         <v>0</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="U12" s="3">
         <v>0</v>
@@ -2799,21 +2861,24 @@
         <v>10000001</v>
       </c>
       <c r="Y12" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="AA12" s="3" t="s">
-        <v>82</v>
+        <v>20000001</v>
+      </c>
+      <c r="Z12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="AB12" s="3" t="s">
+        <v>84</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="2:27">
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="2:28">
       <c r="B13" s="2">
         <v>20000006</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D13" s="3">
         <v>10000003</v>
@@ -2855,10 +2920,10 @@
         <v>0</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="U13" s="2">
         <v>0</v>
@@ -2872,22 +2937,25 @@
       <c r="X13" s="2">
         <v>10000001</v>
       </c>
-      <c r="Y13" s="2">
-        <v>0</v>
+      <c r="Y13" s="3">
+        <v>20000001</v>
       </c>
       <c r="Z13" s="2">
         <v>0</v>
       </c>
-      <c r="AA13" s="2" t="s">
-        <v>84</v>
+      <c r="AA13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="2" t="s">
+        <v>86</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="2:27">
+    <row r="14" customHeight="1" spans="2:28">
       <c r="B14" s="3">
         <v>30000001</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D14" s="3">
         <v>10000004</v>
@@ -2929,10 +2997,10 @@
         <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -2946,22 +3014,25 @@
       <c r="X14" s="3">
         <v>10000001</v>
       </c>
-      <c r="Y14" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>87</v>
+      <c r="Y14" s="3">
+        <v>20000001</v>
+      </c>
+      <c r="Z14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB14" s="3" t="s">
+        <v>89</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="2:27">
+    <row r="15" customHeight="1" spans="2:28">
       <c r="B15" s="3">
         <v>30000002</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D15" s="3">
         <v>10000005</v>
@@ -3003,10 +3074,10 @@
         <v>0</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T15" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U15" s="3">
         <v>1</v>
@@ -3021,21 +3092,24 @@
         <v>10000001</v>
       </c>
       <c r="Y15" s="3">
-        <v>0</v>
+        <v>20000001</v>
       </c>
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>89</v>
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="3" t="s">
+        <v>91</v>
       </c>
     </row>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="2:27">
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="2:28">
       <c r="B16" s="2">
         <v>30000003</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D16" s="3">
         <v>10000006</v>
@@ -3077,10 +3151,10 @@
         <v>0</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U16" s="2">
         <v>2</v>
@@ -3094,22 +3168,25 @@
       <c r="X16" s="2">
         <v>10000001</v>
       </c>
-      <c r="Y16" s="10">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA16" s="2" t="s">
-        <v>92</v>
+      <c r="Y16" s="3">
+        <v>20000001</v>
+      </c>
+      <c r="Z16" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="AB16" s="2" t="s">
+        <v>94</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="2:27">
+    <row r="17" customHeight="1" spans="2:28">
       <c r="B17" s="3">
         <v>30000004</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D17" s="3">
         <v>10000007</v>
@@ -3151,10 +3228,10 @@
         <v>0</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T17" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U17" s="3">
         <v>1</v>
@@ -3169,21 +3246,24 @@
         <v>10000001</v>
       </c>
       <c r="Y17" s="3">
-        <v>0</v>
+        <v>20000001</v>
       </c>
       <c r="Z17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="3">
         <v>10000008</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>94</v>
+      <c r="AB17" s="3" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="18" s="2" customFormat="1" customHeight="1" spans="2:27">
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="2:28">
       <c r="B18" s="2">
         <v>30000005</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D18" s="2">
         <v>10000001</v>
@@ -3225,10 +3305,10 @@
         <v>0</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U18" s="2">
         <v>1</v>
@@ -3242,22 +3322,25 @@
       <c r="X18" s="2">
         <v>10000001</v>
       </c>
-      <c r="Y18" s="2">
-        <v>0</v>
+      <c r="Y18" s="3">
+        <v>20000001</v>
       </c>
       <c r="Z18" s="2">
         <v>0</v>
       </c>
-      <c r="AA18" s="2" t="s">
-        <v>96</v>
+      <c r="AA18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="2" t="s">
+        <v>98</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="2:27">
+    <row r="19" customHeight="1" spans="2:28">
       <c r="B19" s="3">
         <v>30000006</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D19" s="2">
         <v>10000002</v>
@@ -3299,10 +3382,10 @@
         <v>0</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U19" s="3">
         <v>3</v>
@@ -3317,21 +3400,24 @@
         <v>10000001</v>
       </c>
       <c r="Y19" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z19" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="AA19" s="3" t="s">
-        <v>99</v>
+        <v>20000001</v>
+      </c>
+      <c r="Z19" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB19" s="3" t="s">
+        <v>101</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="2:27">
+    <row r="20" customHeight="1" spans="2:28">
       <c r="B20" s="3">
         <v>30000007</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D20" s="2">
         <v>10000003</v>
@@ -3373,10 +3459,10 @@
         <v>0</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T20" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U20" s="3">
         <v>0</v>
@@ -3391,21 +3477,24 @@
         <v>10000001</v>
       </c>
       <c r="Y20" s="3">
-        <v>0</v>
+        <v>20000001</v>
       </c>
       <c r="Z20" s="3">
         <v>0</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>101</v>
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3" t="s">
+        <v>103</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="2:27">
+    <row r="21" customHeight="1" spans="2:28">
       <c r="B21" s="3">
         <v>30000008</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D21" s="2">
         <v>10000004</v>
@@ -3447,10 +3536,10 @@
         <v>0</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T21" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U21" s="3">
         <v>1</v>
@@ -3465,21 +3554,24 @@
         <v>10000001</v>
       </c>
       <c r="Y21" s="3">
-        <v>0</v>
+        <v>20000001</v>
       </c>
       <c r="Z21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="3">
         <v>10000014</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>103</v>
+      <c r="AB21" s="3" t="s">
+        <v>105</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="2:27">
+    <row r="22" customHeight="1" spans="2:28">
       <c r="B22" s="3">
         <v>30000009</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D22" s="2">
         <v>10000005</v>
@@ -3521,10 +3613,10 @@
         <v>0</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T22" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U22" s="3">
         <v>3</v>
@@ -3538,22 +3630,25 @@
       <c r="X22" s="3">
         <v>10000001</v>
       </c>
-      <c r="Y22" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="3" t="s">
-        <v>106</v>
+      <c r="Y22" s="3">
+        <v>20000001</v>
+      </c>
+      <c r="Z22" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="3" t="s">
+        <v>108</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="2:27">
+    <row r="23" customHeight="1" spans="2:28">
       <c r="B23" s="3">
         <v>30000010</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D23" s="2">
         <v>10000006</v>
@@ -3595,10 +3690,10 @@
         <v>0</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T23" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U23" s="3">
         <v>1</v>
@@ -3613,21 +3708,24 @@
         <v>10000001</v>
       </c>
       <c r="Y23" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA23" s="3" t="s">
-        <v>109</v>
+        <v>20000001</v>
+      </c>
+      <c r="Z23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AB23" s="3" t="s">
+        <v>111</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="2:27">
+    <row r="24" customHeight="1" spans="2:28">
       <c r="B24" s="3">
         <v>30000011</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D24" s="2">
         <v>10000007</v>
@@ -3669,10 +3767,10 @@
         <v>0</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T24" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U24" s="3">
         <v>2</v>
@@ -3687,21 +3785,24 @@
         <v>10000001</v>
       </c>
       <c r="Y24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="AA24" s="3" t="s">
-        <v>112</v>
+        <v>20000001</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB24" s="3" t="s">
+        <v>114</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="2:27">
+    <row r="25" customHeight="1" spans="2:28">
       <c r="B25" s="3">
         <v>30000012</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D25" s="3">
         <v>10000001</v>
@@ -3743,10 +3844,10 @@
         <v>0</v>
       </c>
       <c r="S25" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T25" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U25" s="3">
         <v>5</v>
@@ -3761,21 +3862,24 @@
         <v>10000001</v>
       </c>
       <c r="Y25" s="3">
-        <v>0</v>
+        <v>20000001</v>
       </c>
       <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="3">
         <v>10000021</v>
       </c>
-      <c r="AA25" s="3" t="s">
-        <v>114</v>
+      <c r="AB25" s="3" t="s">
+        <v>116</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="2:27">
+    <row r="26" customHeight="1" spans="2:28">
       <c r="B26" s="3">
         <v>30000013</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D26" s="3">
         <v>10000002</v>
@@ -3817,10 +3921,10 @@
         <v>0</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T26" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U26" s="3">
         <v>1</v>
@@ -3835,21 +3939,24 @@
         <v>10000001</v>
       </c>
       <c r="Y26" s="3">
-        <v>0</v>
+        <v>20000001</v>
       </c>
       <c r="Z26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="3">
         <v>10000022</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>116</v>
+      <c r="AB26" s="3" t="s">
+        <v>118</v>
       </c>
     </row>
-    <row r="27" customHeight="1" spans="2:27">
+    <row r="27" customHeight="1" spans="2:28">
       <c r="B27" s="3">
         <v>30000014</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D27" s="3">
         <v>10000003</v>
@@ -3891,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T27" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U27" s="3">
         <v>2</v>
@@ -3909,21 +4016,24 @@
         <v>10000001</v>
       </c>
       <c r="Y27" s="3">
-        <v>0</v>
+        <v>20000001</v>
       </c>
       <c r="Z27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="3">
         <v>10000023</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>118</v>
+      <c r="AB27" s="3" t="s">
+        <v>120</v>
       </c>
     </row>
-    <row r="28" customHeight="1" spans="2:27">
+    <row r="28" customHeight="1" spans="2:28">
       <c r="B28" s="3">
         <v>30000015</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D28" s="3">
         <v>10000004</v>
@@ -3965,10 +4075,10 @@
         <v>0</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T28" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U28" s="3">
         <v>0</v>
@@ -3983,21 +4093,24 @@
         <v>10000001</v>
       </c>
       <c r="Y28" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z28" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="AA28" s="3" t="s">
-        <v>121</v>
+        <v>20000001</v>
+      </c>
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="AB28" s="3" t="s">
+        <v>123</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="2:27">
+    <row r="29" customHeight="1" spans="2:28">
       <c r="B29" s="3">
         <v>30000016</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D29" s="3">
         <v>10000005</v>
@@ -4039,10 +4152,10 @@
         <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T29" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U29" s="3">
         <v>6</v>
@@ -4056,16 +4169,19 @@
       <c r="X29" s="3">
         <v>10000001</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>123</v>
+      <c r="Y29" s="3">
+        <v>20000001</v>
+      </c>
+      <c r="AB29" s="3" t="s">
+        <v>125</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="2:27">
+    <row r="30" customHeight="1" spans="2:28">
       <c r="B30" s="3">
         <v>30000017</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D30" s="3">
         <v>10000006</v>
@@ -4089,18 +4205,21 @@
         <v>5000</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA30" s="3" t="s">
-        <v>125</v>
+        <v>63</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>20000001</v>
+      </c>
+      <c r="AB30" s="3" t="s">
+        <v>127</v>
       </c>
     </row>
-    <row r="31" customHeight="1" spans="2:27">
+    <row r="31" customHeight="1" spans="2:28">
       <c r="B31" s="3">
         <v>30000018</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D31" s="3">
         <v>10000007</v>
@@ -4142,10 +4261,10 @@
         <v>0</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T31" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="U31" s="3">
         <v>1</v>
@@ -4160,13 +4279,16 @@
         <v>10000001</v>
       </c>
       <c r="Y31" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z31" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="AA31" s="3" t="s">
-        <v>128</v>
+        <v>20000001</v>
+      </c>
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="AB31" s="3" t="s">
+        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -366,29 +366,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="X3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-对应配置表EffectConfig
-</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="Y3" authorId="0">
       <text>
         <r>
@@ -412,7 +389,30 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA3" authorId="0">
+    <comment ref="Z3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+对应配置表EffectConfig
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AB3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="134">
   <si>
     <t>##var</t>
   </si>
@@ -511,6 +511,9 @@
     <t>DamageRange</t>
   </si>
   <si>
+    <t>Speed</t>
+  </si>
+  <si>
     <t>SkillEffectID</t>
   </si>
   <si>
@@ -541,6 +544,9 @@
     <t>(array#sep=,),double</t>
   </si>
   <si>
+    <t>float</t>
+  </si>
+  <si>
     <t>(array#sep=,),int</t>
   </si>
   <si>
@@ -610,6 +616,9 @@
     <t>伤害范围</t>
   </si>
   <si>
+    <t>速度</t>
+  </si>
+  <si>
     <t>技能特效Id</t>
   </si>
   <si>
@@ -640,7 +649,7 @@
     <t>远程普通攻击1</t>
   </si>
   <si>
-    <t>Skill_Projectile_Track</t>
+    <t>Skill_RangedBasicAttack</t>
   </si>
   <si>
     <t>gongjian</t>
@@ -1900,7 +1909,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AB31"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.875" style="3" customWidth="1"/>
@@ -1909,13 +1918,15 @@
     <col min="9" max="9" width="21.875" style="3" customWidth="1"/>
     <col min="10" max="13" width="17.875" style="3"/>
     <col min="14" max="14" width="19.125" style="3" customWidth="1"/>
-    <col min="15" max="25" width="17.875" style="3"/>
-    <col min="26" max="27" width="20.375" style="3" customWidth="1"/>
-    <col min="28" max="28" width="100.625" style="3" customWidth="1"/>
-    <col min="29" max="16384" width="17.875" style="3"/>
+    <col min="15" max="23" width="17.875" style="3"/>
+    <col min="24" max="24" width="12.25" style="3" customWidth="1"/>
+    <col min="25" max="26" width="17.875" style="3"/>
+    <col min="27" max="28" width="20.375" style="3" customWidth="1"/>
+    <col min="29" max="29" width="100.625" style="3" customWidth="1"/>
+    <col min="30" max="16384" width="17.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:29">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2000,185 +2011,194 @@
       <c r="AB1" s="5" t="s">
         <v>27</v>
       </c>
+      <c r="AC1" s="5" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:29">
       <c r="A2" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>29</v>
-      </c>
       <c r="G2" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="K2" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>29</v>
-      </c>
       <c r="L2" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="S2" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="N2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O2" s="5" t="s">
+      <c r="T2" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="P2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q2" s="5" t="s">
+      <c r="U2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="W2" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="X2" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA2" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB2" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC2" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="R2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="S2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="T2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="V2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="W2" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="X2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="Z2" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA2" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="AB2" s="5" t="s">
-        <v>30</v>
-      </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:29">
       <c r="A3" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="T3" s="6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="U3" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="V3" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="W3" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="X3" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Y3" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Z3" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AA3" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AB3" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
+      </c>
+      <c r="AC3" s="6" t="s">
+        <v>63</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="2:27">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="2:28">
       <c r="B4" s="3">
         <v>10000001</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D4" s="3">
         <v>10000001</v>
@@ -2193,7 +2213,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3">
@@ -2224,10 +2244,10 @@
         <v>0</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="U4" s="3">
         <v>2</v>
@@ -2239,24 +2259,27 @@
         <v>0</v>
       </c>
       <c r="X4" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3">
         <v>10000001</v>
       </c>
-      <c r="Y4" s="3">
+      <c r="Z4" s="3">
         <v>20000001</v>
       </c>
-      <c r="Z4" s="3">
-        <v>0</v>
-      </c>
       <c r="AA4" s="3">
         <v>0</v>
       </c>
+      <c r="AB4" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="2:27">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="2:28">
       <c r="B5" s="3">
         <v>10000002</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D5" s="3">
         <v>10000002</v>
@@ -2271,7 +2294,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3">
@@ -2302,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="U5" s="3">
         <v>2</v>
@@ -2317,24 +2340,27 @@
         <v>0</v>
       </c>
       <c r="X5" s="3">
+        <v>3</v>
+      </c>
+      <c r="Y5" s="3">
         <v>10000002</v>
       </c>
-      <c r="Y5" s="3">
+      <c r="Z5" s="3">
         <v>20000001</v>
       </c>
-      <c r="Z5" s="3">
-        <v>0</v>
-      </c>
       <c r="AA5" s="3">
         <v>0</v>
       </c>
+      <c r="AB5" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="2:27">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="2:28">
       <c r="B6" s="3">
         <v>10000003</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D6" s="3">
         <v>10000003</v>
@@ -2349,7 +2375,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3">
@@ -2380,10 +2406,10 @@
         <v>0</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="U6" s="3">
         <v>2</v>
@@ -2395,24 +2421,27 @@
         <v>0</v>
       </c>
       <c r="X6" s="3">
+        <v>3</v>
+      </c>
+      <c r="Y6" s="3">
         <v>10000003</v>
       </c>
-      <c r="Y6" s="3">
+      <c r="Z6" s="3">
         <v>20000001</v>
       </c>
-      <c r="Z6" s="3">
-        <v>0</v>
-      </c>
       <c r="AA6" s="3">
         <v>0</v>
       </c>
+      <c r="AB6" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="2:28">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="2:29">
       <c r="B7" s="3">
         <v>10000004</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D7" s="3">
         <v>10000004</v>
@@ -2427,7 +2456,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3">
@@ -2458,10 +2487,10 @@
         <v>100</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="U7" s="3">
         <v>1</v>
@@ -2473,27 +2502,30 @@
         <v>4</v>
       </c>
       <c r="X7" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3">
         <v>10000004</v>
       </c>
-      <c r="Y7" s="3">
+      <c r="Z7" s="3">
         <v>20000001</v>
       </c>
-      <c r="Z7" s="3">
-        <v>0</v>
-      </c>
       <c r="AA7" s="3">
         <v>0</v>
       </c>
-      <c r="AB7" s="3" t="s">
-        <v>72</v>
+      <c r="AB7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="3" t="s">
+        <v>75</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="2:28">
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="2:29">
       <c r="B8" s="2">
         <v>20000001</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D8" s="3">
         <v>10000005</v>
@@ -2535,10 +2567,10 @@
         <v>0</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="U8" s="2">
         <v>2</v>
@@ -2549,28 +2581,31 @@
       <c r="W8" s="2">
         <v>0</v>
       </c>
-      <c r="X8" s="2">
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="2">
         <v>10000001</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>20000001</v>
       </c>
-      <c r="Z8" s="2">
-        <v>0</v>
-      </c>
       <c r="AA8" s="2">
         <v>0</v>
       </c>
-      <c r="AB8" s="2" t="s">
-        <v>74</v>
+      <c r="AB8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="2:28">
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="2:29">
       <c r="B9" s="2">
         <v>20000002</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D9" s="3">
         <v>10000006</v>
@@ -2612,10 +2647,10 @@
         <v>0</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="U9" s="2">
         <v>3</v>
@@ -2626,28 +2661,31 @@
       <c r="W9" s="2">
         <v>0</v>
       </c>
-      <c r="X9" s="2">
+      <c r="X9" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="2">
         <v>10000001</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>20000001</v>
       </c>
-      <c r="Z9" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="AA9" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="2" t="s">
-        <v>77</v>
+      <c r="AA9" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="2" t="s">
+        <v>80</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="2:28">
+    <row r="10" customHeight="1" spans="2:29">
       <c r="B10" s="3">
         <v>20000003</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D10" s="3">
         <v>10000007</v>
@@ -2689,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="U10" s="3">
         <v>4</v>
@@ -2704,27 +2742,30 @@
         <v>0</v>
       </c>
       <c r="X10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3">
         <v>10000001</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>20000001</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>10000002</v>
       </c>
-      <c r="AA10" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="3" t="s">
-        <v>79</v>
+      <c r="AB10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="3" t="s">
+        <v>82</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="2:28">
+    <row r="11" customHeight="1" spans="2:29">
       <c r="B11" s="3">
         <v>20000004</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D11" s="3">
         <v>10000001</v>
@@ -2766,10 +2807,10 @@
         <v>0</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="U11" s="3">
         <v>1</v>
@@ -2781,27 +2822,30 @@
         <v>6</v>
       </c>
       <c r="X11" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="3">
         <v>10000001</v>
       </c>
-      <c r="Y11" s="3">
+      <c r="Z11" s="3">
         <v>20000001</v>
       </c>
-      <c r="Z11" s="3">
-        <v>0</v>
-      </c>
       <c r="AA11" s="3">
         <v>0</v>
       </c>
-      <c r="AB11" s="3" t="s">
-        <v>81</v>
+      <c r="AB11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="3" t="s">
+        <v>84</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="2:28">
+    <row r="12" customHeight="1" spans="2:29">
       <c r="B12" s="3">
         <v>20000005</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D12" s="3">
         <v>10000002</v>
@@ -2843,10 +2887,10 @@
         <v>0</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="U12" s="3">
         <v>0</v>
@@ -2858,27 +2902,30 @@
         <v>3</v>
       </c>
       <c r="X12" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="3">
         <v>10000001</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>20000001</v>
       </c>
-      <c r="Z12" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="AB12" s="3" t="s">
-        <v>84</v>
+      <c r="AA12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC12" s="3" t="s">
+        <v>87</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="2:28">
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="2:29">
       <c r="B13" s="2">
         <v>20000006</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D13" s="3">
         <v>10000003</v>
@@ -2920,10 +2967,10 @@
         <v>0</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="U13" s="2">
         <v>0</v>
@@ -2934,28 +2981,31 @@
       <c r="W13" s="2">
         <v>0</v>
       </c>
-      <c r="X13" s="2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="2">
         <v>10000001</v>
       </c>
-      <c r="Y13" s="3">
+      <c r="Z13" s="3">
         <v>20000001</v>
       </c>
-      <c r="Z13" s="2">
-        <v>0</v>
-      </c>
       <c r="AA13" s="2">
         <v>0</v>
       </c>
-      <c r="AB13" s="2" t="s">
-        <v>86</v>
+      <c r="AB13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="2" t="s">
+        <v>89</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="2:28">
+    <row r="14" customHeight="1" spans="2:29">
       <c r="B14" s="3">
         <v>30000001</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D14" s="3">
         <v>10000004</v>
@@ -2997,10 +3047,10 @@
         <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -3012,27 +3062,30 @@
         <v>2</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>10000001</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>20000001</v>
       </c>
-      <c r="Z14" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>89</v>
+      <c r="AA14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC14" s="3" t="s">
+        <v>92</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="2:28">
+    <row r="15" customHeight="1" spans="2:29">
       <c r="B15" s="3">
         <v>30000002</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D15" s="3">
         <v>10000005</v>
@@ -3074,10 +3127,10 @@
         <v>0</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="T15" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="U15" s="3">
         <v>1</v>
@@ -3089,27 +3142,30 @@
         <v>3</v>
       </c>
       <c r="X15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
         <v>10000001</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>20000001</v>
       </c>
-      <c r="Z15" s="3">
-        <v>0</v>
-      </c>
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-      <c r="AB15" s="3" t="s">
-        <v>91</v>
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="3" t="s">
+        <v>94</v>
       </c>
     </row>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="2:28">
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="2:29">
       <c r="B16" s="2">
         <v>30000003</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D16" s="3">
         <v>10000006</v>
@@ -3151,10 +3207,10 @@
         <v>0</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="U16" s="2">
         <v>2</v>
@@ -3165,28 +3221,31 @@
       <c r="W16" s="2">
         <v>0</v>
       </c>
-      <c r="X16" s="2">
+      <c r="X16" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="2">
         <v>10000001</v>
       </c>
-      <c r="Y16" s="3">
+      <c r="Z16" s="3">
         <v>20000001</v>
       </c>
-      <c r="Z16" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="AB16" s="2" t="s">
-        <v>94</v>
+      <c r="AA16" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="AC16" s="2" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="2:28">
+    <row r="17" customHeight="1" spans="2:29">
       <c r="B17" s="3">
         <v>30000004</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D17" s="3">
         <v>10000007</v>
@@ -3228,10 +3287,10 @@
         <v>0</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="T17" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="U17" s="3">
         <v>1</v>
@@ -3243,27 +3302,30 @@
         <v>3</v>
       </c>
       <c r="X17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="3">
         <v>10000001</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>20000001</v>
       </c>
-      <c r="Z17" s="3">
-        <v>0</v>
-      </c>
       <c r="AA17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="3">
         <v>10000008</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>96</v>
+      <c r="AC17" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
-    <row r="18" s="2" customFormat="1" customHeight="1" spans="2:28">
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="2:29">
       <c r="B18" s="2">
         <v>30000005</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D18" s="2">
         <v>10000001</v>
@@ -3305,10 +3367,10 @@
         <v>0</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="U18" s="2">
         <v>1</v>
@@ -3319,28 +3381,31 @@
       <c r="W18" s="2">
         <v>2</v>
       </c>
-      <c r="X18" s="2">
+      <c r="X18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="2">
         <v>10000001</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>20000001</v>
       </c>
-      <c r="Z18" s="2">
-        <v>0</v>
-      </c>
       <c r="AA18" s="2">
         <v>0</v>
       </c>
-      <c r="AB18" s="2" t="s">
-        <v>98</v>
+      <c r="AB18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="2" t="s">
+        <v>101</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="2:28">
+    <row r="19" customHeight="1" spans="2:29">
       <c r="B19" s="3">
         <v>30000006</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D19" s="2">
         <v>10000002</v>
@@ -3382,10 +3447,10 @@
         <v>0</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="U19" s="3">
         <v>3</v>
@@ -3397,27 +3462,30 @@
         <v>0</v>
       </c>
       <c r="X19" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="3">
         <v>10000001</v>
       </c>
-      <c r="Y19" s="3">
+      <c r="Z19" s="3">
         <v>20000001</v>
       </c>
-      <c r="Z19" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA19" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="AB19" s="3" t="s">
-        <v>101</v>
+      <c r="AA19" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="AC19" s="3" t="s">
+        <v>104</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="2:28">
+    <row r="20" customHeight="1" spans="2:29">
       <c r="B20" s="3">
         <v>30000007</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D20" s="2">
         <v>10000003</v>
@@ -3459,10 +3527,10 @@
         <v>0</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="T20" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="U20" s="3">
         <v>0</v>
@@ -3474,27 +3542,30 @@
         <v>3</v>
       </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>10000001</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>20000001</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>103</v>
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3" t="s">
+        <v>106</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="2:28">
+    <row r="21" customHeight="1" spans="2:29">
       <c r="B21" s="3">
         <v>30000008</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D21" s="2">
         <v>10000004</v>
@@ -3536,10 +3607,10 @@
         <v>0</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="T21" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="U21" s="3">
         <v>1</v>
@@ -3551,27 +3622,30 @@
         <v>4</v>
       </c>
       <c r="X21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3">
         <v>10000001</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>20000001</v>
       </c>
-      <c r="Z21" s="3">
-        <v>0</v>
-      </c>
       <c r="AA21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="3">
         <v>10000014</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>105</v>
+      <c r="AC21" s="3" t="s">
+        <v>108</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="2:28">
+    <row r="22" customHeight="1" spans="2:29">
       <c r="B22" s="3">
         <v>30000009</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D22" s="2">
         <v>10000005</v>
@@ -3613,10 +3687,10 @@
         <v>0</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="T22" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="U22" s="3">
         <v>3</v>
@@ -3628,27 +3702,30 @@
         <v>0</v>
       </c>
       <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
         <v>10000001</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>20000001</v>
       </c>
-      <c r="Z22" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="3" t="s">
-        <v>108</v>
+      <c r="AA22" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3" t="s">
+        <v>111</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="2:28">
+    <row r="23" customHeight="1" spans="2:29">
       <c r="B23" s="3">
         <v>30000010</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D23" s="2">
         <v>10000006</v>
@@ -3690,10 +3767,10 @@
         <v>0</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="T23" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="U23" s="3">
         <v>1</v>
@@ -3705,27 +3782,30 @@
         <v>3</v>
       </c>
       <c r="X23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3">
         <v>10000001</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>20000001</v>
       </c>
-      <c r="Z23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="AB23" s="3" t="s">
-        <v>111</v>
+      <c r="AA23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC23" s="3" t="s">
+        <v>114</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="2:28">
+    <row r="24" customHeight="1" spans="2:29">
       <c r="B24" s="3">
         <v>30000011</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D24" s="2">
         <v>10000007</v>
@@ -3767,10 +3847,10 @@
         <v>0</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="T24" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="U24" s="3">
         <v>2</v>
@@ -3782,27 +3862,30 @@
         <v>0</v>
       </c>
       <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
         <v>10000001</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>20000001</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA24" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="AB24" s="3" t="s">
-        <v>114</v>
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="AC24" s="3" t="s">
+        <v>117</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="2:28">
+    <row r="25" customHeight="1" spans="2:29">
       <c r="B25" s="3">
         <v>30000012</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D25" s="3">
         <v>10000001</v>
@@ -3844,10 +3927,10 @@
         <v>0</v>
       </c>
       <c r="S25" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="T25" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="U25" s="3">
         <v>5</v>
@@ -3859,27 +3942,30 @@
         <v>0</v>
       </c>
       <c r="X25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
         <v>10000001</v>
       </c>
-      <c r="Y25" s="3">
+      <c r="Z25" s="3">
         <v>20000001</v>
       </c>
-      <c r="Z25" s="3">
-        <v>0</v>
-      </c>
       <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="3">
         <v>10000021</v>
       </c>
-      <c r="AB25" s="3" t="s">
-        <v>116</v>
+      <c r="AC25" s="3" t="s">
+        <v>119</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="2:28">
+    <row r="26" customHeight="1" spans="2:29">
       <c r="B26" s="3">
         <v>30000013</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D26" s="3">
         <v>10000002</v>
@@ -3921,10 +4007,10 @@
         <v>0</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="T26" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="U26" s="3">
         <v>1</v>
@@ -3936,27 +4022,30 @@
         <v>3</v>
       </c>
       <c r="X26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
         <v>10000001</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>20000001</v>
       </c>
-      <c r="Z26" s="3">
-        <v>0</v>
-      </c>
       <c r="AA26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="3">
         <v>10000022</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>118</v>
+      <c r="AC26" s="3" t="s">
+        <v>121</v>
       </c>
     </row>
-    <row r="27" customHeight="1" spans="2:28">
+    <row r="27" customHeight="1" spans="2:29">
       <c r="B27" s="3">
         <v>30000014</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D27" s="3">
         <v>10000003</v>
@@ -3998,10 +4087,10 @@
         <v>0</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="T27" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="U27" s="3">
         <v>2</v>
@@ -4013,27 +4102,30 @@
         <v>0</v>
       </c>
       <c r="X27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
         <v>10000001</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>20000001</v>
       </c>
-      <c r="Z27" s="3">
-        <v>0</v>
-      </c>
       <c r="AA27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="3">
         <v>10000023</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>120</v>
+      <c r="AC27" s="3" t="s">
+        <v>123</v>
       </c>
     </row>
-    <row r="28" customHeight="1" spans="2:28">
+    <row r="28" customHeight="1" spans="2:29">
       <c r="B28" s="3">
         <v>30000015</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D28" s="3">
         <v>10000004</v>
@@ -4075,10 +4167,10 @@
         <v>0</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="T28" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="U28" s="3">
         <v>0</v>
@@ -4090,27 +4182,30 @@
         <v>4</v>
       </c>
       <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
         <v>10000001</v>
       </c>
-      <c r="Y28" s="3">
+      <c r="Z28" s="3">
         <v>20000001</v>
       </c>
-      <c r="Z28" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA28" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="AB28" s="3" t="s">
-        <v>123</v>
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC28" s="3" t="s">
+        <v>126</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="2:28">
+    <row r="29" customHeight="1" spans="2:29">
       <c r="B29" s="3">
         <v>30000016</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D29" s="3">
         <v>10000005</v>
@@ -4152,10 +4247,10 @@
         <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="T29" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="U29" s="3">
         <v>6</v>
@@ -4167,21 +4262,24 @@
         <v>0</v>
       </c>
       <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
         <v>10000001</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>20000001</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>125</v>
+      <c r="AC29" s="3" t="s">
+        <v>128</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="2:28">
+    <row r="30" customHeight="1" spans="2:29">
       <c r="B30" s="3">
         <v>30000017</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D30" s="3">
         <v>10000006</v>
@@ -4205,21 +4303,24 @@
         <v>5000</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="Y30" s="3">
+        <v>66</v>
+      </c>
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="3">
         <v>20000001</v>
       </c>
-      <c r="AB30" s="3" t="s">
-        <v>127</v>
+      <c r="AC30" s="3" t="s">
+        <v>130</v>
       </c>
     </row>
-    <row r="31" customHeight="1" spans="2:28">
+    <row r="31" customHeight="1" spans="2:29">
       <c r="B31" s="3">
         <v>30000018</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D31" s="3">
         <v>10000007</v>
@@ -4261,10 +4362,10 @@
         <v>0</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="T31" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="U31" s="3">
         <v>1</v>
@@ -4276,19 +4377,22 @@
         <v>4</v>
       </c>
       <c r="X31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
         <v>10000001</v>
       </c>
-      <c r="Y31" s="3">
+      <c r="Z31" s="3">
         <v>20000001</v>
       </c>
-      <c r="Z31" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA31" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="AB31" s="3" t="s">
-        <v>130</v>
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="AC31" s="3" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -2340,7 +2340,7 @@
         <v>0</v>
       </c>
       <c r="X5" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y5" s="3">
         <v>10000002</v>
@@ -2421,7 +2421,7 @@
         <v>0</v>
       </c>
       <c r="X6" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y6" s="3">
         <v>10000003</v>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -541,12 +541,12 @@
     <t>double</t>
   </si>
   <si>
-    <t>(array#sep=,),double</t>
-  </si>
-  <si>
     <t>float</t>
   </si>
   <si>
+    <t>(array#sep=,),float</t>
+  </si>
+  <si>
     <t>(array#sep=,),int</t>
   </si>
   <si>
@@ -592,7 +592,7 @@
     <t>技能CD</t>
   </si>
   <si>
-    <t>技能存在时间[毫秒]</t>
+    <t>技能存在时间</t>
   </si>
   <si>
     <t>攻击系数</t>
@@ -2062,7 +2062,7 @@
         <v>32</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="Q2" s="5" t="s">
         <v>32</v>
@@ -2083,10 +2083,10 @@
         <v>30</v>
       </c>
       <c r="W2" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="X2" s="5" t="s">
         <v>33</v>
-      </c>
-      <c r="X2" s="5" t="s">
-        <v>34</v>
       </c>
       <c r="Y2" s="5" t="s">
         <v>30</v>
@@ -2235,7 +2235,7 @@
         <v>1</v>
       </c>
       <c r="P4" s="3">
-        <v>3000</v>
+        <v>3</v>
       </c>
       <c r="Q4" s="3">
         <v>1</v>
@@ -2316,7 +2316,7 @@
         <v>1</v>
       </c>
       <c r="P5" s="3">
-        <v>3000</v>
+        <v>3</v>
       </c>
       <c r="Q5" s="3">
         <v>1</v>
@@ -2397,7 +2397,7 @@
         <v>1</v>
       </c>
       <c r="P6" s="3">
-        <v>3000</v>
+        <v>3</v>
       </c>
       <c r="Q6" s="3">
         <v>1</v>
@@ -2478,7 +2478,7 @@
         <v>11</v>
       </c>
       <c r="P7" s="3">
-        <v>5000</v>
+        <v>5</v>
       </c>
       <c r="Q7" s="3">
         <v>1</v>
@@ -2558,7 +2558,7 @@
         <v>1</v>
       </c>
       <c r="P8" s="2">
-        <v>3000</v>
+        <v>3</v>
       </c>
       <c r="Q8" s="2">
         <v>3.5</v>
@@ -2638,7 +2638,7 @@
         <v>1</v>
       </c>
       <c r="P9" s="2">
-        <v>5000</v>
+        <v>5</v>
       </c>
       <c r="Q9" s="2">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>1</v>
       </c>
       <c r="P10" s="3">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="Q10" s="3">
         <v>1</v>
@@ -2798,7 +2798,7 @@
         <v>1</v>
       </c>
       <c r="P11" s="3">
-        <v>3000</v>
+        <v>3</v>
       </c>
       <c r="Q11" s="3">
         <v>1.5</v>
@@ -2878,7 +2878,7 @@
         <v>1</v>
       </c>
       <c r="P12" s="3">
-        <v>5000</v>
+        <v>5</v>
       </c>
       <c r="Q12" s="3">
         <v>0</v>
@@ -2958,7 +2958,7 @@
         <v>1</v>
       </c>
       <c r="P13" s="2">
-        <v>5000</v>
+        <v>5</v>
       </c>
       <c r="Q13" s="2">
         <v>0</v>
@@ -3038,7 +3038,7 @@
         <v>9</v>
       </c>
       <c r="P14" s="3">
-        <v>3000</v>
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -3118,7 +3118,7 @@
         <v>3</v>
       </c>
       <c r="P15" s="3">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="Q15" s="3">
         <v>1.5</v>
@@ -3198,7 +3198,7 @@
         <v>10</v>
       </c>
       <c r="P16" s="2">
-        <v>4000</v>
+        <v>4</v>
       </c>
       <c r="Q16" s="2">
         <v>0.4</v>
@@ -3278,7 +3278,7 @@
         <v>10</v>
       </c>
       <c r="P17" s="3">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="3">
         <v>2</v>
@@ -3358,7 +3358,7 @@
         <v>0</v>
       </c>
       <c r="P18" s="2">
-        <v>3000</v>
+        <v>3</v>
       </c>
       <c r="Q18" s="2">
         <v>0.5</v>
@@ -3438,7 +3438,7 @@
         <v>10</v>
       </c>
       <c r="P19" s="3">
-        <v>5000</v>
+        <v>5</v>
       </c>
       <c r="Q19" s="3">
         <v>0</v>
@@ -3518,7 +3518,7 @@
         <v>10</v>
       </c>
       <c r="P20" s="3">
-        <v>3000</v>
+        <v>3</v>
       </c>
       <c r="Q20" s="3">
         <v>1</v>
@@ -3598,7 +3598,7 @@
         <v>10</v>
       </c>
       <c r="P21" s="3">
-        <v>5000</v>
+        <v>5</v>
       </c>
       <c r="Q21" s="3">
         <v>0</v>
@@ -3678,7 +3678,7 @@
         <v>0</v>
       </c>
       <c r="P22" s="3">
-        <v>3600000</v>
+        <v>3600</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -3758,7 +3758,7 @@
         <v>10</v>
       </c>
       <c r="P23" s="3">
-        <v>4000</v>
+        <v>4</v>
       </c>
       <c r="Q23" s="3">
         <v>2</v>
@@ -3838,7 +3838,7 @@
         <v>10</v>
       </c>
       <c r="P24" s="3">
-        <v>3000</v>
+        <v>3</v>
       </c>
       <c r="Q24" s="3">
         <v>0.5</v>
@@ -3918,7 +3918,7 @@
         <v>0</v>
       </c>
       <c r="P25" s="3">
-        <v>3600000</v>
+        <v>3600</v>
       </c>
       <c r="Q25" s="3">
         <v>0</v>
@@ -3998,7 +3998,7 @@
         <v>10</v>
       </c>
       <c r="P26" s="3">
-        <v>3000</v>
+        <v>3</v>
       </c>
       <c r="Q26" s="3">
         <v>1</v>
@@ -4078,7 +4078,7 @@
         <v>10</v>
       </c>
       <c r="P27" s="3">
-        <v>3000</v>
+        <v>3</v>
       </c>
       <c r="Q27" s="3">
         <v>0</v>
@@ -4158,7 +4158,7 @@
         <v>0</v>
       </c>
       <c r="P28" s="3">
-        <v>3600000</v>
+        <v>3600</v>
       </c>
       <c r="Q28" s="3">
         <v>0</v>
@@ -4238,7 +4238,7 @@
         <v>10</v>
       </c>
       <c r="P29" s="3">
-        <v>5000</v>
+        <v>5</v>
       </c>
       <c r="Q29" s="3">
         <v>0.1</v>
@@ -4300,7 +4300,7 @@
         <v>10</v>
       </c>
       <c r="P30" s="3">
-        <v>5000</v>
+        <v>5</v>
       </c>
       <c r="S30" s="3" t="s">
         <v>66</v>
@@ -4353,7 +4353,7 @@
         <v>10</v>
       </c>
       <c r="P31" s="3">
-        <v>3000</v>
+        <v>3</v>
       </c>
       <c r="Q31" s="3">
         <v>0</v>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -661,7 +661,7 @@
     <t>箭雨</t>
   </si>
   <si>
-    <t>Skill_Circle</t>
+    <t>Skill_AreaDamage</t>
   </si>
   <si>
     <t>jianyu</t>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -2340,7 +2340,7 @@
         <v>0</v>
       </c>
       <c r="X5" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y5" s="3">
         <v>10000002</v>
@@ -2421,7 +2421,7 @@
         <v>0</v>
       </c>
       <c r="X6" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y6" s="3">
         <v>10000003</v>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -1033,12 +1033,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -2077,7 +2077,7 @@
         <v>31</v>
       </c>
       <c r="U2" s="5" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="V2" s="5" t="s">
         <v>30</v>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="135">
   <si>
     <t>##var</t>
   </si>
@@ -698,6 +698,9 @@
   </si>
   <si>
     <t>守护天使</t>
+  </si>
+  <si>
+    <t>Skill_BuffFriendly</t>
   </si>
   <si>
     <t>10000003,10000004</t>
@@ -1033,12 +1036,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -2859,6 +2862,9 @@
       <c r="G12" s="3">
         <v>0</v>
       </c>
+      <c r="H12" s="3" t="s">
+        <v>86</v>
+      </c>
       <c r="J12" s="3">
         <v>0</v>
       </c>
@@ -2875,7 +2881,7 @@
         <v>0</v>
       </c>
       <c r="O12" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="P12" s="3">
         <v>5</v>
@@ -2905,19 +2911,19 @@
         <v>0</v>
       </c>
       <c r="Y12" s="3">
-        <v>10000001</v>
+        <v>0</v>
       </c>
       <c r="Z12" s="3">
-        <v>20000001</v>
+        <v>0</v>
       </c>
       <c r="AA12" s="3">
         <v>0</v>
       </c>
       <c r="AB12" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AC12" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="2:29">
@@ -2925,7 +2931,7 @@
         <v>20000006</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" s="3">
         <v>10000003</v>
@@ -2997,7 +3003,7 @@
         <v>0</v>
       </c>
       <c r="AC13" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="2:29">
@@ -3005,7 +3011,7 @@
         <v>30000001</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" s="3">
         <v>10000004</v>
@@ -3074,10 +3080,10 @@
         <v>0</v>
       </c>
       <c r="AB14" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AC14" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="2:29">
@@ -3085,7 +3091,7 @@
         <v>30000002</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D15" s="3">
         <v>10000005</v>
@@ -3157,7 +3163,7 @@
         <v>0</v>
       </c>
       <c r="AC15" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="2:29">
@@ -3165,7 +3171,7 @@
         <v>30000003</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D16" s="3">
         <v>10000006</v>
@@ -3234,10 +3240,10 @@
         <v>0</v>
       </c>
       <c r="AB16" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AC16" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="2:29">
@@ -3245,7 +3251,7 @@
         <v>30000004</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D17" s="3">
         <v>10000007</v>
@@ -3317,7 +3323,7 @@
         <v>10000008</v>
       </c>
       <c r="AC17" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="2:29">
@@ -3325,7 +3331,7 @@
         <v>30000005</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D18" s="2">
         <v>10000001</v>
@@ -3397,7 +3403,7 @@
         <v>0</v>
       </c>
       <c r="AC18" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="2:29">
@@ -3405,7 +3411,7 @@
         <v>30000006</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D19" s="2">
         <v>10000002</v>
@@ -3474,10 +3480,10 @@
         <v>0</v>
       </c>
       <c r="AB19" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AC19" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="2:29">
@@ -3485,7 +3491,7 @@
         <v>30000007</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D20" s="2">
         <v>10000003</v>
@@ -3557,7 +3563,7 @@
         <v>0</v>
       </c>
       <c r="AC20" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="2:29">
@@ -3565,7 +3571,7 @@
         <v>30000008</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D21" s="2">
         <v>10000004</v>
@@ -3637,7 +3643,7 @@
         <v>10000014</v>
       </c>
       <c r="AC21" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="2:29">
@@ -3645,7 +3651,7 @@
         <v>30000009</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D22" s="2">
         <v>10000005</v>
@@ -3711,13 +3717,13 @@
         <v>20000001</v>
       </c>
       <c r="AA22" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
       </c>
       <c r="AC22" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="2:29">
@@ -3725,7 +3731,7 @@
         <v>30000010</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D23" s="2">
         <v>10000006</v>
@@ -3794,10 +3800,10 @@
         <v>0</v>
       </c>
       <c r="AB23" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AC23" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="2:29">
@@ -3805,7 +3811,7 @@
         <v>30000011</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D24" s="2">
         <v>10000007</v>
@@ -3874,10 +3880,10 @@
         <v>0</v>
       </c>
       <c r="AB24" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AC24" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="2:29">
@@ -3885,7 +3891,7 @@
         <v>30000012</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D25" s="3">
         <v>10000001</v>
@@ -3957,7 +3963,7 @@
         <v>10000021</v>
       </c>
       <c r="AC25" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="2:29">
@@ -3965,7 +3971,7 @@
         <v>30000013</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D26" s="3">
         <v>10000002</v>
@@ -4037,7 +4043,7 @@
         <v>10000022</v>
       </c>
       <c r="AC26" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="2:29">
@@ -4045,7 +4051,7 @@
         <v>30000014</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D27" s="3">
         <v>10000003</v>
@@ -4117,7 +4123,7 @@
         <v>10000023</v>
       </c>
       <c r="AC27" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="2:29">
@@ -4125,7 +4131,7 @@
         <v>30000015</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D28" s="3">
         <v>10000004</v>
@@ -4194,10 +4200,10 @@
         <v>0</v>
       </c>
       <c r="AB28" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AC28" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="2:29">
@@ -4205,7 +4211,7 @@
         <v>30000016</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D29" s="3">
         <v>10000005</v>
@@ -4271,7 +4277,7 @@
         <v>20000001</v>
       </c>
       <c r="AC29" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="2:29">
@@ -4279,7 +4285,7 @@
         <v>30000017</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D30" s="3">
         <v>10000006</v>
@@ -4312,7 +4318,7 @@
         <v>20000001</v>
       </c>
       <c r="AC30" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="2:29">
@@ -4320,7 +4326,7 @@
         <v>30000018</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D31" s="3">
         <v>10000007</v>
@@ -4389,10 +4395,10 @@
         <v>0</v>
       </c>
       <c r="AB31" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AC31" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -2881,7 +2881,7 @@
         <v>0</v>
       </c>
       <c r="O12" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P12" s="3">
         <v>5</v>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -700,7 +700,7 @@
     <t>守护天使</t>
   </si>
   <si>
-    <t>Skill_BuffFriendly</t>
+    <t>Skill_AddBuff</t>
   </si>
   <si>
     <t>10000003,10000004</t>
@@ -2905,7 +2905,7 @@
         <v>1</v>
       </c>
       <c r="W12" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="X12" s="3">
         <v>0</v>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -2905,7 +2905,7 @@
         <v>1</v>
       </c>
       <c r="W12" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X12" s="3">
         <v>0</v>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -122,7 +122,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K3" authorId="0">
+    <comment ref="J3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -145,7 +145,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L3" authorId="0">
+    <comment ref="K3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -175,7 +175,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M3" authorId="0">
+    <comment ref="L3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -197,7 +197,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N3" authorId="0">
+    <comment ref="M3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -223,7 +223,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q3" authorId="0">
+    <comment ref="P3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -245,7 +245,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R3" authorId="0">
+    <comment ref="Q3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -267,7 +267,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="0">
+    <comment ref="S3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -289,7 +289,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U3" authorId="0">
+    <comment ref="T3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -317,7 +317,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V3" authorId="0">
+    <comment ref="U3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -340,7 +340,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W3" authorId="0">
+    <comment ref="V3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -362,6 +362,29 @@
 球的范围
 范围类型为2：
 2个参数;X,Y 表示矩形的大小
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+对应配置表EffectConfig
 </t>
         </r>
       </text>
@@ -389,30 +412,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-对应配置表EffectConfig
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AB3" authorId="0">
+    <comment ref="AA3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="133">
   <si>
     <t>##var</t>
   </si>
@@ -469,9 +469,6 @@
     <t>GameObjectParameter</t>
   </si>
   <si>
-    <t>UnlockStar</t>
-  </si>
-  <si>
     <t>SkillType</t>
   </si>
   <si>
@@ -572,9 +569,6 @@
   </si>
   <si>
     <t>脚本参数</t>
-  </si>
-  <si>
-    <t>解锁星级</t>
   </si>
   <si>
     <t>技能类型</t>
@@ -1030,12 +1024,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1912,24 +1906,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AC31"/>
+  <dimension ref="A1:AB31"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.875" style="3" customWidth="1"/>
     <col min="2" max="7" width="17.875" style="3"/>
     <col min="8" max="8" width="20.375" style="3" customWidth="1"/>
     <col min="9" max="9" width="21.875" style="3" customWidth="1"/>
-    <col min="10" max="13" width="17.875" style="3"/>
-    <col min="14" max="14" width="19.125" style="3" customWidth="1"/>
-    <col min="15" max="23" width="17.875" style="3"/>
-    <col min="24" max="24" width="12.25" style="3" customWidth="1"/>
-    <col min="25" max="26" width="17.875" style="3"/>
-    <col min="27" max="28" width="20.375" style="3" customWidth="1"/>
-    <col min="29" max="29" width="100.625" style="3" customWidth="1"/>
-    <col min="30" max="16384" width="17.875" style="3"/>
+    <col min="10" max="12" width="17.875" style="3"/>
+    <col min="13" max="13" width="19.125" style="3" customWidth="1"/>
+    <col min="14" max="22" width="17.875" style="3"/>
+    <col min="23" max="23" width="12.25" style="3" customWidth="1"/>
+    <col min="24" max="25" width="17.875" style="3"/>
+    <col min="26" max="27" width="20.375" style="3" customWidth="1"/>
+    <col min="28" max="28" width="100.625" style="3" customWidth="1"/>
+    <col min="29" max="16384" width="17.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:29">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2014,194 +2008,185 @@
       <c r="AB1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="5" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:28">
+      <c r="A2" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:29">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="L2" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="M2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" s="5" t="s">
         <v>31</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>30</v>
       </c>
       <c r="O2" s="5" t="s">
         <v>32</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="R2" s="5" t="s">
         <v>30</v>
       </c>
       <c r="S2" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="T2" s="5" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="U2" s="5" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="V2" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="W2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="X2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z2" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA2" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB2" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="W2" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="X2" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA2" s="5" t="s">
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:28">
+      <c r="A3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AB2" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC2" s="5" t="s">
-        <v>31</v>
+      <c r="B3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="S3" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="T3" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="U3" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="V3" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="W3" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="X3" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y3" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA3" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB3" s="6" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:29">
-      <c r="A3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="P3" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q3" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="R3" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="S3" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="T3" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="U3" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="V3" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="W3" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="X3" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="Y3" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z3" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA3" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB3" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="AC3" s="6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="2:28">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="2:27">
       <c r="B4" s="3">
         <v>10000001</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D4" s="3">
         <v>10000001</v>
@@ -2216,14 +2201,14 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="3">
         <v>0</v>
@@ -2232,28 +2217,28 @@
         <v>0</v>
       </c>
       <c r="N4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P4" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="3">
-        <v>1</v>
-      </c>
-      <c r="R4" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="T4" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
+      </c>
+      <c r="T4" s="3">
+        <v>2</v>
       </c>
       <c r="U4" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V4" s="3">
         <v>0</v>
@@ -2262,27 +2247,24 @@
         <v>0</v>
       </c>
       <c r="X4" s="3">
-        <v>0</v>
+        <v>10000001</v>
       </c>
       <c r="Y4" s="3">
-        <v>10000001</v>
+        <v>20000001</v>
       </c>
       <c r="Z4" s="3">
-        <v>20000001</v>
+        <v>0</v>
       </c>
       <c r="AA4" s="3">
         <v>0</v>
       </c>
-      <c r="AB4" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="2:28">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="2:27">
       <c r="B5" s="3">
         <v>10000002</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D5" s="3">
         <v>10000002</v>
@@ -2297,14 +2279,14 @@
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="3">
         <v>0</v>
@@ -2313,57 +2295,54 @@
         <v>0</v>
       </c>
       <c r="N5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P5" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="3">
-        <v>1</v>
-      </c>
-      <c r="R5" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="T5" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
+      </c>
+      <c r="T5" s="3">
+        <v>2</v>
       </c>
       <c r="U5" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V5" s="3">
         <v>0</v>
       </c>
       <c r="W5" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X5" s="3">
-        <v>8</v>
+        <v>10000002</v>
       </c>
       <c r="Y5" s="3">
-        <v>10000002</v>
+        <v>20000001</v>
       </c>
       <c r="Z5" s="3">
-        <v>20000001</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="3">
         <v>0</v>
       </c>
-      <c r="AB5" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="2:28">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="2:27">
       <c r="B6" s="3">
         <v>10000003</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D6" s="3">
         <v>10000003</v>
@@ -2378,14 +2357,14 @@
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" s="3">
         <v>0</v>
@@ -2394,57 +2373,54 @@
         <v>0</v>
       </c>
       <c r="N6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P6" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="3">
-        <v>1</v>
-      </c>
-      <c r="R6" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="T6" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
+      </c>
+      <c r="T6" s="3">
+        <v>2</v>
       </c>
       <c r="U6" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V6" s="3">
         <v>0</v>
       </c>
       <c r="W6" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X6" s="3">
-        <v>8</v>
+        <v>10000003</v>
       </c>
       <c r="Y6" s="3">
-        <v>10000003</v>
+        <v>20000001</v>
       </c>
       <c r="Z6" s="3">
-        <v>20000001</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="3">
         <v>0</v>
       </c>
-      <c r="AB6" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="2:29">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="2:28">
       <c r="B7" s="3">
         <v>10000004</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D7" s="3">
         <v>10000004</v>
@@ -2459,14 +2435,14 @@
         <v>0</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" s="3">
         <v>0</v>
@@ -2475,60 +2451,57 @@
         <v>0</v>
       </c>
       <c r="N7" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O7" s="3">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="P7" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="3">
-        <v>1</v>
-      </c>
-      <c r="R7" s="3">
         <v>100</v>
       </c>
+      <c r="R7" s="3" t="s">
+        <v>64</v>
+      </c>
       <c r="S7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="T7" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
+      </c>
+      <c r="T7" s="3">
+        <v>1</v>
       </c>
       <c r="U7" s="3">
         <v>1</v>
       </c>
       <c r="V7" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W7" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X7" s="3">
-        <v>0</v>
+        <v>10000004</v>
       </c>
       <c r="Y7" s="3">
-        <v>10000004</v>
+        <v>20000001</v>
       </c>
       <c r="Z7" s="3">
-        <v>20000001</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="3">
         <v>0</v>
       </c>
-      <c r="AB7" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="3" t="s">
-        <v>75</v>
+      <c r="AB7" s="3" t="s">
+        <v>73</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="2:29">
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="2:28">
       <c r="B8" s="2">
         <v>20000001</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D8" s="3">
         <v>10000005</v>
@@ -2542,11 +2515,11 @@
       <c r="G8" s="2">
         <v>0</v>
       </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="J8" s="2">
+        <v>1</v>
       </c>
       <c r="K8" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="2">
         <v>0</v>
@@ -2555,60 +2528,57 @@
         <v>0</v>
       </c>
       <c r="N8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P8" s="2">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="Q8" s="2">
-        <v>3.5</v>
-      </c>
-      <c r="R8" s="2">
-        <v>0</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>67</v>
+        <v>0</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="T8" s="2">
+        <v>2</v>
       </c>
       <c r="U8" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V8" s="2">
         <v>0</v>
       </c>
-      <c r="W8" s="2">
-        <v>0</v>
-      </c>
-      <c r="X8" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="2">
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+      <c r="X8" s="2">
         <v>10000001</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="Y8" s="3">
         <v>20000001</v>
       </c>
+      <c r="Z8" s="2">
+        <v>0</v>
+      </c>
       <c r="AA8" s="2">
         <v>0</v>
       </c>
-      <c r="AB8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="2" t="s">
-        <v>77</v>
+      <c r="AB8" s="2" t="s">
+        <v>75</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="2:29">
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="2:28">
       <c r="B9" s="2">
         <v>20000002</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D9" s="3">
         <v>10000006</v>
@@ -2622,11 +2592,11 @@
       <c r="G9" s="2">
         <v>0</v>
       </c>
-      <c r="J9" s="3">
-        <v>0</v>
+      <c r="J9" s="2">
+        <v>1</v>
       </c>
       <c r="K9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" s="2">
         <v>0</v>
@@ -2635,60 +2605,57 @@
         <v>0</v>
       </c>
       <c r="N9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P9" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="2">
         <v>0</v>
       </c>
-      <c r="R9" s="2">
-        <v>0</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>67</v>
+      <c r="R9" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="T9" s="2">
+        <v>3</v>
       </c>
       <c r="U9" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V9" s="2">
         <v>0</v>
       </c>
-      <c r="W9" s="2">
-        <v>0</v>
-      </c>
-      <c r="X9" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="2">
+      <c r="W9" s="3">
+        <v>0</v>
+      </c>
+      <c r="X9" s="2">
         <v>10000001</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="Y9" s="3">
         <v>20000001</v>
       </c>
-      <c r="AA9" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB9" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="2" t="s">
-        <v>80</v>
+      <c r="Z9" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="2" t="s">
+        <v>78</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="2:29">
+    <row r="10" customHeight="1" spans="2:28">
       <c r="B10" s="3">
         <v>20000003</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D10" s="3">
         <v>10000007</v>
@@ -2703,10 +2670,10 @@
         <v>0</v>
       </c>
       <c r="J10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="3">
         <v>0</v>
@@ -2715,28 +2682,28 @@
         <v>0</v>
       </c>
       <c r="N10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P10" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="3">
-        <v>1</v>
-      </c>
-      <c r="R10" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="T10" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
+      </c>
+      <c r="T10" s="3">
+        <v>4</v>
       </c>
       <c r="U10" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V10" s="3">
         <v>0</v>
@@ -2745,30 +2712,27 @@
         <v>0</v>
       </c>
       <c r="X10" s="3">
-        <v>0</v>
+        <v>10000001</v>
       </c>
       <c r="Y10" s="3">
-        <v>10000001</v>
+        <v>20000001</v>
       </c>
       <c r="Z10" s="3">
-        <v>20000001</v>
+        <v>10000002</v>
       </c>
       <c r="AA10" s="3">
-        <v>10000002</v>
-      </c>
-      <c r="AB10" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="3" t="s">
-        <v>82</v>
+        <v>0</v>
+      </c>
+      <c r="AB10" s="3" t="s">
+        <v>80</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="2:29">
+    <row r="11" customHeight="1" spans="2:28">
       <c r="B11" s="3">
         <v>20000004</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D11" s="3">
         <v>10000001</v>
@@ -2783,10 +2747,10 @@
         <v>0</v>
       </c>
       <c r="J11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" s="3">
         <v>0</v>
@@ -2795,60 +2759,57 @@
         <v>0</v>
       </c>
       <c r="N11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P11" s="3">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="Q11" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="R11" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="R11" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="T11" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
+      </c>
+      <c r="T11" s="3">
+        <v>1</v>
       </c>
       <c r="U11" s="3">
         <v>1</v>
       </c>
       <c r="V11" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W11" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="X11" s="3">
-        <v>0</v>
+        <v>10000001</v>
       </c>
       <c r="Y11" s="3">
-        <v>10000001</v>
+        <v>20000001</v>
       </c>
       <c r="Z11" s="3">
-        <v>20000001</v>
+        <v>0</v>
       </c>
       <c r="AA11" s="3">
         <v>0</v>
       </c>
-      <c r="AB11" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="3" t="s">
-        <v>84</v>
+      <c r="AB11" s="3" t="s">
+        <v>82</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="2:29">
+    <row r="12" customHeight="1" spans="2:28">
       <c r="B12" s="3">
         <v>20000005</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D12" s="3">
         <v>10000002</v>
@@ -2863,13 +2824,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" s="3">
         <v>0</v>
@@ -2878,34 +2839,34 @@
         <v>0</v>
       </c>
       <c r="N12" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O12" s="3">
         <v>5</v>
       </c>
       <c r="P12" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="3">
         <v>0</v>
       </c>
-      <c r="R12" s="3">
-        <v>0</v>
+      <c r="R12" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="T12" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
+      </c>
+      <c r="T12" s="3">
+        <v>0</v>
       </c>
       <c r="U12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W12" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="X12" s="3">
         <v>0</v>
@@ -2916,22 +2877,19 @@
       <c r="Z12" s="3">
         <v>0</v>
       </c>
-      <c r="AA12" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="AC12" s="3" t="s">
-        <v>88</v>
+      <c r="AA12" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB12" s="3" t="s">
+        <v>86</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="2:29">
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="2:28">
       <c r="B13" s="2">
         <v>20000006</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D13" s="3">
         <v>10000003</v>
@@ -2945,11 +2903,11 @@
       <c r="G13" s="2">
         <v>0</v>
       </c>
-      <c r="J13" s="3">
-        <v>0</v>
+      <c r="J13" s="2">
+        <v>1</v>
       </c>
       <c r="K13" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" s="2">
         <v>0</v>
@@ -2958,25 +2916,25 @@
         <v>0</v>
       </c>
       <c r="N13" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P13" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="2">
         <v>0</v>
       </c>
-      <c r="R13" s="2">
-        <v>0</v>
-      </c>
-      <c r="S13" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="T13" s="2" t="s">
-        <v>74</v>
+      <c r="R13" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T13" s="2">
+        <v>0</v>
       </c>
       <c r="U13" s="2">
         <v>0</v>
@@ -2984,34 +2942,31 @@
       <c r="V13" s="2">
         <v>0</v>
       </c>
-      <c r="W13" s="2">
-        <v>0</v>
-      </c>
-      <c r="X13" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+      <c r="X13" s="2">
         <v>10000001</v>
       </c>
-      <c r="Z13" s="3">
+      <c r="Y13" s="3">
         <v>20000001</v>
       </c>
+      <c r="Z13" s="2">
+        <v>0</v>
+      </c>
       <c r="AA13" s="2">
         <v>0</v>
       </c>
-      <c r="AB13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="2" t="s">
-        <v>90</v>
+      <c r="AB13" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="2:29">
+    <row r="14" customHeight="1" spans="2:28">
       <c r="B14" s="3">
         <v>30000001</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D14" s="3">
         <v>10000004</v>
@@ -3026,72 +2981,69 @@
         <v>0</v>
       </c>
       <c r="J14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" s="3">
         <v>2</v>
       </c>
       <c r="L14" s="3">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="M14" s="3">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N14" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O14" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="P14" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W14" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X14" s="3">
-        <v>0</v>
+        <v>10000001</v>
       </c>
       <c r="Y14" s="3">
-        <v>10000001</v>
-      </c>
-      <c r="Z14" s="3">
         <v>20000001</v>
       </c>
-      <c r="AA14" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>93</v>
+      <c r="Z14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB14" s="3" t="s">
+        <v>91</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="2:29">
+    <row r="15" customHeight="1" spans="2:28">
       <c r="B15" s="3">
         <v>30000002</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D15" s="3">
         <v>10000005</v>
@@ -3106,72 +3058,69 @@
         <v>0</v>
       </c>
       <c r="J15" s="3">
+        <v>2</v>
+      </c>
+      <c r="K15" s="3">
+        <v>1</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0.17</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
         <v>3</v>
       </c>
-      <c r="K15" s="3">
-        <v>2</v>
-      </c>
-      <c r="L15" s="3">
-        <v>1</v>
-      </c>
-      <c r="M15" s="3">
-        <v>0.17</v>
-      </c>
-      <c r="N15" s="3">
-        <v>0</v>
-      </c>
       <c r="O15" s="3">
+        <v>2</v>
+      </c>
+      <c r="P15" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="T15" s="3">
+        <v>1</v>
+      </c>
+      <c r="U15" s="3">
+        <v>1</v>
+      </c>
+      <c r="V15" s="3">
         <v>3</v>
       </c>
-      <c r="P15" s="3">
-        <v>2</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="R15" s="3">
-        <v>0</v>
-      </c>
-      <c r="S15" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="T15" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="U15" s="3">
-        <v>1</v>
-      </c>
-      <c r="V15" s="3">
-        <v>1</v>
-      </c>
       <c r="W15" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X15" s="3">
-        <v>0</v>
+        <v>10000001</v>
       </c>
       <c r="Y15" s="3">
-        <v>10000001</v>
+        <v>20000001</v>
       </c>
       <c r="Z15" s="3">
-        <v>20000001</v>
+        <v>0</v>
       </c>
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-      <c r="AB15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="3" t="s">
-        <v>95</v>
+      <c r="AB15" s="3" t="s">
+        <v>93</v>
       </c>
     </row>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="2:29">
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="2:28">
       <c r="B16" s="2">
         <v>30000003</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D16" s="3">
         <v>10000006</v>
@@ -3185,73 +3134,70 @@
       <c r="G16" s="2">
         <v>0</v>
       </c>
-      <c r="J16" s="3">
-        <v>5</v>
+      <c r="J16" s="2">
+        <v>2</v>
       </c>
       <c r="K16" s="2">
         <v>2</v>
       </c>
       <c r="L16" s="2">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="M16" s="2">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N16" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O16" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="P16" s="2">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="Q16" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="R16" s="2">
-        <v>0</v>
-      </c>
-      <c r="S16" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="T16" s="2" t="s">
-        <v>67</v>
+        <v>0</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="T16" s="2">
+        <v>2</v>
       </c>
       <c r="U16" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2">
         <v>0</v>
       </c>
-      <c r="W16" s="2">
-        <v>0</v>
-      </c>
-      <c r="X16" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="2">
+      <c r="W16" s="3">
+        <v>0</v>
+      </c>
+      <c r="X16" s="2">
         <v>10000001</v>
       </c>
-      <c r="Z16" s="3">
+      <c r="Y16" s="3">
         <v>20000001</v>
       </c>
-      <c r="AA16" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="AC16" s="2" t="s">
-        <v>98</v>
+      <c r="Z16" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="AB16" s="2" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="2:29">
+    <row r="17" customHeight="1" spans="2:28">
       <c r="B17" s="3">
         <v>30000004</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D17" s="3">
         <v>10000007</v>
@@ -3266,72 +3212,69 @@
         <v>0</v>
       </c>
       <c r="J17" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K17" s="3">
         <v>2</v>
       </c>
       <c r="L17" s="3">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="M17" s="3">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N17" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O17" s="3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P17" s="3">
         <v>2</v>
       </c>
       <c r="Q17" s="3">
-        <v>2</v>
-      </c>
-      <c r="R17" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="T17" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
+      </c>
+      <c r="T17" s="3">
+        <v>1</v>
       </c>
       <c r="U17" s="3">
         <v>1</v>
       </c>
       <c r="V17" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W17" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X17" s="3">
-        <v>0</v>
+        <v>10000001</v>
       </c>
       <c r="Y17" s="3">
-        <v>10000001</v>
+        <v>20000001</v>
       </c>
       <c r="Z17" s="3">
-        <v>20000001</v>
+        <v>0</v>
       </c>
       <c r="AA17" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB17" s="3">
         <v>10000008</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>100</v>
+      <c r="AB17" s="3" t="s">
+        <v>98</v>
       </c>
     </row>
-    <row r="18" s="2" customFormat="1" customHeight="1" spans="2:29">
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="2:28">
       <c r="B18" s="2">
         <v>30000005</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D18" s="2">
         <v>10000001</v>
@@ -3346,72 +3289,69 @@
         <v>0</v>
       </c>
       <c r="J18" s="2">
+        <v>2</v>
+      </c>
+      <c r="K18" s="2">
+        <v>2</v>
+      </c>
+      <c r="L18" s="2">
+        <v>1</v>
+      </c>
+      <c r="M18" s="2">
+        <v>0</v>
+      </c>
+      <c r="N18" s="2">
+        <v>0</v>
+      </c>
+      <c r="O18" s="2">
         <v>3</v>
       </c>
-      <c r="K18" s="2">
-        <v>2</v>
-      </c>
-      <c r="L18" s="2">
-        <v>2</v>
-      </c>
-      <c r="M18" s="2">
-        <v>1</v>
-      </c>
-      <c r="N18" s="2">
-        <v>0</v>
-      </c>
-      <c r="O18" s="2">
-        <v>0</v>
-      </c>
       <c r="P18" s="2">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="Q18" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="R18" s="2">
-        <v>0</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="T18" s="2" t="s">
-        <v>67</v>
+        <v>0</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="T18" s="2">
+        <v>1</v>
       </c>
       <c r="U18" s="2">
         <v>1</v>
       </c>
       <c r="V18" s="2">
-        <v>1</v>
-      </c>
-      <c r="W18" s="2">
-        <v>2</v>
-      </c>
-      <c r="X18" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="2">
+        <v>2</v>
+      </c>
+      <c r="W18" s="3">
+        <v>0</v>
+      </c>
+      <c r="X18" s="2">
         <v>10000001</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="Y18" s="3">
         <v>20000001</v>
       </c>
+      <c r="Z18" s="2">
+        <v>0</v>
+      </c>
       <c r="AA18" s="2">
         <v>0</v>
       </c>
-      <c r="AB18" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC18" s="2" t="s">
-        <v>102</v>
+      <c r="AB18" s="2" t="s">
+        <v>100</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="2:29">
+    <row r="19" customHeight="1" spans="2:28">
       <c r="B19" s="3">
         <v>30000006</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D19" s="2">
         <v>10000002</v>
@@ -3425,41 +3365,41 @@
       <c r="G19" s="3">
         <v>0</v>
       </c>
-      <c r="J19" s="2">
+      <c r="J19" s="3">
+        <v>2</v>
+      </c>
+      <c r="K19" s="3">
+        <v>1</v>
+      </c>
+      <c r="L19" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="M19" s="3">
+        <v>0</v>
+      </c>
+      <c r="N19" s="3">
+        <v>10</v>
+      </c>
+      <c r="O19" s="3">
         <v>5</v>
       </c>
-      <c r="K19" s="3">
-        <v>2</v>
-      </c>
-      <c r="L19" s="3">
-        <v>1</v>
-      </c>
-      <c r="M19" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="N19" s="3">
-        <v>0</v>
-      </c>
-      <c r="O19" s="3">
-        <v>10</v>
-      </c>
       <c r="P19" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="3">
         <v>0</v>
       </c>
-      <c r="R19" s="3">
-        <v>0</v>
+      <c r="R19" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="T19" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
+      </c>
+      <c r="T19" s="3">
+        <v>3</v>
       </c>
       <c r="U19" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V19" s="3">
         <v>0</v>
@@ -3468,30 +3408,27 @@
         <v>0</v>
       </c>
       <c r="X19" s="3">
-        <v>0</v>
+        <v>10000001</v>
       </c>
       <c r="Y19" s="3">
-        <v>10000001</v>
+        <v>20000001</v>
       </c>
       <c r="Z19" s="3">
-        <v>20000001</v>
-      </c>
-      <c r="AA19" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB19" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC19" s="3" t="s">
-        <v>105</v>
+        <v>0</v>
+      </c>
+      <c r="AA19" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="AB19" s="3" t="s">
+        <v>103</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="2:29">
+    <row r="20" customHeight="1" spans="2:28">
       <c r="B20" s="3">
         <v>30000007</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D20" s="2">
         <v>10000003</v>
@@ -3505,73 +3442,70 @@
       <c r="G20" s="3">
         <v>0</v>
       </c>
-      <c r="J20" s="2">
-        <v>1</v>
+      <c r="J20" s="3">
+        <v>2</v>
       </c>
       <c r="K20" s="3">
         <v>2</v>
       </c>
       <c r="L20" s="3">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="M20" s="3">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N20" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O20" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="P20" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
+        <v>1</v>
+      </c>
+      <c r="V20" s="3">
         <v>3</v>
       </c>
-      <c r="Q20" s="3">
-        <v>1</v>
-      </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="T20" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-      <c r="V20" s="3">
-        <v>1</v>
-      </c>
       <c r="W20" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X20" s="3">
-        <v>0</v>
+        <v>10000001</v>
       </c>
       <c r="Y20" s="3">
-        <v>10000001</v>
+        <v>20000001</v>
       </c>
       <c r="Z20" s="3">
-        <v>20000001</v>
+        <v>0</v>
       </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC20" s="3" t="s">
-        <v>107</v>
+      <c r="AB20" s="3" t="s">
+        <v>105</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="2:29">
+    <row r="21" customHeight="1" spans="2:28">
       <c r="B21" s="3">
         <v>30000008</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D21" s="2">
         <v>10000004</v>
@@ -3585,73 +3519,70 @@
       <c r="G21" s="3">
         <v>0</v>
       </c>
-      <c r="J21" s="2">
+      <c r="J21" s="3">
+        <v>2</v>
+      </c>
+      <c r="K21" s="3">
         <v>3</v>
       </c>
-      <c r="K21" s="3">
-        <v>2</v>
-      </c>
       <c r="L21" s="3">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="M21" s="3">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N21" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O21" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="P21" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="3">
         <v>0</v>
       </c>
-      <c r="R21" s="3">
-        <v>0</v>
+      <c r="R21" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
+      </c>
+      <c r="T21" s="3">
+        <v>1</v>
       </c>
       <c r="U21" s="3">
         <v>1</v>
       </c>
       <c r="V21" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W21" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X21" s="3">
-        <v>0</v>
+        <v>10000001</v>
       </c>
       <c r="Y21" s="3">
-        <v>10000001</v>
+        <v>20000001</v>
       </c>
       <c r="Z21" s="3">
-        <v>20000001</v>
+        <v>0</v>
       </c>
       <c r="AA21" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB21" s="3">
         <v>10000014</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>109</v>
+      <c r="AB21" s="3" t="s">
+        <v>107</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="2:29">
+    <row r="22" customHeight="1" spans="2:28">
       <c r="B22" s="3">
         <v>30000009</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D22" s="2">
         <v>10000005</v>
@@ -3665,41 +3596,41 @@
       <c r="G22" s="3">
         <v>0</v>
       </c>
-      <c r="J22" s="2">
-        <v>5</v>
+      <c r="J22" s="3">
+        <v>2</v>
       </c>
       <c r="K22" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L22" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M22" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
       <c r="O22" s="3">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="P22" s="3">
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="R22" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
+      </c>
+      <c r="T22" s="3">
+        <v>3</v>
       </c>
       <c r="U22" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
@@ -3708,30 +3639,27 @@
         <v>0</v>
       </c>
       <c r="X22" s="3">
-        <v>0</v>
+        <v>10000001</v>
       </c>
       <c r="Y22" s="3">
-        <v>10000001</v>
-      </c>
-      <c r="Z22" s="3">
         <v>20000001</v>
       </c>
-      <c r="AA22" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="3" t="s">
-        <v>112</v>
+      <c r="Z22" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="3" t="s">
+        <v>110</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="2:29">
+    <row r="23" customHeight="1" spans="2:28">
       <c r="B23" s="3">
         <v>30000010</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D23" s="2">
         <v>10000006</v>
@@ -3745,73 +3673,70 @@
       <c r="G23" s="3">
         <v>0</v>
       </c>
-      <c r="J23" s="2">
-        <v>1</v>
+      <c r="J23" s="3">
+        <v>2</v>
       </c>
       <c r="K23" s="3">
         <v>2</v>
       </c>
       <c r="L23" s="3">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="M23" s="3">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N23" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O23" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="P23" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q23" s="3">
-        <v>2</v>
-      </c>
-      <c r="R23" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="T23" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
+      </c>
+      <c r="T23" s="3">
+        <v>1</v>
       </c>
       <c r="U23" s="3">
         <v>1</v>
       </c>
       <c r="V23" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W23" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X23" s="3">
-        <v>0</v>
+        <v>10000001</v>
       </c>
       <c r="Y23" s="3">
-        <v>10000001</v>
+        <v>20000001</v>
       </c>
       <c r="Z23" s="3">
-        <v>20000001</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB23" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="AC23" s="3" t="s">
-        <v>115</v>
+        <v>0</v>
+      </c>
+      <c r="AA23" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="AB23" s="3" t="s">
+        <v>113</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="2:29">
+    <row r="24" customHeight="1" spans="2:28">
       <c r="B24" s="3">
         <v>30000011</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D24" s="2">
         <v>10000007</v>
@@ -3825,41 +3750,41 @@
       <c r="G24" s="3">
         <v>0</v>
       </c>
-      <c r="J24" s="2">
+      <c r="J24" s="3">
+        <v>2</v>
+      </c>
+      <c r="K24" s="3">
+        <v>2</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
+        <v>10</v>
+      </c>
+      <c r="O24" s="3">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>2</v>
-      </c>
-      <c r="L24" s="3">
-        <v>2</v>
-      </c>
-      <c r="M24" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
-      <c r="O24" s="3">
-        <v>10</v>
-      </c>
       <c r="P24" s="3">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="Q24" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="R24" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="T24" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
+      </c>
+      <c r="T24" s="3">
+        <v>2</v>
       </c>
       <c r="U24" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V24" s="3">
         <v>0</v>
@@ -3868,30 +3793,27 @@
         <v>0</v>
       </c>
       <c r="X24" s="3">
-        <v>0</v>
+        <v>10000001</v>
       </c>
       <c r="Y24" s="3">
-        <v>10000001</v>
+        <v>20000001</v>
       </c>
       <c r="Z24" s="3">
-        <v>20000001</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB24" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="AC24" s="3" t="s">
-        <v>118</v>
+        <v>0</v>
+      </c>
+      <c r="AA24" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="AB24" s="3" t="s">
+        <v>116</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="2:29">
+    <row r="25" customHeight="1" spans="2:28">
       <c r="B25" s="3">
         <v>30000012</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D25" s="3">
         <v>10000001</v>
@@ -3906,40 +3828,40 @@
         <v>0</v>
       </c>
       <c r="J25" s="3">
+        <v>2</v>
+      </c>
+      <c r="K25" s="3">
+        <v>4</v>
+      </c>
+      <c r="L25" s="3">
+        <v>1</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3">
+        <v>3600</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S25" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="T25" s="3">
         <v>5</v>
       </c>
-      <c r="K25" s="3">
-        <v>2</v>
-      </c>
-      <c r="L25" s="3">
-        <v>4</v>
-      </c>
-      <c r="M25" s="3">
-        <v>1</v>
-      </c>
-      <c r="N25" s="3">
-        <v>0</v>
-      </c>
-      <c r="O25" s="3">
-        <v>0</v>
-      </c>
-      <c r="P25" s="3">
-        <v>3600</v>
-      </c>
-      <c r="Q25" s="3">
-        <v>0</v>
-      </c>
-      <c r="R25" s="3">
-        <v>0</v>
-      </c>
-      <c r="S25" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="T25" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="U25" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V25" s="3">
         <v>0</v>
@@ -3948,30 +3870,27 @@
         <v>0</v>
       </c>
       <c r="X25" s="3">
-        <v>0</v>
+        <v>10000001</v>
       </c>
       <c r="Y25" s="3">
-        <v>10000001</v>
+        <v>20000001</v>
       </c>
       <c r="Z25" s="3">
-        <v>20000001</v>
+        <v>0</v>
       </c>
       <c r="AA25" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB25" s="3">
         <v>10000021</v>
       </c>
-      <c r="AC25" s="3" t="s">
-        <v>120</v>
+      <c r="AB25" s="3" t="s">
+        <v>118</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="2:29">
+    <row r="26" customHeight="1" spans="2:28">
       <c r="B26" s="3">
         <v>30000013</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D26" s="3">
         <v>10000002</v>
@@ -3986,72 +3905,69 @@
         <v>0</v>
       </c>
       <c r="J26" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K26" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L26" s="3">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="M26" s="3">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="N26" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O26" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="P26" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>0</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="T26" s="3">
+        <v>1</v>
+      </c>
+      <c r="U26" s="3">
+        <v>1</v>
+      </c>
+      <c r="V26" s="3">
         <v>3</v>
       </c>
-      <c r="Q26" s="3">
-        <v>1</v>
-      </c>
-      <c r="R26" s="3">
-        <v>0</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="T26" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="U26" s="3">
-        <v>1</v>
-      </c>
-      <c r="V26" s="3">
-        <v>1</v>
-      </c>
       <c r="W26" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X26" s="3">
-        <v>0</v>
+        <v>10000001</v>
       </c>
       <c r="Y26" s="3">
-        <v>10000001</v>
+        <v>20000001</v>
       </c>
       <c r="Z26" s="3">
-        <v>20000001</v>
+        <v>0</v>
       </c>
       <c r="AA26" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB26" s="3">
         <v>10000022</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>122</v>
+      <c r="AB26" s="3" t="s">
+        <v>120</v>
       </c>
     </row>
-    <row r="27" customHeight="1" spans="2:29">
+    <row r="27" customHeight="1" spans="2:28">
       <c r="B27" s="3">
         <v>30000014</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D27" s="3">
         <v>10000003</v>
@@ -4066,40 +3982,40 @@
         <v>0</v>
       </c>
       <c r="J27" s="3">
+        <v>2</v>
+      </c>
+      <c r="K27" s="3">
+        <v>5</v>
+      </c>
+      <c r="L27" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="M27" s="3">
+        <v>0</v>
+      </c>
+      <c r="N27" s="3">
+        <v>10</v>
+      </c>
+      <c r="O27" s="3">
         <v>3</v>
       </c>
-      <c r="K27" s="3">
-        <v>2</v>
-      </c>
-      <c r="L27" s="3">
-        <v>5</v>
-      </c>
-      <c r="M27" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="N27" s="3">
-        <v>0</v>
-      </c>
-      <c r="O27" s="3">
-        <v>10</v>
-      </c>
       <c r="P27" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q27" s="3">
         <v>0</v>
       </c>
-      <c r="R27" s="3">
-        <v>0</v>
+      <c r="R27" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="T27" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
+      </c>
+      <c r="T27" s="3">
+        <v>2</v>
       </c>
       <c r="U27" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V27" s="3">
         <v>0</v>
@@ -4108,30 +4024,27 @@
         <v>0</v>
       </c>
       <c r="X27" s="3">
-        <v>0</v>
+        <v>10000001</v>
       </c>
       <c r="Y27" s="3">
-        <v>10000001</v>
+        <v>20000001</v>
       </c>
       <c r="Z27" s="3">
-        <v>20000001</v>
+        <v>0</v>
       </c>
       <c r="AA27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB27" s="3">
         <v>10000023</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>124</v>
+      <c r="AB27" s="3" t="s">
+        <v>122</v>
       </c>
     </row>
-    <row r="28" customHeight="1" spans="2:29">
+    <row r="28" customHeight="1" spans="2:28">
       <c r="B28" s="3">
         <v>30000015</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D28" s="3">
         <v>10000004</v>
@@ -4146,72 +4059,69 @@
         <v>0</v>
       </c>
       <c r="J28" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K28" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L28" s="3">
+        <v>1</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>3600</v>
+      </c>
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S28" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+      <c r="U28" s="3">
+        <v>1</v>
+      </c>
+      <c r="V28" s="3">
         <v>4</v>
       </c>
-      <c r="M28" s="3">
-        <v>1</v>
-      </c>
-      <c r="N28" s="3">
-        <v>0</v>
-      </c>
-      <c r="O28" s="3">
-        <v>0</v>
-      </c>
-      <c r="P28" s="3">
-        <v>3600</v>
-      </c>
-      <c r="Q28" s="3">
-        <v>0</v>
-      </c>
-      <c r="R28" s="3">
-        <v>0</v>
-      </c>
-      <c r="S28" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="T28" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="U28" s="3">
-        <v>0</v>
-      </c>
-      <c r="V28" s="3">
-        <v>1</v>
-      </c>
       <c r="W28" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X28" s="3">
-        <v>0</v>
+        <v>10000001</v>
       </c>
       <c r="Y28" s="3">
-        <v>10000001</v>
+        <v>20000001</v>
       </c>
       <c r="Z28" s="3">
-        <v>20000001</v>
-      </c>
-      <c r="AA28" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB28" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="AC28" s="3" t="s">
-        <v>127</v>
+        <v>0</v>
+      </c>
+      <c r="AA28" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="AB28" s="3" t="s">
+        <v>125</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="2:29">
+    <row r="29" customHeight="1" spans="2:28">
       <c r="B29" s="3">
         <v>30000016</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D29" s="3">
         <v>10000005</v>
@@ -4226,40 +4136,40 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K29" s="3">
         <v>2</v>
       </c>
       <c r="L29" s="3">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="M29" s="3">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N29" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O29" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="P29" s="3">
-        <v>5</v>
+        <v>0.1</v>
       </c>
       <c r="Q29" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="S29" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
+      </c>
+      <c r="T29" s="3">
+        <v>6</v>
       </c>
       <c r="U29" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V29" s="3">
         <v>0</v>
@@ -4268,24 +4178,21 @@
         <v>0</v>
       </c>
       <c r="X29" s="3">
-        <v>0</v>
+        <v>10000001</v>
       </c>
       <c r="Y29" s="3">
-        <v>10000001</v>
-      </c>
-      <c r="Z29" s="3">
         <v>20000001</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>129</v>
+      <c r="AB29" s="3" t="s">
+        <v>127</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="2:29">
+    <row r="30" customHeight="1" spans="2:28">
       <c r="B30" s="3">
         <v>30000017</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D30" s="3">
         <v>10000006</v>
@@ -4299,34 +4206,31 @@
       <c r="G30" s="3">
         <v>0</v>
       </c>
-      <c r="J30" s="3">
-        <v>3</v>
+      <c r="N30" s="3">
+        <v>10</v>
       </c>
       <c r="O30" s="3">
-        <v>10</v>
-      </c>
-      <c r="P30" s="3">
         <v>5</v>
       </c>
-      <c r="S30" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="X30" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z30" s="3">
+      <c r="R30" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
         <v>20000001</v>
       </c>
-      <c r="AC30" s="3" t="s">
-        <v>131</v>
+      <c r="AB30" s="3" t="s">
+        <v>129</v>
       </c>
     </row>
-    <row r="31" customHeight="1" spans="2:29">
+    <row r="31" customHeight="1" spans="2:28">
       <c r="B31" s="3">
         <v>30000018</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D31" s="3">
         <v>10000007</v>
@@ -4341,64 +4245,61 @@
         <v>0</v>
       </c>
       <c r="J31" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K31" s="3">
         <v>2</v>
       </c>
       <c r="L31" s="3">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="M31" s="3">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N31" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O31" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="P31" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3">
-        <v>0</v>
+      <c r="R31" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="T31" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
+      </c>
+      <c r="T31" s="3">
+        <v>1</v>
       </c>
       <c r="U31" s="3">
         <v>1</v>
       </c>
       <c r="V31" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W31" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X31" s="3">
-        <v>0</v>
+        <v>10000001</v>
       </c>
       <c r="Y31" s="3">
-        <v>10000001</v>
+        <v>20000001</v>
       </c>
       <c r="Z31" s="3">
-        <v>20000001</v>
-      </c>
-      <c r="AA31" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB31" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="AC31" s="3" t="s">
-        <v>134</v>
+        <v>0</v>
+      </c>
+      <c r="AA31" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="AB31" s="3" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -1024,7 +1024,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1035,7 +1035,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -2050,7 +2050,7 @@
         <v>29</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O2" s="5" t="s">
         <v>32</v>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="134">
   <si>
     <t>##var</t>
   </si>
@@ -535,13 +535,16 @@
     <t>string</t>
   </si>
   <si>
+    <t>(array#sep=,),PassiveSkillType</t>
+  </si>
+  <si>
+    <t>(array#sep=,),float</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
     <t>double</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>(array#sep=,),float</t>
   </si>
   <si>
     <t>(array#sep=,),int</t>
@@ -1024,13 +1027,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <b/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
+      <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1913,7 +1916,9 @@
     <col min="2" max="7" width="17.875" style="3"/>
     <col min="8" max="8" width="20.375" style="3" customWidth="1"/>
     <col min="9" max="9" width="21.875" style="3" customWidth="1"/>
-    <col min="10" max="12" width="17.875" style="3"/>
+    <col min="10" max="10" width="17.875" style="3"/>
+    <col min="11" max="11" width="22.75" style="3" customWidth="1"/>
+    <col min="12" max="12" width="17.875" style="3"/>
     <col min="13" max="13" width="19.125" style="3" customWidth="1"/>
     <col min="14" max="22" width="17.875" style="3"/>
     <col min="23" max="23" width="12.25" style="3" customWidth="1"/>
@@ -2023,10 +2028,10 @@
         <v>30</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>29</v>
@@ -2038,25 +2043,25 @@
         <v>30</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M2" s="5" t="s">
         <v>29</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="Q2" s="5" t="s">
         <v>29</v>
@@ -2074,10 +2079,10 @@
         <v>29</v>
       </c>
       <c r="V2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="W2" s="5" t="s">
         <v>33</v>
-      </c>
-      <c r="W2" s="5" t="s">
-        <v>32</v>
       </c>
       <c r="X2" s="5" t="s">
         <v>29</v>
@@ -2086,10 +2091,10 @@
         <v>29</v>
       </c>
       <c r="Z2" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AA2" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AB2" s="5" t="s">
         <v>30</v>
@@ -2097,88 +2102,88 @@
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A3" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T3" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="U3" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="V3" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="W3" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="X3" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Y3" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Z3" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AA3" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AB3" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="2:27">
@@ -2186,7 +2191,7 @@
         <v>10000001</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D4" s="3">
         <v>10000001</v>
@@ -2201,7 +2206,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3">
@@ -2229,10 +2234,10 @@
         <v>0</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T4" s="3">
         <v>2</v>
@@ -2264,7 +2269,7 @@
         <v>10000002</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D5" s="3">
         <v>10000002</v>
@@ -2279,7 +2284,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3">
@@ -2307,10 +2312,10 @@
         <v>0</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="T5" s="3">
         <v>2</v>
@@ -2342,7 +2347,7 @@
         <v>10000003</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D6" s="3">
         <v>10000003</v>
@@ -2357,7 +2362,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3">
@@ -2385,10 +2390,10 @@
         <v>0</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="T6" s="3">
         <v>2</v>
@@ -2420,7 +2425,7 @@
         <v>10000004</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D7" s="3">
         <v>10000004</v>
@@ -2435,7 +2440,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3">
@@ -2463,10 +2468,10 @@
         <v>100</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T7" s="3">
         <v>1</v>
@@ -2493,7 +2498,7 @@
         <v>0</v>
       </c>
       <c r="AB7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="2:28">
@@ -2501,7 +2506,7 @@
         <v>20000001</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D8" s="3">
         <v>10000005</v>
@@ -2540,10 +2545,10 @@
         <v>0</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T8" s="2">
         <v>2</v>
@@ -2570,7 +2575,7 @@
         <v>0</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="2:28">
@@ -2578,7 +2583,7 @@
         <v>20000002</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D9" s="3">
         <v>10000006</v>
@@ -2617,10 +2622,10 @@
         <v>0</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T9" s="2">
         <v>3</v>
@@ -2641,13 +2646,13 @@
         <v>20000001</v>
       </c>
       <c r="Z9" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA9" s="2">
         <v>0</v>
       </c>
       <c r="AB9" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="2:28">
@@ -2655,7 +2660,7 @@
         <v>20000003</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D10" s="3">
         <v>10000007</v>
@@ -2694,10 +2699,10 @@
         <v>0</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T10" s="3">
         <v>4</v>
@@ -2724,7 +2729,7 @@
         <v>0</v>
       </c>
       <c r="AB10" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="2:28">
@@ -2732,7 +2737,7 @@
         <v>20000004</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D11" s="3">
         <v>10000001</v>
@@ -2771,10 +2776,10 @@
         <v>0</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T11" s="3">
         <v>1</v>
@@ -2801,7 +2806,7 @@
         <v>0</v>
       </c>
       <c r="AB11" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="2:28">
@@ -2809,7 +2814,7 @@
         <v>20000005</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D12" s="3">
         <v>10000002</v>
@@ -2824,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J12" s="3">
         <v>1</v>
@@ -2851,10 +2856,10 @@
         <v>0</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T12" s="3">
         <v>0</v>
@@ -2878,10 +2883,10 @@
         <v>0</v>
       </c>
       <c r="AA12" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AB12" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="2:28">
@@ -2889,7 +2894,7 @@
         <v>20000006</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D13" s="3">
         <v>10000003</v>
@@ -2928,10 +2933,10 @@
         <v>0</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T13" s="2">
         <v>0</v>
@@ -2958,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="AB13" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="2:28">
@@ -2966,7 +2971,7 @@
         <v>30000001</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D14" s="3">
         <v>10000004</v>
@@ -3005,10 +3010,10 @@
         <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -3032,10 +3037,10 @@
         <v>0</v>
       </c>
       <c r="AA14" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AB14" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="2:28">
@@ -3043,7 +3048,7 @@
         <v>30000002</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D15" s="3">
         <v>10000005</v>
@@ -3082,10 +3087,10 @@
         <v>0</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T15" s="3">
         <v>1</v>
@@ -3112,7 +3117,7 @@
         <v>0</v>
       </c>
       <c r="AB15" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="2:28">
@@ -3120,7 +3125,7 @@
         <v>30000003</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D16" s="3">
         <v>10000006</v>
@@ -3159,10 +3164,10 @@
         <v>0</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T16" s="2">
         <v>2</v>
@@ -3186,10 +3191,10 @@
         <v>0</v>
       </c>
       <c r="AA16" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AB16" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="2:28">
@@ -3197,7 +3202,7 @@
         <v>30000004</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D17" s="3">
         <v>10000007</v>
@@ -3236,10 +3241,10 @@
         <v>0</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T17" s="3">
         <v>1</v>
@@ -3266,7 +3271,7 @@
         <v>10000008</v>
       </c>
       <c r="AB17" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="2:28">
@@ -3274,7 +3279,7 @@
         <v>30000005</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D18" s="2">
         <v>10000001</v>
@@ -3313,10 +3318,10 @@
         <v>0</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T18" s="2">
         <v>1</v>
@@ -3343,7 +3348,7 @@
         <v>0</v>
       </c>
       <c r="AB18" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="2:28">
@@ -3351,7 +3356,7 @@
         <v>30000006</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D19" s="2">
         <v>10000002</v>
@@ -3390,10 +3395,10 @@
         <v>0</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T19" s="3">
         <v>3</v>
@@ -3417,10 +3422,10 @@
         <v>0</v>
       </c>
       <c r="AA19" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AB19" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="2:28">
@@ -3428,7 +3433,7 @@
         <v>30000007</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D20" s="2">
         <v>10000003</v>
@@ -3467,10 +3472,10 @@
         <v>0</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T20" s="3">
         <v>0</v>
@@ -3497,7 +3502,7 @@
         <v>0</v>
       </c>
       <c r="AB20" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="2:28">
@@ -3505,7 +3510,7 @@
         <v>30000008</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D21" s="2">
         <v>10000004</v>
@@ -3544,10 +3549,10 @@
         <v>0</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T21" s="3">
         <v>1</v>
@@ -3574,7 +3579,7 @@
         <v>10000014</v>
       </c>
       <c r="AB21" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="2:28">
@@ -3582,7 +3587,7 @@
         <v>30000009</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D22" s="2">
         <v>10000005</v>
@@ -3621,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T22" s="3">
         <v>3</v>
@@ -3645,13 +3650,13 @@
         <v>20000001</v>
       </c>
       <c r="Z22" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AA22" s="3">
         <v>0</v>
       </c>
       <c r="AB22" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="2:28">
@@ -3659,7 +3664,7 @@
         <v>30000010</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D23" s="2">
         <v>10000006</v>
@@ -3698,10 +3703,10 @@
         <v>0</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T23" s="3">
         <v>1</v>
@@ -3725,10 +3730,10 @@
         <v>0</v>
       </c>
       <c r="AA23" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AB23" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="2:28">
@@ -3736,7 +3741,7 @@
         <v>30000011</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D24" s="2">
         <v>10000007</v>
@@ -3775,10 +3780,10 @@
         <v>0</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T24" s="3">
         <v>2</v>
@@ -3802,10 +3807,10 @@
         <v>0</v>
       </c>
       <c r="AA24" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AB24" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="2:28">
@@ -3813,7 +3818,7 @@
         <v>30000012</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D25" s="3">
         <v>10000001</v>
@@ -3852,10 +3857,10 @@
         <v>0</v>
       </c>
       <c r="R25" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S25" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T25" s="3">
         <v>5</v>
@@ -3882,7 +3887,7 @@
         <v>10000021</v>
       </c>
       <c r="AB25" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="2:28">
@@ -3890,7 +3895,7 @@
         <v>30000013</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D26" s="3">
         <v>10000002</v>
@@ -3929,10 +3934,10 @@
         <v>0</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T26" s="3">
         <v>1</v>
@@ -3959,7 +3964,7 @@
         <v>10000022</v>
       </c>
       <c r="AB26" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="2:28">
@@ -3967,7 +3972,7 @@
         <v>30000014</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D27" s="3">
         <v>10000003</v>
@@ -4006,10 +4011,10 @@
         <v>0</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T27" s="3">
         <v>2</v>
@@ -4036,7 +4041,7 @@
         <v>10000023</v>
       </c>
       <c r="AB27" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="2:28">
@@ -4044,7 +4049,7 @@
         <v>30000015</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D28" s="3">
         <v>10000004</v>
@@ -4083,10 +4088,10 @@
         <v>0</v>
       </c>
       <c r="R28" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T28" s="3">
         <v>0</v>
@@ -4110,10 +4115,10 @@
         <v>0</v>
       </c>
       <c r="AA28" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AB28" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="2:28">
@@ -4121,7 +4126,7 @@
         <v>30000016</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D29" s="3">
         <v>10000005</v>
@@ -4160,10 +4165,10 @@
         <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S29" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T29" s="3">
         <v>6</v>
@@ -4184,7 +4189,7 @@
         <v>20000001</v>
       </c>
       <c r="AB29" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="2:28">
@@ -4192,7 +4197,7 @@
         <v>30000017</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D30" s="3">
         <v>10000006</v>
@@ -4213,7 +4218,7 @@
         <v>5</v>
       </c>
       <c r="R30" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="W30" s="3">
         <v>0</v>
@@ -4222,7 +4227,7 @@
         <v>20000001</v>
       </c>
       <c r="AB30" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="2:28">
@@ -4230,7 +4235,7 @@
         <v>30000018</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D31" s="3">
         <v>10000007</v>
@@ -4269,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="R31" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T31" s="3">
         <v>1</v>
@@ -4296,10 +4301,10 @@
         <v>0</v>
       </c>
       <c r="AA31" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AB31" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -472,7 +472,7 @@
     <t>SkillType</t>
   </si>
   <si>
-    <t>PassiveSkillType</t>
+    <t>SkillPassiveType</t>
   </si>
   <si>
     <t>PassiveSkillPro</t>
@@ -535,7 +535,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>(array#sep=,),PassiveSkillType</t>
+    <t>(array#sep=,),SkillPassiveType</t>
   </si>
   <si>
     <t>(array#sep=,),float</t>
@@ -1917,7 +1917,7 @@
     <col min="8" max="8" width="20.375" style="3" customWidth="1"/>
     <col min="9" max="9" width="21.875" style="3" customWidth="1"/>
     <col min="10" max="10" width="17.875" style="3"/>
-    <col min="11" max="11" width="22.75" style="3" customWidth="1"/>
+    <col min="11" max="11" width="30.375" style="3" customWidth="1"/>
     <col min="12" max="12" width="17.875" style="3"/>
     <col min="13" max="13" width="19.125" style="3" customWidth="1"/>
     <col min="14" max="22" width="17.875" style="3"/>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="134">
   <si>
     <t>##var</t>
   </si>
@@ -1027,13 +1027,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
+      <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
+      <b/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -2985,6 +2985,7 @@
       <c r="G14" s="3">
         <v>0</v>
       </c>
+      <c r="H14" s="3"/>
       <c r="J14" s="3">
         <v>2</v>
       </c>
@@ -3062,6 +3063,9 @@
       <c r="G15" s="3">
         <v>0</v>
       </c>
+      <c r="H15" s="3" t="s">
+        <v>72</v>
+      </c>
       <c r="J15" s="3">
         <v>2</v>
       </c>
@@ -3105,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="X15" s="3">
-        <v>10000001</v>
+        <v>10000006</v>
       </c>
       <c r="Y15" s="3">
         <v>20000001</v>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -1027,11 +1027,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -1039,6 +1034,11 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -2985,7 +2985,6 @@
       <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="3"/>
       <c r="J14" s="3">
         <v>2</v>
       </c>
@@ -3097,7 +3096,7 @@
         <v>66</v>
       </c>
       <c r="T15" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U15" s="3">
         <v>1</v>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12795"/>
+    <workbookView windowWidth="27945" windowHeight="12960"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="134">
   <si>
     <t>##var</t>
   </si>
@@ -676,6 +676,9 @@
     <t>神之力量</t>
   </si>
   <si>
+    <t>Skill_AddBuff</t>
+  </si>
+  <si>
     <t>10000006,10000012</t>
   </si>
   <si>
@@ -695,9 +698,6 @@
   </si>
   <si>
     <t>守护天使</t>
-  </si>
-  <si>
-    <t>Skill_AddBuff</t>
   </si>
   <si>
     <t>10000003,10000004</t>
@@ -2597,6 +2597,9 @@
       <c r="G9" s="2">
         <v>0</v>
       </c>
+      <c r="H9" s="2" t="s">
+        <v>78</v>
+      </c>
       <c r="J9" s="2">
         <v>1</v>
       </c>
@@ -2646,13 +2649,13 @@
         <v>20000001</v>
       </c>
       <c r="Z9" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AA9" s="2">
         <v>0</v>
       </c>
       <c r="AB9" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="2:28">
@@ -2660,7 +2663,7 @@
         <v>20000003</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D10" s="3">
         <v>10000007</v>
@@ -2729,7 +2732,7 @@
         <v>0</v>
       </c>
       <c r="AB10" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="2:28">
@@ -2737,7 +2740,7 @@
         <v>20000004</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D11" s="3">
         <v>10000001</v>
@@ -2806,7 +2809,7 @@
         <v>0</v>
       </c>
       <c r="AB11" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="2:28">
@@ -2814,7 +2817,7 @@
         <v>20000005</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D12" s="3">
         <v>10000002</v>
@@ -2829,7 +2832,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J12" s="3">
         <v>1</v>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="135">
   <si>
     <t>##var</t>
   </si>
@@ -535,18 +535,15 @@
     <t>string</t>
   </si>
   <si>
+    <t>(array#sep=,),float</t>
+  </si>
+  <si>
     <t>(array#sep=,),SkillPassiveType</t>
   </si>
   <si>
-    <t>(array#sep=,),float</t>
-  </si>
-  <si>
     <t>float</t>
   </si>
   <si>
-    <t>double</t>
-  </si>
-  <si>
     <t>(array#sep=,),int</t>
   </si>
   <si>
@@ -668,6 +665,12 @@
   </si>
   <si>
     <t>淘汰之刃</t>
+  </si>
+  <si>
+    <t>Skill_淘汰之刃</t>
+  </si>
+  <si>
+    <t>3.5,0.3,4,0.5</t>
   </si>
   <si>
     <t>对敌人造成350%物理伤害，如果敌人生命值低于30%，造成400%物理伤害；若成功击杀，将额外恢复50%的怒气。</t>
@@ -2040,16 +2043,16 @@
         <v>30</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>9</v>
       </c>
       <c r="K2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L2" s="5" t="s">
         <v>31</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>32</v>
       </c>
       <c r="M2" s="5" t="s">
         <v>29</v>
@@ -2061,7 +2064,7 @@
         <v>33</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q2" s="5" t="s">
         <v>29</v>
@@ -2079,7 +2082,7 @@
         <v>29</v>
       </c>
       <c r="V2" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="W2" s="5" t="s">
         <v>33</v>
@@ -2091,10 +2094,10 @@
         <v>29</v>
       </c>
       <c r="Z2" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA2" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AB2" s="5" t="s">
         <v>30</v>
@@ -2102,88 +2105,88 @@
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="I3" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="J3" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="K3" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="L3" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="M3" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="N3" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="O3" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="P3" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="Q3" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="Q3" s="6" t="s">
+      <c r="R3" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="R3" s="6" t="s">
+      <c r="S3" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="S3" s="6" t="s">
+      <c r="T3" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="T3" s="6" t="s">
+      <c r="U3" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="U3" s="6" t="s">
+      <c r="V3" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="V3" s="6" t="s">
+      <c r="W3" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="W3" s="6" t="s">
+      <c r="X3" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="X3" s="6" t="s">
+      <c r="Y3" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="Y3" s="6" t="s">
+      <c r="Z3" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="Z3" s="6" t="s">
+      <c r="AA3" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="AA3" s="6" t="s">
+      <c r="AB3" s="6" t="s">
         <v>61</v>
-      </c>
-      <c r="AB3" s="6" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="2:27">
@@ -2191,7 +2194,7 @@
         <v>10000001</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D4" s="3">
         <v>10000001</v>
@@ -2206,7 +2209,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3">
@@ -2234,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="R4" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S4" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="T4" s="3">
         <v>2</v>
@@ -2269,7 +2272,7 @@
         <v>10000002</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D5" s="3">
         <v>10000002</v>
@@ -2284,7 +2287,7 @@
         <v>5</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3">
@@ -2312,10 +2315,10 @@
         <v>0</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="T5" s="3">
         <v>2</v>
@@ -2347,7 +2350,7 @@
         <v>10000003</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D6" s="3">
         <v>10000003</v>
@@ -2362,7 +2365,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3">
@@ -2390,10 +2393,10 @@
         <v>0</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="T6" s="3">
         <v>2</v>
@@ -2425,7 +2428,7 @@
         <v>10000004</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D7" s="3">
         <v>10000004</v>
@@ -2440,7 +2443,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3">
@@ -2468,10 +2471,10 @@
         <v>100</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T7" s="3">
         <v>1</v>
@@ -2498,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="AB7" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="2:28">
@@ -2506,7 +2509,7 @@
         <v>20000001</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D8" s="3">
         <v>10000005</v>
@@ -2520,6 +2523,12 @@
       <c r="G8" s="2">
         <v>0</v>
       </c>
+      <c r="H8" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>76</v>
+      </c>
       <c r="J8" s="2">
         <v>1</v>
       </c>
@@ -2545,10 +2554,10 @@
         <v>0</v>
       </c>
       <c r="R8" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S8" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="S8" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="T8" s="2">
         <v>2</v>
@@ -2575,7 +2584,7 @@
         <v>0</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="2:28">
@@ -2583,7 +2592,7 @@
         <v>20000002</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D9" s="3">
         <v>10000006</v>
@@ -2598,7 +2607,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J9" s="2">
         <v>1</v>
@@ -2625,10 +2634,10 @@
         <v>0</v>
       </c>
       <c r="R9" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S9" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="S9" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="T9" s="2">
         <v>3</v>
@@ -2649,13 +2658,13 @@
         <v>20000001</v>
       </c>
       <c r="Z9" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA9" s="2">
         <v>0</v>
       </c>
       <c r="AB9" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="2:28">
@@ -2663,7 +2672,7 @@
         <v>20000003</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D10" s="3">
         <v>10000007</v>
@@ -2702,10 +2711,10 @@
         <v>0</v>
       </c>
       <c r="R10" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S10" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="S10" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="T10" s="3">
         <v>4</v>
@@ -2732,7 +2741,7 @@
         <v>0</v>
       </c>
       <c r="AB10" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="2:28">
@@ -2740,7 +2749,7 @@
         <v>20000004</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D11" s="3">
         <v>10000001</v>
@@ -2779,10 +2788,10 @@
         <v>0</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T11" s="3">
         <v>1</v>
@@ -2809,7 +2818,7 @@
         <v>0</v>
       </c>
       <c r="AB11" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="2:28">
@@ -2817,7 +2826,7 @@
         <v>20000005</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D12" s="3">
         <v>10000002</v>
@@ -2832,7 +2841,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J12" s="3">
         <v>1</v>
@@ -2859,10 +2868,10 @@
         <v>0</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T12" s="3">
         <v>0</v>
@@ -2886,10 +2895,10 @@
         <v>0</v>
       </c>
       <c r="AA12" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AB12" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="2:28">
@@ -2897,7 +2906,7 @@
         <v>20000006</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" s="3">
         <v>10000003</v>
@@ -2936,10 +2945,10 @@
         <v>0</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T13" s="2">
         <v>0</v>
@@ -2966,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="AB13" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="2:28">
@@ -2974,7 +2983,7 @@
         <v>30000001</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" s="3">
         <v>10000004</v>
@@ -3013,10 +3022,10 @@
         <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S14" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -3040,10 +3049,10 @@
         <v>0</v>
       </c>
       <c r="AA14" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AB14" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="2:28">
@@ -3051,7 +3060,7 @@
         <v>30000002</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D15" s="3">
         <v>10000005</v>
@@ -3066,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J15" s="3">
         <v>2</v>
@@ -3093,10 +3102,10 @@
         <v>0</v>
       </c>
       <c r="R15" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S15" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="S15" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="T15" s="3">
         <v>0</v>
@@ -3123,7 +3132,7 @@
         <v>0</v>
       </c>
       <c r="AB15" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="2:28">
@@ -3131,7 +3140,7 @@
         <v>30000003</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D16" s="3">
         <v>10000006</v>
@@ -3170,10 +3179,10 @@
         <v>0</v>
       </c>
       <c r="R16" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S16" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="S16" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="T16" s="2">
         <v>2</v>
@@ -3197,10 +3206,10 @@
         <v>0</v>
       </c>
       <c r="AA16" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AB16" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="2:28">
@@ -3208,7 +3217,7 @@
         <v>30000004</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D17" s="3">
         <v>10000007</v>
@@ -3247,10 +3256,10 @@
         <v>0</v>
       </c>
       <c r="R17" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S17" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="T17" s="3">
         <v>1</v>
@@ -3277,7 +3286,7 @@
         <v>10000008</v>
       </c>
       <c r="AB17" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="2:28">
@@ -3285,7 +3294,7 @@
         <v>30000005</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D18" s="2">
         <v>10000001</v>
@@ -3324,10 +3333,10 @@
         <v>0</v>
       </c>
       <c r="R18" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S18" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="S18" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="T18" s="2">
         <v>1</v>
@@ -3354,7 +3363,7 @@
         <v>0</v>
       </c>
       <c r="AB18" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="2:28">
@@ -3362,7 +3371,7 @@
         <v>30000006</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D19" s="2">
         <v>10000002</v>
@@ -3401,10 +3410,10 @@
         <v>0</v>
       </c>
       <c r="R19" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S19" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="S19" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="T19" s="3">
         <v>3</v>
@@ -3428,10 +3437,10 @@
         <v>0</v>
       </c>
       <c r="AA19" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB19" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="2:28">
@@ -3439,7 +3448,7 @@
         <v>30000007</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D20" s="2">
         <v>10000003</v>
@@ -3478,10 +3487,10 @@
         <v>0</v>
       </c>
       <c r="R20" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S20" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="T20" s="3">
         <v>0</v>
@@ -3508,7 +3517,7 @@
         <v>0</v>
       </c>
       <c r="AB20" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="2:28">
@@ -3516,7 +3525,7 @@
         <v>30000008</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D21" s="2">
         <v>10000004</v>
@@ -3555,10 +3564,10 @@
         <v>0</v>
       </c>
       <c r="R21" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S21" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="T21" s="3">
         <v>1</v>
@@ -3585,7 +3594,7 @@
         <v>10000014</v>
       </c>
       <c r="AB21" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="2:28">
@@ -3593,7 +3602,7 @@
         <v>30000009</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D22" s="2">
         <v>10000005</v>
@@ -3632,10 +3641,10 @@
         <v>0</v>
       </c>
       <c r="R22" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S22" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="T22" s="3">
         <v>3</v>
@@ -3656,13 +3665,13 @@
         <v>20000001</v>
       </c>
       <c r="Z22" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA22" s="3">
         <v>0</v>
       </c>
       <c r="AB22" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="2:28">
@@ -3670,7 +3679,7 @@
         <v>30000010</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D23" s="2">
         <v>10000006</v>
@@ -3709,10 +3718,10 @@
         <v>0</v>
       </c>
       <c r="R23" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S23" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="T23" s="3">
         <v>1</v>
@@ -3736,10 +3745,10 @@
         <v>0</v>
       </c>
       <c r="AA23" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AB23" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="2:28">
@@ -3747,7 +3756,7 @@
         <v>30000011</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D24" s="2">
         <v>10000007</v>
@@ -3786,10 +3795,10 @@
         <v>0</v>
       </c>
       <c r="R24" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S24" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="S24" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="T24" s="3">
         <v>2</v>
@@ -3813,10 +3822,10 @@
         <v>0</v>
       </c>
       <c r="AA24" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AB24" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="2:28">
@@ -3824,7 +3833,7 @@
         <v>30000012</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D25" s="3">
         <v>10000001</v>
@@ -3863,10 +3872,10 @@
         <v>0</v>
       </c>
       <c r="R25" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S25" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="S25" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="T25" s="3">
         <v>5</v>
@@ -3893,7 +3902,7 @@
         <v>10000021</v>
       </c>
       <c r="AB25" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="2:28">
@@ -3901,7 +3910,7 @@
         <v>30000013</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D26" s="3">
         <v>10000002</v>
@@ -3940,10 +3949,10 @@
         <v>0</v>
       </c>
       <c r="R26" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S26" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="T26" s="3">
         <v>1</v>
@@ -3970,7 +3979,7 @@
         <v>10000022</v>
       </c>
       <c r="AB26" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="2:28">
@@ -3978,7 +3987,7 @@
         <v>30000014</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D27" s="3">
         <v>10000003</v>
@@ -4017,10 +4026,10 @@
         <v>0</v>
       </c>
       <c r="R27" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S27" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="S27" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="T27" s="3">
         <v>2</v>
@@ -4047,7 +4056,7 @@
         <v>10000023</v>
       </c>
       <c r="AB27" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="2:28">
@@ -4055,7 +4064,7 @@
         <v>30000015</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D28" s="3">
         <v>10000004</v>
@@ -4094,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="R28" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S28" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="S28" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="T28" s="3">
         <v>0</v>
@@ -4121,10 +4130,10 @@
         <v>0</v>
       </c>
       <c r="AA28" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AB28" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="2:28">
@@ -4132,7 +4141,7 @@
         <v>30000016</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D29" s="3">
         <v>10000005</v>
@@ -4171,10 +4180,10 @@
         <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S29" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="T29" s="3">
         <v>6</v>
@@ -4195,7 +4204,7 @@
         <v>20000001</v>
       </c>
       <c r="AB29" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="2:28">
@@ -4203,7 +4212,7 @@
         <v>30000017</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D30" s="3">
         <v>10000006</v>
@@ -4224,7 +4233,7 @@
         <v>5</v>
       </c>
       <c r="R30" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="W30" s="3">
         <v>0</v>
@@ -4233,7 +4242,7 @@
         <v>20000001</v>
       </c>
       <c r="AB30" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="2:28">
@@ -4241,7 +4250,7 @@
         <v>30000018</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D31" s="3">
         <v>10000007</v>
@@ -4280,10 +4289,10 @@
         <v>0</v>
       </c>
       <c r="R31" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S31" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="S31" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="T31" s="3">
         <v>1</v>
@@ -4307,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="AA31" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AB31" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="136">
   <si>
     <t>##var</t>
   </si>
@@ -535,18 +535,18 @@
     <t>string</t>
   </si>
   <si>
+    <t>(array#sep=,),int</t>
+  </si>
+  <si>
+    <t>(array#sep=,),SkillPassiveType</t>
+  </si>
+  <si>
     <t>(array#sep=,),float</t>
   </si>
   <si>
-    <t>(array#sep=,),SkillPassiveType</t>
-  </si>
-  <si>
     <t>float</t>
   </si>
   <si>
-    <t>(array#sep=,),int</t>
-  </si>
-  <si>
     <t>##</t>
   </si>
   <si>
@@ -670,7 +670,7 @@
     <t>Skill_淘汰之刃</t>
   </si>
   <si>
-    <t>3.5,0.3,4,0.5</t>
+    <t>35000,3000,40000,5000</t>
   </si>
   <si>
     <t>对敌人造成350%物理伤害，如果敌人生命值低于30%，造成400%物理伤害；若成功击杀，将额外恢复50%的怒气。</t>
@@ -689,6 +689,9 @@
   </si>
   <si>
     <t>无敌击</t>
+  </si>
+  <si>
+    <t>Skill_无敌击</t>
   </si>
   <si>
     <t>快速瞬间出剑5次攻击随机敌人,期间处于无敌状态,无法被攻击。</t>
@@ -851,12 +854,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -1558,7 +1560,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1571,25 +1573,22 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1918,7 +1917,7 @@
     <col min="1" max="1" width="10.875" style="3" customWidth="1"/>
     <col min="2" max="7" width="17.875" style="3"/>
     <col min="8" max="8" width="20.375" style="3" customWidth="1"/>
-    <col min="9" max="9" width="21.875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="23.125" style="3" customWidth="1"/>
     <col min="10" max="10" width="17.875" style="3"/>
     <col min="11" max="11" width="30.375" style="3" customWidth="1"/>
     <col min="12" max="12" width="17.875" style="3"/>
@@ -1932,2394 +1931,2487 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:28">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="5" t="s">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="R1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="S1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="T1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="U1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="V1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="W1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="X1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="Y1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="5" t="s">
+      <c r="Z1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="AA1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="5" t="s">
+      <c r="AB1" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:28">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="S2" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="T2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="U2" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="V2" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="W2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="X2" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y2" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="M2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="S2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="T2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="V2" s="5" t="s">
+      <c r="AA2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="W2" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="X2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="Z2" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA2" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB2" s="5" t="s">
+      <c r="AB2" s="6" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:28">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="6" t="s">
+      <c r="B3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="O3" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="P3" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="Q3" s="6" t="s">
+      <c r="Q3" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="R3" s="6" t="s">
+      <c r="R3" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="S3" s="6" t="s">
+      <c r="S3" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="T3" s="6" t="s">
+      <c r="T3" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="U3" s="6" t="s">
+      <c r="U3" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="V3" s="6" t="s">
+      <c r="V3" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="W3" s="6" t="s">
+      <c r="W3" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="X3" s="6" t="s">
+      <c r="X3" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="Y3" s="6" t="s">
+      <c r="Y3" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="Z3" s="6" t="s">
+      <c r="Z3" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="AA3" s="6" t="s">
+      <c r="AA3" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="AB3" s="6" t="s">
+      <c r="AB3" s="7" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="2:27">
-      <c r="B4" s="3">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:28">
+      <c r="A4" s="4"/>
+      <c r="B4" s="8">
         <v>10000001</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="8">
         <v>10000001</v>
       </c>
-      <c r="E4" s="3">
-        <v>0</v>
-      </c>
-      <c r="F4" s="3">
-        <v>1</v>
-      </c>
-      <c r="G4" s="3">
+      <c r="E4" s="8">
+        <v>0</v>
+      </c>
+      <c r="F4" s="8">
+        <v>1</v>
+      </c>
+      <c r="G4" s="8">
         <v>5</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3">
-        <v>1</v>
-      </c>
-      <c r="K4" s="3">
-        <v>0</v>
-      </c>
-      <c r="L4" s="3">
-        <v>0</v>
-      </c>
-      <c r="M4" s="3">
-        <v>0</v>
-      </c>
-      <c r="N4" s="3">
-        <v>1</v>
-      </c>
-      <c r="O4" s="3">
+      <c r="I4" s="8"/>
+      <c r="J4" s="8">
+        <v>1</v>
+      </c>
+      <c r="K4" s="8">
+        <v>0</v>
+      </c>
+      <c r="L4" s="8">
+        <v>0</v>
+      </c>
+      <c r="M4" s="8">
+        <v>0</v>
+      </c>
+      <c r="N4" s="8">
+        <v>1</v>
+      </c>
+      <c r="O4" s="8">
         <v>3</v>
       </c>
-      <c r="P4" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="3">
-        <v>0</v>
-      </c>
-      <c r="R4" s="3" t="s">
+      <c r="P4" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>0</v>
+      </c>
+      <c r="R4" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="S4" s="3" t="s">
+      <c r="S4" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="T4" s="3">
-        <v>2</v>
-      </c>
-      <c r="U4" s="3">
-        <v>0</v>
-      </c>
-      <c r="V4" s="3">
-        <v>0</v>
-      </c>
-      <c r="W4" s="3">
-        <v>0</v>
-      </c>
-      <c r="X4" s="3">
+      <c r="T4" s="8">
+        <v>2</v>
+      </c>
+      <c r="U4" s="8">
+        <v>0</v>
+      </c>
+      <c r="V4" s="8">
+        <v>0</v>
+      </c>
+      <c r="W4" s="8">
+        <v>0</v>
+      </c>
+      <c r="X4" s="8">
         <v>10000001</v>
       </c>
-      <c r="Y4" s="3">
+      <c r="Y4" s="8">
         <v>20000001</v>
       </c>
-      <c r="Z4" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="3">
-        <v>0</v>
-      </c>
+      <c r="Z4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="4"/>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="2:27">
-      <c r="B5" s="3">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:28">
+      <c r="A5" s="4"/>
+      <c r="B5" s="8">
         <v>10000002</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="8">
         <v>10000002</v>
       </c>
-      <c r="E5" s="3">
-        <v>0</v>
-      </c>
-      <c r="F5" s="3">
-        <v>1</v>
-      </c>
-      <c r="G5" s="3">
+      <c r="E5" s="8">
+        <v>0</v>
+      </c>
+      <c r="F5" s="8">
+        <v>1</v>
+      </c>
+      <c r="G5" s="8">
         <v>5</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3">
-        <v>1</v>
-      </c>
-      <c r="K5" s="3">
-        <v>0</v>
-      </c>
-      <c r="L5" s="3">
-        <v>0</v>
-      </c>
-      <c r="M5" s="3">
-        <v>0</v>
-      </c>
-      <c r="N5" s="3">
-        <v>1</v>
-      </c>
-      <c r="O5" s="3">
+      <c r="I5" s="8"/>
+      <c r="J5" s="8">
+        <v>1</v>
+      </c>
+      <c r="K5" s="8">
+        <v>0</v>
+      </c>
+      <c r="L5" s="8">
+        <v>0</v>
+      </c>
+      <c r="M5" s="8">
+        <v>0</v>
+      </c>
+      <c r="N5" s="8">
+        <v>1</v>
+      </c>
+      <c r="O5" s="8">
         <v>3</v>
       </c>
-      <c r="P5" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="3">
-        <v>0</v>
-      </c>
-      <c r="R5" s="3" t="s">
+      <c r="P5" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>0</v>
+      </c>
+      <c r="R5" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="S5" s="3" t="s">
+      <c r="S5" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="T5" s="3">
-        <v>2</v>
-      </c>
-      <c r="U5" s="3">
-        <v>0</v>
-      </c>
-      <c r="V5" s="3">
-        <v>0</v>
-      </c>
-      <c r="W5" s="3">
+      <c r="T5" s="8">
+        <v>2</v>
+      </c>
+      <c r="U5" s="8">
+        <v>0</v>
+      </c>
+      <c r="V5" s="8">
+        <v>0</v>
+      </c>
+      <c r="W5" s="8">
         <v>8</v>
       </c>
-      <c r="X5" s="3">
+      <c r="X5" s="8">
         <v>10000002</v>
       </c>
-      <c r="Y5" s="3">
+      <c r="Y5" s="8">
         <v>20000001</v>
       </c>
-      <c r="Z5" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="3">
-        <v>0</v>
-      </c>
+      <c r="Z5" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="4"/>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="2:27">
-      <c r="B6" s="3">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:28">
+      <c r="A6" s="4"/>
+      <c r="B6" s="8">
         <v>10000003</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="8">
         <v>10000003</v>
       </c>
-      <c r="E6" s="3">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3">
-        <v>2</v>
-      </c>
-      <c r="G6" s="3">
+      <c r="E6" s="8">
+        <v>0</v>
+      </c>
+      <c r="F6" s="8">
+        <v>2</v>
+      </c>
+      <c r="G6" s="8">
         <v>5</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3">
-        <v>1</v>
-      </c>
-      <c r="K6" s="3">
-        <v>0</v>
-      </c>
-      <c r="L6" s="3">
-        <v>0</v>
-      </c>
-      <c r="M6" s="3">
-        <v>0</v>
-      </c>
-      <c r="N6" s="3">
-        <v>1</v>
-      </c>
-      <c r="O6" s="3">
+      <c r="I6" s="8"/>
+      <c r="J6" s="8">
+        <v>1</v>
+      </c>
+      <c r="K6" s="8">
+        <v>0</v>
+      </c>
+      <c r="L6" s="8">
+        <v>0</v>
+      </c>
+      <c r="M6" s="8">
+        <v>0</v>
+      </c>
+      <c r="N6" s="8">
+        <v>1</v>
+      </c>
+      <c r="O6" s="8">
         <v>3</v>
       </c>
-      <c r="P6" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="3">
-        <v>0</v>
-      </c>
-      <c r="R6" s="3" t="s">
+      <c r="P6" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>0</v>
+      </c>
+      <c r="R6" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="S6" s="3" t="s">
+      <c r="S6" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="T6" s="3">
-        <v>2</v>
-      </c>
-      <c r="U6" s="3">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3">
-        <v>0</v>
-      </c>
-      <c r="W6" s="3">
+      <c r="T6" s="8">
+        <v>2</v>
+      </c>
+      <c r="U6" s="8">
+        <v>0</v>
+      </c>
+      <c r="V6" s="8">
+        <v>0</v>
+      </c>
+      <c r="W6" s="8">
         <v>8</v>
       </c>
-      <c r="X6" s="3">
+      <c r="X6" s="8">
         <v>10000003</v>
       </c>
-      <c r="Y6" s="3">
+      <c r="Y6" s="8">
         <v>20000001</v>
       </c>
-      <c r="Z6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="3">
-        <v>0</v>
-      </c>
+      <c r="Z6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="4"/>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="2:28">
-      <c r="B7" s="3">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:28">
+      <c r="A7" s="4"/>
+      <c r="B7" s="8">
         <v>10000004</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="8">
         <v>10000004</v>
       </c>
-      <c r="E7" s="3">
-        <v>1</v>
-      </c>
-      <c r="F7" s="3">
-        <v>1</v>
-      </c>
-      <c r="G7" s="3">
-        <v>0</v>
-      </c>
-      <c r="H7" s="3" t="s">
+      <c r="E7" s="8">
+        <v>1</v>
+      </c>
+      <c r="F7" s="8">
+        <v>1</v>
+      </c>
+      <c r="G7" s="8">
+        <v>0</v>
+      </c>
+      <c r="H7" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3">
-        <v>1</v>
-      </c>
-      <c r="K7" s="3">
-        <v>0</v>
-      </c>
-      <c r="L7" s="3">
-        <v>0</v>
-      </c>
-      <c r="M7" s="3">
-        <v>0</v>
-      </c>
-      <c r="N7" s="3">
+      <c r="I7" s="8"/>
+      <c r="J7" s="8">
+        <v>1</v>
+      </c>
+      <c r="K7" s="8">
+        <v>0</v>
+      </c>
+      <c r="L7" s="8">
+        <v>0</v>
+      </c>
+      <c r="M7" s="8">
+        <v>0</v>
+      </c>
+      <c r="N7" s="8">
         <v>11</v>
       </c>
-      <c r="O7" s="3">
+      <c r="O7" s="8">
         <v>5</v>
       </c>
-      <c r="P7" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="3">
+      <c r="P7" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="8">
         <v>100</v>
       </c>
-      <c r="R7" s="3" t="s">
+      <c r="R7" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="S7" s="3" t="s">
+      <c r="S7" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="T7" s="3">
-        <v>1</v>
-      </c>
-      <c r="U7" s="3">
-        <v>1</v>
-      </c>
-      <c r="V7" s="3">
+      <c r="T7" s="8">
+        <v>1</v>
+      </c>
+      <c r="U7" s="8">
+        <v>1</v>
+      </c>
+      <c r="V7" s="8">
         <v>4</v>
       </c>
-      <c r="W7" s="3">
-        <v>0</v>
-      </c>
-      <c r="X7" s="3">
+      <c r="W7" s="8">
+        <v>0</v>
+      </c>
+      <c r="X7" s="8">
         <v>10000004</v>
       </c>
-      <c r="Y7" s="3">
+      <c r="Y7" s="8">
         <v>20000001</v>
       </c>
-      <c r="Z7" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="3" t="s">
+      <c r="Z7" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="8" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="2:28">
-      <c r="B8" s="2">
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="1:28">
+      <c r="A8" s="9"/>
+      <c r="B8" s="9">
         <v>20000001</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="8">
         <v>10000005</v>
       </c>
-      <c r="E8" s="2">
-        <v>1</v>
-      </c>
-      <c r="F8" s="2">
-        <v>1</v>
-      </c>
-      <c r="G8" s="2">
-        <v>0</v>
-      </c>
-      <c r="H8" s="2" t="s">
+      <c r="E8" s="9">
+        <v>1</v>
+      </c>
+      <c r="F8" s="9">
+        <v>1</v>
+      </c>
+      <c r="G8" s="9">
+        <v>0</v>
+      </c>
+      <c r="H8" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="I8" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="J8" s="2">
-        <v>1</v>
-      </c>
-      <c r="K8" s="2">
-        <v>0</v>
-      </c>
-      <c r="L8" s="2">
-        <v>0</v>
-      </c>
-      <c r="M8" s="2">
-        <v>0</v>
-      </c>
-      <c r="N8" s="2">
-        <v>1</v>
-      </c>
-      <c r="O8" s="2">
+      <c r="J8" s="9">
+        <v>1</v>
+      </c>
+      <c r="K8" s="9">
+        <v>0</v>
+      </c>
+      <c r="L8" s="9">
+        <v>0</v>
+      </c>
+      <c r="M8" s="9">
+        <v>0</v>
+      </c>
+      <c r="N8" s="9">
+        <v>1</v>
+      </c>
+      <c r="O8" s="9">
         <v>3</v>
       </c>
-      <c r="P8" s="2">
+      <c r="P8" s="9">
         <v>3.5</v>
       </c>
-      <c r="Q8" s="2">
-        <v>0</v>
-      </c>
-      <c r="R8" s="3" t="s">
+      <c r="Q8" s="9">
+        <v>0</v>
+      </c>
+      <c r="R8" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="S8" s="2" t="s">
+      <c r="S8" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="T8" s="2">
-        <v>2</v>
-      </c>
-      <c r="U8" s="2">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2">
-        <v>0</v>
-      </c>
-      <c r="W8" s="3">
-        <v>0</v>
-      </c>
-      <c r="X8" s="2">
+      <c r="T8" s="9">
+        <v>2</v>
+      </c>
+      <c r="U8" s="9">
+        <v>0</v>
+      </c>
+      <c r="V8" s="9">
+        <v>0</v>
+      </c>
+      <c r="W8" s="8">
+        <v>0</v>
+      </c>
+      <c r="X8" s="9">
         <v>10000001</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Y8" s="8">
         <v>20000001</v>
       </c>
-      <c r="Z8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="2" t="s">
+      <c r="Z8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="9" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="2:28">
-      <c r="B9" s="2">
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="1:28">
+      <c r="A9" s="9"/>
+      <c r="B9" s="9">
         <v>20000002</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="8">
         <v>10000006</v>
       </c>
-      <c r="E9" s="2">
-        <v>1</v>
-      </c>
-      <c r="F9" s="2">
-        <v>1</v>
-      </c>
-      <c r="G9" s="2">
-        <v>0</v>
-      </c>
-      <c r="H9" s="2" t="s">
+      <c r="E9" s="9">
+        <v>1</v>
+      </c>
+      <c r="F9" s="9">
+        <v>1</v>
+      </c>
+      <c r="G9" s="9">
+        <v>0</v>
+      </c>
+      <c r="H9" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="J9" s="2">
-        <v>1</v>
-      </c>
-      <c r="K9" s="2">
-        <v>0</v>
-      </c>
-      <c r="L9" s="2">
-        <v>0</v>
-      </c>
-      <c r="M9" s="2">
-        <v>0</v>
-      </c>
-      <c r="N9" s="2">
-        <v>1</v>
-      </c>
-      <c r="O9" s="2">
+      <c r="I9" s="9"/>
+      <c r="J9" s="9">
+        <v>1</v>
+      </c>
+      <c r="K9" s="9">
+        <v>0</v>
+      </c>
+      <c r="L9" s="9">
+        <v>0</v>
+      </c>
+      <c r="M9" s="9">
+        <v>0</v>
+      </c>
+      <c r="N9" s="9">
+        <v>1</v>
+      </c>
+      <c r="O9" s="9">
         <v>5</v>
       </c>
-      <c r="P9" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="2">
-        <v>0</v>
-      </c>
-      <c r="R9" s="3" t="s">
+      <c r="P9" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="9">
+        <v>0</v>
+      </c>
+      <c r="R9" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="S9" s="2" t="s">
+      <c r="S9" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="T9" s="2">
+      <c r="T9" s="9">
         <v>3</v>
       </c>
-      <c r="U9" s="2">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2">
-        <v>0</v>
-      </c>
-      <c r="W9" s="3">
-        <v>0</v>
-      </c>
-      <c r="X9" s="2">
+      <c r="U9" s="9">
+        <v>0</v>
+      </c>
+      <c r="V9" s="9">
+        <v>0</v>
+      </c>
+      <c r="W9" s="8">
+        <v>0</v>
+      </c>
+      <c r="X9" s="9">
         <v>10000001</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Y9" s="8">
         <v>20000001</v>
       </c>
-      <c r="Z9" s="7" t="s">
+      <c r="Z9" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="AA9" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="2" t="s">
+      <c r="AA9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="9" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="2:28">
-      <c r="B10" s="3">
+    <row r="10" customHeight="1" spans="1:28">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8">
         <v>20000003</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="8">
         <v>10000007</v>
       </c>
-      <c r="E10" s="3">
-        <v>1</v>
-      </c>
-      <c r="F10" s="3">
-        <v>1</v>
-      </c>
-      <c r="G10" s="3">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3">
-        <v>1</v>
-      </c>
-      <c r="K10" s="3">
-        <v>0</v>
-      </c>
-      <c r="L10" s="3">
-        <v>0</v>
-      </c>
-      <c r="M10" s="3">
-        <v>0</v>
-      </c>
-      <c r="N10" s="3">
-        <v>1</v>
-      </c>
-      <c r="O10" s="3">
-        <v>2</v>
-      </c>
-      <c r="P10" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>0</v>
-      </c>
-      <c r="R10" s="3" t="s">
+      <c r="E10" s="8">
+        <v>1</v>
+      </c>
+      <c r="F10" s="8">
+        <v>1</v>
+      </c>
+      <c r="G10" s="8">
+        <v>0</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I10" s="8">
+        <v>5</v>
+      </c>
+      <c r="J10" s="8">
+        <v>1</v>
+      </c>
+      <c r="K10" s="8">
+        <v>0</v>
+      </c>
+      <c r="L10" s="8">
+        <v>0</v>
+      </c>
+      <c r="M10" s="8">
+        <v>0</v>
+      </c>
+      <c r="N10" s="8">
+        <v>1</v>
+      </c>
+      <c r="O10" s="8">
+        <v>2</v>
+      </c>
+      <c r="P10" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="8">
+        <v>0</v>
+      </c>
+      <c r="R10" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="S10" s="3" t="s">
+      <c r="S10" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="T10" s="3">
+      <c r="T10" s="8">
         <v>4</v>
       </c>
-      <c r="U10" s="3">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3">
-        <v>0</v>
-      </c>
-      <c r="W10" s="3">
-        <v>0</v>
-      </c>
-      <c r="X10" s="3">
+      <c r="U10" s="8">
+        <v>0</v>
+      </c>
+      <c r="V10" s="8">
+        <v>0</v>
+      </c>
+      <c r="W10" s="8">
+        <v>0</v>
+      </c>
+      <c r="X10" s="8">
         <v>10000001</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Y10" s="8">
         <v>20000001</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="Z10" s="8">
         <v>10000002</v>
       </c>
-      <c r="AA10" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="3" t="s">
-        <v>83</v>
+      <c r="AA10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="8" t="s">
+        <v>84</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="2:28">
-      <c r="B11" s="3">
+    <row r="11" customHeight="1" spans="1:28">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8">
         <v>20000004</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D11" s="3">
+      <c r="C11" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="D11" s="8">
         <v>10000001</v>
       </c>
-      <c r="E11" s="3">
-        <v>1</v>
-      </c>
-      <c r="F11" s="3">
-        <v>2</v>
-      </c>
-      <c r="G11" s="3">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3">
-        <v>1</v>
-      </c>
-      <c r="K11" s="3">
-        <v>0</v>
-      </c>
-      <c r="L11" s="3">
-        <v>0</v>
-      </c>
-      <c r="M11" s="3">
-        <v>0</v>
-      </c>
-      <c r="N11" s="3">
-        <v>1</v>
-      </c>
-      <c r="O11" s="3">
+      <c r="E11" s="8">
+        <v>1</v>
+      </c>
+      <c r="F11" s="8">
+        <v>2</v>
+      </c>
+      <c r="G11" s="8">
+        <v>0</v>
+      </c>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8">
+        <v>1</v>
+      </c>
+      <c r="K11" s="8">
+        <v>0</v>
+      </c>
+      <c r="L11" s="8">
+        <v>0</v>
+      </c>
+      <c r="M11" s="8">
+        <v>0</v>
+      </c>
+      <c r="N11" s="8">
+        <v>1</v>
+      </c>
+      <c r="O11" s="8">
         <v>3</v>
       </c>
-      <c r="P11" s="3">
+      <c r="P11" s="8">
         <v>1.5</v>
       </c>
-      <c r="Q11" s="3">
-        <v>0</v>
-      </c>
-      <c r="R11" s="3" t="s">
+      <c r="Q11" s="8">
+        <v>0</v>
+      </c>
+      <c r="R11" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="S11" s="3" t="s">
+      <c r="S11" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="T11" s="3">
-        <v>1</v>
-      </c>
-      <c r="U11" s="3">
-        <v>1</v>
-      </c>
-      <c r="V11" s="3">
+      <c r="T11" s="8">
+        <v>1</v>
+      </c>
+      <c r="U11" s="8">
+        <v>1</v>
+      </c>
+      <c r="V11" s="8">
         <v>6</v>
       </c>
-      <c r="W11" s="3">
-        <v>0</v>
-      </c>
-      <c r="X11" s="3">
+      <c r="W11" s="8">
+        <v>0</v>
+      </c>
+      <c r="X11" s="8">
         <v>10000001</v>
       </c>
-      <c r="Y11" s="3">
+      <c r="Y11" s="8">
         <v>20000001</v>
       </c>
-      <c r="Z11" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="3" t="s">
-        <v>85</v>
+      <c r="Z11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="8" t="s">
+        <v>86</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="2:28">
-      <c r="B12" s="3">
+    <row r="12" customHeight="1" spans="1:28">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8">
         <v>20000005</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D12" s="3">
+      <c r="C12" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="D12" s="8">
         <v>10000002</v>
       </c>
-      <c r="E12" s="3">
-        <v>1</v>
-      </c>
-      <c r="F12" s="3">
-        <v>1</v>
-      </c>
-      <c r="G12" s="3">
-        <v>0</v>
-      </c>
-      <c r="H12" s="3" t="s">
+      <c r="E12" s="8">
+        <v>1</v>
+      </c>
+      <c r="F12" s="8">
+        <v>1</v>
+      </c>
+      <c r="G12" s="8">
+        <v>0</v>
+      </c>
+      <c r="H12" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="J12" s="3">
-        <v>1</v>
-      </c>
-      <c r="K12" s="3">
-        <v>0</v>
-      </c>
-      <c r="L12" s="3">
-        <v>0</v>
-      </c>
-      <c r="M12" s="3">
-        <v>0</v>
-      </c>
-      <c r="N12" s="3">
+      <c r="I12" s="8"/>
+      <c r="J12" s="8">
+        <v>1</v>
+      </c>
+      <c r="K12" s="8">
+        <v>0</v>
+      </c>
+      <c r="L12" s="8">
+        <v>0</v>
+      </c>
+      <c r="M12" s="8">
+        <v>0</v>
+      </c>
+      <c r="N12" s="8">
         <v>5</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12" s="8">
         <v>5</v>
       </c>
-      <c r="P12" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>0</v>
-      </c>
-      <c r="R12" s="3" t="s">
+      <c r="P12" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="8">
+        <v>0</v>
+      </c>
+      <c r="R12" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="S12" s="3" t="s">
+      <c r="S12" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="T12" s="3">
-        <v>0</v>
-      </c>
-      <c r="U12" s="3">
-        <v>1</v>
-      </c>
-      <c r="V12" s="3">
+      <c r="T12" s="8">
+        <v>0</v>
+      </c>
+      <c r="U12" s="8">
+        <v>1</v>
+      </c>
+      <c r="V12" s="8">
         <v>8</v>
       </c>
-      <c r="W12" s="3">
-        <v>0</v>
-      </c>
-      <c r="X12" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="3">
+      <c r="W12" s="8">
+        <v>0</v>
+      </c>
+      <c r="X12" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="8">
         <v>0</v>
       </c>
       <c r="AA12" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB12" s="3" t="s">
         <v>88</v>
       </c>
+      <c r="AB12" s="8" t="s">
+        <v>89</v>
+      </c>
     </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="2:28">
-      <c r="B13" s="2">
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:28">
+      <c r="A13" s="9"/>
+      <c r="B13" s="9">
         <v>20000006</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D13" s="3">
+      <c r="C13" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D13" s="8">
         <v>10000003</v>
       </c>
-      <c r="E13" s="2">
-        <v>1</v>
-      </c>
-      <c r="F13" s="2">
-        <v>2</v>
-      </c>
-      <c r="G13" s="2">
-        <v>0</v>
-      </c>
-      <c r="J13" s="2">
-        <v>1</v>
-      </c>
-      <c r="K13" s="2">
-        <v>0</v>
-      </c>
-      <c r="L13" s="2">
-        <v>0</v>
-      </c>
-      <c r="M13" s="2">
-        <v>0</v>
-      </c>
-      <c r="N13" s="2">
-        <v>1</v>
-      </c>
-      <c r="O13" s="2">
+      <c r="E13" s="9">
+        <v>1</v>
+      </c>
+      <c r="F13" s="9">
+        <v>2</v>
+      </c>
+      <c r="G13" s="9">
+        <v>0</v>
+      </c>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9">
+        <v>1</v>
+      </c>
+      <c r="K13" s="9">
+        <v>0</v>
+      </c>
+      <c r="L13" s="9">
+        <v>0</v>
+      </c>
+      <c r="M13" s="9">
+        <v>0</v>
+      </c>
+      <c r="N13" s="9">
+        <v>1</v>
+      </c>
+      <c r="O13" s="9">
         <v>5</v>
       </c>
-      <c r="P13" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="2">
-        <v>0</v>
-      </c>
-      <c r="R13" s="3" t="s">
+      <c r="P13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="9">
+        <v>0</v>
+      </c>
+      <c r="R13" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="S13" s="2" t="s">
+      <c r="S13" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="T13" s="2">
-        <v>0</v>
-      </c>
-      <c r="U13" s="2">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2">
-        <v>0</v>
-      </c>
-      <c r="W13" s="3">
-        <v>0</v>
-      </c>
-      <c r="X13" s="2">
+      <c r="T13" s="9">
+        <v>0</v>
+      </c>
+      <c r="U13" s="9">
+        <v>0</v>
+      </c>
+      <c r="V13" s="9">
+        <v>0</v>
+      </c>
+      <c r="W13" s="8">
+        <v>0</v>
+      </c>
+      <c r="X13" s="9">
         <v>10000001</v>
       </c>
-      <c r="Y13" s="3">
+      <c r="Y13" s="8">
         <v>20000001</v>
       </c>
-      <c r="Z13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="2" t="s">
-        <v>90</v>
+      <c r="Z13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="9" t="s">
+        <v>91</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="2:28">
-      <c r="B14" s="3">
+    <row r="14" customHeight="1" spans="1:28">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8">
         <v>30000001</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D14" s="3">
+      <c r="C14" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D14" s="8">
         <v>10000004</v>
       </c>
-      <c r="E14" s="3">
-        <v>1</v>
-      </c>
-      <c r="F14" s="3">
-        <v>1</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>2</v>
-      </c>
-      <c r="K14" s="3">
-        <v>2</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="E14" s="8">
+        <v>1</v>
+      </c>
+      <c r="F14" s="8">
+        <v>1</v>
+      </c>
+      <c r="G14" s="8">
+        <v>0</v>
+      </c>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8">
+        <v>2</v>
+      </c>
+      <c r="K14" s="8">
+        <v>2</v>
+      </c>
+      <c r="L14" s="8">
         <v>0.2</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="M14" s="8">
+        <v>0</v>
+      </c>
+      <c r="N14" s="8">
         <v>9</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="8">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
+      <c r="P14" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>0</v>
+      </c>
+      <c r="R14" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="S14" s="3" t="s">
+      <c r="S14" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3">
-        <v>1</v>
-      </c>
-      <c r="V14" s="3">
-        <v>2</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="T14" s="8">
+        <v>0</v>
+      </c>
+      <c r="U14" s="8">
+        <v>1</v>
+      </c>
+      <c r="V14" s="8">
+        <v>2</v>
+      </c>
+      <c r="W14" s="8">
+        <v>0</v>
+      </c>
+      <c r="X14" s="8">
         <v>10000001</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="8">
         <v>20000001</v>
       </c>
-      <c r="Z14" s="9">
+      <c r="Z14" s="8">
         <v>0</v>
       </c>
       <c r="AA14" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB14" s="3" t="s">
         <v>93</v>
       </c>
+      <c r="AB14" s="8" t="s">
+        <v>94</v>
+      </c>
     </row>
-    <row r="15" customHeight="1" spans="2:28">
-      <c r="B15" s="3">
+    <row r="15" customHeight="1" spans="1:28">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8">
         <v>30000002</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D15" s="3">
+      <c r="C15" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="D15" s="8">
         <v>10000005</v>
       </c>
-      <c r="E15" s="3">
-        <v>1</v>
-      </c>
-      <c r="F15" s="3">
-        <v>1</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3" t="s">
+      <c r="E15" s="8">
+        <v>1</v>
+      </c>
+      <c r="F15" s="8">
+        <v>1</v>
+      </c>
+      <c r="G15" s="8">
+        <v>0</v>
+      </c>
+      <c r="H15" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="J15" s="3">
-        <v>2</v>
-      </c>
-      <c r="K15" s="3">
-        <v>1</v>
-      </c>
-      <c r="L15" s="3">
+      <c r="I15" s="8"/>
+      <c r="J15" s="8">
+        <v>2</v>
+      </c>
+      <c r="K15" s="8">
+        <v>1</v>
+      </c>
+      <c r="L15" s="8">
         <v>0.17</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
-      <c r="N15" s="3">
+      <c r="M15" s="8">
+        <v>0</v>
+      </c>
+      <c r="N15" s="8">
         <v>3</v>
       </c>
-      <c r="O15" s="3">
-        <v>2</v>
-      </c>
-      <c r="P15" s="3">
+      <c r="O15" s="8">
+        <v>2</v>
+      </c>
+      <c r="P15" s="8">
         <v>1.5</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3" t="s">
+      <c r="Q15" s="8">
+        <v>0</v>
+      </c>
+      <c r="R15" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="S15" s="3" t="s">
+      <c r="S15" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="T15" s="3">
-        <v>0</v>
-      </c>
-      <c r="U15" s="3">
-        <v>1</v>
-      </c>
-      <c r="V15" s="3">
+      <c r="T15" s="8">
+        <v>0</v>
+      </c>
+      <c r="U15" s="8">
+        <v>1</v>
+      </c>
+      <c r="V15" s="8">
         <v>3</v>
       </c>
-      <c r="W15" s="3">
-        <v>0</v>
-      </c>
-      <c r="X15" s="3">
+      <c r="W15" s="8">
+        <v>0</v>
+      </c>
+      <c r="X15" s="8">
         <v>10000006</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Y15" s="8">
         <v>20000001</v>
       </c>
-      <c r="Z15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="3" t="s">
-        <v>95</v>
+      <c r="Z15" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="8" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="2:28">
-      <c r="B16" s="2">
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="1:28">
+      <c r="A16" s="9"/>
+      <c r="B16" s="9">
         <v>30000003</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D16" s="3">
+      <c r="C16" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" s="8">
         <v>10000006</v>
       </c>
-      <c r="E16" s="2">
-        <v>1</v>
-      </c>
-      <c r="F16" s="2">
-        <v>1</v>
-      </c>
-      <c r="G16" s="2">
-        <v>0</v>
-      </c>
-      <c r="J16" s="2">
-        <v>2</v>
-      </c>
-      <c r="K16" s="2">
-        <v>2</v>
-      </c>
-      <c r="L16" s="2">
+      <c r="E16" s="9">
+        <v>1</v>
+      </c>
+      <c r="F16" s="9">
+        <v>1</v>
+      </c>
+      <c r="G16" s="9">
+        <v>0</v>
+      </c>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9">
+        <v>2</v>
+      </c>
+      <c r="K16" s="9">
+        <v>2</v>
+      </c>
+      <c r="L16" s="9">
         <v>0.2</v>
       </c>
-      <c r="M16" s="2">
-        <v>0</v>
-      </c>
-      <c r="N16" s="2">
+      <c r="M16" s="9">
+        <v>0</v>
+      </c>
+      <c r="N16" s="9">
         <v>10</v>
       </c>
-      <c r="O16" s="2">
+      <c r="O16" s="9">
         <v>4</v>
       </c>
-      <c r="P16" s="2">
+      <c r="P16" s="9">
         <v>0.4</v>
       </c>
-      <c r="Q16" s="2">
-        <v>0</v>
-      </c>
-      <c r="R16" s="3" t="s">
+      <c r="Q16" s="9">
+        <v>0</v>
+      </c>
+      <c r="R16" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="S16" s="2" t="s">
+      <c r="S16" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="T16" s="2">
-        <v>2</v>
-      </c>
-      <c r="U16" s="2">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2">
-        <v>0</v>
-      </c>
-      <c r="W16" s="3">
-        <v>0</v>
-      </c>
-      <c r="X16" s="2">
+      <c r="T16" s="9">
+        <v>2</v>
+      </c>
+      <c r="U16" s="9">
+        <v>0</v>
+      </c>
+      <c r="V16" s="9">
+        <v>0</v>
+      </c>
+      <c r="W16" s="8">
+        <v>0</v>
+      </c>
+      <c r="X16" s="9">
         <v>10000001</v>
       </c>
-      <c r="Y16" s="3">
+      <c r="Y16" s="8">
         <v>20000001</v>
       </c>
-      <c r="Z16" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="AB16" s="2" t="s">
+      <c r="Z16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="9" t="s">
         <v>98</v>
       </c>
+      <c r="AB16" s="9" t="s">
+        <v>99</v>
+      </c>
     </row>
-    <row r="17" customHeight="1" spans="2:28">
-      <c r="B17" s="3">
+    <row r="17" customHeight="1" spans="1:28">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8">
         <v>30000004</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D17" s="3">
+      <c r="C17" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" s="8">
         <v>10000007</v>
       </c>
-      <c r="E17" s="3">
-        <v>1</v>
-      </c>
-      <c r="F17" s="3">
-        <v>1</v>
-      </c>
-      <c r="G17" s="3">
-        <v>0</v>
-      </c>
-      <c r="J17" s="3">
-        <v>2</v>
-      </c>
-      <c r="K17" s="3">
-        <v>2</v>
-      </c>
-      <c r="L17" s="3">
+      <c r="E17" s="8">
+        <v>1</v>
+      </c>
+      <c r="F17" s="8">
+        <v>1</v>
+      </c>
+      <c r="G17" s="8">
+        <v>0</v>
+      </c>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8">
+        <v>2</v>
+      </c>
+      <c r="K17" s="8">
+        <v>2</v>
+      </c>
+      <c r="L17" s="8">
         <v>0.2</v>
       </c>
-      <c r="M17" s="3">
-        <v>0</v>
-      </c>
-      <c r="N17" s="3">
+      <c r="M17" s="8">
+        <v>0</v>
+      </c>
+      <c r="N17" s="8">
         <v>10</v>
       </c>
-      <c r="O17" s="3">
-        <v>2</v>
-      </c>
-      <c r="P17" s="3">
-        <v>2</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>0</v>
-      </c>
-      <c r="R17" s="3" t="s">
+      <c r="O17" s="8">
+        <v>2</v>
+      </c>
+      <c r="P17" s="8">
+        <v>2</v>
+      </c>
+      <c r="Q17" s="8">
+        <v>0</v>
+      </c>
+      <c r="R17" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="S17" s="3" t="s">
+      <c r="S17" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="T17" s="3">
-        <v>1</v>
-      </c>
-      <c r="U17" s="3">
-        <v>1</v>
-      </c>
-      <c r="V17" s="3">
+      <c r="T17" s="8">
+        <v>1</v>
+      </c>
+      <c r="U17" s="8">
+        <v>1</v>
+      </c>
+      <c r="V17" s="8">
         <v>3</v>
       </c>
-      <c r="W17" s="3">
-        <v>0</v>
-      </c>
-      <c r="X17" s="3">
+      <c r="W17" s="8">
+        <v>0</v>
+      </c>
+      <c r="X17" s="8">
         <v>10000001</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Y17" s="8">
         <v>20000001</v>
       </c>
-      <c r="Z17" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="3">
+      <c r="Z17" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="8">
         <v>10000008</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>100</v>
+      <c r="AB17" s="8" t="s">
+        <v>101</v>
       </c>
     </row>
-    <row r="18" s="2" customFormat="1" customHeight="1" spans="2:28">
-      <c r="B18" s="2">
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="1:28">
+      <c r="A18" s="9"/>
+      <c r="B18" s="9">
         <v>30000005</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="D18" s="2">
+      <c r="C18" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="D18" s="9">
         <v>10000001</v>
       </c>
-      <c r="E18" s="2">
-        <v>1</v>
-      </c>
-      <c r="F18" s="2">
-        <v>1</v>
-      </c>
-      <c r="G18" s="2">
-        <v>0</v>
-      </c>
-      <c r="J18" s="2">
-        <v>2</v>
-      </c>
-      <c r="K18" s="2">
-        <v>2</v>
-      </c>
-      <c r="L18" s="2">
-        <v>1</v>
-      </c>
-      <c r="M18" s="2">
-        <v>0</v>
-      </c>
-      <c r="N18" s="2">
-        <v>0</v>
-      </c>
-      <c r="O18" s="2">
+      <c r="E18" s="9">
+        <v>1</v>
+      </c>
+      <c r="F18" s="9">
+        <v>1</v>
+      </c>
+      <c r="G18" s="9">
+        <v>0</v>
+      </c>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9">
+        <v>2</v>
+      </c>
+      <c r="K18" s="9">
+        <v>2</v>
+      </c>
+      <c r="L18" s="9">
+        <v>1</v>
+      </c>
+      <c r="M18" s="9">
+        <v>0</v>
+      </c>
+      <c r="N18" s="9">
+        <v>0</v>
+      </c>
+      <c r="O18" s="9">
         <v>3</v>
       </c>
-      <c r="P18" s="2">
+      <c r="P18" s="9">
         <v>0.5</v>
       </c>
-      <c r="Q18" s="2">
-        <v>0</v>
-      </c>
-      <c r="R18" s="3" t="s">
+      <c r="Q18" s="9">
+        <v>0</v>
+      </c>
+      <c r="R18" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="S18" s="2" t="s">
+      <c r="S18" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="T18" s="2">
-        <v>1</v>
-      </c>
-      <c r="U18" s="2">
-        <v>1</v>
-      </c>
-      <c r="V18" s="2">
-        <v>2</v>
-      </c>
-      <c r="W18" s="3">
-        <v>0</v>
-      </c>
-      <c r="X18" s="2">
+      <c r="T18" s="9">
+        <v>1</v>
+      </c>
+      <c r="U18" s="9">
+        <v>1</v>
+      </c>
+      <c r="V18" s="9">
+        <v>2</v>
+      </c>
+      <c r="W18" s="8">
+        <v>0</v>
+      </c>
+      <c r="X18" s="9">
         <v>10000001</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Y18" s="8">
         <v>20000001</v>
       </c>
-      <c r="Z18" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB18" s="2" t="s">
-        <v>102</v>
+      <c r="Z18" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="9" t="s">
+        <v>103</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="2:28">
-      <c r="B19" s="3">
+    <row r="19" customHeight="1" spans="1:28">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8">
         <v>30000006</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="D19" s="2">
+      <c r="C19" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D19" s="9">
         <v>10000002</v>
       </c>
-      <c r="E19" s="3">
-        <v>1</v>
-      </c>
-      <c r="F19" s="3">
-        <v>1</v>
-      </c>
-      <c r="G19" s="3">
-        <v>0</v>
-      </c>
-      <c r="J19" s="3">
-        <v>2</v>
-      </c>
-      <c r="K19" s="3">
-        <v>1</v>
-      </c>
-      <c r="L19" s="3">
+      <c r="E19" s="8">
+        <v>1</v>
+      </c>
+      <c r="F19" s="8">
+        <v>1</v>
+      </c>
+      <c r="G19" s="8">
+        <v>0</v>
+      </c>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8">
+        <v>2</v>
+      </c>
+      <c r="K19" s="8">
+        <v>1</v>
+      </c>
+      <c r="L19" s="8">
         <v>0.2</v>
       </c>
-      <c r="M19" s="3">
-        <v>0</v>
-      </c>
-      <c r="N19" s="3">
+      <c r="M19" s="8">
+        <v>0</v>
+      </c>
+      <c r="N19" s="8">
         <v>10</v>
       </c>
-      <c r="O19" s="3">
+      <c r="O19" s="8">
         <v>5</v>
       </c>
-      <c r="P19" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="3">
-        <v>0</v>
-      </c>
-      <c r="R19" s="3" t="s">
+      <c r="P19" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="8">
+        <v>0</v>
+      </c>
+      <c r="R19" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="S19" s="3" t="s">
+      <c r="S19" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="T19" s="3">
+      <c r="T19" s="8">
         <v>3</v>
       </c>
-      <c r="U19" s="3">
-        <v>0</v>
-      </c>
-      <c r="V19" s="3">
-        <v>0</v>
-      </c>
-      <c r="W19" s="3">
-        <v>0</v>
-      </c>
-      <c r="X19" s="3">
+      <c r="U19" s="8">
+        <v>0</v>
+      </c>
+      <c r="V19" s="8">
+        <v>0</v>
+      </c>
+      <c r="W19" s="8">
+        <v>0</v>
+      </c>
+      <c r="X19" s="8">
         <v>10000001</v>
       </c>
-      <c r="Y19" s="3">
+      <c r="Y19" s="8">
         <v>20000001</v>
       </c>
-      <c r="Z19" s="3">
+      <c r="Z19" s="8">
         <v>0</v>
       </c>
       <c r="AA19" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB19" s="3" t="s">
         <v>105</v>
       </c>
+      <c r="AB19" s="8" t="s">
+        <v>106</v>
+      </c>
     </row>
-    <row r="20" customHeight="1" spans="2:28">
-      <c r="B20" s="3">
+    <row r="20" customHeight="1" spans="1:28">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8">
         <v>30000007</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D20" s="2">
+      <c r="C20" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D20" s="9">
         <v>10000003</v>
       </c>
-      <c r="E20" s="3">
-        <v>1</v>
-      </c>
-      <c r="F20" s="3">
-        <v>1</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>2</v>
-      </c>
-      <c r="K20" s="3">
-        <v>2</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="E20" s="8">
+        <v>1</v>
+      </c>
+      <c r="F20" s="8">
+        <v>1</v>
+      </c>
+      <c r="G20" s="8">
+        <v>0</v>
+      </c>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8">
+        <v>2</v>
+      </c>
+      <c r="K20" s="8">
+        <v>2</v>
+      </c>
+      <c r="L20" s="8">
         <v>0.2</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="M20" s="8">
+        <v>0</v>
+      </c>
+      <c r="N20" s="8">
         <v>10</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="8">
         <v>3</v>
       </c>
-      <c r="P20" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3" t="s">
+      <c r="P20" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="8">
+        <v>0</v>
+      </c>
+      <c r="R20" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="S20" s="3" t="s">
+      <c r="S20" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
-      <c r="U20" s="3">
-        <v>1</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="T20" s="8">
+        <v>0</v>
+      </c>
+      <c r="U20" s="8">
+        <v>1</v>
+      </c>
+      <c r="V20" s="8">
         <v>3</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
-      <c r="X20" s="3">
+      <c r="W20" s="8">
+        <v>0</v>
+      </c>
+      <c r="X20" s="8">
         <v>10000001</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Y20" s="8">
         <v>20000001</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB20" s="3" t="s">
-        <v>107</v>
+      <c r="Z20" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="8" t="s">
+        <v>108</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="2:28">
-      <c r="B21" s="3">
+    <row r="21" customHeight="1" spans="1:28">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8">
         <v>30000008</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="D21" s="2">
+      <c r="C21" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D21" s="9">
         <v>10000004</v>
       </c>
-      <c r="E21" s="3">
-        <v>1</v>
-      </c>
-      <c r="F21" s="3">
-        <v>1</v>
-      </c>
-      <c r="G21" s="3">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3">
-        <v>2</v>
-      </c>
-      <c r="K21" s="3">
+      <c r="E21" s="8">
+        <v>1</v>
+      </c>
+      <c r="F21" s="8">
+        <v>1</v>
+      </c>
+      <c r="G21" s="8">
+        <v>0</v>
+      </c>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8">
+        <v>2</v>
+      </c>
+      <c r="K21" s="8">
         <v>3</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="8">
         <v>0.8</v>
       </c>
-      <c r="M21" s="3">
-        <v>0</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="M21" s="8">
+        <v>0</v>
+      </c>
+      <c r="N21" s="8">
         <v>10</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="8">
         <v>5</v>
       </c>
-      <c r="P21" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>0</v>
-      </c>
-      <c r="R21" s="3" t="s">
+      <c r="P21" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="8">
+        <v>0</v>
+      </c>
+      <c r="R21" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="S21" s="3" t="s">
+      <c r="S21" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="T21" s="3">
-        <v>1</v>
-      </c>
-      <c r="U21" s="3">
-        <v>1</v>
-      </c>
-      <c r="V21" s="3">
+      <c r="T21" s="8">
+        <v>1</v>
+      </c>
+      <c r="U21" s="8">
+        <v>1</v>
+      </c>
+      <c r="V21" s="8">
         <v>4</v>
       </c>
-      <c r="W21" s="3">
-        <v>0</v>
-      </c>
-      <c r="X21" s="3">
+      <c r="W21" s="8">
+        <v>0</v>
+      </c>
+      <c r="X21" s="8">
         <v>10000001</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="8">
         <v>20000001</v>
       </c>
-      <c r="Z21" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="3">
+      <c r="Z21" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="8">
         <v>10000014</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>109</v>
+      <c r="AB21" s="8" t="s">
+        <v>110</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="2:28">
-      <c r="B22" s="3">
+    <row r="22" customHeight="1" spans="1:28">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8">
         <v>30000009</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D22" s="2">
+      <c r="C22" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="D22" s="9">
         <v>10000005</v>
       </c>
-      <c r="E22" s="3">
-        <v>1</v>
-      </c>
-      <c r="F22" s="3">
-        <v>1</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>2</v>
-      </c>
-      <c r="K22" s="3">
+      <c r="E22" s="8">
+        <v>1</v>
+      </c>
+      <c r="F22" s="8">
+        <v>1</v>
+      </c>
+      <c r="G22" s="8">
+        <v>0</v>
+      </c>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8">
+        <v>2</v>
+      </c>
+      <c r="K22" s="8">
         <v>4</v>
       </c>
-      <c r="L22" s="3">
-        <v>1</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
-      <c r="O22" s="3">
+      <c r="L22" s="8">
+        <v>1</v>
+      </c>
+      <c r="M22" s="8">
+        <v>0</v>
+      </c>
+      <c r="N22" s="8">
+        <v>0</v>
+      </c>
+      <c r="O22" s="8">
         <v>3600</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3" t="s">
+      <c r="P22" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="8">
+        <v>0</v>
+      </c>
+      <c r="R22" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="S22" s="3" t="s">
+      <c r="S22" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="T22" s="3">
+      <c r="T22" s="8">
         <v>3</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
-      </c>
-      <c r="V22" s="3">
-        <v>0</v>
-      </c>
-      <c r="W22" s="3">
-        <v>0</v>
-      </c>
-      <c r="X22" s="3">
+      <c r="U22" s="8">
+        <v>0</v>
+      </c>
+      <c r="V22" s="8">
+        <v>0</v>
+      </c>
+      <c r="W22" s="8">
+        <v>0</v>
+      </c>
+      <c r="X22" s="8">
         <v>10000001</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Y22" s="8">
         <v>20000001</v>
       </c>
       <c r="Z22" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="3" t="s">
         <v>112</v>
       </c>
+      <c r="AA22" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="8" t="s">
+        <v>113</v>
+      </c>
     </row>
-    <row r="23" customHeight="1" spans="2:28">
-      <c r="B23" s="3">
+    <row r="23" customHeight="1" spans="1:28">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8">
         <v>30000010</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D23" s="2">
+      <c r="C23" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D23" s="9">
         <v>10000006</v>
       </c>
-      <c r="E23" s="3">
-        <v>1</v>
-      </c>
-      <c r="F23" s="3">
-        <v>2</v>
-      </c>
-      <c r="G23" s="3">
-        <v>0</v>
-      </c>
-      <c r="J23" s="3">
-        <v>2</v>
-      </c>
-      <c r="K23" s="3">
-        <v>2</v>
-      </c>
-      <c r="L23" s="3">
+      <c r="E23" s="8">
+        <v>1</v>
+      </c>
+      <c r="F23" s="8">
+        <v>2</v>
+      </c>
+      <c r="G23" s="8">
+        <v>0</v>
+      </c>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8">
+        <v>2</v>
+      </c>
+      <c r="K23" s="8">
+        <v>2</v>
+      </c>
+      <c r="L23" s="8">
         <v>0.2</v>
       </c>
-      <c r="M23" s="3">
-        <v>0</v>
-      </c>
-      <c r="N23" s="3">
+      <c r="M23" s="8">
+        <v>0</v>
+      </c>
+      <c r="N23" s="8">
         <v>10</v>
       </c>
-      <c r="O23" s="3">
+      <c r="O23" s="8">
         <v>4</v>
       </c>
-      <c r="P23" s="3">
-        <v>2</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>0</v>
-      </c>
-      <c r="R23" s="3" t="s">
+      <c r="P23" s="8">
+        <v>2</v>
+      </c>
+      <c r="Q23" s="8">
+        <v>0</v>
+      </c>
+      <c r="R23" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="S23" s="3" t="s">
+      <c r="S23" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="T23" s="3">
-        <v>1</v>
-      </c>
-      <c r="U23" s="3">
-        <v>1</v>
-      </c>
-      <c r="V23" s="3">
+      <c r="T23" s="8">
+        <v>1</v>
+      </c>
+      <c r="U23" s="8">
+        <v>1</v>
+      </c>
+      <c r="V23" s="8">
         <v>3</v>
       </c>
-      <c r="W23" s="3">
-        <v>0</v>
-      </c>
-      <c r="X23" s="3">
+      <c r="W23" s="8">
+        <v>0</v>
+      </c>
+      <c r="X23" s="8">
         <v>10000001</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Y23" s="8">
         <v>20000001</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="Z23" s="8">
         <v>0</v>
       </c>
       <c r="AA23" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="AB23" s="3" t="s">
         <v>115</v>
       </c>
+      <c r="AB23" s="8" t="s">
+        <v>116</v>
+      </c>
     </row>
-    <row r="24" customHeight="1" spans="2:28">
-      <c r="B24" s="3">
+    <row r="24" customHeight="1" spans="1:28">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8">
         <v>30000011</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D24" s="2">
+      <c r="C24" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="D24" s="9">
         <v>10000007</v>
       </c>
-      <c r="E24" s="3">
-        <v>1</v>
-      </c>
-      <c r="F24" s="3">
-        <v>2</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>2</v>
-      </c>
-      <c r="K24" s="3">
-        <v>2</v>
-      </c>
-      <c r="L24" s="3">
+      <c r="E24" s="8">
+        <v>1</v>
+      </c>
+      <c r="F24" s="8">
+        <v>2</v>
+      </c>
+      <c r="G24" s="8">
+        <v>0</v>
+      </c>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8">
+        <v>2</v>
+      </c>
+      <c r="K24" s="8">
+        <v>2</v>
+      </c>
+      <c r="L24" s="8">
         <v>0.2</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3">
+      <c r="M24" s="8">
+        <v>0</v>
+      </c>
+      <c r="N24" s="8">
         <v>10</v>
       </c>
-      <c r="O24" s="3">
+      <c r="O24" s="8">
         <v>3</v>
       </c>
-      <c r="P24" s="3">
+      <c r="P24" s="8">
         <v>0.5</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
-      <c r="R24" s="3" t="s">
+      <c r="Q24" s="8">
+        <v>0</v>
+      </c>
+      <c r="R24" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="S24" s="3" t="s">
+      <c r="S24" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="T24" s="3">
-        <v>2</v>
-      </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
-      <c r="X24" s="3">
+      <c r="T24" s="8">
+        <v>2</v>
+      </c>
+      <c r="U24" s="8">
+        <v>0</v>
+      </c>
+      <c r="V24" s="8">
+        <v>0</v>
+      </c>
+      <c r="W24" s="8">
+        <v>0</v>
+      </c>
+      <c r="X24" s="8">
         <v>10000001</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Y24" s="8">
         <v>20000001</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="Z24" s="8">
         <v>0</v>
       </c>
       <c r="AA24" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="AB24" s="3" t="s">
         <v>118</v>
       </c>
+      <c r="AB24" s="8" t="s">
+        <v>119</v>
+      </c>
     </row>
-    <row r="25" customHeight="1" spans="2:28">
-      <c r="B25" s="3">
+    <row r="25" customHeight="1" spans="1:28">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8">
         <v>30000012</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D25" s="3">
+      <c r="C25" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="D25" s="8">
         <v>10000001</v>
       </c>
-      <c r="E25" s="3">
-        <v>1</v>
-      </c>
-      <c r="F25" s="3">
-        <v>2</v>
-      </c>
-      <c r="G25" s="3">
-        <v>0</v>
-      </c>
-      <c r="J25" s="3">
-        <v>2</v>
-      </c>
-      <c r="K25" s="3">
+      <c r="E25" s="8">
+        <v>1</v>
+      </c>
+      <c r="F25" s="8">
+        <v>2</v>
+      </c>
+      <c r="G25" s="8">
+        <v>0</v>
+      </c>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8">
+        <v>2</v>
+      </c>
+      <c r="K25" s="8">
         <v>4</v>
       </c>
-      <c r="L25" s="3">
-        <v>1</v>
-      </c>
-      <c r="M25" s="3">
-        <v>0</v>
-      </c>
-      <c r="N25" s="3">
-        <v>0</v>
-      </c>
-      <c r="O25" s="3">
+      <c r="L25" s="8">
+        <v>1</v>
+      </c>
+      <c r="M25" s="8">
+        <v>0</v>
+      </c>
+      <c r="N25" s="8">
+        <v>0</v>
+      </c>
+      <c r="O25" s="8">
         <v>3600</v>
       </c>
-      <c r="P25" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="3">
-        <v>0</v>
-      </c>
-      <c r="R25" s="3" t="s">
+      <c r="P25" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="8">
+        <v>0</v>
+      </c>
+      <c r="R25" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="S25" s="3" t="s">
+      <c r="S25" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="T25" s="3">
+      <c r="T25" s="8">
         <v>5</v>
       </c>
-      <c r="U25" s="3">
-        <v>0</v>
-      </c>
-      <c r="V25" s="3">
-        <v>0</v>
-      </c>
-      <c r="W25" s="3">
-        <v>0</v>
-      </c>
-      <c r="X25" s="3">
+      <c r="U25" s="8">
+        <v>0</v>
+      </c>
+      <c r="V25" s="8">
+        <v>0</v>
+      </c>
+      <c r="W25" s="8">
+        <v>0</v>
+      </c>
+      <c r="X25" s="8">
         <v>10000001</v>
       </c>
-      <c r="Y25" s="3">
+      <c r="Y25" s="8">
         <v>20000001</v>
       </c>
-      <c r="Z25" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA25" s="3">
+      <c r="Z25" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="8">
         <v>10000021</v>
       </c>
-      <c r="AB25" s="3" t="s">
-        <v>120</v>
+      <c r="AB25" s="8" t="s">
+        <v>121</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="2:28">
-      <c r="B26" s="3">
+    <row r="26" customHeight="1" spans="1:28">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8">
         <v>30000013</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D26" s="3">
+      <c r="C26" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="D26" s="8">
         <v>10000002</v>
       </c>
-      <c r="E26" s="3">
-        <v>1</v>
-      </c>
-      <c r="F26" s="3">
-        <v>1</v>
-      </c>
-      <c r="G26" s="3">
-        <v>0</v>
-      </c>
-      <c r="J26" s="3">
-        <v>2</v>
-      </c>
-      <c r="K26" s="3">
+      <c r="E26" s="8">
+        <v>1</v>
+      </c>
+      <c r="F26" s="8">
+        <v>1</v>
+      </c>
+      <c r="G26" s="8">
+        <v>0</v>
+      </c>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8">
+        <v>2</v>
+      </c>
+      <c r="K26" s="8">
         <v>5</v>
       </c>
-      <c r="L26" s="3">
+      <c r="L26" s="8">
         <v>0.6</v>
       </c>
-      <c r="M26" s="3">
-        <v>0</v>
-      </c>
-      <c r="N26" s="3">
+      <c r="M26" s="8">
+        <v>0</v>
+      </c>
+      <c r="N26" s="8">
         <v>10</v>
       </c>
-      <c r="O26" s="3">
+      <c r="O26" s="8">
         <v>3</v>
       </c>
-      <c r="P26" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>0</v>
-      </c>
-      <c r="R26" s="3" t="s">
+      <c r="P26" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="8">
+        <v>0</v>
+      </c>
+      <c r="R26" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="S26" s="3" t="s">
+      <c r="S26" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="T26" s="3">
-        <v>1</v>
-      </c>
-      <c r="U26" s="3">
-        <v>1</v>
-      </c>
-      <c r="V26" s="3">
+      <c r="T26" s="8">
+        <v>1</v>
+      </c>
+      <c r="U26" s="8">
+        <v>1</v>
+      </c>
+      <c r="V26" s="8">
         <v>3</v>
       </c>
-      <c r="W26" s="3">
-        <v>0</v>
-      </c>
-      <c r="X26" s="3">
+      <c r="W26" s="8">
+        <v>0</v>
+      </c>
+      <c r="X26" s="8">
         <v>10000001</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Y26" s="8">
         <v>20000001</v>
       </c>
-      <c r="Z26" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA26" s="3">
+      <c r="Z26" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="8">
         <v>10000022</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>122</v>
+      <c r="AB26" s="8" t="s">
+        <v>123</v>
       </c>
     </row>
-    <row r="27" customHeight="1" spans="2:28">
-      <c r="B27" s="3">
+    <row r="27" customHeight="1" spans="1:28">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8">
         <v>30000014</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D27" s="3">
+      <c r="C27" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D27" s="8">
         <v>10000003</v>
       </c>
-      <c r="E27" s="3">
-        <v>1</v>
-      </c>
-      <c r="F27" s="3">
-        <v>1</v>
-      </c>
-      <c r="G27" s="3">
-        <v>0</v>
-      </c>
-      <c r="J27" s="3">
-        <v>2</v>
-      </c>
-      <c r="K27" s="3">
+      <c r="E27" s="8">
+        <v>1</v>
+      </c>
+      <c r="F27" s="8">
+        <v>1</v>
+      </c>
+      <c r="G27" s="8">
+        <v>0</v>
+      </c>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8">
+        <v>2</v>
+      </c>
+      <c r="K27" s="8">
         <v>5</v>
       </c>
-      <c r="L27" s="3">
+      <c r="L27" s="8">
         <v>0.3</v>
       </c>
-      <c r="M27" s="3">
-        <v>0</v>
-      </c>
-      <c r="N27" s="3">
+      <c r="M27" s="8">
+        <v>0</v>
+      </c>
+      <c r="N27" s="8">
         <v>10</v>
       </c>
-      <c r="O27" s="3">
+      <c r="O27" s="8">
         <v>3</v>
       </c>
-      <c r="P27" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>0</v>
-      </c>
-      <c r="R27" s="3" t="s">
+      <c r="P27" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="8">
+        <v>0</v>
+      </c>
+      <c r="R27" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="S27" s="3" t="s">
+      <c r="S27" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="T27" s="3">
-        <v>2</v>
-      </c>
-      <c r="U27" s="3">
-        <v>0</v>
-      </c>
-      <c r="V27" s="3">
-        <v>0</v>
-      </c>
-      <c r="W27" s="3">
-        <v>0</v>
-      </c>
-      <c r="X27" s="3">
+      <c r="T27" s="8">
+        <v>2</v>
+      </c>
+      <c r="U27" s="8">
+        <v>0</v>
+      </c>
+      <c r="V27" s="8">
+        <v>0</v>
+      </c>
+      <c r="W27" s="8">
+        <v>0</v>
+      </c>
+      <c r="X27" s="8">
         <v>10000001</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Y27" s="8">
         <v>20000001</v>
       </c>
-      <c r="Z27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA27" s="3">
+      <c r="Z27" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="8">
         <v>10000023</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>124</v>
+      <c r="AB27" s="8" t="s">
+        <v>125</v>
       </c>
     </row>
-    <row r="28" customHeight="1" spans="2:28">
-      <c r="B28" s="3">
+    <row r="28" customHeight="1" spans="1:28">
+      <c r="A28" s="8"/>
+      <c r="B28" s="8">
         <v>30000015</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D28" s="3">
+      <c r="C28" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="D28" s="8">
         <v>10000004</v>
       </c>
-      <c r="E28" s="3">
-        <v>1</v>
-      </c>
-      <c r="F28" s="3">
-        <v>1</v>
-      </c>
-      <c r="G28" s="3">
-        <v>0</v>
-      </c>
-      <c r="J28" s="3">
-        <v>2</v>
-      </c>
-      <c r="K28" s="3">
+      <c r="E28" s="8">
+        <v>1</v>
+      </c>
+      <c r="F28" s="8">
+        <v>1</v>
+      </c>
+      <c r="G28" s="8">
+        <v>0</v>
+      </c>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8">
+        <v>2</v>
+      </c>
+      <c r="K28" s="8">
         <v>4</v>
       </c>
-      <c r="L28" s="3">
-        <v>1</v>
-      </c>
-      <c r="M28" s="3">
-        <v>0</v>
-      </c>
-      <c r="N28" s="3">
-        <v>0</v>
-      </c>
-      <c r="O28" s="3">
+      <c r="L28" s="8">
+        <v>1</v>
+      </c>
+      <c r="M28" s="8">
+        <v>0</v>
+      </c>
+      <c r="N28" s="8">
+        <v>0</v>
+      </c>
+      <c r="O28" s="8">
         <v>3600</v>
       </c>
-      <c r="P28" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="3">
-        <v>0</v>
-      </c>
-      <c r="R28" s="3" t="s">
+      <c r="P28" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="8">
+        <v>0</v>
+      </c>
+      <c r="R28" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="S28" s="3" t="s">
+      <c r="S28" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="T28" s="3">
-        <v>0</v>
-      </c>
-      <c r="U28" s="3">
-        <v>1</v>
-      </c>
-      <c r="V28" s="3">
+      <c r="T28" s="8">
+        <v>0</v>
+      </c>
+      <c r="U28" s="8">
+        <v>1</v>
+      </c>
+      <c r="V28" s="8">
         <v>4</v>
       </c>
-      <c r="W28" s="3">
-        <v>0</v>
-      </c>
-      <c r="X28" s="3">
+      <c r="W28" s="8">
+        <v>0</v>
+      </c>
+      <c r="X28" s="8">
         <v>10000001</v>
       </c>
-      <c r="Y28" s="3">
+      <c r="Y28" s="8">
         <v>20000001</v>
       </c>
-      <c r="Z28" s="3">
+      <c r="Z28" s="8">
         <v>0</v>
       </c>
       <c r="AA28" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="AB28" s="3" t="s">
         <v>127</v>
       </c>
+      <c r="AB28" s="8" t="s">
+        <v>128</v>
+      </c>
     </row>
-    <row r="29" customHeight="1" spans="2:28">
-      <c r="B29" s="3">
+    <row r="29" customHeight="1" spans="1:28">
+      <c r="A29" s="8"/>
+      <c r="B29" s="8">
         <v>30000016</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D29" s="3">
+      <c r="C29" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="D29" s="8">
         <v>10000005</v>
       </c>
-      <c r="E29" s="3">
-        <v>1</v>
-      </c>
-      <c r="F29" s="3">
-        <v>2</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>2</v>
-      </c>
-      <c r="K29" s="3">
-        <v>2</v>
-      </c>
-      <c r="L29" s="3">
+      <c r="E29" s="8">
+        <v>1</v>
+      </c>
+      <c r="F29" s="8">
+        <v>2</v>
+      </c>
+      <c r="G29" s="8">
+        <v>0</v>
+      </c>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8">
+        <v>2</v>
+      </c>
+      <c r="K29" s="8">
+        <v>2</v>
+      </c>
+      <c r="L29" s="8">
         <v>0.2</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
-      <c r="N29" s="3">
+      <c r="M29" s="8">
+        <v>0</v>
+      </c>
+      <c r="N29" s="8">
         <v>10</v>
       </c>
-      <c r="O29" s="3">
+      <c r="O29" s="8">
         <v>5</v>
       </c>
-      <c r="P29" s="3">
+      <c r="P29" s="8">
         <v>0.1</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3" t="s">
+      <c r="Q29" s="8">
+        <v>0</v>
+      </c>
+      <c r="R29" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="S29" s="3" t="s">
+      <c r="S29" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="T29" s="3">
+      <c r="T29" s="8">
         <v>6</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-      <c r="X29" s="3">
+      <c r="U29" s="8">
+        <v>0</v>
+      </c>
+      <c r="V29" s="8">
+        <v>0</v>
+      </c>
+      <c r="W29" s="8">
+        <v>0</v>
+      </c>
+      <c r="X29" s="8">
         <v>10000001</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="8">
         <v>20000001</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>129</v>
+      <c r="Z29" s="8"/>
+      <c r="AA29" s="8"/>
+      <c r="AB29" s="8" t="s">
+        <v>130</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="2:28">
-      <c r="B30" s="3">
+    <row r="30" customHeight="1" spans="1:28">
+      <c r="A30" s="8"/>
+      <c r="B30" s="8">
         <v>30000017</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D30" s="3">
+      <c r="C30" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="D30" s="8">
         <v>10000006</v>
       </c>
-      <c r="E30" s="3">
-        <v>1</v>
-      </c>
-      <c r="F30" s="3">
-        <v>2</v>
-      </c>
-      <c r="G30" s="3">
-        <v>0</v>
-      </c>
-      <c r="N30" s="3">
+      <c r="E30" s="8">
+        <v>1</v>
+      </c>
+      <c r="F30" s="8">
+        <v>2</v>
+      </c>
+      <c r="G30" s="8">
+        <v>0</v>
+      </c>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
+      <c r="N30" s="8">
         <v>10</v>
       </c>
-      <c r="O30" s="3">
+      <c r="O30" s="8">
         <v>5</v>
       </c>
-      <c r="R30" s="3" t="s">
+      <c r="P30" s="8"/>
+      <c r="Q30" s="8"/>
+      <c r="R30" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="W30" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y30" s="3">
+      <c r="S30" s="8"/>
+      <c r="T30" s="8"/>
+      <c r="U30" s="8"/>
+      <c r="V30" s="8"/>
+      <c r="W30" s="8">
+        <v>0</v>
+      </c>
+      <c r="X30" s="8"/>
+      <c r="Y30" s="8">
         <v>20000001</v>
       </c>
-      <c r="AB30" s="3" t="s">
-        <v>131</v>
+      <c r="Z30" s="8"/>
+      <c r="AA30" s="8"/>
+      <c r="AB30" s="8" t="s">
+        <v>132</v>
       </c>
     </row>
-    <row r="31" customHeight="1" spans="2:28">
-      <c r="B31" s="3">
+    <row r="31" customHeight="1" spans="1:28">
+      <c r="A31" s="8"/>
+      <c r="B31" s="8">
         <v>30000018</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="D31" s="3">
+      <c r="C31" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="D31" s="8">
         <v>10000007</v>
       </c>
-      <c r="E31" s="3">
-        <v>1</v>
-      </c>
-      <c r="F31" s="3">
-        <v>2</v>
-      </c>
-      <c r="G31" s="3">
-        <v>0</v>
-      </c>
-      <c r="J31" s="3">
-        <v>2</v>
-      </c>
-      <c r="K31" s="3">
-        <v>2</v>
-      </c>
-      <c r="L31" s="3">
+      <c r="E31" s="8">
+        <v>1</v>
+      </c>
+      <c r="F31" s="8">
+        <v>2</v>
+      </c>
+      <c r="G31" s="8">
+        <v>0</v>
+      </c>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="8">
+        <v>2</v>
+      </c>
+      <c r="K31" s="8">
+        <v>2</v>
+      </c>
+      <c r="L31" s="8">
         <v>0.2</v>
       </c>
-      <c r="M31" s="3">
-        <v>0</v>
-      </c>
-      <c r="N31" s="3">
+      <c r="M31" s="8">
+        <v>0</v>
+      </c>
+      <c r="N31" s="8">
         <v>10</v>
       </c>
-      <c r="O31" s="3">
+      <c r="O31" s="8">
         <v>3</v>
       </c>
-      <c r="P31" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="3">
-        <v>0</v>
-      </c>
-      <c r="R31" s="3" t="s">
+      <c r="P31" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="8">
+        <v>0</v>
+      </c>
+      <c r="R31" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="S31" s="3" t="s">
+      <c r="S31" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="T31" s="3">
-        <v>1</v>
-      </c>
-      <c r="U31" s="3">
-        <v>1</v>
-      </c>
-      <c r="V31" s="3">
+      <c r="T31" s="8">
+        <v>1</v>
+      </c>
+      <c r="U31" s="8">
+        <v>1</v>
+      </c>
+      <c r="V31" s="8">
         <v>4</v>
       </c>
-      <c r="W31" s="3">
-        <v>0</v>
-      </c>
-      <c r="X31" s="3">
+      <c r="W31" s="8">
+        <v>0</v>
+      </c>
+      <c r="X31" s="8">
         <v>10000001</v>
       </c>
-      <c r="Y31" s="3">
+      <c r="Y31" s="8">
         <v>20000001</v>
       </c>
-      <c r="Z31" s="3">
+      <c r="Z31" s="8">
         <v>0</v>
       </c>
       <c r="AA31" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="AB31" s="3" t="s">
         <v>134</v>
+      </c>
+      <c r="AB31" s="8" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -631,7 +631,7 @@
     <t>近战普通攻击1</t>
   </si>
   <si>
-    <t>Skill_MeleeBasicAttack</t>
+    <t>Skill_近战普通攻击</t>
   </si>
   <si>
     <t>attack</t>
@@ -643,7 +643,7 @@
     <t>远程普通攻击1</t>
   </si>
   <si>
-    <t>Skill_RangedBasicAttack</t>
+    <t>Skill_远程普通攻击</t>
   </si>
   <si>
     <t>gongjian</t>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="138">
   <si>
     <t>##var</t>
   </si>
@@ -655,79 +655,85 @@
     <t>箭雨</t>
   </si>
   <si>
+    <t>Skill_箭雨</t>
+  </si>
+  <si>
+    <t>jianyu</t>
+  </si>
+  <si>
+    <t>对全体敌人射出箭矢，造成伤害。</t>
+  </si>
+  <si>
+    <t>淘汰之刃</t>
+  </si>
+  <si>
+    <t>Skill_淘汰之刃</t>
+  </si>
+  <si>
+    <t>35000,3000,40000,5000</t>
+  </si>
+  <si>
+    <t>对敌人造成350%物理伤害，如果敌人生命值低于30%，造成400%物理伤害；若成功击杀，将额外恢复50%的怒气。</t>
+  </si>
+  <si>
+    <t>神之力量</t>
+  </si>
+  <si>
+    <t>Skill_神之力量</t>
+  </si>
+  <si>
+    <t>10000006,10000012</t>
+  </si>
+  <si>
+    <t>增加额外的100%攻击力,持续5秒,并且自身的普通攻击变成溅射伤害。</t>
+  </si>
+  <si>
+    <t>无敌击</t>
+  </si>
+  <si>
+    <t>Skill_无敌击</t>
+  </si>
+  <si>
+    <t>快速瞬间出剑5次攻击随机敌人,期间处于无敌状态,无法被攻击。</t>
+  </si>
+  <si>
+    <t>极寒领域</t>
+  </si>
+  <si>
+    <t>在目标范围造成大面积持续伤害,每秒造成150%伤害,持续3秒。</t>
+  </si>
+  <si>
+    <t>守护天使</t>
+  </si>
+  <si>
+    <t>Skill_守护天使</t>
+  </si>
+  <si>
+    <t>10000003,10000004</t>
+  </si>
+  <si>
+    <t>使周围的友方单位对物理攻击免疫,且每秒恢复2%生命值,持续5秒。</t>
+  </si>
+  <si>
+    <t>混乱之雨</t>
+  </si>
+  <si>
+    <t>召唤一个地狱火协助自己进行战斗，持续5秒(地狱火继承角色100%属性,拥有燃烧技能,持续对附近单位每秒造成100%伤害)。</t>
+  </si>
+  <si>
+    <t>怒吼</t>
+  </si>
+  <si>
+    <t>10000001,10000006</t>
+  </si>
+  <si>
+    <t>每次攻击有概率强迫附近单位攻击自己且自身受到的伤害降低50%,持续3秒。</t>
+  </si>
+  <si>
+    <t>反击螺旋</t>
+  </si>
+  <si>
     <t>Skill_AreaDamage</t>
-  </si>
-  <si>
-    <t>jianyu</t>
-  </si>
-  <si>
-    <t>对全体敌人射出箭矢，造成伤害。</t>
-  </si>
-  <si>
-    <t>淘汰之刃</t>
-  </si>
-  <si>
-    <t>Skill_淘汰之刃</t>
-  </si>
-  <si>
-    <t>35000,3000,40000,5000</t>
-  </si>
-  <si>
-    <t>对敌人造成350%物理伤害，如果敌人生命值低于30%，造成400%物理伤害；若成功击杀，将额外恢复50%的怒气。</t>
-  </si>
-  <si>
-    <t>神之力量</t>
-  </si>
-  <si>
-    <t>Skill_AddBuff</t>
-  </si>
-  <si>
-    <t>10000006,10000012</t>
-  </si>
-  <si>
-    <t>增加额外的100%攻击力,持续5秒,并且自身的普通攻击变成溅射伤害。</t>
-  </si>
-  <si>
-    <t>无敌击</t>
-  </si>
-  <si>
-    <t>Skill_无敌击</t>
-  </si>
-  <si>
-    <t>快速瞬间出剑5次攻击随机敌人,期间处于无敌状态,无法被攻击。</t>
-  </si>
-  <si>
-    <t>极寒领域</t>
-  </si>
-  <si>
-    <t>在目标范围造成大面积持续伤害,每秒造成150%伤害,持续3秒。</t>
-  </si>
-  <si>
-    <t>守护天使</t>
-  </si>
-  <si>
-    <t>10000003,10000004</t>
-  </si>
-  <si>
-    <t>使周围的友方单位对物理攻击免疫,且每秒恢复2%生命值,持续5秒。</t>
-  </si>
-  <si>
-    <t>混乱之雨</t>
-  </si>
-  <si>
-    <t>召唤一个地狱火协助自己进行战斗，持续5秒(地狱火继承角色100%属性,拥有燃烧技能,持续对附近单位每秒造成100%伤害)。</t>
-  </si>
-  <si>
-    <t>怒吼</t>
-  </si>
-  <si>
-    <t>10000001,10000006</t>
-  </si>
-  <si>
-    <t>每次攻击有概率强迫附近单位攻击自己且自身受到的伤害降低50%,持续3秒。</t>
-  </si>
-  <si>
-    <t>反击螺旋</t>
   </si>
   <si>
     <t>在受到攻击时有17%的概率触发旋风斩,对附近单位造成150%伤害。</t>
@@ -2861,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I12" s="8"/>
       <c r="J12" s="8">
@@ -2916,10 +2922,10 @@
         <v>0</v>
       </c>
       <c r="AA12" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AB12" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="1:28">
@@ -2928,7 +2934,7 @@
         <v>20000006</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D13" s="8">
         <v>10000003</v>
@@ -2999,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="AB13" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:28">
@@ -3008,7 +3014,7 @@
         <v>30000001</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D14" s="8">
         <v>10000004</v>
@@ -3076,10 +3082,10 @@
         <v>0</v>
       </c>
       <c r="AA14" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AB14" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:28">
@@ -3088,7 +3094,7 @@
         <v>30000002</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D15" s="8">
         <v>10000005</v>
@@ -3103,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="I15" s="8"/>
       <c r="J15" s="8">
@@ -3161,7 +3167,7 @@
         <v>0</v>
       </c>
       <c r="AB15" s="8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="1:28">
@@ -3170,7 +3176,7 @@
         <v>30000003</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D16" s="8">
         <v>10000006</v>
@@ -3238,10 +3244,10 @@
         <v>0</v>
       </c>
       <c r="AA16" s="9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AB16" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:28">
@@ -3250,7 +3256,7 @@
         <v>30000004</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D17" s="8">
         <v>10000007</v>
@@ -3321,7 +3327,7 @@
         <v>10000008</v>
       </c>
       <c r="AB17" s="8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="1:28">
@@ -3330,7 +3336,7 @@
         <v>30000005</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D18" s="9">
         <v>10000001</v>
@@ -3401,7 +3407,7 @@
         <v>0</v>
       </c>
       <c r="AB18" s="9" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:28">
@@ -3410,7 +3416,7 @@
         <v>30000006</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D19" s="9">
         <v>10000002</v>
@@ -3478,10 +3484,10 @@
         <v>0</v>
       </c>
       <c r="AA19" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AB19" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:28">
@@ -3490,7 +3496,7 @@
         <v>30000007</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D20" s="9">
         <v>10000003</v>
@@ -3561,7 +3567,7 @@
         <v>0</v>
       </c>
       <c r="AB20" s="8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:28">
@@ -3570,7 +3576,7 @@
         <v>30000008</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D21" s="9">
         <v>10000004</v>
@@ -3641,7 +3647,7 @@
         <v>10000014</v>
       </c>
       <c r="AB21" s="8" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:28">
@@ -3650,7 +3656,7 @@
         <v>30000009</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D22" s="9">
         <v>10000005</v>
@@ -3715,13 +3721,13 @@
         <v>20000001</v>
       </c>
       <c r="Z22" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AA22" s="8">
         <v>0</v>
       </c>
       <c r="AB22" s="8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:28">
@@ -3730,7 +3736,7 @@
         <v>30000010</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D23" s="9">
         <v>10000006</v>
@@ -3798,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="AA23" s="8" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AB23" s="8" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:28">
@@ -3810,7 +3816,7 @@
         <v>30000011</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D24" s="9">
         <v>10000007</v>
@@ -3878,10 +3884,10 @@
         <v>0</v>
       </c>
       <c r="AA24" s="8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="AB24" s="8" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:28">
@@ -3890,7 +3896,7 @@
         <v>30000012</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D25" s="8">
         <v>10000001</v>
@@ -3961,7 +3967,7 @@
         <v>10000021</v>
       </c>
       <c r="AB25" s="8" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:28">
@@ -3970,7 +3976,7 @@
         <v>30000013</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D26" s="8">
         <v>10000002</v>
@@ -4041,7 +4047,7 @@
         <v>10000022</v>
       </c>
       <c r="AB26" s="8" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:28">
@@ -4050,7 +4056,7 @@
         <v>30000014</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D27" s="8">
         <v>10000003</v>
@@ -4121,7 +4127,7 @@
         <v>10000023</v>
       </c>
       <c r="AB27" s="8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:28">
@@ -4130,7 +4136,7 @@
         <v>30000015</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D28" s="8">
         <v>10000004</v>
@@ -4198,10 +4204,10 @@
         <v>0</v>
       </c>
       <c r="AA28" s="8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AB28" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:28">
@@ -4210,7 +4216,7 @@
         <v>30000016</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D29" s="8">
         <v>10000005</v>
@@ -4277,7 +4283,7 @@
       <c r="Z29" s="8"/>
       <c r="AA29" s="8"/>
       <c r="AB29" s="8" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:28">
@@ -4286,7 +4292,7 @@
         <v>30000017</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D30" s="8">
         <v>10000006</v>
@@ -4331,7 +4337,7 @@
       <c r="Z30" s="8"/>
       <c r="AA30" s="8"/>
       <c r="AB30" s="8" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:28">
@@ -4340,7 +4346,7 @@
         <v>30000018</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D31" s="8">
         <v>10000007</v>
@@ -4408,10 +4414,10 @@
         <v>0</v>
       </c>
       <c r="AA31" s="8" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AB31" s="8" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="141">
   <si>
     <t>##var</t>
   </si>
@@ -697,7 +697,16 @@
     <t>快速瞬间出剑5次攻击随机敌人,期间处于无敌状态,无法被攻击。</t>
   </si>
   <si>
+    <t>20000004</t>
+  </si>
+  <si>
     <t>极寒领域</t>
+  </si>
+  <si>
+    <t>Skill_极寒领域</t>
+  </si>
+  <si>
+    <t>10000</t>
   </si>
   <si>
     <t>在目标范围造成大面积持续伤害,每秒造成150%伤害,持续3秒。</t>
@@ -2768,11 +2777,11 @@
     </row>
     <row r="11" customHeight="1" spans="1:28">
       <c r="A11" s="8"/>
-      <c r="B11" s="8">
-        <v>20000004</v>
+      <c r="B11" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D11" s="8">
         <v>10000001</v>
@@ -2786,8 +2795,12 @@
       <c r="G11" s="8">
         <v>0</v>
       </c>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
+      <c r="H11" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>88</v>
+      </c>
       <c r="J11" s="8">
         <v>1</v>
       </c>
@@ -2843,7 +2856,7 @@
         <v>0</v>
       </c>
       <c r="AB11" s="8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:28">
@@ -2852,7 +2865,7 @@
         <v>20000005</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D12" s="8">
         <v>10000002</v>
@@ -2867,7 +2880,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I12" s="8"/>
       <c r="J12" s="8">
@@ -2922,10 +2935,10 @@
         <v>0</v>
       </c>
       <c r="AA12" s="8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="AB12" s="8" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="1:28">
@@ -2934,7 +2947,7 @@
         <v>20000006</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D13" s="8">
         <v>10000003</v>
@@ -3005,7 +3018,7 @@
         <v>0</v>
       </c>
       <c r="AB13" s="9" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:28">
@@ -3014,7 +3027,7 @@
         <v>30000001</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D14" s="8">
         <v>10000004</v>
@@ -3082,10 +3095,10 @@
         <v>0</v>
       </c>
       <c r="AA14" s="8" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="AB14" s="8" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:28">
@@ -3094,7 +3107,7 @@
         <v>30000002</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D15" s="8">
         <v>10000005</v>
@@ -3109,7 +3122,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I15" s="8"/>
       <c r="J15" s="8">
@@ -3167,7 +3180,7 @@
         <v>0</v>
       </c>
       <c r="AB15" s="8" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="1:28">
@@ -3176,7 +3189,7 @@
         <v>30000003</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D16" s="8">
         <v>10000006</v>
@@ -3244,10 +3257,10 @@
         <v>0</v>
       </c>
       <c r="AA16" s="9" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AB16" s="9" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:28">
@@ -3256,7 +3269,7 @@
         <v>30000004</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D17" s="8">
         <v>10000007</v>
@@ -3327,7 +3340,7 @@
         <v>10000008</v>
       </c>
       <c r="AB17" s="8" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="1:28">
@@ -3336,7 +3349,7 @@
         <v>30000005</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D18" s="9">
         <v>10000001</v>
@@ -3407,7 +3420,7 @@
         <v>0</v>
       </c>
       <c r="AB18" s="9" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:28">
@@ -3416,7 +3429,7 @@
         <v>30000006</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D19" s="9">
         <v>10000002</v>
@@ -3484,10 +3497,10 @@
         <v>0</v>
       </c>
       <c r="AA19" s="8" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="AB19" s="8" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:28">
@@ -3496,7 +3509,7 @@
         <v>30000007</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D20" s="9">
         <v>10000003</v>
@@ -3567,7 +3580,7 @@
         <v>0</v>
       </c>
       <c r="AB20" s="8" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:28">
@@ -3576,7 +3589,7 @@
         <v>30000008</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D21" s="9">
         <v>10000004</v>
@@ -3647,7 +3660,7 @@
         <v>10000014</v>
       </c>
       <c r="AB21" s="8" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:28">
@@ -3656,7 +3669,7 @@
         <v>30000009</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D22" s="9">
         <v>10000005</v>
@@ -3721,13 +3734,13 @@
         <v>20000001</v>
       </c>
       <c r="Z22" s="8" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AA22" s="8">
         <v>0</v>
       </c>
       <c r="AB22" s="8" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:28">
@@ -3736,7 +3749,7 @@
         <v>30000010</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D23" s="9">
         <v>10000006</v>
@@ -3804,10 +3817,10 @@
         <v>0</v>
       </c>
       <c r="AA23" s="8" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="AB23" s="8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:28">
@@ -3816,7 +3829,7 @@
         <v>30000011</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D24" s="9">
         <v>10000007</v>
@@ -3884,10 +3897,10 @@
         <v>0</v>
       </c>
       <c r="AA24" s="8" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="AB24" s="8" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:28">
@@ -3896,7 +3909,7 @@
         <v>30000012</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D25" s="8">
         <v>10000001</v>
@@ -3967,7 +3980,7 @@
         <v>10000021</v>
       </c>
       <c r="AB25" s="8" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:28">
@@ -3976,7 +3989,7 @@
         <v>30000013</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D26" s="8">
         <v>10000002</v>
@@ -4047,7 +4060,7 @@
         <v>10000022</v>
       </c>
       <c r="AB26" s="8" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:28">
@@ -4056,7 +4069,7 @@
         <v>30000014</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D27" s="8">
         <v>10000003</v>
@@ -4127,7 +4140,7 @@
         <v>10000023</v>
       </c>
       <c r="AB27" s="8" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:28">
@@ -4136,7 +4149,7 @@
         <v>30000015</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D28" s="8">
         <v>10000004</v>
@@ -4204,10 +4217,10 @@
         <v>0</v>
       </c>
       <c r="AA28" s="8" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="AB28" s="8" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:28">
@@ -4216,7 +4229,7 @@
         <v>30000016</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D29" s="8">
         <v>10000005</v>
@@ -4283,7 +4296,7 @@
       <c r="Z29" s="8"/>
       <c r="AA29" s="8"/>
       <c r="AB29" s="8" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:28">
@@ -4292,7 +4305,7 @@
         <v>30000017</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D30" s="8">
         <v>10000006</v>
@@ -4337,7 +4350,7 @@
       <c r="Z30" s="8"/>
       <c r="AA30" s="8"/>
       <c r="AB30" s="8" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:28">
@@ -4346,7 +4359,7 @@
         <v>30000018</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D31" s="8">
         <v>10000007</v>
@@ -4414,10 +4427,10 @@
         <v>0</v>
       </c>
       <c r="AA31" s="8" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AB31" s="8" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="142">
   <si>
     <t>##var</t>
   </si>
@@ -707,6 +707,9 @@
   </si>
   <si>
     <t>10000</t>
+  </si>
+  <si>
+    <t>10000006</t>
   </si>
   <si>
     <t>在目标范围造成大面积持续伤害,每秒造成150%伤害,持续3秒。</t>
@@ -2843,8 +2846,8 @@
       <c r="W11" s="8">
         <v>0</v>
       </c>
-      <c r="X11" s="8">
-        <v>10000001</v>
+      <c r="X11" s="8" t="s">
+        <v>89</v>
       </c>
       <c r="Y11" s="8">
         <v>20000001</v>
@@ -2856,7 +2859,7 @@
         <v>0</v>
       </c>
       <c r="AB11" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:28">
@@ -2865,7 +2868,7 @@
         <v>20000005</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D12" s="8">
         <v>10000002</v>
@@ -2880,7 +2883,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I12" s="8"/>
       <c r="J12" s="8">
@@ -2935,10 +2938,10 @@
         <v>0</v>
       </c>
       <c r="AA12" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AB12" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="1:28">
@@ -2947,7 +2950,7 @@
         <v>20000006</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D13" s="8">
         <v>10000003</v>
@@ -3018,7 +3021,7 @@
         <v>0</v>
       </c>
       <c r="AB13" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:28">
@@ -3027,7 +3030,7 @@
         <v>30000001</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D14" s="8">
         <v>10000004</v>
@@ -3095,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AA14" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AB14" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:28">
@@ -3107,7 +3110,7 @@
         <v>30000002</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D15" s="8">
         <v>10000005</v>
@@ -3122,7 +3125,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I15" s="8"/>
       <c r="J15" s="8">
@@ -3180,7 +3183,7 @@
         <v>0</v>
       </c>
       <c r="AB15" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="1:28">
@@ -3189,7 +3192,7 @@
         <v>30000003</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D16" s="8">
         <v>10000006</v>
@@ -3257,10 +3260,10 @@
         <v>0</v>
       </c>
       <c r="AA16" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB16" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:28">
@@ -3269,7 +3272,7 @@
         <v>30000004</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D17" s="8">
         <v>10000007</v>
@@ -3340,7 +3343,7 @@
         <v>10000008</v>
       </c>
       <c r="AB17" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="1:28">
@@ -3349,7 +3352,7 @@
         <v>30000005</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D18" s="9">
         <v>10000001</v>
@@ -3420,7 +3423,7 @@
         <v>0</v>
       </c>
       <c r="AB18" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:28">
@@ -3429,7 +3432,7 @@
         <v>30000006</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D19" s="9">
         <v>10000002</v>
@@ -3497,10 +3500,10 @@
         <v>0</v>
       </c>
       <c r="AA19" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB19" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:28">
@@ -3509,7 +3512,7 @@
         <v>30000007</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D20" s="9">
         <v>10000003</v>
@@ -3580,7 +3583,7 @@
         <v>0</v>
       </c>
       <c r="AB20" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:28">
@@ -3589,7 +3592,7 @@
         <v>30000008</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D21" s="9">
         <v>10000004</v>
@@ -3660,7 +3663,7 @@
         <v>10000014</v>
       </c>
       <c r="AB21" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:28">
@@ -3669,7 +3672,7 @@
         <v>30000009</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D22" s="9">
         <v>10000005</v>
@@ -3734,13 +3737,13 @@
         <v>20000001</v>
       </c>
       <c r="Z22" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AA22" s="8">
         <v>0</v>
       </c>
       <c r="AB22" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:28">
@@ -3749,7 +3752,7 @@
         <v>30000010</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D23" s="9">
         <v>10000006</v>
@@ -3817,10 +3820,10 @@
         <v>0</v>
       </c>
       <c r="AA23" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AB23" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:28">
@@ -3829,7 +3832,7 @@
         <v>30000011</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D24" s="9">
         <v>10000007</v>
@@ -3897,10 +3900,10 @@
         <v>0</v>
       </c>
       <c r="AA24" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AB24" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:28">
@@ -3909,7 +3912,7 @@
         <v>30000012</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D25" s="8">
         <v>10000001</v>
@@ -3980,7 +3983,7 @@
         <v>10000021</v>
       </c>
       <c r="AB25" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:28">
@@ -3989,7 +3992,7 @@
         <v>30000013</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D26" s="8">
         <v>10000002</v>
@@ -4060,7 +4063,7 @@
         <v>10000022</v>
       </c>
       <c r="AB26" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:28">
@@ -4069,7 +4072,7 @@
         <v>30000014</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D27" s="8">
         <v>10000003</v>
@@ -4140,7 +4143,7 @@
         <v>10000023</v>
       </c>
       <c r="AB27" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:28">
@@ -4149,7 +4152,7 @@
         <v>30000015</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D28" s="8">
         <v>10000004</v>
@@ -4217,10 +4220,10 @@
         <v>0</v>
       </c>
       <c r="AA28" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AB28" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:28">
@@ -4229,7 +4232,7 @@
         <v>30000016</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D29" s="8">
         <v>10000005</v>
@@ -4296,7 +4299,7 @@
       <c r="Z29" s="8"/>
       <c r="AA29" s="8"/>
       <c r="AB29" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:28">
@@ -4305,7 +4308,7 @@
         <v>30000017</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D30" s="8">
         <v>10000006</v>
@@ -4350,7 +4353,7 @@
       <c r="Z30" s="8"/>
       <c r="AA30" s="8"/>
       <c r="AB30" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:28">
@@ -4359,7 +4362,7 @@
         <v>30000018</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D31" s="8">
         <v>10000007</v>
@@ -4427,10 +4430,10 @@
         <v>0</v>
       </c>
       <c r="AA31" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AB31" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="145">
   <si>
     <t>##var</t>
   </si>
@@ -727,7 +727,16 @@
     <t>使周围的友方单位对物理攻击免疫,且每秒恢复2%生命值,持续5秒。</t>
   </si>
   <si>
+    <t>20000006</t>
+  </si>
+  <si>
     <t>混乱之雨</t>
+  </si>
+  <si>
+    <t>Skill_混乱之雨</t>
+  </si>
+  <si>
+    <t>2,50000</t>
   </si>
   <si>
     <t>召唤一个地狱火协助自己进行战斗，持续5秒(地狱火继承角色100%属性,拥有燃烧技能,持续对附近单位每秒造成100%伤害)。</t>
@@ -2946,11 +2955,11 @@
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="1:28">
       <c r="A13" s="9"/>
-      <c r="B13" s="9">
-        <v>20000006</v>
+      <c r="B13" s="9" t="s">
+        <v>95</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D13" s="8">
         <v>10000003</v>
@@ -2964,8 +2973,12 @@
       <c r="G13" s="9">
         <v>0</v>
       </c>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
+      <c r="H13" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="J13" s="9">
         <v>1</v>
       </c>
@@ -3021,7 +3034,7 @@
         <v>0</v>
       </c>
       <c r="AB13" s="9" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:28">
@@ -3030,7 +3043,7 @@
         <v>30000001</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D14" s="8">
         <v>10000004</v>
@@ -3098,10 +3111,10 @@
         <v>0</v>
       </c>
       <c r="AA14" s="8" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AB14" s="8" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:28">
@@ -3110,7 +3123,7 @@
         <v>30000002</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D15" s="8">
         <v>10000005</v>
@@ -3125,7 +3138,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="I15" s="8"/>
       <c r="J15" s="8">
@@ -3183,7 +3196,7 @@
         <v>0</v>
       </c>
       <c r="AB15" s="8" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="1:28">
@@ -3192,7 +3205,7 @@
         <v>30000003</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D16" s="8">
         <v>10000006</v>
@@ -3260,10 +3273,10 @@
         <v>0</v>
       </c>
       <c r="AA16" s="9" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="AB16" s="9" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:28">
@@ -3272,7 +3285,7 @@
         <v>30000004</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D17" s="8">
         <v>10000007</v>
@@ -3343,7 +3356,7 @@
         <v>10000008</v>
       </c>
       <c r="AB17" s="8" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="1:28">
@@ -3352,7 +3365,7 @@
         <v>30000005</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D18" s="9">
         <v>10000001</v>
@@ -3423,7 +3436,7 @@
         <v>0</v>
       </c>
       <c r="AB18" s="9" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:28">
@@ -3432,7 +3445,7 @@
         <v>30000006</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D19" s="9">
         <v>10000002</v>
@@ -3500,10 +3513,10 @@
         <v>0</v>
       </c>
       <c r="AA19" s="8" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="AB19" s="8" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:28">
@@ -3512,7 +3525,7 @@
         <v>30000007</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D20" s="9">
         <v>10000003</v>
@@ -3583,7 +3596,7 @@
         <v>0</v>
       </c>
       <c r="AB20" s="8" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:28">
@@ -3592,7 +3605,7 @@
         <v>30000008</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D21" s="9">
         <v>10000004</v>
@@ -3663,7 +3676,7 @@
         <v>10000014</v>
       </c>
       <c r="AB21" s="8" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:28">
@@ -3672,7 +3685,7 @@
         <v>30000009</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D22" s="9">
         <v>10000005</v>
@@ -3737,13 +3750,13 @@
         <v>20000001</v>
       </c>
       <c r="Z22" s="8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AA22" s="8">
         <v>0</v>
       </c>
       <c r="AB22" s="8" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:28">
@@ -3752,7 +3765,7 @@
         <v>30000010</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D23" s="9">
         <v>10000006</v>
@@ -3820,10 +3833,10 @@
         <v>0</v>
       </c>
       <c r="AA23" s="8" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AB23" s="8" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:28">
@@ -3832,7 +3845,7 @@
         <v>30000011</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D24" s="9">
         <v>10000007</v>
@@ -3900,10 +3913,10 @@
         <v>0</v>
       </c>
       <c r="AA24" s="8" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="AB24" s="8" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:28">
@@ -3912,7 +3925,7 @@
         <v>30000012</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D25" s="8">
         <v>10000001</v>
@@ -3983,7 +3996,7 @@
         <v>10000021</v>
       </c>
       <c r="AB25" s="8" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:28">
@@ -3992,7 +4005,7 @@
         <v>30000013</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D26" s="8">
         <v>10000002</v>
@@ -4063,7 +4076,7 @@
         <v>10000022</v>
       </c>
       <c r="AB26" s="8" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:28">
@@ -4072,7 +4085,7 @@
         <v>30000014</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D27" s="8">
         <v>10000003</v>
@@ -4143,7 +4156,7 @@
         <v>10000023</v>
       </c>
       <c r="AB27" s="8" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:28">
@@ -4152,7 +4165,7 @@
         <v>30000015</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D28" s="8">
         <v>10000004</v>
@@ -4220,10 +4233,10 @@
         <v>0</v>
       </c>
       <c r="AA28" s="8" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="AB28" s="8" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:28">
@@ -4232,7 +4245,7 @@
         <v>30000016</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D29" s="8">
         <v>10000005</v>
@@ -4299,7 +4312,7 @@
       <c r="Z29" s="8"/>
       <c r="AA29" s="8"/>
       <c r="AB29" s="8" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:28">
@@ -4308,7 +4321,7 @@
         <v>30000017</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D30" s="8">
         <v>10000006</v>
@@ -4353,7 +4366,7 @@
       <c r="Z30" s="8"/>
       <c r="AA30" s="8"/>
       <c r="AB30" s="8" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:28">
@@ -4362,7 +4375,7 @@
         <v>30000018</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D31" s="8">
         <v>10000007</v>
@@ -4430,10 +4443,10 @@
         <v>0</v>
       </c>
       <c r="AA31" s="8" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="AB31" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="147">
   <si>
     <t>##var</t>
   </si>
@@ -535,18 +535,18 @@
     <t>string</t>
   </si>
   <si>
+    <t>(array#sep=,),float</t>
+  </si>
+  <si>
+    <t>(array#sep=,),SkillPassiveType</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
     <t>(array#sep=,),int</t>
   </si>
   <si>
-    <t>(array#sep=,),SkillPassiveType</t>
-  </si>
-  <si>
-    <t>(array#sep=,),float</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
     <t>##</t>
   </si>
   <si>
@@ -670,7 +670,7 @@
     <t>Skill_淘汰之刃</t>
   </si>
   <si>
-    <t>35000,3000,40000,5000</t>
+    <t>3.5,0.3,4,0.5</t>
   </si>
   <si>
     <t>对敌人造成350%物理伤害，如果敌人生命值低于30%，造成400%物理伤害；若成功击杀，将额外恢复50%的怒气。</t>
@@ -706,7 +706,7 @@
     <t>Skill_极寒领域</t>
   </si>
   <si>
-    <t>10000</t>
+    <t>1</t>
   </si>
   <si>
     <t>10000006</t>
@@ -736,16 +736,22 @@
     <t>Skill_混乱之雨</t>
   </si>
   <si>
-    <t>2,50000</t>
+    <t>2,5</t>
   </si>
   <si>
     <t>召唤一个地狱火协助自己进行战斗，持续5秒(地狱火继承角色100%属性,拥有燃烧技能,持续对附近单位每秒造成100%伤害)。</t>
   </si>
   <si>
+    <t>30000001</t>
+  </si>
+  <si>
     <t>怒吼</t>
   </si>
   <si>
-    <t>10000001,10000006</t>
+    <t>Skill_怒吼</t>
+  </si>
+  <si>
+    <t>10000001</t>
   </si>
   <si>
     <t>每次攻击有概率强迫附近单位攻击自己且自身受到的伤害降低50%,持续3秒。</t>
@@ -2078,19 +2084,19 @@
         <v>32</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M2" s="6" t="s">
         <v>29</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q2" s="6" t="s">
         <v>29</v>
@@ -2108,10 +2114,10 @@
         <v>29</v>
       </c>
       <c r="V2" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="W2" s="6" t="s">
         <v>33</v>
-      </c>
-      <c r="W2" s="6" t="s">
-        <v>34</v>
       </c>
       <c r="X2" s="6" t="s">
         <v>29</v>
@@ -2120,10 +2126,10 @@
         <v>29</v>
       </c>
       <c r="Z2" s="6" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="AA2" s="6" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="AB2" s="6" t="s">
         <v>30</v>
@@ -3039,11 +3045,11 @@
     </row>
     <row r="14" customHeight="1" spans="1:28">
       <c r="A14" s="8"/>
-      <c r="B14" s="8">
-        <v>30000001</v>
+      <c r="B14" s="8" t="s">
+        <v>100</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D14" s="8">
         <v>10000004</v>
@@ -3057,7 +3063,9 @@
       <c r="G14" s="8">
         <v>0</v>
       </c>
-      <c r="H14" s="8"/>
+      <c r="H14" s="8" t="s">
+        <v>102</v>
+      </c>
       <c r="I14" s="8"/>
       <c r="J14" s="8">
         <v>2</v>
@@ -3107,14 +3115,14 @@
       <c r="Y14" s="8">
         <v>20000001</v>
       </c>
-      <c r="Z14" s="8">
-        <v>0</v>
+      <c r="Z14" s="8" t="s">
+        <v>89</v>
       </c>
       <c r="AA14" s="8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AB14" s="8" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:28">
@@ -3123,7 +3131,7 @@
         <v>30000002</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D15" s="8">
         <v>10000005</v>
@@ -3138,7 +3146,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I15" s="8"/>
       <c r="J15" s="8">
@@ -3196,7 +3204,7 @@
         <v>0</v>
       </c>
       <c r="AB15" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="1:28">
@@ -3205,7 +3213,7 @@
         <v>30000003</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D16" s="8">
         <v>10000006</v>
@@ -3273,10 +3281,10 @@
         <v>0</v>
       </c>
       <c r="AA16" s="9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AB16" s="9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:28">
@@ -3285,7 +3293,7 @@
         <v>30000004</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D17" s="8">
         <v>10000007</v>
@@ -3356,7 +3364,7 @@
         <v>10000008</v>
       </c>
       <c r="AB17" s="8" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="1:28">
@@ -3365,7 +3373,7 @@
         <v>30000005</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D18" s="9">
         <v>10000001</v>
@@ -3436,7 +3444,7 @@
         <v>0</v>
       </c>
       <c r="AB18" s="9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:28">
@@ -3445,7 +3453,7 @@
         <v>30000006</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D19" s="9">
         <v>10000002</v>
@@ -3513,10 +3521,10 @@
         <v>0</v>
       </c>
       <c r="AA19" s="8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AB19" s="8" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:28">
@@ -3525,7 +3533,7 @@
         <v>30000007</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D20" s="9">
         <v>10000003</v>
@@ -3596,7 +3604,7 @@
         <v>0</v>
       </c>
       <c r="AB20" s="8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:28">
@@ -3605,7 +3613,7 @@
         <v>30000008</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D21" s="9">
         <v>10000004</v>
@@ -3676,7 +3684,7 @@
         <v>10000014</v>
       </c>
       <c r="AB21" s="8" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:28">
@@ -3685,7 +3693,7 @@
         <v>30000009</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D22" s="9">
         <v>10000005</v>
@@ -3750,13 +3758,13 @@
         <v>20000001</v>
       </c>
       <c r="Z22" s="8" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="AA22" s="8">
         <v>0</v>
       </c>
       <c r="AB22" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:28">
@@ -3765,7 +3773,7 @@
         <v>30000010</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D23" s="9">
         <v>10000006</v>
@@ -3833,10 +3841,10 @@
         <v>0</v>
       </c>
       <c r="AA23" s="8" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AB23" s="8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:28">
@@ -3845,7 +3853,7 @@
         <v>30000011</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D24" s="9">
         <v>10000007</v>
@@ -3913,10 +3921,10 @@
         <v>0</v>
       </c>
       <c r="AA24" s="8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AB24" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:28">
@@ -3925,7 +3933,7 @@
         <v>30000012</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D25" s="8">
         <v>10000001</v>
@@ -3996,7 +4004,7 @@
         <v>10000021</v>
       </c>
       <c r="AB25" s="8" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:28">
@@ -4005,7 +4013,7 @@
         <v>30000013</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D26" s="8">
         <v>10000002</v>
@@ -4076,7 +4084,7 @@
         <v>10000022</v>
       </c>
       <c r="AB26" s="8" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:28">
@@ -4085,7 +4093,7 @@
         <v>30000014</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D27" s="8">
         <v>10000003</v>
@@ -4156,7 +4164,7 @@
         <v>10000023</v>
       </c>
       <c r="AB27" s="8" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:28">
@@ -4165,7 +4173,7 @@
         <v>30000015</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D28" s="8">
         <v>10000004</v>
@@ -4233,10 +4241,10 @@
         <v>0</v>
       </c>
       <c r="AA28" s="8" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AB28" s="8" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:28">
@@ -4245,7 +4253,7 @@
         <v>30000016</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D29" s="8">
         <v>10000005</v>
@@ -4312,7 +4320,7 @@
       <c r="Z29" s="8"/>
       <c r="AA29" s="8"/>
       <c r="AB29" s="8" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:28">
@@ -4321,7 +4329,7 @@
         <v>30000017</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D30" s="8">
         <v>10000006</v>
@@ -4366,7 +4374,7 @@
       <c r="Z30" s="8"/>
       <c r="AA30" s="8"/>
       <c r="AB30" s="8" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:28">
@@ -4375,7 +4383,7 @@
         <v>30000018</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D31" s="8">
         <v>10000007</v>
@@ -4443,10 +4451,10 @@
         <v>0</v>
       </c>
       <c r="AA31" s="8" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AB31" s="8" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="148">
   <si>
     <t>##var</t>
   </si>
@@ -757,10 +757,13 @@
     <t>每次攻击有概率强迫附近单位攻击自己且自身受到的伤害降低50%,持续3秒。</t>
   </si>
   <si>
+    <t>30000002</t>
+  </si>
+  <si>
     <t>反击螺旋</t>
   </si>
   <si>
-    <t>Skill_AreaDamage</t>
+    <t>Skill_反击螺旋</t>
   </si>
   <si>
     <t>在受到攻击时有17%的概率触发旋风斩,对附近单位造成150%伤害。</t>
@@ -3127,11 +3130,11 @@
     </row>
     <row r="15" customHeight="1" spans="1:28">
       <c r="A15" s="8"/>
-      <c r="B15" s="8">
-        <v>30000002</v>
+      <c r="B15" s="8" t="s">
+        <v>105</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D15" s="8">
         <v>10000005</v>
@@ -3146,7 +3149,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I15" s="8"/>
       <c r="J15" s="8">
@@ -3204,7 +3207,7 @@
         <v>0</v>
       </c>
       <c r="AB15" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="1:28">
@@ -3213,7 +3216,7 @@
         <v>30000003</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D16" s="8">
         <v>10000006</v>
@@ -3281,10 +3284,10 @@
         <v>0</v>
       </c>
       <c r="AA16" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AB16" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:28">
@@ -3293,7 +3296,7 @@
         <v>30000004</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D17" s="8">
         <v>10000007</v>
@@ -3364,7 +3367,7 @@
         <v>10000008</v>
       </c>
       <c r="AB17" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="1:28">
@@ -3373,7 +3376,7 @@
         <v>30000005</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D18" s="9">
         <v>10000001</v>
@@ -3444,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="AB18" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:28">
@@ -3453,7 +3456,7 @@
         <v>30000006</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D19" s="9">
         <v>10000002</v>
@@ -3521,10 +3524,10 @@
         <v>0</v>
       </c>
       <c r="AA19" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AB19" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:28">
@@ -3533,7 +3536,7 @@
         <v>30000007</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D20" s="9">
         <v>10000003</v>
@@ -3604,7 +3607,7 @@
         <v>0</v>
       </c>
       <c r="AB20" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:28">
@@ -3613,7 +3616,7 @@
         <v>30000008</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D21" s="9">
         <v>10000004</v>
@@ -3684,7 +3687,7 @@
         <v>10000014</v>
       </c>
       <c r="AB21" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:28">
@@ -3693,7 +3696,7 @@
         <v>30000009</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D22" s="9">
         <v>10000005</v>
@@ -3758,13 +3761,13 @@
         <v>20000001</v>
       </c>
       <c r="Z22" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AA22" s="8">
         <v>0</v>
       </c>
       <c r="AB22" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:28">
@@ -3773,7 +3776,7 @@
         <v>30000010</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D23" s="9">
         <v>10000006</v>
@@ -3841,10 +3844,10 @@
         <v>0</v>
       </c>
       <c r="AA23" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AB23" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:28">
@@ -3853,7 +3856,7 @@
         <v>30000011</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D24" s="9">
         <v>10000007</v>
@@ -3921,10 +3924,10 @@
         <v>0</v>
       </c>
       <c r="AA24" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AB24" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:28">
@@ -3933,7 +3936,7 @@
         <v>30000012</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D25" s="8">
         <v>10000001</v>
@@ -4004,7 +4007,7 @@
         <v>10000021</v>
       </c>
       <c r="AB25" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:28">
@@ -4013,7 +4016,7 @@
         <v>30000013</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D26" s="8">
         <v>10000002</v>
@@ -4084,7 +4087,7 @@
         <v>10000022</v>
       </c>
       <c r="AB26" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:28">
@@ -4093,7 +4096,7 @@
         <v>30000014</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D27" s="8">
         <v>10000003</v>
@@ -4164,7 +4167,7 @@
         <v>10000023</v>
       </c>
       <c r="AB27" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:28">
@@ -4173,7 +4176,7 @@
         <v>30000015</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D28" s="8">
         <v>10000004</v>
@@ -4241,10 +4244,10 @@
         <v>0</v>
       </c>
       <c r="AA28" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AB28" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:28">
@@ -4253,7 +4256,7 @@
         <v>30000016</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D29" s="8">
         <v>10000005</v>
@@ -4320,7 +4323,7 @@
       <c r="Z29" s="8"/>
       <c r="AA29" s="8"/>
       <c r="AB29" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:28">
@@ -4329,7 +4332,7 @@
         <v>30000017</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D30" s="8">
         <v>10000006</v>
@@ -4374,7 +4377,7 @@
       <c r="Z30" s="8"/>
       <c r="AA30" s="8"/>
       <c r="AB30" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:28">
@@ -4383,7 +4386,7 @@
         <v>30000018</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D31" s="8">
         <v>10000007</v>
@@ -4451,10 +4454,10 @@
         <v>0</v>
       </c>
       <c r="AA31" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AB31" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="149">
   <si>
     <t>##var</t>
   </si>
@@ -772,10 +772,13 @@
     <t>战斗饥渴</t>
   </si>
   <si>
-    <t>10000007,10000010</t>
-  </si>
-  <si>
-    <t>每次攻击有概率对当前目标造成血量流失效果,使其每秒造成40%伤害,且造成伤害降低20%，持续4秒。</t>
+    <t>Skill_战斗饥渴</t>
+  </si>
+  <si>
+    <t>10000007,10000013</t>
+  </si>
+  <si>
+    <t>每次攻击有概率对当前目标造成血量流失效果,使其每秒造成4%伤害,且造成伤害降低20%，持续4秒。</t>
   </si>
   <si>
     <t>巨力挥舞</t>
@@ -3230,7 +3233,9 @@
       <c r="G16" s="9">
         <v>0</v>
       </c>
-      <c r="H16" s="9"/>
+      <c r="H16" s="9" t="s">
+        <v>110</v>
+      </c>
       <c r="I16" s="9"/>
       <c r="J16" s="9">
         <v>2</v>
@@ -3284,10 +3289,10 @@
         <v>0</v>
       </c>
       <c r="AA16" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB16" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:28">
@@ -3296,7 +3301,7 @@
         <v>30000004</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D17" s="8">
         <v>10000007</v>
@@ -3367,7 +3372,7 @@
         <v>10000008</v>
       </c>
       <c r="AB17" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="1:28">
@@ -3376,7 +3381,7 @@
         <v>30000005</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D18" s="9">
         <v>10000001</v>
@@ -3447,7 +3452,7 @@
         <v>0</v>
       </c>
       <c r="AB18" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:28">
@@ -3456,7 +3461,7 @@
         <v>30000006</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D19" s="9">
         <v>10000002</v>
@@ -3524,10 +3529,10 @@
         <v>0</v>
       </c>
       <c r="AA19" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AB19" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:28">
@@ -3536,7 +3541,7 @@
         <v>30000007</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D20" s="9">
         <v>10000003</v>
@@ -3607,7 +3612,7 @@
         <v>0</v>
       </c>
       <c r="AB20" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:28">
@@ -3616,7 +3621,7 @@
         <v>30000008</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D21" s="9">
         <v>10000004</v>
@@ -3687,7 +3692,7 @@
         <v>10000014</v>
       </c>
       <c r="AB21" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:28">
@@ -3696,7 +3701,7 @@
         <v>30000009</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D22" s="9">
         <v>10000005</v>
@@ -3761,13 +3766,13 @@
         <v>20000001</v>
       </c>
       <c r="Z22" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AA22" s="8">
         <v>0</v>
       </c>
       <c r="AB22" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:28">
@@ -3776,7 +3781,7 @@
         <v>30000010</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D23" s="9">
         <v>10000006</v>
@@ -3844,10 +3849,10 @@
         <v>0</v>
       </c>
       <c r="AA23" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AB23" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:28">
@@ -3856,7 +3861,7 @@
         <v>30000011</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D24" s="9">
         <v>10000007</v>
@@ -3924,10 +3929,10 @@
         <v>0</v>
       </c>
       <c r="AA24" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AB24" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:28">
@@ -3936,7 +3941,7 @@
         <v>30000012</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D25" s="8">
         <v>10000001</v>
@@ -4007,7 +4012,7 @@
         <v>10000021</v>
       </c>
       <c r="AB25" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:28">
@@ -4016,7 +4021,7 @@
         <v>30000013</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D26" s="8">
         <v>10000002</v>
@@ -4087,7 +4092,7 @@
         <v>10000022</v>
       </c>
       <c r="AB26" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:28">
@@ -4096,7 +4101,7 @@
         <v>30000014</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D27" s="8">
         <v>10000003</v>
@@ -4167,7 +4172,7 @@
         <v>10000023</v>
       </c>
       <c r="AB27" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:28">
@@ -4176,7 +4181,7 @@
         <v>30000015</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D28" s="8">
         <v>10000004</v>
@@ -4244,10 +4249,10 @@
         <v>0</v>
       </c>
       <c r="AA28" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AB28" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:28">
@@ -4256,7 +4261,7 @@
         <v>30000016</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D29" s="8">
         <v>10000005</v>
@@ -4323,7 +4328,7 @@
       <c r="Z29" s="8"/>
       <c r="AA29" s="8"/>
       <c r="AB29" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:28">
@@ -4332,7 +4337,7 @@
         <v>30000017</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D30" s="8">
         <v>10000006</v>
@@ -4377,7 +4382,7 @@
       <c r="Z30" s="8"/>
       <c r="AA30" s="8"/>
       <c r="AB30" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:28">
@@ -4386,7 +4391,7 @@
         <v>30000018</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D31" s="8">
         <v>10000007</v>
@@ -4454,10 +4459,10 @@
         <v>0</v>
       </c>
       <c r="AA31" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AB31" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="150">
   <si>
     <t>##var</t>
   </si>
@@ -784,7 +784,10 @@
     <t>巨力挥舞</t>
   </si>
   <si>
-    <t>攻击有20%概率释放,向目标区域的敌人投掷风暴之锤,造成200%伤害,并使其造成眩晕效果,持续1秒。</t>
+    <t>Skill_巨力挥舞</t>
+  </si>
+  <si>
+    <t>攻击有20%概率释放,向目标区域的敌人投掷风暴之锤,造成200%伤害,并使其造成眩晕效果,持续3秒。</t>
   </si>
   <si>
     <t>溅射</t>
@@ -3315,7 +3318,9 @@
       <c r="G17" s="8">
         <v>0</v>
       </c>
-      <c r="H17" s="8"/>
+      <c r="H17" s="8" t="s">
+        <v>114</v>
+      </c>
       <c r="I17" s="8"/>
       <c r="J17" s="8">
         <v>2</v>
@@ -3372,7 +3377,7 @@
         <v>10000008</v>
       </c>
       <c r="AB17" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="1:28">
@@ -3381,7 +3386,7 @@
         <v>30000005</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D18" s="9">
         <v>10000001</v>
@@ -3452,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AB18" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:28">
@@ -3461,7 +3466,7 @@
         <v>30000006</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D19" s="9">
         <v>10000002</v>
@@ -3529,10 +3534,10 @@
         <v>0</v>
       </c>
       <c r="AA19" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AB19" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:28">
@@ -3541,7 +3546,7 @@
         <v>30000007</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D20" s="9">
         <v>10000003</v>
@@ -3612,7 +3617,7 @@
         <v>0</v>
       </c>
       <c r="AB20" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:28">
@@ -3621,7 +3626,7 @@
         <v>30000008</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D21" s="9">
         <v>10000004</v>
@@ -3692,7 +3697,7 @@
         <v>10000014</v>
       </c>
       <c r="AB21" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:28">
@@ -3701,7 +3706,7 @@
         <v>30000009</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D22" s="9">
         <v>10000005</v>
@@ -3766,13 +3771,13 @@
         <v>20000001</v>
       </c>
       <c r="Z22" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AA22" s="8">
         <v>0</v>
       </c>
       <c r="AB22" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:28">
@@ -3781,7 +3786,7 @@
         <v>30000010</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D23" s="9">
         <v>10000006</v>
@@ -3849,10 +3854,10 @@
         <v>0</v>
       </c>
       <c r="AA23" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AB23" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:28">
@@ -3861,7 +3866,7 @@
         <v>30000011</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D24" s="9">
         <v>10000007</v>
@@ -3929,10 +3934,10 @@
         <v>0</v>
       </c>
       <c r="AA24" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AB24" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:28">
@@ -3941,7 +3946,7 @@
         <v>30000012</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D25" s="8">
         <v>10000001</v>
@@ -4012,7 +4017,7 @@
         <v>10000021</v>
       </c>
       <c r="AB25" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:28">
@@ -4021,7 +4026,7 @@
         <v>30000013</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D26" s="8">
         <v>10000002</v>
@@ -4092,7 +4097,7 @@
         <v>10000022</v>
       </c>
       <c r="AB26" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:28">
@@ -4101,7 +4106,7 @@
         <v>30000014</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D27" s="8">
         <v>10000003</v>
@@ -4172,7 +4177,7 @@
         <v>10000023</v>
       </c>
       <c r="AB27" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:28">
@@ -4181,7 +4186,7 @@
         <v>30000015</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D28" s="8">
         <v>10000004</v>
@@ -4249,10 +4254,10 @@
         <v>0</v>
       </c>
       <c r="AA28" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AB28" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:28">
@@ -4261,7 +4266,7 @@
         <v>30000016</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D29" s="8">
         <v>10000005</v>
@@ -4328,7 +4333,7 @@
       <c r="Z29" s="8"/>
       <c r="AA29" s="8"/>
       <c r="AB29" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:28">
@@ -4337,7 +4342,7 @@
         <v>30000017</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D30" s="8">
         <v>10000006</v>
@@ -4382,7 +4387,7 @@
       <c r="Z30" s="8"/>
       <c r="AA30" s="8"/>
       <c r="AB30" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:28">
@@ -4391,7 +4396,7 @@
         <v>30000018</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D31" s="8">
         <v>10000007</v>
@@ -4459,10 +4464,10 @@
         <v>0</v>
       </c>
       <c r="AA31" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AB31" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="151">
   <si>
     <t>##var</t>
   </si>
@@ -791,6 +791,9 @@
   </si>
   <si>
     <t>溅射</t>
+  </si>
+  <si>
+    <t>Skill_溅射</t>
   </si>
   <si>
     <t>每次攻击会对附近单位造成50%溅射伤害。</t>
@@ -3400,7 +3403,9 @@
       <c r="G18" s="9">
         <v>0</v>
       </c>
-      <c r="H18" s="9"/>
+      <c r="H18" s="9" t="s">
+        <v>117</v>
+      </c>
       <c r="I18" s="9"/>
       <c r="J18" s="9">
         <v>2</v>
@@ -3457,7 +3462,7 @@
         <v>0</v>
       </c>
       <c r="AB18" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:28">
@@ -3466,7 +3471,7 @@
         <v>30000006</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D19" s="9">
         <v>10000002</v>
@@ -3534,10 +3539,10 @@
         <v>0</v>
       </c>
       <c r="AA19" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AB19" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:28">
@@ -3546,7 +3551,7 @@
         <v>30000007</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D20" s="9">
         <v>10000003</v>
@@ -3617,7 +3622,7 @@
         <v>0</v>
       </c>
       <c r="AB20" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:28">
@@ -3626,7 +3631,7 @@
         <v>30000008</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D21" s="9">
         <v>10000004</v>
@@ -3697,7 +3702,7 @@
         <v>10000014</v>
       </c>
       <c r="AB21" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:28">
@@ -3706,7 +3711,7 @@
         <v>30000009</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D22" s="9">
         <v>10000005</v>
@@ -3771,13 +3776,13 @@
         <v>20000001</v>
       </c>
       <c r="Z22" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AA22" s="8">
         <v>0</v>
       </c>
       <c r="AB22" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:28">
@@ -3786,7 +3791,7 @@
         <v>30000010</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D23" s="9">
         <v>10000006</v>
@@ -3854,10 +3859,10 @@
         <v>0</v>
       </c>
       <c r="AA23" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AB23" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:28">
@@ -3866,7 +3871,7 @@
         <v>30000011</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D24" s="9">
         <v>10000007</v>
@@ -3934,10 +3939,10 @@
         <v>0</v>
       </c>
       <c r="AA24" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AB24" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:28">
@@ -3946,7 +3951,7 @@
         <v>30000012</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D25" s="8">
         <v>10000001</v>
@@ -4017,7 +4022,7 @@
         <v>10000021</v>
       </c>
       <c r="AB25" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:28">
@@ -4026,7 +4031,7 @@
         <v>30000013</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D26" s="8">
         <v>10000002</v>
@@ -4097,7 +4102,7 @@
         <v>10000022</v>
       </c>
       <c r="AB26" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:28">
@@ -4106,7 +4111,7 @@
         <v>30000014</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D27" s="8">
         <v>10000003</v>
@@ -4177,7 +4182,7 @@
         <v>10000023</v>
       </c>
       <c r="AB27" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:28">
@@ -4186,7 +4191,7 @@
         <v>30000015</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D28" s="8">
         <v>10000004</v>
@@ -4254,10 +4259,10 @@
         <v>0</v>
       </c>
       <c r="AA28" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AB28" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:28">
@@ -4266,7 +4271,7 @@
         <v>30000016</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D29" s="8">
         <v>10000005</v>
@@ -4333,7 +4338,7 @@
       <c r="Z29" s="8"/>
       <c r="AA29" s="8"/>
       <c r="AB29" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:28">
@@ -4342,7 +4347,7 @@
         <v>30000017</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D30" s="8">
         <v>10000006</v>
@@ -4387,7 +4392,7 @@
       <c r="Z30" s="8"/>
       <c r="AA30" s="8"/>
       <c r="AB30" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:28">
@@ -4396,7 +4401,7 @@
         <v>30000018</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D31" s="8">
         <v>10000007</v>
@@ -4464,10 +4469,10 @@
         <v>0</v>
       </c>
       <c r="AA31" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AB31" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="152">
   <si>
     <t>##var</t>
   </si>
@@ -802,7 +802,10 @@
     <t>战吼</t>
   </si>
   <si>
-    <t>10000009,10000010,100000111</t>
+    <t>Skill_战吼</t>
+  </si>
+  <si>
+    <t>10000009,10000010,10000011</t>
   </si>
   <si>
     <t>受到攻击有20%概率触发,提升自身的30%攻击速度和移动速度,并使自身的受到的伤害降低30%,持续5秒。</t>
@@ -1970,7 +1973,8 @@
     <col min="14" max="22" width="17.875" style="3"/>
     <col min="23" max="23" width="12.25" style="3" customWidth="1"/>
     <col min="24" max="25" width="17.875" style="3"/>
-    <col min="26" max="27" width="20.375" style="3" customWidth="1"/>
+    <col min="26" max="26" width="28" style="3" customWidth="1"/>
+    <col min="27" max="27" width="29.75" style="3" customWidth="1"/>
     <col min="28" max="28" width="100.625" style="3" customWidth="1"/>
     <col min="29" max="16384" width="17.875" style="3"/>
   </cols>
@@ -3485,7 +3489,9 @@
       <c r="G19" s="8">
         <v>0</v>
       </c>
-      <c r="H19" s="8"/>
+      <c r="H19" s="8" t="s">
+        <v>120</v>
+      </c>
       <c r="I19" s="8"/>
       <c r="J19" s="8">
         <v>2</v>
@@ -3535,14 +3541,12 @@
       <c r="Y19" s="8">
         <v>20000001</v>
       </c>
-      <c r="Z19" s="8">
-        <v>0</v>
-      </c>
-      <c r="AA19" s="8" t="s">
-        <v>120</v>
-      </c>
+      <c r="Z19" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA19" s="8"/>
       <c r="AB19" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:28">
@@ -3551,7 +3555,7 @@
         <v>30000007</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D20" s="9">
         <v>10000003</v>
@@ -3622,7 +3626,7 @@
         <v>0</v>
       </c>
       <c r="AB20" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:28">
@@ -3631,7 +3635,7 @@
         <v>30000008</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D21" s="9">
         <v>10000004</v>
@@ -3702,7 +3706,7 @@
         <v>10000014</v>
       </c>
       <c r="AB21" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:28">
@@ -3711,7 +3715,7 @@
         <v>30000009</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D22" s="9">
         <v>10000005</v>
@@ -3776,13 +3780,13 @@
         <v>20000001</v>
       </c>
       <c r="Z22" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AA22" s="8">
         <v>0</v>
       </c>
       <c r="AB22" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:28">
@@ -3791,7 +3795,7 @@
         <v>30000010</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D23" s="9">
         <v>10000006</v>
@@ -3859,10 +3863,10 @@
         <v>0</v>
       </c>
       <c r="AA23" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AB23" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:28">
@@ -3871,7 +3875,7 @@
         <v>30000011</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D24" s="9">
         <v>10000007</v>
@@ -3939,10 +3943,10 @@
         <v>0</v>
       </c>
       <c r="AA24" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AB24" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:28">
@@ -3951,7 +3955,7 @@
         <v>30000012</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D25" s="8">
         <v>10000001</v>
@@ -4022,7 +4026,7 @@
         <v>10000021</v>
       </c>
       <c r="AB25" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:28">
@@ -4031,7 +4035,7 @@
         <v>30000013</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D26" s="8">
         <v>10000002</v>
@@ -4102,7 +4106,7 @@
         <v>10000022</v>
       </c>
       <c r="AB26" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:28">
@@ -4111,7 +4115,7 @@
         <v>30000014</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D27" s="8">
         <v>10000003</v>
@@ -4182,7 +4186,7 @@
         <v>10000023</v>
       </c>
       <c r="AB27" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:28">
@@ -4191,7 +4195,7 @@
         <v>30000015</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D28" s="8">
         <v>10000004</v>
@@ -4259,10 +4263,10 @@
         <v>0</v>
       </c>
       <c r="AA28" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AB28" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:28">
@@ -4271,7 +4275,7 @@
         <v>30000016</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D29" s="8">
         <v>10000005</v>
@@ -4338,7 +4342,7 @@
       <c r="Z29" s="8"/>
       <c r="AA29" s="8"/>
       <c r="AB29" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:28">
@@ -4347,7 +4351,7 @@
         <v>30000017</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D30" s="8">
         <v>10000006</v>
@@ -4392,7 +4396,7 @@
       <c r="Z30" s="8"/>
       <c r="AA30" s="8"/>
       <c r="AB30" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:28">
@@ -4401,7 +4405,7 @@
         <v>30000018</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D31" s="8">
         <v>10000007</v>
@@ -4469,10 +4473,10 @@
         <v>0</v>
       </c>
       <c r="AA31" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AB31" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="154">
   <si>
     <t>##var</t>
   </si>
@@ -812,6 +812,12 @@
   </si>
   <si>
     <t>剑刃风暴</t>
+  </si>
+  <si>
+    <t>Skill_剑刃风暴</t>
+  </si>
+  <si>
+    <t>0.5</t>
   </si>
   <si>
     <t>挥动剑刃造成风暴,对附近敌人持续旋转3秒,每0.5秒造成100%伤害。</t>
@@ -3569,8 +3575,12 @@
       <c r="G20" s="8">
         <v>0</v>
       </c>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
+      <c r="H20" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>125</v>
+      </c>
       <c r="J20" s="8">
         <v>2</v>
       </c>
@@ -3626,7 +3636,7 @@
         <v>0</v>
       </c>
       <c r="AB20" s="8" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:28">
@@ -3635,7 +3645,7 @@
         <v>30000008</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D21" s="9">
         <v>10000004</v>
@@ -3706,7 +3716,7 @@
         <v>10000014</v>
       </c>
       <c r="AB21" s="8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:28">
@@ -3715,7 +3725,7 @@
         <v>30000009</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D22" s="9">
         <v>10000005</v>
@@ -3780,13 +3790,13 @@
         <v>20000001</v>
       </c>
       <c r="Z22" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AA22" s="8">
         <v>0</v>
       </c>
       <c r="AB22" s="8" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:28">
@@ -3795,7 +3805,7 @@
         <v>30000010</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D23" s="9">
         <v>10000006</v>
@@ -3863,10 +3873,10 @@
         <v>0</v>
       </c>
       <c r="AA23" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AB23" s="8" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:28">
@@ -3875,7 +3885,7 @@
         <v>30000011</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D24" s="9">
         <v>10000007</v>
@@ -3943,10 +3953,10 @@
         <v>0</v>
       </c>
       <c r="AA24" s="8" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AB24" s="8" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:28">
@@ -3955,7 +3965,7 @@
         <v>30000012</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D25" s="8">
         <v>10000001</v>
@@ -4026,7 +4036,7 @@
         <v>10000021</v>
       </c>
       <c r="AB25" s="8" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:28">
@@ -4035,7 +4045,7 @@
         <v>30000013</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D26" s="8">
         <v>10000002</v>
@@ -4106,7 +4116,7 @@
         <v>10000022</v>
       </c>
       <c r="AB26" s="8" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:28">
@@ -4115,7 +4125,7 @@
         <v>30000014</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D27" s="8">
         <v>10000003</v>
@@ -4186,7 +4196,7 @@
         <v>10000023</v>
       </c>
       <c r="AB27" s="8" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:28">
@@ -4195,7 +4205,7 @@
         <v>30000015</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D28" s="8">
         <v>10000004</v>
@@ -4263,10 +4273,10 @@
         <v>0</v>
       </c>
       <c r="AA28" s="8" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AB28" s="8" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:28">
@@ -4275,7 +4285,7 @@
         <v>30000016</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D29" s="8">
         <v>10000005</v>
@@ -4342,7 +4352,7 @@
       <c r="Z29" s="8"/>
       <c r="AA29" s="8"/>
       <c r="AB29" s="8" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:28">
@@ -4351,7 +4361,7 @@
         <v>30000017</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D30" s="8">
         <v>10000006</v>
@@ -4396,7 +4406,7 @@
       <c r="Z30" s="8"/>
       <c r="AA30" s="8"/>
       <c r="AB30" s="8" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:28">
@@ -4405,7 +4415,7 @@
         <v>30000018</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D31" s="8">
         <v>10000007</v>
@@ -4473,10 +4483,10 @@
         <v>0</v>
       </c>
       <c r="AA31" s="8" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AB31" s="8" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="156">
   <si>
     <t>##var</t>
   </si>
@@ -824,6 +824,12 @@
   </si>
   <si>
     <t>治疗守卫</t>
+  </si>
+  <si>
+    <t>Skill_治疗守卫</t>
+  </si>
+  <si>
+    <t>10000014</t>
   </si>
   <si>
     <t>在自己身后附带一个生命图腾,图腾每秒恢复附近己方单位最大生命值的1.5%,持续5秒。</t>
@@ -3659,7 +3665,9 @@
       <c r="G21" s="8">
         <v>0</v>
       </c>
-      <c r="H21" s="8"/>
+      <c r="H21" s="8" t="s">
+        <v>128</v>
+      </c>
       <c r="I21" s="8"/>
       <c r="J21" s="8">
         <v>2</v>
@@ -3709,14 +3717,12 @@
       <c r="Y21" s="8">
         <v>20000001</v>
       </c>
-      <c r="Z21" s="8">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="8">
-        <v>10000014</v>
-      </c>
+      <c r="Z21" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="AA21" s="8"/>
       <c r="AB21" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:28">
@@ -3725,7 +3731,7 @@
         <v>30000009</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D22" s="9">
         <v>10000005</v>
@@ -3790,13 +3796,13 @@
         <v>20000001</v>
       </c>
       <c r="Z22" s="8" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AA22" s="8">
         <v>0</v>
       </c>
       <c r="AB22" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:28">
@@ -3805,7 +3811,7 @@
         <v>30000010</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D23" s="9">
         <v>10000006</v>
@@ -3873,10 +3879,10 @@
         <v>0</v>
       </c>
       <c r="AA23" s="8" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AB23" s="8" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:28">
@@ -3885,7 +3891,7 @@
         <v>30000011</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D24" s="9">
         <v>10000007</v>
@@ -3953,10 +3959,10 @@
         <v>0</v>
       </c>
       <c r="AA24" s="8" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AB24" s="8" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:28">
@@ -3965,7 +3971,7 @@
         <v>30000012</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D25" s="8">
         <v>10000001</v>
@@ -4036,7 +4042,7 @@
         <v>10000021</v>
       </c>
       <c r="AB25" s="8" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:28">
@@ -4045,7 +4051,7 @@
         <v>30000013</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D26" s="8">
         <v>10000002</v>
@@ -4116,7 +4122,7 @@
         <v>10000022</v>
       </c>
       <c r="AB26" s="8" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:28">
@@ -4125,7 +4131,7 @@
         <v>30000014</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D27" s="8">
         <v>10000003</v>
@@ -4196,7 +4202,7 @@
         <v>10000023</v>
       </c>
       <c r="AB27" s="8" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:28">
@@ -4205,7 +4211,7 @@
         <v>30000015</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D28" s="8">
         <v>10000004</v>
@@ -4273,10 +4279,10 @@
         <v>0</v>
       </c>
       <c r="AA28" s="8" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AB28" s="8" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:28">
@@ -4285,7 +4291,7 @@
         <v>30000016</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D29" s="8">
         <v>10000005</v>
@@ -4352,7 +4358,7 @@
       <c r="Z29" s="8"/>
       <c r="AA29" s="8"/>
       <c r="AB29" s="8" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:28">
@@ -4361,7 +4367,7 @@
         <v>30000017</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D30" s="8">
         <v>10000006</v>
@@ -4406,7 +4412,7 @@
       <c r="Z30" s="8"/>
       <c r="AA30" s="8"/>
       <c r="AB30" s="8" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:28">
@@ -4415,7 +4421,7 @@
         <v>30000018</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D31" s="8">
         <v>10000007</v>
@@ -4483,10 +4489,10 @@
         <v>0</v>
       </c>
       <c r="AA31" s="8" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AB31" s="8" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="157">
   <si>
     <t>##var</t>
   </si>
@@ -836,6 +836,9 @@
   </si>
   <si>
     <t>剑舞</t>
+  </si>
+  <si>
+    <t>Skill_剑舞</t>
   </si>
   <si>
     <t>10000015,10000016</t>
@@ -3745,7 +3748,9 @@
       <c r="G22" s="8">
         <v>0</v>
       </c>
-      <c r="H22" s="8"/>
+      <c r="H22" s="8" t="s">
+        <v>132</v>
+      </c>
       <c r="I22" s="8"/>
       <c r="J22" s="8">
         <v>2</v>
@@ -3796,13 +3801,13 @@
         <v>20000001</v>
       </c>
       <c r="Z22" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AA22" s="8">
         <v>0</v>
       </c>
       <c r="AB22" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:28">
@@ -3811,7 +3816,7 @@
         <v>30000010</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D23" s="9">
         <v>10000006</v>
@@ -3879,10 +3884,10 @@
         <v>0</v>
       </c>
       <c r="AA23" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AB23" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:28">
@@ -3891,7 +3896,7 @@
         <v>30000011</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D24" s="9">
         <v>10000007</v>
@@ -3959,10 +3964,10 @@
         <v>0</v>
       </c>
       <c r="AA24" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AB24" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:28">
@@ -3971,7 +3976,7 @@
         <v>30000012</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D25" s="8">
         <v>10000001</v>
@@ -4042,7 +4047,7 @@
         <v>10000021</v>
       </c>
       <c r="AB25" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:28">
@@ -4051,7 +4056,7 @@
         <v>30000013</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D26" s="8">
         <v>10000002</v>
@@ -4122,7 +4127,7 @@
         <v>10000022</v>
       </c>
       <c r="AB26" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:28">
@@ -4131,7 +4136,7 @@
         <v>30000014</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D27" s="8">
         <v>10000003</v>
@@ -4202,7 +4207,7 @@
         <v>10000023</v>
       </c>
       <c r="AB27" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:28">
@@ -4211,7 +4216,7 @@
         <v>30000015</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D28" s="8">
         <v>10000004</v>
@@ -4279,10 +4284,10 @@
         <v>0</v>
       </c>
       <c r="AA28" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AB28" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:28">
@@ -4291,7 +4296,7 @@
         <v>30000016</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D29" s="8">
         <v>10000005</v>
@@ -4358,7 +4363,7 @@
       <c r="Z29" s="8"/>
       <c r="AA29" s="8"/>
       <c r="AB29" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:28">
@@ -4367,7 +4372,7 @@
         <v>30000017</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D30" s="8">
         <v>10000006</v>
@@ -4412,7 +4417,7 @@
       <c r="Z30" s="8"/>
       <c r="AA30" s="8"/>
       <c r="AB30" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:28">
@@ -4421,7 +4426,7 @@
         <v>30000018</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D31" s="8">
         <v>10000007</v>
@@ -4489,10 +4494,10 @@
         <v>0</v>
       </c>
       <c r="AA31" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AB31" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="158">
   <si>
     <t>##var</t>
   </si>
@@ -848,6 +848,9 @@
   </si>
   <si>
     <t>冰霜新星</t>
+  </si>
+  <si>
+    <t>Skill_冰霜新星</t>
   </si>
   <si>
     <t>10000017,10000018</t>
@@ -3830,7 +3833,9 @@
       <c r="G23" s="8">
         <v>0</v>
       </c>
-      <c r="H23" s="8"/>
+      <c r="H23" s="8" t="s">
+        <v>136</v>
+      </c>
       <c r="I23" s="8"/>
       <c r="J23" s="8">
         <v>2</v>
@@ -3884,10 +3889,10 @@
         <v>0</v>
       </c>
       <c r="AA23" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AB23" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:28">
@@ -3896,7 +3901,7 @@
         <v>30000011</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D24" s="9">
         <v>10000007</v>
@@ -3964,10 +3969,10 @@
         <v>0</v>
       </c>
       <c r="AA24" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AB24" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:28">
@@ -3976,7 +3981,7 @@
         <v>30000012</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D25" s="8">
         <v>10000001</v>
@@ -4047,7 +4052,7 @@
         <v>10000021</v>
       </c>
       <c r="AB25" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:28">
@@ -4056,7 +4061,7 @@
         <v>30000013</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D26" s="8">
         <v>10000002</v>
@@ -4127,7 +4132,7 @@
         <v>10000022</v>
       </c>
       <c r="AB26" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:28">
@@ -4136,7 +4141,7 @@
         <v>30000014</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D27" s="8">
         <v>10000003</v>
@@ -4207,7 +4212,7 @@
         <v>10000023</v>
       </c>
       <c r="AB27" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:28">
@@ -4216,7 +4221,7 @@
         <v>30000015</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D28" s="8">
         <v>10000004</v>
@@ -4284,10 +4289,10 @@
         <v>0</v>
       </c>
       <c r="AA28" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AB28" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:28">
@@ -4296,7 +4301,7 @@
         <v>30000016</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D29" s="8">
         <v>10000005</v>
@@ -4363,7 +4368,7 @@
       <c r="Z29" s="8"/>
       <c r="AA29" s="8"/>
       <c r="AB29" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:28">
@@ -4372,7 +4377,7 @@
         <v>30000017</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D30" s="8">
         <v>10000006</v>
@@ -4417,7 +4422,7 @@
       <c r="Z30" s="8"/>
       <c r="AA30" s="8"/>
       <c r="AB30" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:28">
@@ -4426,7 +4431,7 @@
         <v>30000018</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D31" s="8">
         <v>10000007</v>
@@ -4494,10 +4499,10 @@
         <v>0</v>
       </c>
       <c r="AA31" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AB31" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="159">
   <si>
     <t>##var</t>
   </si>
@@ -860,6 +860,9 @@
   </si>
   <si>
     <t>冰封禁制</t>
+  </si>
+  <si>
+    <t>Skill_冰封禁制</t>
   </si>
   <si>
     <t>10000019,10000020</t>
@@ -3915,7 +3918,9 @@
       <c r="G24" s="8">
         <v>0</v>
       </c>
-      <c r="H24" s="8"/>
+      <c r="H24" s="8" t="s">
+        <v>140</v>
+      </c>
       <c r="I24" s="8"/>
       <c r="J24" s="8">
         <v>2</v>
@@ -3969,10 +3974,10 @@
         <v>0</v>
       </c>
       <c r="AA24" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AB24" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:28">
@@ -3981,7 +3986,7 @@
         <v>30000012</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D25" s="8">
         <v>10000001</v>
@@ -4052,7 +4057,7 @@
         <v>10000021</v>
       </c>
       <c r="AB25" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:28">
@@ -4061,7 +4066,7 @@
         <v>30000013</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D26" s="8">
         <v>10000002</v>
@@ -4132,7 +4137,7 @@
         <v>10000022</v>
       </c>
       <c r="AB26" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:28">
@@ -4141,7 +4146,7 @@
         <v>30000014</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D27" s="8">
         <v>10000003</v>
@@ -4212,7 +4217,7 @@
         <v>10000023</v>
       </c>
       <c r="AB27" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:28">
@@ -4221,7 +4226,7 @@
         <v>30000015</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D28" s="8">
         <v>10000004</v>
@@ -4289,10 +4294,10 @@
         <v>0</v>
       </c>
       <c r="AA28" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AB28" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:28">
@@ -4301,7 +4306,7 @@
         <v>30000016</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D29" s="8">
         <v>10000005</v>
@@ -4368,7 +4373,7 @@
       <c r="Z29" s="8"/>
       <c r="AA29" s="8"/>
       <c r="AB29" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:28">
@@ -4377,7 +4382,7 @@
         <v>30000017</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D30" s="8">
         <v>10000006</v>
@@ -4422,7 +4427,7 @@
       <c r="Z30" s="8"/>
       <c r="AA30" s="8"/>
       <c r="AB30" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:28">
@@ -4431,7 +4436,7 @@
         <v>30000018</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D31" s="8">
         <v>10000007</v>
@@ -4499,10 +4504,10 @@
         <v>0</v>
       </c>
       <c r="AA31" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AB31" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="160">
   <si>
     <t>##var</t>
   </si>
@@ -872,6 +872,9 @@
   </si>
   <si>
     <t>辉煌光环</t>
+  </si>
+  <si>
+    <t>Skill_辉煌光环</t>
   </si>
   <si>
     <t>提升场内所有队友的怒气恢复速度,每秒恢复1点。</t>
@@ -4000,7 +4003,9 @@
       <c r="G25" s="8">
         <v>0</v>
       </c>
-      <c r="H25" s="8"/>
+      <c r="H25" s="8" t="s">
+        <v>144</v>
+      </c>
       <c r="I25" s="8"/>
       <c r="J25" s="8">
         <v>2</v>
@@ -4057,7 +4062,7 @@
         <v>10000021</v>
       </c>
       <c r="AB25" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:28">
@@ -4066,7 +4071,7 @@
         <v>30000013</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D26" s="8">
         <v>10000002</v>
@@ -4137,7 +4142,7 @@
         <v>10000022</v>
       </c>
       <c r="AB26" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:28">
@@ -4146,7 +4151,7 @@
         <v>30000014</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D27" s="8">
         <v>10000003</v>
@@ -4217,7 +4222,7 @@
         <v>10000023</v>
       </c>
       <c r="AB27" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:28">
@@ -4226,7 +4231,7 @@
         <v>30000015</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D28" s="8">
         <v>10000004</v>
@@ -4294,10 +4299,10 @@
         <v>0</v>
       </c>
       <c r="AA28" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AB28" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:28">
@@ -4306,7 +4311,7 @@
         <v>30000016</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D29" s="8">
         <v>10000005</v>
@@ -4373,7 +4378,7 @@
       <c r="Z29" s="8"/>
       <c r="AA29" s="8"/>
       <c r="AB29" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:28">
@@ -4382,7 +4387,7 @@
         <v>30000017</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D30" s="8">
         <v>10000006</v>
@@ -4427,7 +4432,7 @@
       <c r="Z30" s="8"/>
       <c r="AA30" s="8"/>
       <c r="AB30" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:28">
@@ -4436,7 +4441,7 @@
         <v>30000018</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D31" s="8">
         <v>10000007</v>
@@ -4504,10 +4509,10 @@
         <v>0</v>
       </c>
       <c r="AA31" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AB31" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="161">
   <si>
     <t>##var</t>
   </si>
@@ -881,6 +881,9 @@
   </si>
   <si>
     <t>洗礼</t>
+  </si>
+  <si>
+    <t>Skill_洗礼</t>
   </si>
   <si>
     <t>立即恢复一个友方20%的最大生命值,并对其附近单位造成100%伤害。</t>
@@ -4085,7 +4088,9 @@
       <c r="G26" s="8">
         <v>0</v>
       </c>
-      <c r="H26" s="8"/>
+      <c r="H26" s="8" t="s">
+        <v>147</v>
+      </c>
       <c r="I26" s="8"/>
       <c r="J26" s="8">
         <v>2</v>
@@ -4142,7 +4147,7 @@
         <v>10000022</v>
       </c>
       <c r="AB26" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:28">
@@ -4151,7 +4156,7 @@
         <v>30000014</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D27" s="8">
         <v>10000003</v>
@@ -4222,7 +4227,7 @@
         <v>10000023</v>
       </c>
       <c r="AB27" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:28">
@@ -4231,7 +4236,7 @@
         <v>30000015</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D28" s="8">
         <v>10000004</v>
@@ -4299,10 +4304,10 @@
         <v>0</v>
       </c>
       <c r="AA28" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AB28" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:28">
@@ -4311,7 +4316,7 @@
         <v>30000016</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D29" s="8">
         <v>10000005</v>
@@ -4378,7 +4383,7 @@
       <c r="Z29" s="8"/>
       <c r="AA29" s="8"/>
       <c r="AB29" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:28">
@@ -4387,7 +4392,7 @@
         <v>30000017</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D30" s="8">
         <v>10000006</v>
@@ -4432,7 +4437,7 @@
       <c r="Z30" s="8"/>
       <c r="AA30" s="8"/>
       <c r="AB30" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:28">
@@ -4441,7 +4446,7 @@
         <v>30000018</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D31" s="8">
         <v>10000007</v>
@@ -4509,10 +4514,10 @@
         <v>0</v>
       </c>
       <c r="AA31" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AB31" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="162">
   <si>
     <t>##var</t>
   </si>
@@ -890,6 +890,9 @@
   </si>
   <si>
     <t>驱逐</t>
+  </si>
+  <si>
+    <t>Skill_驱逐</t>
   </si>
   <si>
     <t>当己方有队友血量下降到30%后会激励保护其免受后面4次的攻击或技能伤害。</t>
@@ -4170,7 +4173,9 @@
       <c r="G27" s="8">
         <v>0</v>
       </c>
-      <c r="H27" s="8"/>
+      <c r="H27" s="8" t="s">
+        <v>150</v>
+      </c>
       <c r="I27" s="8"/>
       <c r="J27" s="8">
         <v>2</v>
@@ -4227,7 +4232,7 @@
         <v>10000023</v>
       </c>
       <c r="AB27" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:28">
@@ -4236,7 +4241,7 @@
         <v>30000015</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D28" s="8">
         <v>10000004</v>
@@ -4304,10 +4309,10 @@
         <v>0</v>
       </c>
       <c r="AA28" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AB28" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:28">
@@ -4316,7 +4321,7 @@
         <v>30000016</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D29" s="8">
         <v>10000005</v>
@@ -4383,7 +4388,7 @@
       <c r="Z29" s="8"/>
       <c r="AA29" s="8"/>
       <c r="AB29" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:28">
@@ -4392,7 +4397,7 @@
         <v>30000017</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D30" s="8">
         <v>10000006</v>
@@ -4437,7 +4442,7 @@
       <c r="Z30" s="8"/>
       <c r="AA30" s="8"/>
       <c r="AB30" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:28">
@@ -4446,7 +4451,7 @@
         <v>30000018</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D31" s="8">
         <v>10000007</v>
@@ -4514,10 +4519,10 @@
         <v>0</v>
       </c>
       <c r="AA31" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AB31" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="163">
   <si>
     <t>##var</t>
   </si>
@@ -899,6 +899,9 @@
   </si>
   <si>
     <t>退化光环</t>
+  </si>
+  <si>
+    <t>Skill_退化光环</t>
   </si>
   <si>
     <t>10000024,10000025</t>
@@ -4255,7 +4258,9 @@
       <c r="G28" s="8">
         <v>0</v>
       </c>
-      <c r="H28" s="8"/>
+      <c r="H28" s="8" t="s">
+        <v>153</v>
+      </c>
       <c r="I28" s="8"/>
       <c r="J28" s="8">
         <v>2</v>
@@ -4309,10 +4314,10 @@
         <v>0</v>
       </c>
       <c r="AA28" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AB28" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:28">
@@ -4321,7 +4326,7 @@
         <v>30000016</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D29" s="8">
         <v>10000005</v>
@@ -4388,7 +4393,7 @@
       <c r="Z29" s="8"/>
       <c r="AA29" s="8"/>
       <c r="AB29" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:28">
@@ -4397,7 +4402,7 @@
         <v>30000017</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D30" s="8">
         <v>10000006</v>
@@ -4442,7 +4447,7 @@
       <c r="Z30" s="8"/>
       <c r="AA30" s="8"/>
       <c r="AB30" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:28">
@@ -4451,7 +4456,7 @@
         <v>30000018</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D31" s="8">
         <v>10000007</v>
@@ -4519,10 +4524,10 @@
         <v>0</v>
       </c>
       <c r="AA31" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AB31" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="164">
   <si>
     <t>##var</t>
   </si>
@@ -923,6 +923,9 @@
   </si>
   <si>
     <t>剧变</t>
+  </si>
+  <si>
+    <t>Skill_剧变</t>
   </si>
   <si>
     <t>10000026,10000027</t>
@@ -4470,7 +4473,9 @@
       <c r="G31" s="8">
         <v>0</v>
       </c>
-      <c r="H31" s="8"/>
+      <c r="H31" s="8" t="s">
+        <v>161</v>
+      </c>
       <c r="I31" s="8"/>
       <c r="J31" s="8">
         <v>2</v>
@@ -4524,10 +4529,10 @@
         <v>0</v>
       </c>
       <c r="AA31" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AB31" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="165">
   <si>
     <t>##var</t>
   </si>
@@ -911,6 +911,9 @@
   </si>
   <si>
     <t>致命链接</t>
+  </si>
+  <si>
+    <t>Skill_致命链接</t>
   </si>
   <si>
     <t>将敌方所有目标链接到一起,其中任意一个受到伤害,其他所有单位都额外承受当前伤害的10%,持续5秒。</t>
@@ -4343,7 +4346,9 @@
       <c r="G29" s="8">
         <v>0</v>
       </c>
-      <c r="H29" s="8"/>
+      <c r="H29" s="8" t="s">
+        <v>157</v>
+      </c>
       <c r="I29" s="8"/>
       <c r="J29" s="8">
         <v>2</v>
@@ -4396,7 +4401,7 @@
       <c r="Z29" s="8"/>
       <c r="AA29" s="8"/>
       <c r="AB29" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:28">
@@ -4405,7 +4410,7 @@
         <v>30000017</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D30" s="8">
         <v>10000006</v>
@@ -4450,7 +4455,7 @@
       <c r="Z30" s="8"/>
       <c r="AA30" s="8"/>
       <c r="AB30" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:28">
@@ -4459,7 +4464,7 @@
         <v>30000018</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D31" s="8">
         <v>10000007</v>
@@ -4474,7 +4479,7 @@
         <v>0</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I31" s="8"/>
       <c r="J31" s="8">
@@ -4529,10 +4534,10 @@
         <v>0</v>
       </c>
       <c r="AA31" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AB31" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="147">
   <si>
     <t>##var</t>
   </si>
@@ -652,10 +652,13 @@
     <t>远程普通攻击2</t>
   </si>
   <si>
+    <t>10000004</t>
+  </si>
+  <si>
     <t>箭雨</t>
   </si>
   <si>
-    <t>Skill_箭雨</t>
+    <t>Skill_Common</t>
   </si>
   <si>
     <t>jianyu</t>
@@ -679,9 +682,6 @@
     <t>神之力量</t>
   </si>
   <si>
-    <t>Skill_神之力量</t>
-  </si>
-  <si>
     <t>10000006,10000012</t>
   </si>
   <si>
@@ -703,9 +703,6 @@
     <t>极寒领域</t>
   </si>
   <si>
-    <t>Skill_极寒领域</t>
-  </si>
-  <si>
     <t>1</t>
   </si>
   <si>
@@ -718,9 +715,6 @@
     <t>守护天使</t>
   </si>
   <si>
-    <t>Skill_守护天使</t>
-  </si>
-  <si>
     <t>10000003,10000004</t>
   </si>
   <si>
@@ -748,9 +742,6 @@
     <t>怒吼</t>
   </si>
   <si>
-    <t>Skill_怒吼</t>
-  </si>
-  <si>
     <t>10000001</t>
   </si>
   <si>
@@ -763,18 +754,12 @@
     <t>反击螺旋</t>
   </si>
   <si>
-    <t>Skill_反击螺旋</t>
-  </si>
-  <si>
     <t>在受到攻击时有17%的概率触发旋风斩,对附近单位造成150%伤害。</t>
   </si>
   <si>
     <t>战斗饥渴</t>
   </si>
   <si>
-    <t>Skill_战斗饥渴</t>
-  </si>
-  <si>
     <t>10000007,10000013</t>
   </si>
   <si>
@@ -784,27 +769,18 @@
     <t>巨力挥舞</t>
   </si>
   <si>
-    <t>Skill_巨力挥舞</t>
-  </si>
-  <si>
     <t>攻击有20%概率释放,向目标区域的敌人投掷风暴之锤,造成200%伤害,并使其造成眩晕效果,持续3秒。</t>
   </si>
   <si>
     <t>溅射</t>
   </si>
   <si>
-    <t>Skill_溅射</t>
-  </si>
-  <si>
     <t>每次攻击会对附近单位造成50%溅射伤害。</t>
   </si>
   <si>
     <t>战吼</t>
   </si>
   <si>
-    <t>Skill_战吼</t>
-  </si>
-  <si>
     <t>10000009,10000010,10000011</t>
   </si>
   <si>
@@ -814,9 +790,6 @@
     <t>剑刃风暴</t>
   </si>
   <si>
-    <t>Skill_剑刃风暴</t>
-  </si>
-  <si>
     <t>0.5</t>
   </si>
   <si>
@@ -826,9 +799,6 @@
     <t>治疗守卫</t>
   </si>
   <si>
-    <t>Skill_治疗守卫</t>
-  </si>
-  <si>
     <t>10000014</t>
   </si>
   <si>
@@ -838,9 +808,6 @@
     <t>剑舞</t>
   </si>
   <si>
-    <t>Skill_剑舞</t>
-  </si>
-  <si>
     <t>10000015,10000016</t>
   </si>
   <si>
@@ -850,9 +817,6 @@
     <t>冰霜新星</t>
   </si>
   <si>
-    <t>Skill_冰霜新星</t>
-  </si>
-  <si>
     <t>10000017,10000018</t>
   </si>
   <si>
@@ -862,9 +826,6 @@
     <t>冰封禁制</t>
   </si>
   <si>
-    <t>Skill_冰封禁制</t>
-  </si>
-  <si>
     <t>10000019,10000020</t>
   </si>
   <si>
@@ -874,36 +835,24 @@
     <t>辉煌光环</t>
   </si>
   <si>
-    <t>Skill_辉煌光环</t>
-  </si>
-  <si>
     <t>提升场内所有队友的怒气恢复速度,每秒恢复1点。</t>
   </si>
   <si>
     <t>洗礼</t>
   </si>
   <si>
-    <t>Skill_洗礼</t>
-  </si>
-  <si>
     <t>立即恢复一个友方20%的最大生命值,并对其附近单位造成100%伤害。</t>
   </si>
   <si>
     <t>驱逐</t>
   </si>
   <si>
-    <t>Skill_驱逐</t>
-  </si>
-  <si>
     <t>当己方有队友血量下降到30%后会激励保护其免受后面4次的攻击或技能伤害。</t>
   </si>
   <si>
     <t>退化光环</t>
   </si>
   <si>
-    <t>Skill_退化光环</t>
-  </si>
-  <si>
     <t>10000024,10000025</t>
   </si>
   <si>
@@ -926,9 +875,6 @@
   </si>
   <si>
     <t>剧变</t>
-  </si>
-  <si>
-    <t>Skill_剧变</t>
   </si>
   <si>
     <t>10000026,10000027</t>
@@ -2518,11 +2464,11 @@
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A7" s="4"/>
-      <c r="B7" s="8">
-        <v>10000004</v>
+      <c r="B7" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D7" s="8">
         <v>10000004</v>
@@ -2537,7 +2483,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="8">
@@ -2568,7 +2514,7 @@
         <v>64</v>
       </c>
       <c r="S7" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T7" s="8">
         <v>1</v>
@@ -2595,7 +2541,7 @@
         <v>0</v>
       </c>
       <c r="AB7" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="1:28">
@@ -2604,7 +2550,7 @@
         <v>20000001</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D8" s="8">
         <v>10000005</v>
@@ -2619,10 +2565,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J8" s="9">
         <v>1</v>
@@ -2679,7 +2625,7 @@
         <v>0</v>
       </c>
       <c r="AB8" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="1:28">
@@ -2688,7 +2634,7 @@
         <v>20000002</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D9" s="8">
         <v>10000006</v>
@@ -2703,7 +2649,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="9">
@@ -2869,10 +2815,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I11" s="8" t="s">
         <v>87</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>88</v>
       </c>
       <c r="J11" s="8">
         <v>1</v>
@@ -2902,7 +2848,7 @@
         <v>64</v>
       </c>
       <c r="S11" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T11" s="8">
         <v>1</v>
@@ -2917,7 +2863,7 @@
         <v>0</v>
       </c>
       <c r="X11" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Y11" s="8">
         <v>20000001</v>
@@ -2929,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="AB11" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:28">
@@ -2938,7 +2884,7 @@
         <v>20000005</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D12" s="8">
         <v>10000002</v>
@@ -2953,7 +2899,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="I12" s="8"/>
       <c r="J12" s="8">
@@ -2984,7 +2930,7 @@
         <v>64</v>
       </c>
       <c r="S12" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T12" s="8">
         <v>0</v>
@@ -3008,19 +2954,19 @@
         <v>0</v>
       </c>
       <c r="AA12" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="AB12" s="8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="1:28">
       <c r="A13" s="9"/>
       <c r="B13" s="9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D13" s="8">
         <v>10000003</v>
@@ -3035,10 +2981,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="J13" s="9">
         <v>1</v>
@@ -3068,7 +3014,7 @@
         <v>64</v>
       </c>
       <c r="S13" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T13" s="9">
         <v>0</v>
@@ -3095,16 +3041,16 @@
         <v>0</v>
       </c>
       <c r="AB13" s="9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:28">
       <c r="A14" s="8"/>
       <c r="B14" s="8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D14" s="8">
         <v>10000004</v>
@@ -3119,7 +3065,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="I14" s="8"/>
       <c r="J14" s="8">
@@ -3171,22 +3117,22 @@
         <v>20000001</v>
       </c>
       <c r="Z14" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AA14" s="8" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="AB14" s="8" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:28">
       <c r="A15" s="8"/>
       <c r="B15" s="8" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D15" s="8">
         <v>10000005</v>
@@ -3201,7 +3147,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="I15" s="8"/>
       <c r="J15" s="8">
@@ -3259,7 +3205,7 @@
         <v>0</v>
       </c>
       <c r="AB15" s="8" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="1:28">
@@ -3268,7 +3214,7 @@
         <v>30000003</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D16" s="8">
         <v>10000006</v>
@@ -3283,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="I16" s="9"/>
       <c r="J16" s="9">
@@ -3338,10 +3284,10 @@
         <v>0</v>
       </c>
       <c r="AA16" s="9" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="AB16" s="9" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:28">
@@ -3350,7 +3296,7 @@
         <v>30000004</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D17" s="8">
         <v>10000007</v>
@@ -3365,7 +3311,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>114</v>
+        <v>72</v>
       </c>
       <c r="I17" s="8"/>
       <c r="J17" s="8">
@@ -3423,7 +3369,7 @@
         <v>10000008</v>
       </c>
       <c r="AB17" s="8" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="1:28">
@@ -3432,7 +3378,7 @@
         <v>30000005</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D18" s="9">
         <v>10000001</v>
@@ -3447,7 +3393,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>117</v>
+        <v>72</v>
       </c>
       <c r="I18" s="9"/>
       <c r="J18" s="9">
@@ -3505,7 +3451,7 @@
         <v>0</v>
       </c>
       <c r="AB18" s="9" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:28">
@@ -3514,7 +3460,7 @@
         <v>30000006</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D19" s="9">
         <v>10000002</v>
@@ -3529,7 +3475,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="I19" s="8"/>
       <c r="J19" s="8">
@@ -3581,11 +3527,11 @@
         <v>20000001</v>
       </c>
       <c r="Z19" s="8" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="AA19" s="8"/>
       <c r="AB19" s="8" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:28">
@@ -3594,7 +3540,7 @@
         <v>30000007</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="D20" s="9">
         <v>10000003</v>
@@ -3609,10 +3555,10 @@
         <v>0</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>124</v>
+        <v>72</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="J20" s="8">
         <v>2</v>
@@ -3669,7 +3615,7 @@
         <v>0</v>
       </c>
       <c r="AB20" s="8" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:28">
@@ -3678,7 +3624,7 @@
         <v>30000008</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D21" s="9">
         <v>10000004</v>
@@ -3693,7 +3639,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>128</v>
+        <v>72</v>
       </c>
       <c r="I21" s="8"/>
       <c r="J21" s="8">
@@ -3745,11 +3691,11 @@
         <v>20000001</v>
       </c>
       <c r="Z21" s="8" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="AA21" s="8"/>
       <c r="AB21" s="8" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:28">
@@ -3758,7 +3704,7 @@
         <v>30000009</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="D22" s="9">
         <v>10000005</v>
@@ -3773,7 +3719,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="I22" s="8"/>
       <c r="J22" s="8">
@@ -3825,13 +3771,13 @@
         <v>20000001</v>
       </c>
       <c r="Z22" s="8" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="AA22" s="8">
         <v>0</v>
       </c>
       <c r="AB22" s="8" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:28">
@@ -3840,7 +3786,7 @@
         <v>30000010</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="D23" s="9">
         <v>10000006</v>
@@ -3855,7 +3801,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>136</v>
+        <v>72</v>
       </c>
       <c r="I23" s="8"/>
       <c r="J23" s="8">
@@ -3910,10 +3856,10 @@
         <v>0</v>
       </c>
       <c r="AA23" s="8" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="AB23" s="8" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:28">
@@ -3922,7 +3868,7 @@
         <v>30000011</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="D24" s="9">
         <v>10000007</v>
@@ -3937,7 +3883,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>140</v>
+        <v>72</v>
       </c>
       <c r="I24" s="8"/>
       <c r="J24" s="8">
@@ -3992,10 +3938,10 @@
         <v>0</v>
       </c>
       <c r="AA24" s="8" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="AB24" s="8" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:28">
@@ -4004,7 +3950,7 @@
         <v>30000012</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="D25" s="8">
         <v>10000001</v>
@@ -4019,7 +3965,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>144</v>
+        <v>72</v>
       </c>
       <c r="I25" s="8"/>
       <c r="J25" s="8">
@@ -4077,7 +4023,7 @@
         <v>10000021</v>
       </c>
       <c r="AB25" s="8" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:28">
@@ -4086,7 +4032,7 @@
         <v>30000013</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="D26" s="8">
         <v>10000002</v>
@@ -4101,7 +4047,7 @@
         <v>0</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>147</v>
+        <v>72</v>
       </c>
       <c r="I26" s="8"/>
       <c r="J26" s="8">
@@ -4159,7 +4105,7 @@
         <v>10000022</v>
       </c>
       <c r="AB26" s="8" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:28">
@@ -4168,7 +4114,7 @@
         <v>30000014</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="D27" s="8">
         <v>10000003</v>
@@ -4183,7 +4129,7 @@
         <v>0</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>150</v>
+        <v>72</v>
       </c>
       <c r="I27" s="8"/>
       <c r="J27" s="8">
@@ -4241,7 +4187,7 @@
         <v>10000023</v>
       </c>
       <c r="AB27" s="8" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:28">
@@ -4250,7 +4196,7 @@
         <v>30000015</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="D28" s="8">
         <v>10000004</v>
@@ -4265,7 +4211,7 @@
         <v>0</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>153</v>
+        <v>72</v>
       </c>
       <c r="I28" s="8"/>
       <c r="J28" s="8">
@@ -4320,10 +4266,10 @@
         <v>0</v>
       </c>
       <c r="AA28" s="8" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="AB28" s="8" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:28">
@@ -4332,7 +4278,7 @@
         <v>30000016</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="D29" s="8">
         <v>10000005</v>
@@ -4347,7 +4293,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="I29" s="8"/>
       <c r="J29" s="8">
@@ -4401,7 +4347,7 @@
       <c r="Z29" s="8"/>
       <c r="AA29" s="8"/>
       <c r="AB29" s="8" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:28">
@@ -4410,7 +4356,7 @@
         <v>30000017</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="D30" s="8">
         <v>10000006</v>
@@ -4455,7 +4401,7 @@
       <c r="Z30" s="8"/>
       <c r="AA30" s="8"/>
       <c r="AB30" s="8" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:28">
@@ -4464,7 +4410,7 @@
         <v>30000018</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="D31" s="8">
         <v>10000007</v>
@@ -4479,7 +4425,7 @@
         <v>0</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="I31" s="8"/>
       <c r="J31" s="8">
@@ -4534,10 +4480,10 @@
         <v>0</v>
       </c>
       <c r="AA31" s="8" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="AB31" s="8" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="149">
   <si>
     <t>##var</t>
   </si>
@@ -662,6 +662,12 @@
   </si>
   <si>
     <t>jianyu</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>0</t>
   </si>
   <si>
     <t>对全体敌人射出箭矢，造成伤害。</t>
@@ -2516,14 +2522,14 @@
       <c r="S7" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="T7" s="8">
-        <v>1</v>
-      </c>
-      <c r="U7" s="8">
-        <v>1</v>
-      </c>
-      <c r="V7" s="8">
-        <v>4</v>
+      <c r="T7" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="U7" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="V7" s="8" t="s">
+        <v>75</v>
       </c>
       <c r="W7" s="8">
         <v>0</v>
@@ -2541,7 +2547,7 @@
         <v>0</v>
       </c>
       <c r="AB7" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="1:28">
@@ -2550,7 +2556,7 @@
         <v>20000001</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D8" s="8">
         <v>10000005</v>
@@ -2565,10 +2571,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J8" s="9">
         <v>1</v>
@@ -2625,7 +2631,7 @@
         <v>0</v>
       </c>
       <c r="AB8" s="9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="1:28">
@@ -2634,7 +2640,7 @@
         <v>20000002</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D9" s="8">
         <v>10000006</v>
@@ -2701,13 +2707,13 @@
         <v>20000001</v>
       </c>
       <c r="Z9" s="9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AA9" s="9">
         <v>0</v>
       </c>
       <c r="AB9" s="9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:28">
@@ -2716,7 +2722,7 @@
         <v>20000003</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D10" s="8">
         <v>10000007</v>
@@ -2731,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I10" s="8">
         <v>5</v>
@@ -2791,16 +2797,16 @@
         <v>0</v>
       </c>
       <c r="AB10" s="8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:28">
       <c r="A11" s="8"/>
       <c r="B11" s="8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D11" s="8">
         <v>10000001</v>
@@ -2818,7 +2824,7 @@
         <v>72</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J11" s="8">
         <v>1</v>
@@ -2863,7 +2869,7 @@
         <v>0</v>
       </c>
       <c r="X11" s="8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Y11" s="8">
         <v>20000001</v>
@@ -2875,7 +2881,7 @@
         <v>0</v>
       </c>
       <c r="AB11" s="8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:28">
@@ -2884,7 +2890,7 @@
         <v>20000005</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D12" s="8">
         <v>10000002</v>
@@ -2954,19 +2960,19 @@
         <v>0</v>
       </c>
       <c r="AA12" s="8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AB12" s="8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="1:28">
       <c r="A13" s="9"/>
       <c r="B13" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D13" s="8">
         <v>10000003</v>
@@ -2981,10 +2987,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J13" s="9">
         <v>1</v>
@@ -3041,16 +3047,16 @@
         <v>0</v>
       </c>
       <c r="AB13" s="9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:28">
       <c r="A14" s="8"/>
       <c r="B14" s="8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D14" s="8">
         <v>10000004</v>
@@ -3117,22 +3123,22 @@
         <v>20000001</v>
       </c>
       <c r="Z14" s="8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AA14" s="8" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AB14" s="8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:28">
       <c r="A15" s="8"/>
       <c r="B15" s="8" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D15" s="8">
         <v>10000005</v>
@@ -3205,7 +3211,7 @@
         <v>0</v>
       </c>
       <c r="AB15" s="8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="1:28">
@@ -3214,7 +3220,7 @@
         <v>30000003</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D16" s="8">
         <v>10000006</v>
@@ -3284,10 +3290,10 @@
         <v>0</v>
       </c>
       <c r="AA16" s="9" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AB16" s="9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:28">
@@ -3296,7 +3302,7 @@
         <v>30000004</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D17" s="8">
         <v>10000007</v>
@@ -3369,7 +3375,7 @@
         <v>10000008</v>
       </c>
       <c r="AB17" s="8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="1:28">
@@ -3378,7 +3384,7 @@
         <v>30000005</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D18" s="9">
         <v>10000001</v>
@@ -3451,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AB18" s="9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:28">
@@ -3460,7 +3466,7 @@
         <v>30000006</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D19" s="9">
         <v>10000002</v>
@@ -3527,11 +3533,11 @@
         <v>20000001</v>
       </c>
       <c r="Z19" s="8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AA19" s="8"/>
       <c r="AB19" s="8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:28">
@@ -3540,7 +3546,7 @@
         <v>30000007</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D20" s="9">
         <v>10000003</v>
@@ -3558,7 +3564,7 @@
         <v>72</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="J20" s="8">
         <v>2</v>
@@ -3615,7 +3621,7 @@
         <v>0</v>
       </c>
       <c r="AB20" s="8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:28">
@@ -3624,7 +3630,7 @@
         <v>30000008</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D21" s="9">
         <v>10000004</v>
@@ -3691,11 +3697,11 @@
         <v>20000001</v>
       </c>
       <c r="Z21" s="8" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AA21" s="8"/>
       <c r="AB21" s="8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:28">
@@ -3704,7 +3710,7 @@
         <v>30000009</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D22" s="9">
         <v>10000005</v>
@@ -3771,13 +3777,13 @@
         <v>20000001</v>
       </c>
       <c r="Z22" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AA22" s="8">
         <v>0</v>
       </c>
       <c r="AB22" s="8" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:28">
@@ -3786,7 +3792,7 @@
         <v>30000010</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D23" s="9">
         <v>10000006</v>
@@ -3856,10 +3862,10 @@
         <v>0</v>
       </c>
       <c r="AA23" s="8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AB23" s="8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:28">
@@ -3868,7 +3874,7 @@
         <v>30000011</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D24" s="9">
         <v>10000007</v>
@@ -3938,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA24" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AB24" s="8" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:28">
@@ -3950,7 +3956,7 @@
         <v>30000012</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D25" s="8">
         <v>10000001</v>
@@ -4023,7 +4029,7 @@
         <v>10000021</v>
       </c>
       <c r="AB25" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:28">
@@ -4032,7 +4038,7 @@
         <v>30000013</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D26" s="8">
         <v>10000002</v>
@@ -4105,7 +4111,7 @@
         <v>10000022</v>
       </c>
       <c r="AB26" s="8" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:28">
@@ -4114,7 +4120,7 @@
         <v>30000014</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D27" s="8">
         <v>10000003</v>
@@ -4187,7 +4193,7 @@
         <v>10000023</v>
       </c>
       <c r="AB27" s="8" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:28">
@@ -4196,7 +4202,7 @@
         <v>30000015</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D28" s="8">
         <v>10000004</v>
@@ -4266,10 +4272,10 @@
         <v>0</v>
       </c>
       <c r="AA28" s="8" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AB28" s="8" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:28">
@@ -4278,7 +4284,7 @@
         <v>30000016</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D29" s="8">
         <v>10000005</v>
@@ -4293,7 +4299,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I29" s="8"/>
       <c r="J29" s="8">
@@ -4347,7 +4353,7 @@
       <c r="Z29" s="8"/>
       <c r="AA29" s="8"/>
       <c r="AB29" s="8" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:28">
@@ -4356,7 +4362,7 @@
         <v>30000017</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D30" s="8">
         <v>10000006</v>
@@ -4401,7 +4407,7 @@
       <c r="Z30" s="8"/>
       <c r="AA30" s="8"/>
       <c r="AB30" s="8" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:28">
@@ -4410,7 +4416,7 @@
         <v>30000018</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D31" s="8">
         <v>10000007</v>
@@ -4480,10 +4486,10 @@
         <v>0</v>
       </c>
       <c r="AA31" s="8" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AB31" s="8" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="149">
   <si>
     <t>##var</t>
   </si>
@@ -3426,9 +3426,7 @@
       <c r="Q18" s="9">
         <v>0</v>
       </c>
-      <c r="R18" s="8" t="s">
-        <v>64</v>
-      </c>
+      <c r="R18" s="8"/>
       <c r="S18" s="9" t="s">
         <v>65</v>
       </c>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="154">
   <si>
     <t>##var</t>
   </si>
@@ -887,6 +887,21 @@
   </si>
   <si>
     <t>对一个区域进行施法,使其攻击速度和移动速度降低至50%,持续3秒。</t>
+  </si>
+  <si>
+    <t>30000019</t>
+  </si>
+  <si>
+    <t>燃烧</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>9999</t>
+  </si>
+  <si>
+    <t>持续对附近单位每秒造成100%伤害，类似阿木木的W?</t>
   </si>
 </sst>
 </file>
@@ -1950,7 +1965,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AB31"/>
+  <dimension ref="A1:AB32"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.875" style="3" customWidth="1"/>
@@ -4490,6 +4505,88 @@
         <v>148</v>
       </c>
     </row>
+    <row r="32" customHeight="1" spans="1:28">
+      <c r="A32" s="8"/>
+      <c r="B32" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D32" s="8">
+        <v>10000007</v>
+      </c>
+      <c r="E32" s="8">
+        <v>1</v>
+      </c>
+      <c r="F32" s="8">
+        <v>2</v>
+      </c>
+      <c r="G32" s="8">
+        <v>0</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I32" s="8"/>
+      <c r="J32" s="8">
+        <v>2</v>
+      </c>
+      <c r="K32" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="L32" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="M32" s="8">
+        <v>0</v>
+      </c>
+      <c r="N32" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="O32" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="P32" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q32" s="8">
+        <v>0</v>
+      </c>
+      <c r="R32" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="S32" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="T32" s="8">
+        <v>1</v>
+      </c>
+      <c r="U32" s="8">
+        <v>1</v>
+      </c>
+      <c r="V32" s="8">
+        <v>4</v>
+      </c>
+      <c r="W32" s="8">
+        <v>0</v>
+      </c>
+      <c r="X32" s="8">
+        <v>10000001</v>
+      </c>
+      <c r="Y32" s="8">
+        <v>20000001</v>
+      </c>
+      <c r="Z32" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="AB32" s="8" t="s">
+        <v>153</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="154">
   <si>
     <t>##var</t>
   </si>
@@ -4559,8 +4559,8 @@
       <c r="S32" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="T32" s="8">
-        <v>1</v>
+      <c r="T32" s="8" t="s">
+        <v>75</v>
       </c>
       <c r="U32" s="8">
         <v>1</v>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="156">
   <si>
     <t>##var</t>
   </si>
@@ -895,10 +895,16 @@
     <t>燃烧</t>
   </si>
   <si>
+    <t>Skill_燃烧</t>
+  </si>
+  <si>
     <t>4</t>
   </si>
   <si>
     <t>9999</t>
+  </si>
+  <si>
+    <t>10000009</t>
   </si>
   <si>
     <t>持续对附近单位每秒造成100%伤害，类似阿木木的W?</t>
@@ -4526,14 +4532,14 @@
         <v>0</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>72</v>
+        <v>151</v>
       </c>
       <c r="I32" s="8"/>
       <c r="J32" s="8">
         <v>2</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L32" s="8" t="s">
         <v>89</v>
@@ -4542,10 +4548,10 @@
         <v>0</v>
       </c>
       <c r="N32" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O32" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P32" s="8" t="s">
         <v>89</v>
@@ -4571,8 +4577,8 @@
       <c r="W32" s="8">
         <v>0</v>
       </c>
-      <c r="X32" s="8">
-        <v>10000001</v>
+      <c r="X32" s="8" t="s">
+        <v>154</v>
       </c>
       <c r="Y32" s="8">
         <v>20000001</v>
@@ -4581,10 +4587,10 @@
         <v>0</v>
       </c>
       <c r="AA32" s="8" t="s">
-        <v>147</v>
+        <v>75</v>
       </c>
       <c r="AB32" s="8" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -769,7 +769,7 @@
     <t>10000007,10000013</t>
   </si>
   <si>
-    <t>每次攻击有概率对当前目标造成血量流失效果,使其每秒造成4%伤害,且造成伤害降低20%，持续4秒。</t>
+    <t>每次攻击有概率对当前目标造成血量流失效果,使其每秒造成40%伤害,且造成伤害降低20%，持续4秒。</t>
   </si>
   <si>
     <t>巨力挥舞</t>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="156">
   <si>
     <t>##var</t>
   </si>
@@ -3383,8 +3383,8 @@
       <c r="W17" s="8">
         <v>0</v>
       </c>
-      <c r="X17" s="8">
-        <v>10000001</v>
+      <c r="X17" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="Y17" s="8">
         <v>20000001</v>
@@ -3627,8 +3627,8 @@
       <c r="W20" s="8">
         <v>0</v>
       </c>
-      <c r="X20" s="8">
-        <v>10000001</v>
+      <c r="X20" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="Y20" s="8">
         <v>20000001</v>
@@ -3871,8 +3871,8 @@
       <c r="W23" s="8">
         <v>0</v>
       </c>
-      <c r="X23" s="8">
-        <v>10000001</v>
+      <c r="X23" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="Y23" s="8">
         <v>20000001</v>
@@ -4495,8 +4495,8 @@
       <c r="W31" s="8">
         <v>0</v>
       </c>
-      <c r="X31" s="8">
-        <v>10000001</v>
+      <c r="X31" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="Y31" s="8">
         <v>20000001</v>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="158">
   <si>
     <t>##var</t>
   </si>
@@ -805,7 +805,13 @@
     <t>治疗守卫</t>
   </si>
   <si>
-    <t>10000014</t>
+    <t>Skill_治疗守卫</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>10000005</t>
   </si>
   <si>
     <t>在自己身后附带一个生命图腾,图腾每秒恢复附近己方单位最大生命值的1.5%,持续5秒。</t>
@@ -1092,8 +1098,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
+      <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1103,7 +1108,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
+      <b/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -3664,9 +3670,11 @@
         <v>0</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="I21" s="8"/>
+        <v>121</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>122</v>
+      </c>
       <c r="J21" s="8">
         <v>2</v>
       </c>
@@ -3709,18 +3717,16 @@
       <c r="W21" s="8">
         <v>0</v>
       </c>
-      <c r="X21" s="8">
-        <v>10000001</v>
+      <c r="X21" s="8" t="s">
+        <v>123</v>
       </c>
       <c r="Y21" s="8">
         <v>20000001</v>
       </c>
-      <c r="Z21" s="8" t="s">
-        <v>121</v>
-      </c>
+      <c r="Z21" s="8"/>
       <c r="AA21" s="8"/>
       <c r="AB21" s="8" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:28">
@@ -3729,7 +3735,7 @@
         <v>30000009</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D22" s="9">
         <v>10000005</v>
@@ -3796,13 +3802,13 @@
         <v>20000001</v>
       </c>
       <c r="Z22" s="8" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AA22" s="8">
         <v>0</v>
       </c>
       <c r="AB22" s="8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:28">
@@ -3811,7 +3817,7 @@
         <v>30000010</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D23" s="9">
         <v>10000006</v>
@@ -3881,10 +3887,10 @@
         <v>0</v>
       </c>
       <c r="AA23" s="8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AB23" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:28">
@@ -3893,7 +3899,7 @@
         <v>30000011</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D24" s="9">
         <v>10000007</v>
@@ -3963,10 +3969,10 @@
         <v>0</v>
       </c>
       <c r="AA24" s="8" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AB24" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:28">
@@ -3975,7 +3981,7 @@
         <v>30000012</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D25" s="8">
         <v>10000001</v>
@@ -4048,7 +4054,7 @@
         <v>10000021</v>
       </c>
       <c r="AB25" s="8" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:28">
@@ -4057,7 +4063,7 @@
         <v>30000013</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D26" s="8">
         <v>10000002</v>
@@ -4130,7 +4136,7 @@
         <v>10000022</v>
       </c>
       <c r="AB26" s="8" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:28">
@@ -4139,7 +4145,7 @@
         <v>30000014</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D27" s="8">
         <v>10000003</v>
@@ -4212,7 +4218,7 @@
         <v>10000023</v>
       </c>
       <c r="AB27" s="8" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:28">
@@ -4221,7 +4227,7 @@
         <v>30000015</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D28" s="8">
         <v>10000004</v>
@@ -4291,10 +4297,10 @@
         <v>0</v>
       </c>
       <c r="AA28" s="8" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AB28" s="8" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:28">
@@ -4303,7 +4309,7 @@
         <v>30000016</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D29" s="8">
         <v>10000005</v>
@@ -4318,7 +4324,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I29" s="8"/>
       <c r="J29" s="8">
@@ -4372,7 +4378,7 @@
       <c r="Z29" s="8"/>
       <c r="AA29" s="8"/>
       <c r="AB29" s="8" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:28">
@@ -4381,7 +4387,7 @@
         <v>30000017</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D30" s="8">
         <v>10000006</v>
@@ -4426,7 +4432,7 @@
       <c r="Z30" s="8"/>
       <c r="AA30" s="8"/>
       <c r="AB30" s="8" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:28">
@@ -4435,7 +4441,7 @@
         <v>30000018</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D31" s="8">
         <v>10000007</v>
@@ -4505,19 +4511,19 @@
         <v>0</v>
       </c>
       <c r="AA31" s="8" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="AB31" s="8" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:28">
       <c r="A32" s="8"/>
       <c r="B32" s="8" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D32" s="8">
         <v>10000007</v>
@@ -4532,14 +4538,14 @@
         <v>0</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I32" s="8"/>
       <c r="J32" s="8">
         <v>2</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="L32" s="8" t="s">
         <v>89</v>
@@ -4548,10 +4554,10 @@
         <v>0</v>
       </c>
       <c r="N32" s="8" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O32" s="8" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="P32" s="8" t="s">
         <v>89</v>
@@ -4578,7 +4584,7 @@
         <v>0</v>
       </c>
       <c r="X32" s="8" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Y32" s="8">
         <v>20000001</v>
@@ -4590,7 +4596,7 @@
         <v>75</v>
       </c>
       <c r="AB32" s="8" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="158">
   <si>
     <t>##var</t>
   </si>
@@ -4123,8 +4123,8 @@
       <c r="W26" s="8">
         <v>0</v>
       </c>
-      <c r="X26" s="8">
-        <v>10000001</v>
+      <c r="X26" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="Y26" s="8">
         <v>20000001</v>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -440,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="159">
   <si>
     <t>##var</t>
   </si>
@@ -871,10 +871,13 @@
     <t>对附近单位造成退化效果,使其移动速度降低25%,并使其造成伤害降低10%。</t>
   </si>
   <si>
+    <t>30000016</t>
+  </si>
+  <si>
     <t>致命链接</t>
   </si>
   <si>
-    <t>Skill_致命链接</t>
+    <t>10000028</t>
   </si>
   <si>
     <t>将敌方所有目标链接到一起,其中任意一个受到伤害,其他所有单位都额外承受当前伤害的10%,持续5秒。</t>
@@ -1098,7 +1101,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <b/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1108,8 +1112,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
+      <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -4287,8 +4290,8 @@
       <c r="W28" s="8">
         <v>0</v>
       </c>
-      <c r="X28" s="8">
-        <v>10000001</v>
+      <c r="X28" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="Y28" s="8">
         <v>20000001</v>
@@ -4305,11 +4308,11 @@
     </row>
     <row r="29" customHeight="1" spans="1:28">
       <c r="A29" s="8"/>
-      <c r="B29" s="8">
-        <v>30000016</v>
+      <c r="B29" s="8" t="s">
+        <v>143</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D29" s="8">
         <v>10000005</v>
@@ -4324,7 +4327,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>144</v>
+        <v>72</v>
       </c>
       <c r="I29" s="8"/>
       <c r="J29" s="8">
@@ -4376,9 +4379,11 @@
         <v>20000001</v>
       </c>
       <c r="Z29" s="8"/>
-      <c r="AA29" s="8"/>
+      <c r="AA29" s="8" t="s">
+        <v>145</v>
+      </c>
       <c r="AB29" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:28">
@@ -4387,7 +4392,7 @@
         <v>30000017</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D30" s="8">
         <v>10000006</v>
@@ -4432,7 +4437,7 @@
       <c r="Z30" s="8"/>
       <c r="AA30" s="8"/>
       <c r="AB30" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:28">
@@ -4441,7 +4446,7 @@
         <v>30000018</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D31" s="8">
         <v>10000007</v>
@@ -4511,19 +4516,19 @@
         <v>0</v>
       </c>
       <c r="AA31" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AB31" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:28">
       <c r="A32" s="8"/>
       <c r="B32" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D32" s="8">
         <v>10000007</v>
@@ -4538,14 +4543,14 @@
         <v>0</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I32" s="8"/>
       <c r="J32" s="8">
         <v>2</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L32" s="8" t="s">
         <v>89</v>
@@ -4554,10 +4559,10 @@
         <v>0</v>
       </c>
       <c r="N32" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O32" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P32" s="8" t="s">
         <v>89</v>
@@ -4584,7 +4589,7 @@
         <v>0</v>
       </c>
       <c r="X32" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y32" s="8">
         <v>20000001</v>
@@ -4596,7 +4601,7 @@
         <v>75</v>
       </c>
       <c r="AB32" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -1,38 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\DreamGit\Unity\Assets\Config\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4F96FBB-E8C0-41BE-9A29-45D5CC1B3D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12960"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="D3" authorId="0">
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -54,7 +47,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E3" authorId="0">
+    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -77,7 +70,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F3" authorId="0">
+    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -100,7 +93,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0">
+    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -122,7 +115,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="0">
+    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -145,7 +138,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K3" authorId="0">
+    <comment ref="K3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -175,7 +168,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L3" authorId="0">
+    <comment ref="L3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
@@ -197,7 +190,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M3" authorId="0">
+    <comment ref="M3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
       <text>
         <r>
           <rPr>
@@ -223,7 +216,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P3" authorId="0">
+    <comment ref="P3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
       <text>
         <r>
           <rPr>
@@ -245,7 +238,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q3" authorId="0">
+    <comment ref="Q3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -267,7 +260,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S3" authorId="0">
+    <comment ref="S3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -289,7 +282,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="0">
+    <comment ref="T3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
       <text>
         <r>
           <rPr>
@@ -317,7 +310,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U3" authorId="0">
+    <comment ref="U3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000D000000}">
       <text>
         <r>
           <rPr>
@@ -340,7 +333,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V3" authorId="0">
+    <comment ref="V3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
       <text>
         <r>
           <rPr>
@@ -366,7 +359,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X3" authorId="0">
+    <comment ref="X3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000F000000}">
       <text>
         <r>
           <rPr>
@@ -389,7 +382,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y3" authorId="0">
+    <comment ref="Y3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000010000000}">
       <text>
         <r>
           <rPr>
@@ -412,7 +405,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA3" authorId="0">
+    <comment ref="AA3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000011000000}">
       <text>
         <r>
           <rPr>
@@ -440,7 +433,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="150">
   <si>
     <t>##var</t>
   </si>
@@ -652,9 +645,6 @@
     <t>远程普通攻击2</t>
   </si>
   <si>
-    <t>10000004</t>
-  </si>
-  <si>
     <t>箭雨</t>
   </si>
   <si>
@@ -664,9 +654,6 @@
     <t>jianyu</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>0</t>
   </si>
   <si>
@@ -703,15 +690,9 @@
     <t>快速瞬间出剑5次攻击随机敌人,期间处于无敌状态,无法被攻击。</t>
   </si>
   <si>
-    <t>20000004</t>
-  </si>
-  <si>
     <t>极寒领域</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>10000006</t>
   </si>
   <si>
@@ -727,9 +708,6 @@
     <t>使周围的友方单位对物理攻击免疫,且每秒恢复2%生命值,持续5秒。</t>
   </si>
   <si>
-    <t>20000006</t>
-  </si>
-  <si>
     <t>混乱之雨</t>
   </si>
   <si>
@@ -742,9 +720,6 @@
     <t>召唤一个地狱火协助自己进行战斗，持续5秒(地狱火继承角色100%属性,拥有燃烧技能,持续对附近单位每秒造成100%伤害)。</t>
   </si>
   <si>
-    <t>30000001</t>
-  </si>
-  <si>
     <t>怒吼</t>
   </si>
   <si>
@@ -754,9 +729,6 @@
     <t>每次攻击有概率强迫附近单位攻击自己且自身受到的伤害降低50%,持续3秒。</t>
   </si>
   <si>
-    <t>30000002</t>
-  </si>
-  <si>
     <t>反击螺旋</t>
   </si>
   <si>
@@ -796,9 +768,6 @@
     <t>剑刃风暴</t>
   </si>
   <si>
-    <t>0.5</t>
-  </si>
-  <si>
     <t>挥动剑刃造成风暴,对附近敌人持续旋转3秒,每0.5秒造成100%伤害。</t>
   </si>
   <si>
@@ -808,12 +777,6 @@
     <t>Skill_治疗守卫</t>
   </si>
   <si>
-    <t>1.5</t>
-  </si>
-  <si>
-    <t>10000005</t>
-  </si>
-  <si>
     <t>在自己身后附带一个生命图腾,图腾每秒恢复附近己方单位最大生命值的1.5%,持续5秒。</t>
   </si>
   <si>
@@ -871,9 +834,6 @@
     <t>对附近单位造成退化效果,使其移动速度降低25%,并使其造成伤害降低10%。</t>
   </si>
   <si>
-    <t>30000016</t>
-  </si>
-  <si>
     <t>致命链接</t>
   </si>
   <si>
@@ -886,9 +846,6 @@
     <t>暗言术</t>
   </si>
   <si>
-    <t>释放强大的魔法治疗一个队友或伤害一个敌人,使其每秒造成60%伤害或每秒恢复2.5%最大生命生命,持续5秒。</t>
-  </si>
-  <si>
     <t>剧变</t>
   </si>
   <si>
@@ -898,38 +855,49 @@
     <t>对一个区域进行施法,使其攻击速度和移动速度降低至50%,持续3秒。</t>
   </si>
   <si>
-    <t>30000019</t>
-  </si>
-  <si>
     <t>燃烧</t>
   </si>
   <si>
     <t>Skill_燃烧</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>9999</t>
-  </si>
-  <si>
-    <t>10000009</t>
-  </si>
-  <si>
-    <t>持续对附近单位每秒造成100%伤害，类似阿木木的W?</t>
+    <t>2,5</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.2,0.6</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>dao</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>持续对附近单位每秒造成100%伤害，类似阿木木的W。</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>attack</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>10000029</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>10000030</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>释放强大的魔法伤害一个敌人或治疗一个队友,使其每秒造成60%伤害或每秒恢复2.5%最大生命生命,持续5秒。</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="26">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -957,147 +925,10 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1116,8 +947,21 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="36">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1142,194 +986,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="12">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1380,256 +1038,14 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1648,10 +1064,10 @@
     <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1660,63 +1076,31 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 6" xfId="49"/>
+    <cellStyle name="常规 6" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1974,14 +1358,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AB32"/>
-  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.875" style="3" customWidth="1"/>
     <col min="2" max="7" width="17.875" style="3"/>
@@ -2000,7 +1384,7 @@
     <col min="29" max="16384" width="17.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="1" spans="1:28" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2086,7 +1470,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="2" spans="1:28" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>28</v>
       </c>
@@ -2172,7 +1556,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="3" spans="1:28" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -2258,7 +1642,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="4" spans="1:28" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4"/>
       <c r="B4" s="8">
         <v>10000001</v>
@@ -2338,7 +1722,7 @@
       </c>
       <c r="AB4" s="4"/>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="5" spans="1:28" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4"/>
       <c r="B5" s="8">
         <v>10000002</v>
@@ -2418,7 +1802,7 @@
       </c>
       <c r="AB5" s="4"/>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="6" spans="1:28" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4"/>
       <c r="B6" s="8">
         <v>10000003</v>
@@ -2498,13 +1882,13 @@
       </c>
       <c r="AB6" s="4"/>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:28">
+    <row r="7" spans="1:28" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4"/>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="10">
+        <v>10000004</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>70</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>71</v>
       </c>
       <c r="D7" s="8">
         <v>10000004</v>
@@ -2519,7 +1903,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="8">
@@ -2550,16 +1934,16 @@
         <v>64</v>
       </c>
       <c r="S7" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="T7" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="U7" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="V7" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
+      </c>
+      <c r="T7" s="10">
+        <v>6</v>
+      </c>
+      <c r="U7" s="10">
+        <v>0</v>
+      </c>
+      <c r="V7" s="10">
+        <v>0</v>
       </c>
       <c r="W7" s="8">
         <v>0</v>
@@ -2577,16 +1961,16 @@
         <v>0</v>
       </c>
       <c r="AB7" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="1:28">
+    <row r="8" spans="1:28" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9"/>
       <c r="B8" s="9">
         <v>20000001</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D8" s="8">
         <v>10000005</v>
@@ -2601,10 +1985,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J8" s="9">
         <v>1</v>
@@ -2661,16 +2045,16 @@
         <v>0</v>
       </c>
       <c r="AB8" s="9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="1:28">
+    <row r="9" spans="1:28" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9"/>
       <c r="B9" s="9">
         <v>20000002</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D9" s="8">
         <v>10000006</v>
@@ -2685,7 +2069,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="9">
@@ -2737,22 +2121,22 @@
         <v>20000001</v>
       </c>
       <c r="Z9" s="9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AA9" s="9">
         <v>0</v>
       </c>
       <c r="AB9" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:28">
+    <row r="10" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="8"/>
       <c r="B10" s="8">
         <v>20000003</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D10" s="8">
         <v>10000007</v>
@@ -2767,7 +2151,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I10" s="8">
         <v>5</v>
@@ -2827,16 +2211,16 @@
         <v>0</v>
       </c>
       <c r="AB10" s="8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:28">
+    <row r="11" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8"/>
-      <c r="B11" s="8" t="s">
-        <v>87</v>
+      <c r="B11" s="10">
+        <v>20000004</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D11" s="8">
         <v>10000001</v>
@@ -2851,10 +2235,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>89</v>
+        <v>71</v>
+      </c>
+      <c r="I11" s="10">
+        <v>1</v>
       </c>
       <c r="J11" s="8">
         <v>1</v>
@@ -2884,7 +2268,7 @@
         <v>64</v>
       </c>
       <c r="S11" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T11" s="8">
         <v>1</v>
@@ -2898,8 +2282,8 @@
       <c r="W11" s="8">
         <v>0</v>
       </c>
-      <c r="X11" s="8" t="s">
-        <v>90</v>
+      <c r="X11" s="10">
+        <v>10000006</v>
       </c>
       <c r="Y11" s="8">
         <v>20000001</v>
@@ -2911,16 +2295,16 @@
         <v>0</v>
       </c>
       <c r="AB11" s="8" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:28">
+    <row r="12" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8"/>
       <c r="B12" s="8">
         <v>20000005</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D12" s="8">
         <v>10000002</v>
@@ -2935,7 +2319,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I12" s="8"/>
       <c r="J12" s="8">
@@ -2966,7 +2350,7 @@
         <v>64</v>
       </c>
       <c r="S12" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T12" s="8">
         <v>0</v>
@@ -2990,19 +2374,19 @@
         <v>0</v>
       </c>
       <c r="AA12" s="8" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="AB12" s="8" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:28">
+    <row r="13" spans="1:28" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9"/>
-      <c r="B13" s="9" t="s">
-        <v>95</v>
+      <c r="B13" s="13">
+        <v>20000006</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D13" s="8">
         <v>10000003</v>
@@ -3017,10 +2401,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="J13" s="9">
         <v>1</v>
@@ -3050,7 +2434,7 @@
         <v>64</v>
       </c>
       <c r="S13" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T13" s="9">
         <v>0</v>
@@ -3077,16 +2461,16 @@
         <v>0</v>
       </c>
       <c r="AB13" s="9" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:28">
+    <row r="14" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8"/>
-      <c r="B14" s="8" t="s">
-        <v>100</v>
+      <c r="B14" s="10">
+        <v>30000001</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D14" s="8">
         <v>10000004</v>
@@ -3101,7 +2485,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I14" s="8"/>
       <c r="J14" s="8">
@@ -3153,22 +2537,22 @@
         <v>20000001</v>
       </c>
       <c r="Z14" s="8" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="AA14" s="8" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="AB14" s="8" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:28">
+    <row r="15" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="8"/>
-      <c r="B15" s="8" t="s">
-        <v>104</v>
+      <c r="B15" s="10">
+        <v>30000002</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="D15" s="8">
         <v>10000005</v>
@@ -3183,7 +2567,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I15" s="8"/>
       <c r="J15" s="8">
@@ -3241,16 +2625,16 @@
         <v>0</v>
       </c>
       <c r="AB15" s="8" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="1:28">
+    <row r="16" spans="1:28" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="9"/>
       <c r="B16" s="9">
         <v>30000003</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D16" s="8">
         <v>10000006</v>
@@ -3265,7 +2649,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I16" s="9"/>
       <c r="J16" s="9">
@@ -3320,19 +2704,19 @@
         <v>0</v>
       </c>
       <c r="AA16" s="9" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="AB16" s="9" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="1:28">
+    <row r="17" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="8"/>
       <c r="B17" s="8">
         <v>30000004</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="D17" s="8">
         <v>10000007</v>
@@ -3347,7 +2731,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I17" s="8"/>
       <c r="J17" s="8">
@@ -3392,8 +2776,8 @@
       <c r="W17" s="8">
         <v>0</v>
       </c>
-      <c r="X17" s="8" t="s">
-        <v>70</v>
+      <c r="X17" s="10">
+        <v>10000004</v>
       </c>
       <c r="Y17" s="8">
         <v>20000001</v>
@@ -3405,16 +2789,16 @@
         <v>10000008</v>
       </c>
       <c r="AB17" s="8" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
-    <row r="18" s="2" customFormat="1" customHeight="1" spans="1:28">
+    <row r="18" spans="1:28" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="9"/>
       <c r="B18" s="9">
         <v>30000005</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="D18" s="9">
         <v>10000001</v>
@@ -3429,7 +2813,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I18" s="9"/>
       <c r="J18" s="9">
@@ -3456,7 +2840,9 @@
       <c r="Q18" s="9">
         <v>0</v>
       </c>
-      <c r="R18" s="8"/>
+      <c r="R18" s="11" t="s">
+        <v>146</v>
+      </c>
       <c r="S18" s="9" t="s">
         <v>65</v>
       </c>
@@ -3485,16 +2871,16 @@
         <v>0</v>
       </c>
       <c r="AB18" s="9" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="1:28">
+    <row r="19" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="8"/>
       <c r="B19" s="8">
         <v>30000006</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D19" s="9">
         <v>10000002</v>
@@ -3509,7 +2895,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I19" s="8"/>
       <c r="J19" s="8">
@@ -3561,20 +2947,22 @@
         <v>20000001</v>
       </c>
       <c r="Z19" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA19" s="8"/>
+        <v>108</v>
+      </c>
+      <c r="AA19" s="12">
+        <v>0</v>
+      </c>
       <c r="AB19" s="8" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="1:28">
+    <row r="20" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="8"/>
       <c r="B20" s="8">
         <v>30000007</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="D20" s="9">
         <v>10000003</v>
@@ -3589,10 +2977,10 @@
         <v>0</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="I20" s="8" t="s">
-        <v>118</v>
+        <v>71</v>
+      </c>
+      <c r="I20" s="10">
+        <v>0.5</v>
       </c>
       <c r="J20" s="8">
         <v>2</v>
@@ -3636,8 +3024,8 @@
       <c r="W20" s="8">
         <v>0</v>
       </c>
-      <c r="X20" s="8" t="s">
-        <v>70</v>
+      <c r="X20" s="10">
+        <v>10000004</v>
       </c>
       <c r="Y20" s="8">
         <v>20000001</v>
@@ -3649,16 +3037,16 @@
         <v>0</v>
       </c>
       <c r="AB20" s="8" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="1:28">
+    <row r="21" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="8"/>
       <c r="B21" s="8">
         <v>30000008</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="D21" s="9">
         <v>10000004</v>
@@ -3673,10 +3061,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="I21" s="8" t="s">
-        <v>122</v>
+        <v>113</v>
+      </c>
+      <c r="I21" s="10">
+        <v>1.5</v>
       </c>
       <c r="J21" s="8">
         <v>2</v>
@@ -3720,25 +3108,29 @@
       <c r="W21" s="8">
         <v>0</v>
       </c>
-      <c r="X21" s="8" t="s">
-        <v>123</v>
+      <c r="X21" s="10">
+        <v>10000005</v>
       </c>
       <c r="Y21" s="8">
         <v>20000001</v>
       </c>
-      <c r="Z21" s="8"/>
-      <c r="AA21" s="8"/>
+      <c r="Z21" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="12">
+        <v>0</v>
+      </c>
       <c r="AB21" s="8" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="1:28">
+    <row r="22" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="8"/>
       <c r="B22" s="8">
         <v>30000009</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="D22" s="9">
         <v>10000005</v>
@@ -3753,7 +3145,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I22" s="8"/>
       <c r="J22" s="8">
@@ -3805,22 +3197,22 @@
         <v>20000001</v>
       </c>
       <c r="Z22" s="8" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="AA22" s="8">
         <v>0</v>
       </c>
       <c r="AB22" s="8" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="1:28">
+    <row r="23" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="8"/>
       <c r="B23" s="8">
         <v>30000010</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D23" s="9">
         <v>10000006</v>
@@ -3835,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I23" s="8"/>
       <c r="J23" s="8">
@@ -3880,8 +3272,8 @@
       <c r="W23" s="8">
         <v>0</v>
       </c>
-      <c r="X23" s="8" t="s">
-        <v>70</v>
+      <c r="X23" s="10">
+        <v>10000004</v>
       </c>
       <c r="Y23" s="8">
         <v>20000001</v>
@@ -3890,19 +3282,19 @@
         <v>0</v>
       </c>
       <c r="AA23" s="8" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="AB23" s="8" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="1:28">
+    <row r="24" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="8"/>
       <c r="B24" s="8">
         <v>30000011</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="D24" s="9">
         <v>10000007</v>
@@ -3917,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I24" s="8"/>
       <c r="J24" s="8">
@@ -3972,19 +3364,19 @@
         <v>0</v>
       </c>
       <c r="AA24" s="8" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="AB24" s="8" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="1:28">
+    <row r="25" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="8"/>
       <c r="B25" s="8">
         <v>30000012</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="D25" s="8">
         <v>10000001</v>
@@ -3999,7 +3391,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I25" s="8"/>
       <c r="J25" s="8">
@@ -4057,16 +3449,16 @@
         <v>10000021</v>
       </c>
       <c r="AB25" s="8" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="1:28">
+    <row r="26" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="8"/>
       <c r="B26" s="8">
         <v>30000013</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D26" s="8">
         <v>10000002</v>
@@ -4081,7 +3473,7 @@
         <v>0</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I26" s="8"/>
       <c r="J26" s="8">
@@ -4126,8 +3518,8 @@
       <c r="W26" s="8">
         <v>0</v>
       </c>
-      <c r="X26" s="8" t="s">
-        <v>70</v>
+      <c r="X26" s="10">
+        <v>10000004</v>
       </c>
       <c r="Y26" s="8">
         <v>20000001</v>
@@ -4139,16 +3531,16 @@
         <v>10000022</v>
       </c>
       <c r="AB26" s="8" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
     </row>
-    <row r="27" customHeight="1" spans="1:28">
+    <row r="27" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="8"/>
       <c r="B27" s="8">
         <v>30000014</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="D27" s="8">
         <v>10000003</v>
@@ -4163,7 +3555,7 @@
         <v>0</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I27" s="8"/>
       <c r="J27" s="8">
@@ -4221,16 +3613,16 @@
         <v>10000023</v>
       </c>
       <c r="AB27" s="8" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
     </row>
-    <row r="28" customHeight="1" spans="1:28">
+    <row r="28" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="8"/>
       <c r="B28" s="8">
         <v>30000015</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="D28" s="8">
         <v>10000004</v>
@@ -4245,7 +3637,7 @@
         <v>0</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I28" s="8"/>
       <c r="J28" s="8">
@@ -4290,8 +3682,8 @@
       <c r="W28" s="8">
         <v>0</v>
       </c>
-      <c r="X28" s="8" t="s">
-        <v>70</v>
+      <c r="X28" s="10">
+        <v>10000004</v>
       </c>
       <c r="Y28" s="8">
         <v>20000001</v>
@@ -4300,19 +3692,19 @@
         <v>0</v>
       </c>
       <c r="AA28" s="8" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="AB28" s="8" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="1:28">
+    <row r="29" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="8"/>
-      <c r="B29" s="8" t="s">
-        <v>143</v>
+      <c r="B29" s="10">
+        <v>30000016</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="D29" s="8">
         <v>10000005</v>
@@ -4327,7 +3719,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I29" s="8"/>
       <c r="J29" s="8">
@@ -4378,21 +3770,23 @@
       <c r="Y29" s="8">
         <v>20000001</v>
       </c>
-      <c r="Z29" s="8"/>
+      <c r="Z29" s="12">
+        <v>0</v>
+      </c>
       <c r="AA29" s="8" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="AB29" s="8" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="1:28">
+    <row r="30" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="8"/>
       <c r="B30" s="8">
         <v>30000017</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="D30" s="8">
         <v>10000006</v>
@@ -4408,45 +3802,71 @@
       </c>
       <c r="H30" s="8"/>
       <c r="I30" s="8"/>
-      <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
-      <c r="L30" s="8"/>
-      <c r="M30" s="8"/>
+      <c r="J30" s="12">
+        <v>2</v>
+      </c>
+      <c r="K30" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="L30" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="M30" s="12">
+        <v>0</v>
+      </c>
       <c r="N30" s="8">
         <v>10</v>
       </c>
       <c r="O30" s="8">
         <v>5</v>
       </c>
-      <c r="P30" s="8"/>
-      <c r="Q30" s="8"/>
+      <c r="P30" s="12">
+        <v>0.6</v>
+      </c>
+      <c r="Q30" s="12">
+        <v>0</v>
+      </c>
       <c r="R30" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="S30" s="8"/>
-      <c r="T30" s="8"/>
-      <c r="U30" s="8"/>
-      <c r="V30" s="8"/>
+      <c r="S30" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="T30" s="12">
+        <v>0</v>
+      </c>
+      <c r="U30" s="12">
+        <v>1</v>
+      </c>
+      <c r="V30" s="12">
+        <v>1</v>
+      </c>
       <c r="W30" s="8">
         <v>0</v>
       </c>
-      <c r="X30" s="8"/>
+      <c r="X30" s="12">
+        <v>10000001</v>
+      </c>
       <c r="Y30" s="8">
         <v>20000001</v>
       </c>
-      <c r="Z30" s="8"/>
-      <c r="AA30" s="8"/>
-      <c r="AB30" s="8" t="s">
+      <c r="Z30" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="AA30" s="11" t="s">
         <v>148</v>
       </c>
+      <c r="AB30" s="11" t="s">
+        <v>149</v>
+      </c>
     </row>
-    <row r="31" customHeight="1" spans="1:28">
+    <row r="31" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="8"/>
       <c r="B31" s="8">
         <v>30000018</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="D31" s="8">
         <v>10000007</v>
@@ -4461,7 +3881,7 @@
         <v>0</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I31" s="8"/>
       <c r="J31" s="8">
@@ -4506,8 +3926,8 @@
       <c r="W31" s="8">
         <v>0</v>
       </c>
-      <c r="X31" s="8" t="s">
-        <v>70</v>
+      <c r="X31" s="10">
+        <v>10000004</v>
       </c>
       <c r="Y31" s="8">
         <v>20000001</v>
@@ -4516,19 +3936,19 @@
         <v>0</v>
       </c>
       <c r="AA31" s="8" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="AB31" s="8" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
     </row>
-    <row r="32" customHeight="1" spans="1:28">
+    <row r="32" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="8"/>
-      <c r="B32" s="8" t="s">
-        <v>152</v>
+      <c r="B32" s="10">
+        <v>30000019</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="D32" s="8">
         <v>10000007</v>
@@ -4543,29 +3963,29 @@
         <v>0</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="I32" s="8"/>
       <c r="J32" s="8">
         <v>2</v>
       </c>
-      <c r="K32" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="L32" s="8" t="s">
-        <v>89</v>
+      <c r="K32" s="10">
+        <v>4</v>
+      </c>
+      <c r="L32" s="10">
+        <v>1</v>
       </c>
       <c r="M32" s="8">
         <v>0</v>
       </c>
-      <c r="N32" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="O32" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="P32" s="8" t="s">
-        <v>89</v>
+      <c r="N32" s="10">
+        <v>9999</v>
+      </c>
+      <c r="O32" s="10">
+        <v>9999</v>
+      </c>
+      <c r="P32" s="10">
+        <v>1</v>
       </c>
       <c r="Q32" s="8">
         <v>0</v>
@@ -4576,8 +3996,8 @@
       <c r="S32" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="T32" s="8" t="s">
-        <v>75</v>
+      <c r="T32" s="10">
+        <v>0</v>
       </c>
       <c r="U32" s="8">
         <v>1</v>
@@ -4588,8 +4008,8 @@
       <c r="W32" s="8">
         <v>0</v>
       </c>
-      <c r="X32" s="8" t="s">
-        <v>157</v>
+      <c r="X32" s="10">
+        <v>10000009</v>
       </c>
       <c r="Y32" s="8">
         <v>20000001</v>
@@ -4598,15 +4018,15 @@
         <v>0</v>
       </c>
       <c r="AA32" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="AB32" s="8" t="s">
-        <v>158</v>
+        <v>73</v>
+      </c>
+      <c r="AB32" s="11" t="s">
+        <v>145</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Unity/Assets/Config/Excel/SkillConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SkillConfig.xlsx
@@ -1,31 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\DreamGit\Unity\Assets\Config\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4F96FBB-E8C0-41BE-9A29-45D5CC1B3D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="D3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -47,7 +54,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="E3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -70,7 +77,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="F3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -93,7 +100,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="G3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -115,7 +122,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="J3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -138,7 +145,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="K3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -168,7 +175,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+    <comment ref="L3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -190,7 +197,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
+    <comment ref="M3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -216,7 +223,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
+    <comment ref="P3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -238,7 +245,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
+    <comment ref="Q3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -260,7 +267,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
+    <comment ref="S3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -282,7 +289,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
+    <comment ref="T3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -310,7 +317,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000D000000}">
+    <comment ref="U3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -333,7 +340,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
+    <comment ref="V3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -359,7 +366,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000F000000}">
+    <comment ref="X3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -382,7 +389,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000010000000}">
+    <comment ref="Y3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -405,7 +412,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000011000000}">
+    <comment ref="AA3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -433,7 +440,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="147">
   <si>
     <t>##var</t>
   </si>
@@ -654,250 +661,239 @@
     <t>jianyu</t>
   </si>
   <si>
+    <t>对全体敌人射出箭矢，造成伤害。</t>
+  </si>
+  <si>
+    <t>淘汰之刃</t>
+  </si>
+  <si>
+    <t>Skill_淘汰之刃</t>
+  </si>
+  <si>
+    <t>3.5,0.3,4,0.5</t>
+  </si>
+  <si>
+    <t>对敌人造成350%物理伤害，如果敌人生命值低于30%，造成400%物理伤害；若成功击杀，将额外恢复50%的怒气。</t>
+  </si>
+  <si>
+    <t>神之力量</t>
+  </si>
+  <si>
+    <t>10000006,10000012</t>
+  </si>
+  <si>
+    <t>增加额外的100%攻击力,持续5秒,并且自身的普通攻击变成溅射伤害。</t>
+  </si>
+  <si>
+    <t>无敌击</t>
+  </si>
+  <si>
+    <t>Skill_无敌击</t>
+  </si>
+  <si>
+    <t>快速瞬间出剑5次攻击随机敌人,期间处于无敌状态,无法被攻击。</t>
+  </si>
+  <si>
+    <t>极寒领域</t>
+  </si>
+  <si>
+    <t>在目标范围造成大面积持续伤害,每秒造成150%伤害,持续3秒。</t>
+  </si>
+  <si>
+    <t>守护天使</t>
+  </si>
+  <si>
+    <t>10000003,10000004</t>
+  </si>
+  <si>
+    <t>使周围的友方单位对物理攻击免疫,且每秒恢复2%生命值,持续5秒。</t>
+  </si>
+  <si>
+    <t>混乱之雨</t>
+  </si>
+  <si>
+    <t>Skill_混乱之雨</t>
+  </si>
+  <si>
+    <t>2,5</t>
+  </si>
+  <si>
+    <t>召唤一个地狱火协助自己进行战斗，持续5秒(地狱火继承角色100%属性,拥有燃烧技能,持续对附近单位每秒造成100%伤害)。</t>
+  </si>
+  <si>
+    <t>怒吼</t>
+  </si>
+  <si>
+    <t>10000006</t>
+  </si>
+  <si>
+    <t>10000001</t>
+  </si>
+  <si>
+    <t>每次攻击有概率强迫附近单位攻击自己且自身受到的伤害降低50%,持续3秒。</t>
+  </si>
+  <si>
+    <t>反击螺旋</t>
+  </si>
+  <si>
+    <t>在受到攻击时有17%的概率触发旋风斩,对附近单位造成150%伤害。</t>
+  </si>
+  <si>
+    <t>战斗饥渴</t>
+  </si>
+  <si>
+    <t>10000007,10000013</t>
+  </si>
+  <si>
+    <t>每次攻击有概率对当前目标造成血量流失效果,使其每秒造成40%伤害,且造成伤害降低20%，持续4秒。</t>
+  </si>
+  <si>
+    <t>巨力挥舞</t>
+  </si>
+  <si>
+    <t>攻击有20%概率释放,向目标区域的敌人投掷风暴之锤,造成200%伤害,并使其造成眩晕效果,持续3秒。</t>
+  </si>
+  <si>
+    <t>溅射</t>
+  </si>
+  <si>
+    <t>每次攻击会对附近单位造成50%溅射伤害。</t>
+  </si>
+  <si>
+    <t>战吼</t>
+  </si>
+  <si>
+    <t>10000009,10000010,10000011</t>
+  </si>
+  <si>
+    <t>受到攻击有20%概率触发,提升自身的30%攻击速度和移动速度,并使自身的受到的伤害降低30%,持续5秒。</t>
+  </si>
+  <si>
+    <t>剑刃风暴</t>
+  </si>
+  <si>
+    <t>挥动剑刃造成风暴,对附近敌人持续旋转3秒,每0.5秒造成100%伤害。</t>
+  </si>
+  <si>
+    <t>治疗守卫</t>
+  </si>
+  <si>
+    <t>Skill_治疗守卫</t>
+  </si>
+  <si>
+    <t>在自己身后附带一个生命图腾,图腾每秒恢复附近己方单位最大生命值的1.5%,持续5秒。</t>
+  </si>
+  <si>
+    <t>剑舞</t>
+  </si>
+  <si>
+    <t>10000015,10000016</t>
+  </si>
+  <si>
+    <t>提升自身20%攻击速度和暴击率。</t>
+  </si>
+  <si>
+    <t>冰霜新星</t>
+  </si>
+  <si>
+    <t>10000017,10000018</t>
+  </si>
+  <si>
+    <t>立即对目标及其周围的单位造成200%伤害,并且使其移动速度和攻击速度降低50%,持续4秒。</t>
+  </si>
+  <si>
+    <t>冰封禁制</t>
+  </si>
+  <si>
+    <t>10000019,10000020</t>
+  </si>
+  <si>
+    <t>将当前目标锁定在冰块之中,使其不能移动和攻击，并且造成每秒50%伤害的冻伤效果,持续3秒。</t>
+  </si>
+  <si>
+    <t>辉煌光环</t>
+  </si>
+  <si>
+    <t>提升场内所有队友的怒气恢复速度,每秒恢复1点。</t>
+  </si>
+  <si>
+    <t>洗礼</t>
+  </si>
+  <si>
+    <t>立即恢复一个友方20%的最大生命值,并对其附近单位造成100%伤害。</t>
+  </si>
+  <si>
+    <t>驱逐</t>
+  </si>
+  <si>
+    <t>当己方有队友血量下降到30%后会激励保护其免受后面4次的攻击或技能伤害。</t>
+  </si>
+  <si>
+    <t>退化光环</t>
+  </si>
+  <si>
+    <t>10000024,10000025</t>
+  </si>
+  <si>
+    <t>对附近单位造成退化效果,使其移动速度降低25%,并使其造成伤害降低10%。</t>
+  </si>
+  <si>
+    <t>致命链接</t>
+  </si>
+  <si>
+    <t>10000028</t>
+  </si>
+  <si>
+    <t>将敌方所有目标链接到一起,其中任意一个受到伤害,其他所有单位都额外承受当前伤害的10%,持续5秒。</t>
+  </si>
+  <si>
+    <t>暗言术</t>
+  </si>
+  <si>
+    <t>0.2,0.6</t>
+  </si>
+  <si>
+    <t>10000029</t>
+  </si>
+  <si>
+    <t>10000030</t>
+  </si>
+  <si>
+    <t>释放强大的魔法伤害一个敌人或治疗一个队友,使其每秒造成60%伤害或每秒恢复2.5%最大生命生命,持续5秒。</t>
+  </si>
+  <si>
+    <t>剧变</t>
+  </si>
+  <si>
+    <t>10000026,10000027</t>
+  </si>
+  <si>
+    <t>对一个区域进行施法,使其攻击速度和移动速度降低至50%,持续3秒。</t>
+  </si>
+  <si>
+    <t>燃烧</t>
+  </si>
+  <si>
+    <t>Skill_燃烧</t>
+  </si>
+  <si>
     <t>0</t>
   </si>
   <si>
-    <t>对全体敌人射出箭矢，造成伤害。</t>
-  </si>
-  <si>
-    <t>淘汰之刃</t>
-  </si>
-  <si>
-    <t>Skill_淘汰之刃</t>
-  </si>
-  <si>
-    <t>3.5,0.3,4,0.5</t>
-  </si>
-  <si>
-    <t>对敌人造成350%物理伤害，如果敌人生命值低于30%，造成400%物理伤害；若成功击杀，将额外恢复50%的怒气。</t>
-  </si>
-  <si>
-    <t>神之力量</t>
-  </si>
-  <si>
-    <t>10000006,10000012</t>
-  </si>
-  <si>
-    <t>增加额外的100%攻击力,持续5秒,并且自身的普通攻击变成溅射伤害。</t>
-  </si>
-  <si>
-    <t>无敌击</t>
-  </si>
-  <si>
-    <t>Skill_无敌击</t>
-  </si>
-  <si>
-    <t>快速瞬间出剑5次攻击随机敌人,期间处于无敌状态,无法被攻击。</t>
-  </si>
-  <si>
-    <t>极寒领域</t>
-  </si>
-  <si>
-    <t>10000006</t>
-  </si>
-  <si>
-    <t>在目标范围造成大面积持续伤害,每秒造成150%伤害,持续3秒。</t>
-  </si>
-  <si>
-    <t>守护天使</t>
-  </si>
-  <si>
-    <t>10000003,10000004</t>
-  </si>
-  <si>
-    <t>使周围的友方单位对物理攻击免疫,且每秒恢复2%生命值,持续5秒。</t>
-  </si>
-  <si>
-    <t>混乱之雨</t>
-  </si>
-  <si>
-    <t>Skill_混乱之雨</t>
-  </si>
-  <si>
-    <t>2,5</t>
-  </si>
-  <si>
-    <t>召唤一个地狱火协助自己进行战斗，持续5秒(地狱火继承角色100%属性,拥有燃烧技能,持续对附近单位每秒造成100%伤害)。</t>
-  </si>
-  <si>
-    <t>怒吼</t>
-  </si>
-  <si>
-    <t>10000001</t>
-  </si>
-  <si>
-    <t>每次攻击有概率强迫附近单位攻击自己且自身受到的伤害降低50%,持续3秒。</t>
-  </si>
-  <si>
-    <t>反击螺旋</t>
-  </si>
-  <si>
-    <t>在受到攻击时有17%的概率触发旋风斩,对附近单位造成150%伤害。</t>
-  </si>
-  <si>
-    <t>战斗饥渴</t>
-  </si>
-  <si>
-    <t>10000007,10000013</t>
-  </si>
-  <si>
-    <t>每次攻击有概率对当前目标造成血量流失效果,使其每秒造成40%伤害,且造成伤害降低20%，持续4秒。</t>
-  </si>
-  <si>
-    <t>巨力挥舞</t>
-  </si>
-  <si>
-    <t>攻击有20%概率释放,向目标区域的敌人投掷风暴之锤,造成200%伤害,并使其造成眩晕效果,持续3秒。</t>
-  </si>
-  <si>
-    <t>溅射</t>
-  </si>
-  <si>
-    <t>每次攻击会对附近单位造成50%溅射伤害。</t>
-  </si>
-  <si>
-    <t>战吼</t>
-  </si>
-  <si>
-    <t>10000009,10000010,10000011</t>
-  </si>
-  <si>
-    <t>受到攻击有20%概率触发,提升自身的30%攻击速度和移动速度,并使自身的受到的伤害降低30%,持续5秒。</t>
-  </si>
-  <si>
-    <t>剑刃风暴</t>
-  </si>
-  <si>
-    <t>挥动剑刃造成风暴,对附近敌人持续旋转3秒,每0.5秒造成100%伤害。</t>
-  </si>
-  <si>
-    <t>治疗守卫</t>
-  </si>
-  <si>
-    <t>Skill_治疗守卫</t>
-  </si>
-  <si>
-    <t>在自己身后附带一个生命图腾,图腾每秒恢复附近己方单位最大生命值的1.5%,持续5秒。</t>
-  </si>
-  <si>
-    <t>剑舞</t>
-  </si>
-  <si>
-    <t>10000015,10000016</t>
-  </si>
-  <si>
-    <t>提升自身20%攻击速度和暴击率。</t>
-  </si>
-  <si>
-    <t>冰霜新星</t>
-  </si>
-  <si>
-    <t>10000017,10000018</t>
-  </si>
-  <si>
-    <t>立即对目标及其周围的单位造成200%伤害,并且使其移动速度和攻击速度降低50%,持续4秒。</t>
-  </si>
-  <si>
-    <t>冰封禁制</t>
-  </si>
-  <si>
-    <t>10000019,10000020</t>
-  </si>
-  <si>
-    <t>将当前目标锁定在冰块之中,使其不能移动和攻击，并且造成每秒50%伤害的冻伤效果,持续3秒。</t>
-  </si>
-  <si>
-    <t>辉煌光环</t>
-  </si>
-  <si>
-    <t>提升场内所有队友的怒气恢复速度,每秒恢复1点。</t>
-  </si>
-  <si>
-    <t>洗礼</t>
-  </si>
-  <si>
-    <t>立即恢复一个友方20%的最大生命值,并对其附近单位造成100%伤害。</t>
-  </si>
-  <si>
-    <t>驱逐</t>
-  </si>
-  <si>
-    <t>当己方有队友血量下降到30%后会激励保护其免受后面4次的攻击或技能伤害。</t>
-  </si>
-  <si>
-    <t>退化光环</t>
-  </si>
-  <si>
-    <t>10000024,10000025</t>
-  </si>
-  <si>
-    <t>对附近单位造成退化效果,使其移动速度降低25%,并使其造成伤害降低10%。</t>
-  </si>
-  <si>
-    <t>致命链接</t>
-  </si>
-  <si>
-    <t>10000028</t>
-  </si>
-  <si>
-    <t>将敌方所有目标链接到一起,其中任意一个受到伤害,其他所有单位都额外承受当前伤害的10%,持续5秒。</t>
-  </si>
-  <si>
-    <t>暗言术</t>
-  </si>
-  <si>
-    <t>剧变</t>
-  </si>
-  <si>
-    <t>10000026,10000027</t>
-  </si>
-  <si>
-    <t>对一个区域进行施法,使其攻击速度和移动速度降低至50%,持续3秒。</t>
-  </si>
-  <si>
-    <t>燃烧</t>
-  </si>
-  <si>
-    <t>Skill_燃烧</t>
-  </si>
-  <si>
-    <t>2,5</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.2,0.6</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>dao</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>持续对附近单位每秒造成100%伤害，类似阿木木的W。</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>attack</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>10000029</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>10000030</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>释放强大的魔法伤害一个敌人或治疗一个队友,使其每秒造成60%伤害或每秒恢复2.5%最大生命生命,持续5秒。</t>
-    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -925,19 +921,162 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -947,21 +1086,8 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -986,8 +1112,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -1038,12 +1350,254 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -1064,43 +1618,87 @@
     <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 6" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 6" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1358,14 +1956,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:AB32"/>
-  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.875" style="3" customWidth="1"/>
     <col min="2" max="7" width="17.875" style="3"/>
@@ -1384,7 +1982,7 @@
     <col min="29" max="16384" width="17.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1470,7 +2068,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A2" s="4" t="s">
         <v>28</v>
       </c>
@@ -1556,7 +2154,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:28" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A3" s="4" t="s">
         <v>35</v>
       </c>
@@ -1642,7 +2240,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:28" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A4" s="4"/>
       <c r="B4" s="8">
         <v>10000001</v>
@@ -1722,7 +2320,7 @@
       </c>
       <c r="AB4" s="4"/>
     </row>
-    <row r="5" spans="1:28" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A5" s="4"/>
       <c r="B5" s="8">
         <v>10000002</v>
@@ -1802,7 +2400,7 @@
       </c>
       <c r="AB5" s="4"/>
     </row>
-    <row r="6" spans="1:28" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A6" s="4"/>
       <c r="B6" s="8">
         <v>10000003</v>
@@ -1882,9 +2480,9 @@
       </c>
       <c r="AB6" s="4"/>
     </row>
-    <row r="7" spans="1:28" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A7" s="4"/>
-      <c r="B7" s="10">
+      <c r="B7" s="9">
         <v>10000004</v>
       </c>
       <c r="C7" s="8" t="s">
@@ -1936,13 +2534,13 @@
       <c r="S7" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="T7" s="10">
+      <c r="T7" s="9">
         <v>6</v>
       </c>
-      <c r="U7" s="10">
-        <v>0</v>
-      </c>
-      <c r="V7" s="10">
+      <c r="U7" s="9">
+        <v>0</v>
+      </c>
+      <c r="V7" s="9">
         <v>0</v>
       </c>
       <c r="W7" s="8">
@@ -1961,182 +2559,182 @@
         <v>0</v>
       </c>
       <c r="AB7" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="1:28">
+      <c r="A8" s="10"/>
+      <c r="B8" s="10">
+        <v>20000001</v>
+      </c>
+      <c r="C8" s="10" t="s">
         <v>74</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9">
-        <v>20000001</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>75</v>
       </c>
       <c r="D8" s="8">
         <v>10000005</v>
       </c>
-      <c r="E8" s="9">
-        <v>1</v>
-      </c>
-      <c r="F8" s="9">
-        <v>1</v>
-      </c>
-      <c r="G8" s="9">
-        <v>0</v>
-      </c>
-      <c r="H8" s="9" t="s">
+      <c r="E8" s="10">
+        <v>1</v>
+      </c>
+      <c r="F8" s="10">
+        <v>1</v>
+      </c>
+      <c r="G8" s="10">
+        <v>0</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="I8" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="I8" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="J8" s="9">
-        <v>1</v>
-      </c>
-      <c r="K8" s="9">
-        <v>0</v>
-      </c>
-      <c r="L8" s="9">
-        <v>0</v>
-      </c>
-      <c r="M8" s="9">
-        <v>0</v>
-      </c>
-      <c r="N8" s="9">
-        <v>1</v>
-      </c>
-      <c r="O8" s="9">
+      <c r="J8" s="10">
+        <v>1</v>
+      </c>
+      <c r="K8" s="10">
+        <v>0</v>
+      </c>
+      <c r="L8" s="10">
+        <v>0</v>
+      </c>
+      <c r="M8" s="10">
+        <v>0</v>
+      </c>
+      <c r="N8" s="10">
+        <v>1</v>
+      </c>
+      <c r="O8" s="10">
         <v>3</v>
       </c>
-      <c r="P8" s="9">
+      <c r="P8" s="10">
         <v>3.5</v>
       </c>
-      <c r="Q8" s="9">
+      <c r="Q8" s="10">
         <v>0</v>
       </c>
       <c r="R8" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="S8" s="9" t="s">
+      <c r="S8" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="T8" s="9">
-        <v>2</v>
-      </c>
-      <c r="U8" s="9">
-        <v>0</v>
-      </c>
-      <c r="V8" s="9">
+      <c r="T8" s="10">
+        <v>2</v>
+      </c>
+      <c r="U8" s="10">
+        <v>0</v>
+      </c>
+      <c r="V8" s="10">
         <v>0</v>
       </c>
       <c r="W8" s="8">
         <v>0</v>
       </c>
-      <c r="X8" s="9">
+      <c r="X8" s="10">
         <v>10000001</v>
       </c>
       <c r="Y8" s="8">
         <v>20000001</v>
       </c>
-      <c r="Z8" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="9" t="s">
+      <c r="Z8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="1:28">
+      <c r="A9" s="10"/>
+      <c r="B9" s="10">
+        <v>20000002</v>
+      </c>
+      <c r="C9" s="10" t="s">
         <v>78</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9">
-        <v>20000002</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>79</v>
       </c>
       <c r="D9" s="8">
         <v>10000006</v>
       </c>
-      <c r="E9" s="9">
-        <v>1</v>
-      </c>
-      <c r="F9" s="9">
-        <v>1</v>
-      </c>
-      <c r="G9" s="9">
-        <v>0</v>
-      </c>
-      <c r="H9" s="9" t="s">
+      <c r="E9" s="10">
+        <v>1</v>
+      </c>
+      <c r="F9" s="10">
+        <v>1</v>
+      </c>
+      <c r="G9" s="10">
+        <v>0</v>
+      </c>
+      <c r="H9" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9">
-        <v>1</v>
-      </c>
-      <c r="K9" s="9">
-        <v>0</v>
-      </c>
-      <c r="L9" s="9">
-        <v>0</v>
-      </c>
-      <c r="M9" s="9">
-        <v>0</v>
-      </c>
-      <c r="N9" s="9">
-        <v>1</v>
-      </c>
-      <c r="O9" s="9">
+      <c r="I9" s="10"/>
+      <c r="J9" s="10">
+        <v>1</v>
+      </c>
+      <c r="K9" s="10">
+        <v>0</v>
+      </c>
+      <c r="L9" s="10">
+        <v>0</v>
+      </c>
+      <c r="M9" s="10">
+        <v>0</v>
+      </c>
+      <c r="N9" s="10">
+        <v>1</v>
+      </c>
+      <c r="O9" s="10">
         <v>5</v>
       </c>
-      <c r="P9" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="9">
+      <c r="P9" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="10">
         <v>0</v>
       </c>
       <c r="R9" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="S9" s="9" t="s">
+      <c r="S9" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="T9" s="9">
+      <c r="T9" s="10">
         <v>3</v>
       </c>
-      <c r="U9" s="9">
-        <v>0</v>
-      </c>
-      <c r="V9" s="9">
+      <c r="U9" s="10">
+        <v>0</v>
+      </c>
+      <c r="V9" s="10">
         <v>0</v>
       </c>
       <c r="W9" s="8">
         <v>0</v>
       </c>
-      <c r="X9" s="9">
+      <c r="X9" s="10">
         <v>10000001</v>
       </c>
       <c r="Y9" s="8">
         <v>20000001</v>
       </c>
-      <c r="Z9" s="9" t="s">
+      <c r="Z9" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="AA9" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="9" t="s">
-        <v>81</v>
-      </c>
     </row>
-    <row r="10" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" customHeight="1" spans="1:28">
       <c r="A10" s="8"/>
       <c r="B10" s="8">
         <v>20000003</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D10" s="8">
         <v>10000007</v>
@@ -2151,7 +2749,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I10" s="8">
         <v>5</v>
@@ -2211,16 +2809,16 @@
         <v>0</v>
       </c>
       <c r="AB10" s="8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:28">
+      <c r="A11" s="8"/>
+      <c r="B11" s="9">
+        <v>20000004</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>84</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="8"/>
-      <c r="B11" s="10">
-        <v>20000004</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>85</v>
       </c>
       <c r="D11" s="8">
         <v>10000001</v>
@@ -2237,7 +2835,7 @@
       <c r="H11" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="I11" s="10">
+      <c r="I11" s="9">
         <v>1</v>
       </c>
       <c r="J11" s="8">
@@ -2282,7 +2880,7 @@
       <c r="W11" s="8">
         <v>0</v>
       </c>
-      <c r="X11" s="10">
+      <c r="X11" s="9">
         <v>10000006</v>
       </c>
       <c r="Y11" s="8">
@@ -2295,16 +2893,16 @@
         <v>0</v>
       </c>
       <c r="AB11" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
-    <row r="12" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" customHeight="1" spans="1:28">
       <c r="A12" s="8"/>
       <c r="B12" s="8">
         <v>20000005</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D12" s="8">
         <v>10000002</v>
@@ -2374,103 +2972,103 @@
         <v>0</v>
       </c>
       <c r="AA12" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB12" s="8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:28">
+      <c r="A13" s="10"/>
+      <c r="B13" s="11">
+        <v>20000006</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>89</v>
-      </c>
-      <c r="AB12" s="8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="13" spans="1:28" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="9"/>
-      <c r="B13" s="13">
-        <v>20000006</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>91</v>
       </c>
       <c r="D13" s="8">
         <v>10000003</v>
       </c>
-      <c r="E13" s="9">
-        <v>1</v>
-      </c>
-      <c r="F13" s="9">
-        <v>2</v>
-      </c>
-      <c r="G13" s="9">
-        <v>0</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="J13" s="9">
-        <v>1</v>
-      </c>
-      <c r="K13" s="9">
-        <v>0</v>
-      </c>
-      <c r="L13" s="9">
-        <v>0</v>
-      </c>
-      <c r="M13" s="9">
-        <v>0</v>
-      </c>
-      <c r="N13" s="9">
-        <v>1</v>
-      </c>
-      <c r="O13" s="9">
+      <c r="E13" s="10">
+        <v>1</v>
+      </c>
+      <c r="F13" s="10">
+        <v>2</v>
+      </c>
+      <c r="G13" s="10">
+        <v>0</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="J13" s="10">
+        <v>1</v>
+      </c>
+      <c r="K13" s="10">
+        <v>0</v>
+      </c>
+      <c r="L13" s="10">
+        <v>0</v>
+      </c>
+      <c r="M13" s="10">
+        <v>0</v>
+      </c>
+      <c r="N13" s="10">
+        <v>1</v>
+      </c>
+      <c r="O13" s="10">
         <v>5</v>
       </c>
-      <c r="P13" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="9">
+      <c r="P13" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="10">
         <v>0</v>
       </c>
       <c r="R13" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="S13" s="9" t="s">
+      <c r="S13" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="T13" s="9">
-        <v>0</v>
-      </c>
-      <c r="U13" s="9">
-        <v>0</v>
-      </c>
-      <c r="V13" s="9">
+      <c r="T13" s="10">
+        <v>0</v>
+      </c>
+      <c r="U13" s="10">
+        <v>0</v>
+      </c>
+      <c r="V13" s="10">
         <v>0</v>
       </c>
       <c r="W13" s="8">
         <v>0</v>
       </c>
-      <c r="X13" s="9">
+      <c r="X13" s="10">
         <v>10000001</v>
       </c>
       <c r="Y13" s="8">
         <v>20000001</v>
       </c>
-      <c r="Z13" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="9" t="s">
-        <v>94</v>
+      <c r="Z13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="10" t="s">
+        <v>92</v>
       </c>
     </row>
-    <row r="14" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" customHeight="1" spans="1:28">
       <c r="A14" s="8"/>
-      <c r="B14" s="10">
+      <c r="B14" s="9">
         <v>30000001</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D14" s="8">
         <v>10000004</v>
@@ -2537,22 +3135,22 @@
         <v>20000001</v>
       </c>
       <c r="Z14" s="8" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="AA14" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="AB14" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="AB14" s="8" t="s">
+    </row>
+    <row r="15" customHeight="1" spans="1:28">
+      <c r="A15" s="8"/>
+      <c r="B15" s="9">
+        <v>30000002</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>97</v>
-      </c>
-    </row>
-    <row r="15" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="8"/>
-      <c r="B15" s="10">
-        <v>30000002</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>98</v>
       </c>
       <c r="D15" s="8">
         <v>10000005</v>
@@ -2612,8 +3210,8 @@
       <c r="W15" s="8">
         <v>0</v>
       </c>
-      <c r="X15" s="8">
-        <v>10000006</v>
+      <c r="X15" s="9">
+        <v>10000001</v>
       </c>
       <c r="Y15" s="8">
         <v>20000001</v>
@@ -2625,98 +3223,98 @@
         <v>0</v>
       </c>
       <c r="AB15" s="8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="1:28">
+      <c r="A16" s="10"/>
+      <c r="B16" s="10">
+        <v>30000003</v>
+      </c>
+      <c r="C16" s="10" t="s">
         <v>99</v>
-      </c>
-    </row>
-    <row r="16" spans="1:28" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9">
-        <v>30000003</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="D16" s="8">
         <v>10000006</v>
       </c>
-      <c r="E16" s="9">
-        <v>1</v>
-      </c>
-      <c r="F16" s="9">
-        <v>1</v>
-      </c>
-      <c r="G16" s="9">
-        <v>0</v>
-      </c>
-      <c r="H16" s="9" t="s">
+      <c r="E16" s="10">
+        <v>1</v>
+      </c>
+      <c r="F16" s="10">
+        <v>1</v>
+      </c>
+      <c r="G16" s="10">
+        <v>0</v>
+      </c>
+      <c r="H16" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9">
-        <v>2</v>
-      </c>
-      <c r="K16" s="9">
-        <v>2</v>
-      </c>
-      <c r="L16" s="9">
+      <c r="I16" s="10"/>
+      <c r="J16" s="10">
+        <v>2</v>
+      </c>
+      <c r="K16" s="10">
+        <v>2</v>
+      </c>
+      <c r="L16" s="10">
         <v>0.2</v>
       </c>
-      <c r="M16" s="9">
-        <v>0</v>
-      </c>
-      <c r="N16" s="9">
+      <c r="M16" s="10">
+        <v>0</v>
+      </c>
+      <c r="N16" s="10">
         <v>10</v>
       </c>
-      <c r="O16" s="9">
+      <c r="O16" s="10">
         <v>4</v>
       </c>
-      <c r="P16" s="9">
+      <c r="P16" s="10">
         <v>0.4</v>
       </c>
-      <c r="Q16" s="9">
+      <c r="Q16" s="10">
         <v>0</v>
       </c>
       <c r="R16" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="S16" s="9" t="s">
+      <c r="S16" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="T16" s="9">
-        <v>2</v>
-      </c>
-      <c r="U16" s="9">
-        <v>0</v>
-      </c>
-      <c r="V16" s="9">
+      <c r="T16" s="10">
+        <v>2</v>
+      </c>
+      <c r="U16" s="10">
+        <v>0</v>
+      </c>
+      <c r="V16" s="10">
         <v>0</v>
       </c>
       <c r="W16" s="8">
         <v>0</v>
       </c>
-      <c r="X16" s="9">
+      <c r="X16" s="10">
         <v>10000001</v>
       </c>
       <c r="Y16" s="8">
         <v>20000001</v>
       </c>
-      <c r="Z16" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="9" t="s">
+      <c r="Z16" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB16" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="AB16" s="9" t="s">
-        <v>102</v>
-      </c>
     </row>
-    <row r="17" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" customHeight="1" spans="1:28">
       <c r="A17" s="8"/>
       <c r="B17" s="8">
         <v>30000004</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D17" s="8">
         <v>10000007</v>
@@ -2776,7 +3374,7 @@
       <c r="W17" s="8">
         <v>0</v>
       </c>
-      <c r="X17" s="10">
+      <c r="X17" s="9">
         <v>10000004</v>
       </c>
       <c r="Y17" s="8">
@@ -2789,100 +3387,100 @@
         <v>10000008</v>
       </c>
       <c r="AB17" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="1:28">
+      <c r="A18" s="10"/>
+      <c r="B18" s="10">
+        <v>30000005</v>
+      </c>
+      <c r="C18" s="10" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="18" spans="1:28" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9">
-        <v>30000005</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="D18" s="9">
+      <c r="D18" s="10">
         <v>10000001</v>
       </c>
-      <c r="E18" s="9">
-        <v>1</v>
-      </c>
-      <c r="F18" s="9">
-        <v>1</v>
-      </c>
-      <c r="G18" s="9">
-        <v>0</v>
-      </c>
-      <c r="H18" s="9" t="s">
+      <c r="E18" s="10">
+        <v>1</v>
+      </c>
+      <c r="F18" s="10">
+        <v>1</v>
+      </c>
+      <c r="G18" s="10">
+        <v>0</v>
+      </c>
+      <c r="H18" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9">
-        <v>2</v>
-      </c>
-      <c r="K18" s="9">
-        <v>2</v>
-      </c>
-      <c r="L18" s="9">
-        <v>1</v>
-      </c>
-      <c r="M18" s="9">
-        <v>0</v>
-      </c>
-      <c r="N18" s="9">
-        <v>0</v>
-      </c>
-      <c r="O18" s="9">
+      <c r="I18" s="10"/>
+      <c r="J18" s="10">
+        <v>2</v>
+      </c>
+      <c r="K18" s="10">
+        <v>2</v>
+      </c>
+      <c r="L18" s="10">
+        <v>1</v>
+      </c>
+      <c r="M18" s="10">
+        <v>0</v>
+      </c>
+      <c r="N18" s="10">
+        <v>0</v>
+      </c>
+      <c r="O18" s="10">
         <v>3</v>
       </c>
-      <c r="P18" s="9">
+      <c r="P18" s="10">
         <v>0.5</v>
       </c>
-      <c r="Q18" s="9">
-        <v>0</v>
-      </c>
-      <c r="R18" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="S18" s="9" t="s">
+      <c r="Q18" s="10">
+        <v>0</v>
+      </c>
+      <c r="R18" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="S18" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="T18" s="9">
-        <v>1</v>
-      </c>
-      <c r="U18" s="9">
-        <v>1</v>
-      </c>
-      <c r="V18" s="9">
+      <c r="T18" s="10">
+        <v>1</v>
+      </c>
+      <c r="U18" s="10">
+        <v>1</v>
+      </c>
+      <c r="V18" s="10">
         <v>2</v>
       </c>
       <c r="W18" s="8">
         <v>0</v>
       </c>
-      <c r="X18" s="9">
+      <c r="X18" s="10">
         <v>10000001</v>
       </c>
       <c r="Y18" s="8">
         <v>20000001</v>
       </c>
-      <c r="Z18" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB18" s="9" t="s">
-        <v>106</v>
+      <c r="Z18" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="10" t="s">
+        <v>105</v>
       </c>
     </row>
-    <row r="19" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" customHeight="1" spans="1:28">
       <c r="A19" s="8"/>
       <c r="B19" s="8">
         <v>30000006</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="D19" s="9">
+        <v>106</v>
+      </c>
+      <c r="D19" s="10">
         <v>10000002</v>
       </c>
       <c r="E19" s="8">
@@ -2947,24 +3545,24 @@
         <v>20000001</v>
       </c>
       <c r="Z19" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="AA19" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="AA19" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB19" s="8" t="s">
-        <v>109</v>
-      </c>
     </row>
-    <row r="20" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" customHeight="1" spans="1:28">
       <c r="A20" s="8"/>
       <c r="B20" s="8">
         <v>30000007</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D20" s="9">
+        <v>109</v>
+      </c>
+      <c r="D20" s="10">
         <v>10000003</v>
       </c>
       <c r="E20" s="8">
@@ -2979,7 +3577,7 @@
       <c r="H20" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="I20" s="10">
+      <c r="I20" s="9">
         <v>0.5</v>
       </c>
       <c r="J20" s="8">
@@ -3024,7 +3622,7 @@
       <c r="W20" s="8">
         <v>0</v>
       </c>
-      <c r="X20" s="10">
+      <c r="X20" s="9">
         <v>10000004</v>
       </c>
       <c r="Y20" s="8">
@@ -3037,33 +3635,33 @@
         <v>0</v>
       </c>
       <c r="AB20" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
-    <row r="21" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" customHeight="1" spans="1:28">
       <c r="A21" s="8"/>
       <c r="B21" s="8">
         <v>30000008</v>
       </c>
       <c r="C21" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="D21" s="10">
+        <v>10000004</v>
+      </c>
+      <c r="E21" s="8">
+        <v>1</v>
+      </c>
+      <c r="F21" s="8">
+        <v>1</v>
+      </c>
+      <c r="G21" s="8">
+        <v>0</v>
+      </c>
+      <c r="H21" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="D21" s="9">
-        <v>10000004</v>
-      </c>
-      <c r="E21" s="8">
-        <v>1</v>
-      </c>
-      <c r="F21" s="8">
-        <v>1</v>
-      </c>
-      <c r="G21" s="8">
-        <v>0</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="I21" s="10">
+      <c r="I21" s="9">
         <v>1.5</v>
       </c>
       <c r="J21" s="8">
@@ -3108,31 +3706,31 @@
       <c r="W21" s="8">
         <v>0</v>
       </c>
-      <c r="X21" s="10">
+      <c r="X21" s="9">
         <v>10000005</v>
       </c>
       <c r="Y21" s="8">
         <v>20000001</v>
       </c>
-      <c r="Z21" s="12">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="12">
+      <c r="Z21" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="13">
         <v>0</v>
       </c>
       <c r="AB21" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
-    <row r="22" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" customHeight="1" spans="1:28">
       <c r="A22" s="8"/>
       <c r="B22" s="8">
         <v>30000009</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D22" s="9">
+        <v>114</v>
+      </c>
+      <c r="D22" s="10">
         <v>10000005</v>
       </c>
       <c r="E22" s="8">
@@ -3197,24 +3795,24 @@
         <v>20000001</v>
       </c>
       <c r="Z22" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA22" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="AA22" s="8">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="8" t="s">
-        <v>117</v>
-      </c>
     </row>
-    <row r="23" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" customHeight="1" spans="1:28">
       <c r="A23" s="8"/>
       <c r="B23" s="8">
         <v>30000010</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="D23" s="9">
+        <v>117</v>
+      </c>
+      <c r="D23" s="10">
         <v>10000006</v>
       </c>
       <c r="E23" s="8">
@@ -3272,7 +3870,7 @@
       <c r="W23" s="8">
         <v>0</v>
       </c>
-      <c r="X23" s="10">
+      <c r="X23" s="9">
         <v>10000004</v>
       </c>
       <c r="Y23" s="8">
@@ -3282,21 +3880,21 @@
         <v>0</v>
       </c>
       <c r="AA23" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB23" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="AB23" s="8" t="s">
-        <v>120</v>
-      </c>
     </row>
-    <row r="24" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" customHeight="1" spans="1:28">
       <c r="A24" s="8"/>
       <c r="B24" s="8">
         <v>30000011</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="D24" s="9">
+        <v>120</v>
+      </c>
+      <c r="D24" s="10">
         <v>10000007</v>
       </c>
       <c r="E24" s="8">
@@ -3364,19 +3962,19 @@
         <v>0</v>
       </c>
       <c r="AA24" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB24" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="AB24" s="8" t="s">
-        <v>123</v>
-      </c>
     </row>
-    <row r="25" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" customHeight="1" spans="1:28">
       <c r="A25" s="8"/>
       <c r="B25" s="8">
         <v>30000012</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D25" s="8">
         <v>10000001</v>
@@ -3449,16 +4047,16 @@
         <v>10000021</v>
       </c>
       <c r="AB25" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
-    <row r="26" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" customHeight="1" spans="1:28">
       <c r="A26" s="8"/>
       <c r="B26" s="8">
         <v>30000013</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D26" s="8">
         <v>10000002</v>
@@ -3518,7 +4116,7 @@
       <c r="W26" s="8">
         <v>0</v>
       </c>
-      <c r="X26" s="10">
+      <c r="X26" s="9">
         <v>10000004</v>
       </c>
       <c r="Y26" s="8">
@@ -3531,16 +4129,16 @@
         <v>10000022</v>
       </c>
       <c r="AB26" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
-    <row r="27" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" customHeight="1" spans="1:28">
       <c r="A27" s="8"/>
       <c r="B27" s="8">
         <v>30000014</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D27" s="8">
         <v>10000003</v>
@@ -3613,16 +4211,16 @@
         <v>10000023</v>
       </c>
       <c r="AB27" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
-    <row r="28" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" customHeight="1" spans="1:28">
       <c r="A28" s="8"/>
       <c r="B28" s="8">
         <v>30000015</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D28" s="8">
         <v>10000004</v>
@@ -3682,7 +4280,7 @@
       <c r="W28" s="8">
         <v>0</v>
       </c>
-      <c r="X28" s="10">
+      <c r="X28" s="9">
         <v>10000004</v>
       </c>
       <c r="Y28" s="8">
@@ -3692,19 +4290,19 @@
         <v>0</v>
       </c>
       <c r="AA28" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="AB28" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="AB28" s="8" t="s">
+    </row>
+    <row r="29" customHeight="1" spans="1:28">
+      <c r="A29" s="8"/>
+      <c r="B29" s="9">
+        <v>30000016</v>
+      </c>
+      <c r="C29" s="8" t="s">
         <v>132</v>
-      </c>
-    </row>
-    <row r="29" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="8"/>
-      <c r="B29" s="10">
-        <v>30000016</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>133</v>
       </c>
       <c r="D29" s="8">
         <v>10000005</v>
@@ -3770,23 +4368,23 @@
       <c r="Y29" s="8">
         <v>20000001</v>
       </c>
-      <c r="Z29" s="12">
+      <c r="Z29" s="13">
         <v>0</v>
       </c>
       <c r="AA29" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="AB29" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="AB29" s="8" t="s">
-        <v>135</v>
-      </c>
     </row>
-    <row r="30" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" customHeight="1" spans="1:28">
       <c r="A30" s="8"/>
       <c r="B30" s="8">
         <v>30000017</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D30" s="8">
         <v>10000006</v>
@@ -3802,16 +4400,16 @@
       </c>
       <c r="H30" s="8"/>
       <c r="I30" s="8"/>
-      <c r="J30" s="12">
-        <v>2</v>
-      </c>
-      <c r="K30" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="L30" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="M30" s="12">
+      <c r="J30" s="13">
+        <v>2</v>
+      </c>
+      <c r="K30" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="L30" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="M30" s="13">
         <v>0</v>
       </c>
       <c r="N30" s="8">
@@ -3820,53 +4418,53 @@
       <c r="O30" s="8">
         <v>5</v>
       </c>
-      <c r="P30" s="12">
+      <c r="P30" s="13">
         <v>0.6</v>
       </c>
-      <c r="Q30" s="12">
+      <c r="Q30" s="13">
         <v>0</v>
       </c>
       <c r="R30" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="S30" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="T30" s="12">
-        <v>0</v>
-      </c>
-      <c r="U30" s="12">
-        <v>1</v>
-      </c>
-      <c r="V30" s="12">
+      <c r="S30" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="T30" s="13">
+        <v>0</v>
+      </c>
+      <c r="U30" s="13">
+        <v>1</v>
+      </c>
+      <c r="V30" s="13">
         <v>1</v>
       </c>
       <c r="W30" s="8">
         <v>0</v>
       </c>
-      <c r="X30" s="12">
+      <c r="X30" s="13">
         <v>10000001</v>
       </c>
       <c r="Y30" s="8">
         <v>20000001</v>
       </c>
-      <c r="Z30" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="AA30" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="AB30" s="11" t="s">
-        <v>149</v>
+      <c r="Z30" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA30" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="AB30" s="12" t="s">
+        <v>139</v>
       </c>
     </row>
-    <row r="31" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" customHeight="1" spans="1:28">
       <c r="A31" s="8"/>
       <c r="B31" s="8">
         <v>30000018</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D31" s="8">
         <v>10000007</v>
@@ -3926,7 +4524,7 @@
       <c r="W31" s="8">
         <v>0</v>
       </c>
-      <c r="X31" s="10">
+      <c r="X31" s="9">
         <v>10000004</v>
       </c>
       <c r="Y31" s="8">
@@ -3936,19 +4534,19 @@
         <v>0</v>
       </c>
       <c r="AA31" s="8" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AB31" s="8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
-    <row r="32" spans="1:28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" customHeight="1" spans="1:28">
       <c r="A32" s="8"/>
-      <c r="B32" s="10">
+      <c r="B32" s="9">
         <v>30000019</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D32" s="8">
         <v>10000007</v>
@@ -3963,28 +4561,28 @@
         <v>0</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I32" s="8"/>
       <c r="J32" s="8">
         <v>2</v>
       </c>
-      <c r="K32" s="10">
+      <c r="K32" s="9">
         <v>4</v>
       </c>
-      <c r="L32" s="10">
+      <c r="L32" s="9">
         <v>1</v>
       </c>
       <c r="M32" s="8">
         <v>0</v>
       </c>
-      <c r="N32" s="10">
+      <c r="N32" s="9">
         <v>9999</v>
       </c>
-      <c r="O32" s="10">
+      <c r="O32" s="9">
         <v>9999</v>
       </c>
-      <c r="P32" s="10">
+      <c r="P32" s="9">
         <v>1</v>
       </c>
       <c r="Q32" s="8">
@@ -3996,7 +4594,7 @@
       <c r="S32" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="T32" s="10">
+      <c r="T32" s="9">
         <v>0</v>
       </c>
       <c r="U32" s="8">
@@ -4008,7 +4606,7 @@
       <c r="W32" s="8">
         <v>0</v>
       </c>
-      <c r="X32" s="10">
+      <c r="X32" s="9">
         <v>10000009</v>
       </c>
       <c r="Y32" s="8">
@@ -4018,15 +4616,15 @@
         <v>0</v>
       </c>
       <c r="AA32" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB32" s="11" t="s">
         <v>145</v>
+      </c>
+      <c r="AB32" s="12" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>